--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -50,14 +50,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-        <bgColor rgb="00C00000"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
       </patternFill>
     </fill>
     <fill>
@@ -105,10 +105,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -561,36 +561,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4119.29</v>
+        <v>4000.78</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4113.7</v>
+        <v>4008.7</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-2.32%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-5.59</v>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>7.92</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -598,8 +598,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>23.59</v>
+      <c r="J2" s="3" t="n">
+        <v>24.18</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -610,36 +610,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4123.38</v>
+        <v>4119.29</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4130.6</v>
+        <v>4104.1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-15.19</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -647,8 +647,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>28.82</v>
+      <c r="J3" s="3" t="n">
+        <v>24.27</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -659,36 +659,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4077.4</v>
+        <v>4123.38</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4070.9</v>
+        <v>4130.6</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>7.22</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -696,8 +696,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="5" t="n">
-        <v>35.09</v>
+      <c r="J4" s="3" t="n">
+        <v>28.82</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -708,36 +708,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4105.67</v>
+        <v>4077.4</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4145.3</v>
+        <v>4070.9</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>39.63</v>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-6.5</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -746,47 +746,47 @@
         </is>
       </c>
       <c r="J5" s="5" t="n">
-        <v>33.16</v>
+        <v>35.09</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4165.04</v>
+        <v>4105.67</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4155.1</v>
+        <v>4145.3</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-9.94</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>39.63</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -795,45 +795,45 @@
         </is>
       </c>
       <c r="J6" s="5" t="n">
-        <v>31.24</v>
+        <v>33.16</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4123.77</v>
+        <v>4165.04</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4112.7</v>
+        <v>4155.1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>-11.07</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
+        <v>-9.94</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="J7" s="5" t="n">
-        <v>39.5</v>
+        <v>31.24</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -855,36 +855,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4031.01</v>
+        <v>4123.77</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4068.3</v>
+        <v>4112.7</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-11.07</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
         </is>
       </c>
       <c r="J8" s="5" t="n">
-        <v>47.28</v>
+        <v>39.5</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4007.41</v>
+        <v>4031.01</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4022.9</v>
+        <v>4068.3</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>15.49</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>37.29</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -942,43 +942,43 @@
         </is>
       </c>
       <c r="J9" s="5" t="n">
-        <v>48.31</v>
+        <v>47.28</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4016.54</v>
+        <v>4007.41</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4022.3</v>
+        <v>4022.9</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5.76</v>
+        <v>15.49</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="J10" s="5" t="n">
-        <v>48</v>
+        <v>48.31</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1002,36 +1002,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4089.95</v>
+        <v>4016.54</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4078.7</v>
+        <v>4022.3</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>-11.25</v>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>5.76</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="J11" s="5" t="n">
-        <v>46.99</v>
+        <v>48</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1051,36 +1051,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4026.57</v>
+        <v>4089.95</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4030.5</v>
+        <v>4078.7</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-11.25</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>46.5</v>
+        <v>46.99</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1100,36 +1100,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3999.06</v>
+        <v>4026.57</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3990.3</v>
+        <v>4030.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-8.76</v>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>3.93</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="J13" s="5" t="n">
-        <v>45.73</v>
+        <v>46.5</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1149,36 +1149,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4110.14</v>
+        <v>3999.06</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4129.9</v>
+        <v>3990.3</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>19.76</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-8.76</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>43.77</v>
+        <v>45.73</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1198,36 +1198,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4191.26</v>
+        <v>4110.14</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4181.9</v>
+        <v>4129.9</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.24%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>19.76</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="J15" s="5" t="n">
-        <v>42.46</v>
+        <v>43.77</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1247,36 +1247,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4209.02</v>
+        <v>4191.26</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4224.1</v>
+        <v>4181.9</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>42.84</v>
+        <v>42.46</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1296,134 +1296,134 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4257.71</v>
+        <v>4209.02</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4358.9</v>
+        <v>4224.1</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>101.19</v>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
+        <v>15.08</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
         </is>
       </c>
       <c r="J17" s="5" t="n">
-        <v>37.86</v>
+        <v>42.84</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4331.14</v>
+        <v>4257.71</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$7.23</t>
+          <t>+$1.76</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4330.9</v>
+        <v>4358.9</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>101.19</v>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J18" s="5" t="n">
-        <v>31.5</v>
+        <v>37.86</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4309.03</v>
+        <v>4331.14</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$52.77</t>
+          <t>+$7.23</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4328</v>
+        <v>4330.9</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>18.97</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0.24</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1431,8 +1431,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n">
-        <v>30.25</v>
+      <c r="J19" s="5" t="n">
+        <v>31.5</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1443,36 +1443,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4218.71</v>
+        <v>4309.03</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-1.08</t>
+          <t>+$52.77</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4215</v>
+        <v>4328</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+3.05%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>-3.71</v>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>18.97</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1480,8 +1480,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J20" s="4" t="n">
-        <v>29.98</v>
+      <c r="J20" s="3" t="n">
+        <v>30.25</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1492,34 +1492,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4210.69</v>
+        <v>4218.71</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$10.16</t>
+          <t>$-1.08</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4090.3</v>
+        <v>4215</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+3.05%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-120.39</v>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
+        <v>-3.71</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1529,57 +1529,57 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n">
-        <v>22.73</v>
+      <c r="J21" s="3" t="n">
+        <v>29.98</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4071.28</v>
+        <v>4210.69</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-5.95</t>
+          <t>+$10.16</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4108.2</v>
+        <v>4090.3</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-3.56%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>36.92</v>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>12.14</v>
+        <v>-120.39</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>22.73</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1590,81 +1590,81 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4259.29</v>
+        <v>4071.28</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-4.41%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-5.95</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4260</v>
+        <v>4108.2</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>12.17</v>
+        <v>36.92</v>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>12.14</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4329.75</v>
+        <v>4259.29</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-2.37</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4335.9</v>
+        <v>4260</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>6.15</v>
+        <v>0.71</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1676,8 +1676,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J24" s="4" t="n">
-        <v>14.5</v>
+      <c r="J24" s="3" t="n">
+        <v>12.17</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1688,32 +1688,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4328.15</v>
+        <v>4329.75</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3.29%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$7.90</t>
+          <t>$-2.37</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4337.1</v>
+        <v>4335.9</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3.10%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>8.949999999999999</v>
+        <v>6.15</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1725,8 +1725,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n">
-        <v>16.4</v>
+      <c r="J25" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1737,32 +1737,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4475.25</v>
+        <v>4328.15</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-3.29%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$7.80</t>
+          <t>+$7.90</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4475.8</v>
+        <v>4337.1</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-3.10%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.55</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1774,8 +1774,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n">
-        <v>16.51</v>
+      <c r="J26" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1786,32 +1786,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4434.3</v>
+        <v>4475.25</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$3.39</t>
+          <t>+$7.80</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4436.7</v>
+        <v>4475.8</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2.4</v>
+        <v>0.55</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1823,8 +1823,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n">
-        <v>17.59</v>
+      <c r="J27" s="3" t="n">
+        <v>16.51</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1835,32 +1835,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4487.78</v>
+        <v>4434.3</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-3.86</t>
+          <t>+$3.39</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4489.1</v>
+        <v>4436.7</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1.32</v>
+        <v>2.4</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1872,8 +1872,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="4" t="n">
-        <v>20.84</v>
+      <c r="J28" s="3" t="n">
+        <v>17.59</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1884,36 +1884,36 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4484.69</v>
+        <v>4487.78</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-1.44</t>
+          <t>$-3.86</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4475.2</v>
+        <v>4489.1</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-9.49</v>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>1.32</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1921,8 +1921,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n">
-        <v>21.61</v>
+      <c r="J29" s="3" t="n">
+        <v>20.84</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1933,36 +1933,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4540.28</v>
+        <v>4484.69</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$1.89</t>
+          <t>$-1.44</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4560.5</v>
+        <v>4475.2</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>20.22</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-9.49</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1970,8 +1970,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n">
-        <v>20.95</v>
+      <c r="J30" s="3" t="n">
+        <v>21.61</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1982,32 +1982,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4495.57</v>
+        <v>4540.28</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-4.31</t>
+          <t>+$1.89</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4499.3</v>
+        <v>4560.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+1.16%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3.73</v>
+        <v>20.22</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2019,8 +2019,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n">
-        <v>20.36</v>
+      <c r="J31" s="3" t="n">
+        <v>20.95</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -561,32 +561,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4000.78</v>
+        <v>4052.92</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$5.21</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4008.7</v>
+        <v>4061.1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-2.32%</t>
+          <t>+1.60%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7.92</v>
+        <v>8.18</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>24.18</v>
+        <v>22.12</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -610,32 +610,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4119.29</v>
+        <v>4000.78</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4104.1</v>
+        <v>3997</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-2.61%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-15.19</v>
+        <v>-3.78</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>24.27</v>
+        <v>23.34</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -659,36 +659,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4123.38</v>
+        <v>4119.29</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4130.6</v>
+        <v>4104.1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-15.19</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>28.82</v>
+        <v>24.27</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -708,36 +708,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4077.4</v>
+        <v>4123.38</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4070.9</v>
+        <v>4130.6</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>7.22</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -745,8 +745,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="5" t="n">
-        <v>35.09</v>
+      <c r="J5" s="3" t="n">
+        <v>28.82</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -757,36 +757,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4105.67</v>
+        <v>4077.4</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4145.3</v>
+        <v>4070.9</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>39.63</v>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-6.5</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -795,47 +795,47 @@
         </is>
       </c>
       <c r="J6" s="5" t="n">
-        <v>33.16</v>
+        <v>35.09</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4165.04</v>
+        <v>4105.67</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4155.1</v>
+        <v>4145.3</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>-9.94</v>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>39.63</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -844,43 +844,43 @@
         </is>
       </c>
       <c r="J7" s="5" t="n">
-        <v>31.24</v>
+        <v>33.16</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4123.77</v>
+        <v>4165.04</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4112.7</v>
+        <v>4155.1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>-11.07</v>
+        <v>-9.94</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="J8" s="5" t="n">
-        <v>39.5</v>
+        <v>31.24</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -904,36 +904,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4031.01</v>
+        <v>4123.77</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4068.3</v>
+        <v>4112.7</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-11.07</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -942,47 +942,47 @@
         </is>
       </c>
       <c r="J9" s="5" t="n">
-        <v>47.28</v>
+        <v>39.5</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4007.41</v>
+        <v>4031.01</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4022.9</v>
+        <v>4068.3</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>15.49</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>37.29</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -991,43 +991,43 @@
         </is>
       </c>
       <c r="J10" s="5" t="n">
-        <v>48.31</v>
+        <v>47.28</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4016.54</v>
+        <v>4007.41</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4022.3</v>
+        <v>4022.9</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>5.76</v>
+        <v>15.49</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="J11" s="5" t="n">
-        <v>48</v>
+        <v>48.31</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1051,36 +1051,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4089.95</v>
+        <v>4016.54</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4078.7</v>
+        <v>4022.3</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>-11.25</v>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>5.76</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>46.99</v>
+        <v>48</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1100,36 +1100,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4026.57</v>
+        <v>4089.95</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4030.5</v>
+        <v>4078.7</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-11.25</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="J13" s="5" t="n">
-        <v>46.5</v>
+        <v>46.99</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1149,36 +1149,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3999.06</v>
+        <v>4026.57</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3990.3</v>
+        <v>4030.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-8.76</v>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>3.93</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>45.73</v>
+        <v>46.5</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1198,36 +1198,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4110.14</v>
+        <v>3999.06</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4129.9</v>
+        <v>3990.3</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>19.76</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-8.76</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="J15" s="5" t="n">
-        <v>43.77</v>
+        <v>45.73</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1247,36 +1247,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4191.26</v>
+        <v>4110.14</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4181.9</v>
+        <v>4129.9</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.24%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>19.76</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>42.46</v>
+        <v>43.77</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1296,36 +1296,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4209.02</v>
+        <v>4191.26</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4224.1</v>
+        <v>4181.9</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="J17" s="5" t="n">
-        <v>42.84</v>
+        <v>42.46</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1345,134 +1345,134 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4257.71</v>
+        <v>4209.02</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4358.9</v>
+        <v>4224.1</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>101.19</v>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
+        <v>15.08</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
         </is>
       </c>
       <c r="J18" s="5" t="n">
-        <v>37.86</v>
+        <v>42.84</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4331.14</v>
+        <v>4257.71</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$7.23</t>
+          <t>+$1.76</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4330.9</v>
+        <v>4358.9</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>101.19</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>31.5</v>
+        <v>37.86</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4309.03</v>
+        <v>4331.14</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$52.77</t>
+          <t>+$7.23</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4328</v>
+        <v>4330.9</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>18.97</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0.24</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1480,8 +1480,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J20" s="3" t="n">
-        <v>30.25</v>
+      <c r="J20" s="5" t="n">
+        <v>31.5</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1492,36 +1492,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4218.71</v>
+        <v>4309.03</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-1.08</t>
+          <t>+$52.77</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4215</v>
+        <v>4328</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+3.05%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-3.71</v>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>18.97</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>29.98</v>
+        <v>30.25</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1541,32 +1541,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4210.69</v>
+        <v>4218.71</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$10.16</t>
+          <t>$-1.08</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4090.3</v>
+        <v>4215</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+3.05%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-120.39</v>
+        <v>-3.71</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
@@ -1579,56 +1579,56 @@
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>22.73</v>
+        <v>29.98</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4071.28</v>
+        <v>4210.69</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-5.95</t>
+          <t>+$10.16</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4108.2</v>
+        <v>4090.3</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3.56%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>36.92</v>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
+        <v>-120.39</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>12.14</v>
+        <v>22.73</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1639,81 +1639,81 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4259.29</v>
+        <v>4071.28</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-4.41%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-5.95</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4260</v>
+        <v>4108.2</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>36.92</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>12.17</v>
+        <v>12.14</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4329.75</v>
+        <v>4259.29</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-2.37</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4335.9</v>
+        <v>4260</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>6.15</v>
+        <v>0.71</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>14.5</v>
+        <v>12.17</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1737,32 +1737,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4328.15</v>
+        <v>4329.75</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-3.29%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$7.90</t>
+          <t>$-2.37</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4337.1</v>
+        <v>4335.9</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-3.10%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>8.949999999999999</v>
+        <v>6.15</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>16.4</v>
+        <v>14.5</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1786,32 +1786,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4475.25</v>
+        <v>4328.15</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-3.29%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$7.80</t>
+          <t>+$7.90</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4475.8</v>
+        <v>4337.1</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-3.10%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.55</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>16.51</v>
+        <v>16.4</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1835,32 +1835,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4434.3</v>
+        <v>4475.25</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$3.39</t>
+          <t>+$7.80</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4436.7</v>
+        <v>4475.8</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2.4</v>
+        <v>0.55</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>17.59</v>
+        <v>16.51</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1884,32 +1884,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4487.78</v>
+        <v>4434.3</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-3.86</t>
+          <t>+$3.39</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4489.1</v>
+        <v>4436.7</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1.32</v>
+        <v>2.4</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>20.84</v>
+        <v>17.59</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1933,36 +1933,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4484.69</v>
+        <v>4487.78</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-1.44</t>
+          <t>$-3.86</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4475.2</v>
+        <v>4489.1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-9.49</v>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>1.32</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>21.61</v>
+        <v>20.84</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1982,36 +1982,36 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4540.28</v>
+        <v>4484.69</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$1.89</t>
+          <t>$-1.44</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4560.5</v>
+        <v>4475.2</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>20.22</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-9.49</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>20.95</v>
+        <v>21.61</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -50,14 +50,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-        <bgColor rgb="00C00000"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -105,10 +105,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -561,36 +561,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4052.92</v>
+        <v>4060.55</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$5.21</t>
+          <t>+$0.46</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4061.1</v>
+        <v>4044</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+1.60%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-16.55</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -598,8 +598,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n">
-        <v>22.12</v>
+      <c r="J2" s="4" t="n">
+        <v>21.84</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -610,36 +610,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4000.78</v>
+        <v>4052.92</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$5.21</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3997</v>
+        <v>4061.1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-2.61%</t>
+          <t>+1.60%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>8.18</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -647,8 +647,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n">
-        <v>23.34</v>
+      <c r="J3" s="4" t="n">
+        <v>22.12</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -659,34 +659,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4119.29</v>
+        <v>4000.78</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4104.1</v>
+        <v>3997</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-2.61%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-15.19</v>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
+        <v>-3.78</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -696,8 +696,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
-        <v>24.27</v>
+      <c r="J4" s="4" t="n">
+        <v>23.34</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -708,36 +708,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4123.38</v>
+        <v>4119.29</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4130.6</v>
+        <v>4104.1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-15.19</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -745,8 +745,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
-        <v>28.82</v>
+      <c r="J5" s="4" t="n">
+        <v>24.27</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -757,36 +757,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4077.4</v>
+        <v>4123.38</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4070.9</v>
+        <v>4130.6</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>7.22</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -794,8 +794,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="5" t="n">
-        <v>35.09</v>
+      <c r="J6" s="4" t="n">
+        <v>28.82</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -806,36 +806,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4105.67</v>
+        <v>4077.4</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4145.3</v>
+        <v>4070.9</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>39.63</v>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-6.5</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -844,47 +844,47 @@
         </is>
       </c>
       <c r="J7" s="5" t="n">
-        <v>33.16</v>
+        <v>35.09</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4165.04</v>
+        <v>4105.67</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4155.1</v>
+        <v>4145.3</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>-9.94</v>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>39.63</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -893,45 +893,45 @@
         </is>
       </c>
       <c r="J8" s="5" t="n">
-        <v>31.24</v>
+        <v>33.16</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4123.77</v>
+        <v>4165.04</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4112.7</v>
+        <v>4155.1</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>-11.07</v>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
+        <v>-9.94</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="J9" s="5" t="n">
-        <v>39.5</v>
+        <v>31.24</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -953,36 +953,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4031.01</v>
+        <v>4123.77</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4068.3</v>
+        <v>4112.7</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-11.07</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -991,47 +991,47 @@
         </is>
       </c>
       <c r="J10" s="5" t="n">
-        <v>47.28</v>
+        <v>39.5</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4007.41</v>
+        <v>4031.01</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4022.9</v>
+        <v>4068.3</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>15.49</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>37.29</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1040,43 +1040,43 @@
         </is>
       </c>
       <c r="J11" s="5" t="n">
-        <v>48.31</v>
+        <v>47.28</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4016.54</v>
+        <v>4007.41</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4022.3</v>
+        <v>4022.9</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>5.76</v>
+        <v>15.49</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>48</v>
+        <v>48.31</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1100,36 +1100,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4089.95</v>
+        <v>4016.54</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4078.7</v>
+        <v>4022.3</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-11.25</v>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>5.76</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="J13" s="5" t="n">
-        <v>46.99</v>
+        <v>48</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1149,36 +1149,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4026.57</v>
+        <v>4089.95</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4030.5</v>
+        <v>4078.7</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-11.25</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>46.5</v>
+        <v>46.99</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1198,36 +1198,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3999.06</v>
+        <v>4026.57</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3990.3</v>
+        <v>4030.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-8.76</v>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>3.93</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="J15" s="5" t="n">
-        <v>45.73</v>
+        <v>46.5</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1247,36 +1247,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4110.14</v>
+        <v>3999.06</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4129.9</v>
+        <v>3990.3</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>19.76</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-8.76</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>43.77</v>
+        <v>45.73</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1296,36 +1296,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4191.26</v>
+        <v>4110.14</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4181.9</v>
+        <v>4129.9</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.24%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>19.76</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="J17" s="5" t="n">
-        <v>42.46</v>
+        <v>43.77</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1345,36 +1345,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4209.02</v>
+        <v>4191.26</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4224.1</v>
+        <v>4181.9</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="J18" s="5" t="n">
-        <v>42.84</v>
+        <v>42.46</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1394,134 +1394,134 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4257.71</v>
+        <v>4209.02</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4358.9</v>
+        <v>4224.1</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>101.19</v>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
+        <v>15.08</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>37.86</v>
+        <v>42.84</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4331.14</v>
+        <v>4257.71</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$7.23</t>
+          <t>+$1.76</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4330.9</v>
+        <v>4358.9</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>101.19</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>31.5</v>
+        <v>37.86</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4309.03</v>
+        <v>4331.14</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$52.77</t>
+          <t>+$7.23</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4328</v>
+        <v>4330.9</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>18.97</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0.24</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1529,8 +1529,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J21" s="3" t="n">
-        <v>30.25</v>
+      <c r="J21" s="5" t="n">
+        <v>31.5</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1541,36 +1541,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4218.71</v>
+        <v>4309.03</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-1.08</t>
+          <t>+$52.77</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4215</v>
+        <v>4328</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+3.05%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-3.71</v>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>18.97</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1578,8 +1578,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J22" s="3" t="n">
-        <v>29.98</v>
+      <c r="J22" s="4" t="n">
+        <v>30.25</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1590,34 +1590,34 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4210.69</v>
+        <v>4218.71</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$10.16</t>
+          <t>$-1.08</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4090.3</v>
+        <v>4215</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+3.05%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-120.39</v>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
+        <v>-3.71</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1627,57 +1627,57 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="3" t="n">
-        <v>22.73</v>
+      <c r="J23" s="4" t="n">
+        <v>29.98</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4071.28</v>
+        <v>4210.69</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-5.95</t>
+          <t>+$10.16</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4108.2</v>
+        <v>4090.3</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-3.56%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>36.92</v>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>12.14</v>
+        <v>-120.39</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>22.73</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1688,81 +1688,81 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4259.29</v>
+        <v>4071.28</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-4.41%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-5.95</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4260</v>
+        <v>4108.2</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>12.17</v>
+        <v>36.92</v>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>12.14</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4329.75</v>
+        <v>4259.29</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-2.37</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4335.9</v>
+        <v>4260</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>6.15</v>
+        <v>0.71</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1774,8 +1774,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="3" t="n">
-        <v>14.5</v>
+      <c r="J26" s="4" t="n">
+        <v>12.17</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1786,32 +1786,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4328.15</v>
+        <v>4329.75</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-3.29%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$7.90</t>
+          <t>$-2.37</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4337.1</v>
+        <v>4335.9</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-3.10%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>8.949999999999999</v>
+        <v>6.15</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1823,8 +1823,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="3" t="n">
-        <v>16.4</v>
+      <c r="J27" s="4" t="n">
+        <v>14.5</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1835,32 +1835,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4475.25</v>
+        <v>4328.15</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-3.29%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$7.80</t>
+          <t>+$7.90</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4475.8</v>
+        <v>4337.1</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-3.10%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.55</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1872,8 +1872,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="3" t="n">
-        <v>16.51</v>
+      <c r="J28" s="4" t="n">
+        <v>16.4</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1884,32 +1884,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4434.3</v>
+        <v>4475.25</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$3.39</t>
+          <t>+$7.80</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4436.7</v>
+        <v>4475.8</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2.4</v>
+        <v>0.55</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1921,8 +1921,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="3" t="n">
-        <v>17.59</v>
+      <c r="J29" s="4" t="n">
+        <v>16.51</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1933,32 +1933,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4487.78</v>
+        <v>4434.3</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-3.86</t>
+          <t>+$3.39</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4489.1</v>
+        <v>4436.7</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1.32</v>
+        <v>2.4</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1970,8 +1970,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="3" t="n">
-        <v>20.84</v>
+      <c r="J30" s="4" t="n">
+        <v>17.59</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1982,36 +1982,36 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4484.69</v>
+        <v>4487.78</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-1.44</t>
+          <t>$-3.86</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4475.2</v>
+        <v>4489.1</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>-9.49</v>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>1.32</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2019,8 +2019,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="3" t="n">
-        <v>21.61</v>
+      <c r="J31" s="4" t="n">
+        <v>20.84</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -50,14 +50,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-        <bgColor rgb="00C00000"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
       </patternFill>
     </fill>
     <fill>
@@ -105,10 +105,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -561,36 +561,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4060.55</v>
+        <v>3976.48</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$0.46</t>
+          <t>+$4.31</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4044</v>
+        <v>3983.5</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.50%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-16.55</v>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>7.02</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -598,8 +598,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>21.84</v>
+      <c r="J2" s="3" t="n">
+        <v>22.62</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -610,36 +610,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4052.92</v>
+        <v>4060.55</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$5.21</t>
+          <t>+$0.46</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4061.1</v>
+        <v>4044</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+1.60%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-16.55</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -647,8 +647,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>22.12</v>
+      <c r="J3" s="3" t="n">
+        <v>21.84</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -659,36 +659,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4000.78</v>
+        <v>4052.92</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$5.21</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3997</v>
+        <v>4061.1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2.61%</t>
+          <t>+1.60%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>8.18</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -696,8 +696,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>23.34</v>
+      <c r="J4" s="3" t="n">
+        <v>22.12</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -708,34 +708,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4119.29</v>
+        <v>4000.78</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4104.1</v>
+        <v>3997</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-2.61%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-15.19</v>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
+        <v>-3.78</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -745,8 +745,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>24.27</v>
+      <c r="J5" s="3" t="n">
+        <v>23.34</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -757,36 +757,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4123.38</v>
+        <v>4119.29</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4130.6</v>
+        <v>4104.1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-15.19</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -794,8 +794,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="4" t="n">
-        <v>28.82</v>
+      <c r="J6" s="3" t="n">
+        <v>24.27</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -806,36 +806,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4077.4</v>
+        <v>4123.38</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4070.9</v>
+        <v>4130.6</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>7.22</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -843,8 +843,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="5" t="n">
-        <v>35.09</v>
+      <c r="J7" s="3" t="n">
+        <v>28.82</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -855,36 +855,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4105.67</v>
+        <v>4077.4</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4145.3</v>
+        <v>4070.9</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>39.63</v>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-6.5</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
         </is>
       </c>
       <c r="J8" s="5" t="n">
-        <v>33.16</v>
+        <v>35.09</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4165.04</v>
+        <v>4105.67</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4155.1</v>
+        <v>4145.3</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>-9.94</v>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>39.63</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -942,45 +942,45 @@
         </is>
       </c>
       <c r="J9" s="5" t="n">
-        <v>31.24</v>
+        <v>33.16</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4123.77</v>
+        <v>4165.04</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4112.7</v>
+        <v>4155.1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>-11.07</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+        <v>-9.94</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="J10" s="5" t="n">
-        <v>39.5</v>
+        <v>31.24</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1002,36 +1002,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4031.01</v>
+        <v>4123.77</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4068.3</v>
+        <v>4112.7</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-11.07</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1040,47 +1040,47 @@
         </is>
       </c>
       <c r="J11" s="5" t="n">
-        <v>47.28</v>
+        <v>39.5</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4007.41</v>
+        <v>4031.01</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4022.9</v>
+        <v>4068.3</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>15.49</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>37.29</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1089,43 +1089,43 @@
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>48.31</v>
+        <v>47.28</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4016.54</v>
+        <v>4007.41</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4022.3</v>
+        <v>4022.9</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>5.76</v>
+        <v>15.49</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="J13" s="5" t="n">
-        <v>48</v>
+        <v>48.31</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1149,36 +1149,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4089.95</v>
+        <v>4016.54</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4078.7</v>
+        <v>4022.3</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-11.25</v>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>5.76</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>46.99</v>
+        <v>48</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1198,36 +1198,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4026.57</v>
+        <v>4089.95</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4030.5</v>
+        <v>4078.7</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-11.25</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="J15" s="5" t="n">
-        <v>46.5</v>
+        <v>46.99</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1247,36 +1247,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3999.06</v>
+        <v>4026.57</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3990.3</v>
+        <v>4030.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-8.76</v>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>3.93</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>45.73</v>
+        <v>46.5</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1296,36 +1296,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4110.14</v>
+        <v>3999.06</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4129.9</v>
+        <v>3990.3</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>19.76</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-8.76</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="J17" s="5" t="n">
-        <v>43.77</v>
+        <v>45.73</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1345,36 +1345,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4191.26</v>
+        <v>4110.14</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4181.9</v>
+        <v>4129.9</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.24%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>19.76</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="J18" s="5" t="n">
-        <v>42.46</v>
+        <v>43.77</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1394,36 +1394,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4209.02</v>
+        <v>4191.26</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4224.1</v>
+        <v>4181.9</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>42.84</v>
+        <v>42.46</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1443,134 +1443,134 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4257.71</v>
+        <v>4209.02</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4358.9</v>
+        <v>4224.1</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>101.19</v>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
+        <v>15.08</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>37.86</v>
+        <v>42.84</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4331.14</v>
+        <v>4257.71</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$7.23</t>
+          <t>+$1.76</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4330.9</v>
+        <v>4358.9</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>101.19</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>31.5</v>
+        <v>37.86</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4309.03</v>
+        <v>4331.14</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$52.77</t>
+          <t>+$7.23</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4328</v>
+        <v>4330.9</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>18.97</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0.24</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1578,8 +1578,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J22" s="4" t="n">
-        <v>30.25</v>
+      <c r="J22" s="5" t="n">
+        <v>31.5</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1590,36 +1590,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4218.71</v>
+        <v>4309.03</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-1.08</t>
+          <t>+$52.77</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4215</v>
+        <v>4328</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+3.05%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-3.71</v>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>18.97</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1627,8 +1627,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n">
-        <v>29.98</v>
+      <c r="J23" s="3" t="n">
+        <v>30.25</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1639,34 +1639,34 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4210.69</v>
+        <v>4218.71</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$10.16</t>
+          <t>$-1.08</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4090.3</v>
+        <v>4215</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+3.05%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-120.39</v>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
+        <v>-3.71</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1676,57 +1676,57 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J24" s="4" t="n">
-        <v>22.73</v>
+      <c r="J24" s="3" t="n">
+        <v>29.98</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4071.28</v>
+        <v>4210.69</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-5.95</t>
+          <t>+$10.16</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4108.2</v>
+        <v>4090.3</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3.56%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>36.92</v>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>12.14</v>
+        <v>-120.39</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>22.73</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1737,81 +1737,81 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4259.29</v>
+        <v>4071.28</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-4.41%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-5.95</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4260</v>
+        <v>4108.2</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>12.17</v>
+        <v>36.92</v>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>12.14</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4329.75</v>
+        <v>4259.29</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-2.37</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4335.9</v>
+        <v>4260</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>6.15</v>
+        <v>0.71</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1823,8 +1823,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n">
-        <v>14.5</v>
+      <c r="J27" s="3" t="n">
+        <v>12.17</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1835,32 +1835,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4328.15</v>
+        <v>4329.75</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-3.29%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$7.90</t>
+          <t>$-2.37</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4337.1</v>
+        <v>4335.9</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-3.10%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>8.949999999999999</v>
+        <v>6.15</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1872,8 +1872,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="4" t="n">
-        <v>16.4</v>
+      <c r="J28" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1884,32 +1884,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4475.25</v>
+        <v>4328.15</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-3.29%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$7.80</t>
+          <t>+$7.90</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4475.8</v>
+        <v>4337.1</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-3.10%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.55</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1921,8 +1921,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n">
-        <v>16.51</v>
+      <c r="J29" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1933,32 +1933,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4434.3</v>
+        <v>4475.25</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$3.39</t>
+          <t>+$7.80</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4436.7</v>
+        <v>4475.8</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2.4</v>
+        <v>0.55</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1970,8 +1970,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n">
-        <v>17.59</v>
+      <c r="J30" s="3" t="n">
+        <v>16.51</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1982,32 +1982,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4487.78</v>
+        <v>4434.3</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-3.86</t>
+          <t>+$3.39</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4489.1</v>
+        <v>4436.7</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1.32</v>
+        <v>2.4</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2019,8 +2019,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n">
-        <v>20.84</v>
+      <c r="J31" s="3" t="n">
+        <v>17.59</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -561,32 +561,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3976.48</v>
+        <v>4017.04</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$4.31</t>
+          <t>+$1.19</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3983.5</v>
+        <v>4023</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-1.50%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7.02</v>
+        <v>5.96</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>22.62</v>
+        <v>21.91</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -610,36 +610,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4060.55</v>
+        <v>3976.48</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$0.46</t>
+          <t>+$4.31</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4044</v>
+        <v>3985.6</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-16.55</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>9.119999999999999</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>21.84</v>
+        <v>22.77</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -659,36 +659,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4052.92</v>
+        <v>4060.55</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$5.21</t>
+          <t>+$0.46</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4061.1</v>
+        <v>4044</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+1.60%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-16.55</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>22.12</v>
+        <v>21.84</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -708,36 +708,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4000.78</v>
+        <v>4052.92</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$5.21</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3997</v>
+        <v>4061.1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2.61%</t>
+          <t>+1.60%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>8.18</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>23.34</v>
+        <v>22.12</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -757,32 +757,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4119.29</v>
+        <v>4000.78</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4104.1</v>
+        <v>3997</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-2.61%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-15.19</v>
+        <v>-3.78</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>24.27</v>
+        <v>23.34</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -806,36 +806,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4123.38</v>
+        <v>4119.29</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4130.6</v>
+        <v>4104.1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-15.19</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>28.82</v>
+        <v>24.27</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -855,36 +855,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4077.4</v>
+        <v>4123.38</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4070.9</v>
+        <v>4130.6</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>7.22</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -892,8 +892,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="5" t="n">
-        <v>35.09</v>
+      <c r="J8" s="3" t="n">
+        <v>28.82</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -904,36 +904,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4105.67</v>
+        <v>4077.4</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4145.3</v>
+        <v>4070.9</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>39.63</v>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-6.5</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -942,47 +942,47 @@
         </is>
       </c>
       <c r="J9" s="5" t="n">
-        <v>33.16</v>
+        <v>35.09</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4165.04</v>
+        <v>4105.67</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4155.1</v>
+        <v>4145.3</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>-9.94</v>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>39.63</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -991,43 +991,43 @@
         </is>
       </c>
       <c r="J10" s="5" t="n">
-        <v>31.24</v>
+        <v>33.16</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4123.77</v>
+        <v>4165.04</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4112.7</v>
+        <v>4155.1</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>-11.07</v>
+        <v>-9.94</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="J11" s="5" t="n">
-        <v>39.5</v>
+        <v>31.24</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1051,36 +1051,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4031.01</v>
+        <v>4123.77</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4068.3</v>
+        <v>4112.7</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-11.07</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1089,47 +1089,47 @@
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>47.28</v>
+        <v>39.5</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4007.41</v>
+        <v>4031.01</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4022.9</v>
+        <v>4068.3</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>15.49</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>37.29</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1138,43 +1138,43 @@
         </is>
       </c>
       <c r="J13" s="5" t="n">
-        <v>48.31</v>
+        <v>47.28</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4016.54</v>
+        <v>4007.41</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4022.3</v>
+        <v>4022.9</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>5.76</v>
+        <v>15.49</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>48</v>
+        <v>48.31</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1198,36 +1198,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4089.95</v>
+        <v>4016.54</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4078.7</v>
+        <v>4022.3</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-11.25</v>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>5.76</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="J15" s="5" t="n">
-        <v>46.99</v>
+        <v>48</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1247,36 +1247,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4026.57</v>
+        <v>4089.95</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4030.5</v>
+        <v>4078.7</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-11.25</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>46.5</v>
+        <v>46.99</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1296,36 +1296,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3999.06</v>
+        <v>4026.57</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3990.3</v>
+        <v>4030.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-8.76</v>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>3.93</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="J17" s="5" t="n">
-        <v>45.73</v>
+        <v>46.5</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1345,36 +1345,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4110.14</v>
+        <v>3999.06</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4129.9</v>
+        <v>3990.3</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>19.76</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-8.76</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="J18" s="5" t="n">
-        <v>43.77</v>
+        <v>45.73</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1394,36 +1394,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4191.26</v>
+        <v>4110.14</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4181.9</v>
+        <v>4129.9</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.24%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>19.76</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>42.46</v>
+        <v>43.77</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1443,36 +1443,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4209.02</v>
+        <v>4191.26</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4224.1</v>
+        <v>4181.9</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>42.84</v>
+        <v>42.46</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1492,134 +1492,134 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4257.71</v>
+        <v>4209.02</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4358.9</v>
+        <v>4224.1</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>101.19</v>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
+        <v>15.08</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>37.86</v>
+        <v>42.84</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4331.14</v>
+        <v>4257.71</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$7.23</t>
+          <t>+$1.76</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4330.9</v>
+        <v>4358.9</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>101.19</v>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>31.5</v>
+        <v>37.86</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4309.03</v>
+        <v>4331.14</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$52.77</t>
+          <t>+$7.23</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4328</v>
+        <v>4330.9</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>18.97</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0.24</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1627,8 +1627,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="3" t="n">
-        <v>30.25</v>
+      <c r="J23" s="5" t="n">
+        <v>31.5</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1639,36 +1639,36 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4218.71</v>
+        <v>4309.03</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-1.08</t>
+          <t>+$52.77</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4215</v>
+        <v>4328</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+3.05%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-3.71</v>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>18.97</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>29.98</v>
+        <v>30.25</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1688,32 +1688,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4210.69</v>
+        <v>4218.71</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$10.16</t>
+          <t>$-1.08</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4090.3</v>
+        <v>4215</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+3.05%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-120.39</v>
+        <v>-3.71</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -1726,56 +1726,56 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>22.73</v>
+        <v>29.98</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4071.28</v>
+        <v>4210.69</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-5.95</t>
+          <t>+$10.16</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4108.2</v>
+        <v>4090.3</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-3.56%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>36.92</v>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
+        <v>-120.39</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>12.14</v>
+        <v>22.73</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1786,81 +1786,81 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4259.29</v>
+        <v>4071.28</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-4.41%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-5.95</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4260</v>
+        <v>4108.2</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>36.92</v>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>12.17</v>
+        <v>12.14</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4329.75</v>
+        <v>4259.29</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-2.37</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4335.9</v>
+        <v>4260</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>6.15</v>
+        <v>0.71</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>14.5</v>
+        <v>12.17</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1884,32 +1884,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4328.15</v>
+        <v>4329.75</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3.29%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$7.90</t>
+          <t>$-2.37</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4337.1</v>
+        <v>4335.9</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3.10%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>8.949999999999999</v>
+        <v>6.15</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>16.4</v>
+        <v>14.5</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1933,32 +1933,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4475.25</v>
+        <v>4328.15</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-3.29%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$7.80</t>
+          <t>+$7.90</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4475.8</v>
+        <v>4337.1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-3.10%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.55</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>16.51</v>
+        <v>16.4</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1982,32 +1982,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4434.3</v>
+        <v>4475.25</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$3.39</t>
+          <t>+$7.80</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4436.7</v>
+        <v>4475.8</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2.4</v>
+        <v>0.55</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>17.59</v>
+        <v>16.51</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -50,14 +50,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-        <bgColor rgb="00C00000"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -105,10 +105,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -578,19 +578,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4023</v>
+        <v>4012.7</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>+0.68%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-4.34</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -598,8 +598,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n">
-        <v>21.91</v>
+      <c r="J2" s="4" t="n">
+        <v>22.65</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J3" s="4" t="n">
         <v>22.77</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -686,7 +686,7 @@
       <c r="G4" t="n">
         <v>-16.55</v>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -696,7 +696,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J4" s="4" t="n">
         <v>21.84</v>
       </c>
       <c r="K4" t="inlineStr">
@@ -745,7 +745,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J5" s="4" t="n">
         <v>22.12</v>
       </c>
       <c r="K5" t="inlineStr">
@@ -784,7 +784,7 @@
       <c r="G6" t="n">
         <v>-3.78</v>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -794,7 +794,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J6" s="4" t="n">
         <v>23.34</v>
       </c>
       <c r="K6" t="inlineStr">
@@ -833,7 +833,7 @@
       <c r="G7" t="n">
         <v>-15.19</v>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -843,7 +843,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J7" s="4" t="n">
         <v>24.27</v>
       </c>
       <c r="K7" t="inlineStr">
@@ -892,7 +892,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J8" s="4" t="n">
         <v>28.82</v>
       </c>
       <c r="K8" t="inlineStr">
@@ -931,7 +931,7 @@
       <c r="G9" t="n">
         <v>-6.5</v>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1029,7 +1029,7 @@
       <c r="G11" t="n">
         <v>-9.94</v>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1078,7 +1078,7 @@
       <c r="G12" t="n">
         <v>-11.07</v>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1274,7 +1274,7 @@
       <c r="G16" t="n">
         <v>-11.25</v>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1372,7 +1372,7 @@
       <c r="G18" t="n">
         <v>-8.76</v>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1470,7 +1470,7 @@
       <c r="G20" t="n">
         <v>-9.359999999999999</v>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1617,7 +1617,7 @@
       <c r="G23" t="n">
         <v>-0.24</v>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1676,7 +1676,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J24" s="3" t="n">
+      <c r="J24" s="4" t="n">
         <v>30.25</v>
       </c>
       <c r="K24" t="inlineStr">
@@ -1715,7 +1715,7 @@
       <c r="G25" t="n">
         <v>-3.71</v>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1725,7 +1725,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="3" t="n">
+      <c r="J25" s="4" t="n">
         <v>29.98</v>
       </c>
       <c r="K25" t="inlineStr">
@@ -1764,7 +1764,7 @@
       <c r="G26" t="n">
         <v>-120.39</v>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1774,7 +1774,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="3" t="n">
+      <c r="J26" s="4" t="n">
         <v>22.73</v>
       </c>
       <c r="K26" t="inlineStr">
@@ -1823,7 +1823,7 @@
           <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
-      <c r="J27" s="3" t="n">
+      <c r="J27" s="4" t="n">
         <v>12.14</v>
       </c>
       <c r="K27" t="inlineStr">
@@ -1872,7 +1872,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="3" t="n">
+      <c r="J28" s="4" t="n">
         <v>12.17</v>
       </c>
       <c r="K28" t="inlineStr">
@@ -1921,7 +1921,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="3" t="n">
+      <c r="J29" s="4" t="n">
         <v>14.5</v>
       </c>
       <c r="K29" t="inlineStr">
@@ -1970,7 +1970,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="3" t="n">
+      <c r="J30" s="4" t="n">
         <v>16.4</v>
       </c>
       <c r="K30" t="inlineStr">
@@ -2019,7 +2019,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="3" t="n">
+      <c r="J31" s="4" t="n">
         <v>16.51</v>
       </c>
       <c r="K31" t="inlineStr">

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -50,14 +50,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-        <bgColor rgb="00C00000"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
       </patternFill>
     </fill>
     <fill>
@@ -105,10 +105,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -561,36 +561,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4017.04</v>
+        <v>4007.49</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$1.19</t>
+          <t>$-12.24</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4012.7</v>
+        <v>4010.3</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-4.34</v>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>2.81</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -598,8 +598,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>22.65</v>
+      <c r="J2" s="3" t="n">
+        <v>21.95</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -610,36 +610,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3976.48</v>
+        <v>4017.04</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$4.31</t>
+          <t>+$1.19</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3985.6</v>
+        <v>4012.7</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+0.68%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-4.34</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -647,8 +647,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>22.77</v>
+      <c r="J3" s="3" t="n">
+        <v>22.65</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -659,36 +659,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4060.55</v>
+        <v>3976.48</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$0.46</t>
+          <t>+$4.31</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4044</v>
+        <v>3985.6</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-16.55</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>9.119999999999999</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -696,8 +696,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>21.84</v>
+      <c r="J4" s="3" t="n">
+        <v>22.77</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -708,36 +708,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4052.92</v>
+        <v>4060.55</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$5.21</t>
+          <t>+$0.46</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4061.1</v>
+        <v>4044</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+1.60%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-16.55</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -745,8 +745,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>22.12</v>
+      <c r="J5" s="3" t="n">
+        <v>21.84</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -757,36 +757,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4000.78</v>
+        <v>4052.92</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$5.21</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3997</v>
+        <v>4061.1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2.61%</t>
+          <t>+1.60%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>8.18</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -794,8 +794,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="4" t="n">
-        <v>23.34</v>
+      <c r="J6" s="3" t="n">
+        <v>22.12</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -806,34 +806,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4119.29</v>
+        <v>4000.78</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4104.1</v>
+        <v>3997</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-2.61%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>-15.19</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
+        <v>-3.78</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -843,8 +843,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
-        <v>24.27</v>
+      <c r="J7" s="3" t="n">
+        <v>23.34</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -855,36 +855,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4123.38</v>
+        <v>4119.29</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4130.6</v>
+        <v>4104.1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-15.19</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -892,8 +892,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n">
-        <v>28.82</v>
+      <c r="J8" s="3" t="n">
+        <v>24.27</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -904,36 +904,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4077.4</v>
+        <v>4123.38</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4070.9</v>
+        <v>4130.6</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>7.22</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -941,8 +941,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="5" t="n">
-        <v>35.09</v>
+      <c r="J9" s="3" t="n">
+        <v>28.82</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -953,36 +953,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4105.67</v>
+        <v>4077.4</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4145.3</v>
+        <v>4070.9</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>39.63</v>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-6.5</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -991,47 +991,47 @@
         </is>
       </c>
       <c r="J10" s="5" t="n">
-        <v>33.16</v>
+        <v>35.09</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4165.04</v>
+        <v>4105.67</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4155.1</v>
+        <v>4145.3</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>-9.94</v>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>39.63</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1040,45 +1040,45 @@
         </is>
       </c>
       <c r="J11" s="5" t="n">
-        <v>31.24</v>
+        <v>33.16</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4123.77</v>
+        <v>4165.04</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4112.7</v>
+        <v>4155.1</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>-11.07</v>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
+        <v>-9.94</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>39.5</v>
+        <v>31.24</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1100,36 +1100,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4031.01</v>
+        <v>4123.77</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4068.3</v>
+        <v>4112.7</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-11.07</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1138,47 +1138,47 @@
         </is>
       </c>
       <c r="J13" s="5" t="n">
-        <v>47.28</v>
+        <v>39.5</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4007.41</v>
+        <v>4031.01</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4022.9</v>
+        <v>4068.3</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>15.49</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>37.29</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1187,43 +1187,43 @@
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>48.31</v>
+        <v>47.28</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4016.54</v>
+        <v>4007.41</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4022.3</v>
+        <v>4022.9</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5.76</v>
+        <v>15.49</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="J15" s="5" t="n">
-        <v>48</v>
+        <v>48.31</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1247,36 +1247,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4089.95</v>
+        <v>4016.54</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4078.7</v>
+        <v>4022.3</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-11.25</v>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>5.76</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>46.99</v>
+        <v>48</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1296,36 +1296,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4026.57</v>
+        <v>4089.95</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4030.5</v>
+        <v>4078.7</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-11.25</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="J17" s="5" t="n">
-        <v>46.5</v>
+        <v>46.99</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1345,36 +1345,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3999.06</v>
+        <v>4026.57</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3990.3</v>
+        <v>4030.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-8.76</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>3.93</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="J18" s="5" t="n">
-        <v>45.73</v>
+        <v>46.5</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1394,36 +1394,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4110.14</v>
+        <v>3999.06</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4129.9</v>
+        <v>3990.3</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>19.76</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-8.76</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>43.77</v>
+        <v>45.73</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1443,36 +1443,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4191.26</v>
+        <v>4110.14</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4181.9</v>
+        <v>4129.9</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.24%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>19.76</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>42.46</v>
+        <v>43.77</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1492,36 +1492,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4209.02</v>
+        <v>4191.26</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4224.1</v>
+        <v>4181.9</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>42.84</v>
+        <v>42.46</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1541,134 +1541,134 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4257.71</v>
+        <v>4209.02</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4358.9</v>
+        <v>4224.1</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>101.19</v>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
+        <v>15.08</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>37.86</v>
+        <v>42.84</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4331.14</v>
+        <v>4257.71</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$7.23</t>
+          <t>+$1.76</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4330.9</v>
+        <v>4358.9</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>101.19</v>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J23" s="5" t="n">
-        <v>31.5</v>
+        <v>37.86</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4309.03</v>
+        <v>4331.14</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$52.77</t>
+          <t>+$7.23</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4328</v>
+        <v>4330.9</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>18.97</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0.24</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1676,8 +1676,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J24" s="4" t="n">
-        <v>30.25</v>
+      <c r="J24" s="5" t="n">
+        <v>31.5</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1688,36 +1688,36 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4218.71</v>
+        <v>4309.03</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-1.08</t>
+          <t>+$52.77</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4215</v>
+        <v>4328</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+3.05%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-3.71</v>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>18.97</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1725,8 +1725,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n">
-        <v>29.98</v>
+      <c r="J25" s="5" t="n">
+        <v>30.25</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1737,34 +1737,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4210.69</v>
+        <v>4218.71</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$10.16</t>
+          <t>$-1.08</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4090.3</v>
+        <v>4215</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+3.05%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-120.39</v>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
+        <v>-3.71</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1774,57 +1774,57 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n">
-        <v>22.73</v>
+      <c r="J26" s="3" t="n">
+        <v>29.98</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4071.28</v>
+        <v>4210.69</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-5.95</t>
+          <t>+$10.16</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4108.2</v>
+        <v>4090.3</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-3.56%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>36.92</v>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>12.14</v>
+        <v>-120.39</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>22.73</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1835,81 +1835,81 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4259.29</v>
+        <v>4071.28</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-4.41%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-5.95</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4260</v>
+        <v>4108.2</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v>12.17</v>
+        <v>36.92</v>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>12.14</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4329.75</v>
+        <v>4259.29</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-2.37</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4335.9</v>
+        <v>4260</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>6.15</v>
+        <v>0.71</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1921,8 +1921,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n">
-        <v>14.5</v>
+      <c r="J29" s="3" t="n">
+        <v>12.17</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1933,32 +1933,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4328.15</v>
+        <v>4329.75</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-3.29%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$7.90</t>
+          <t>$-2.37</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4337.1</v>
+        <v>4335.9</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-3.10%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>8.949999999999999</v>
+        <v>6.15</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1970,8 +1970,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n">
-        <v>16.4</v>
+      <c r="J30" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1982,32 +1982,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4475.25</v>
+        <v>4328.15</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-3.29%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$7.80</t>
+          <t>+$7.90</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4475.8</v>
+        <v>4337.1</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-3.10%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.55</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2019,8 +2019,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n">
-        <v>16.51</v>
+      <c r="J31" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -50,14 +50,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-        <bgColor rgb="00C00000"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -105,10 +105,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -561,36 +561,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4007.49</v>
+        <v>4077.87</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>$-12.24</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4010.3</v>
+        <v>4071.1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-6.77</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -598,8 +598,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n">
-        <v>21.95</v>
+      <c r="J2" s="4" t="n">
+        <v>21.93</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -610,36 +610,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4017.04</v>
+        <v>4007.49</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$1.19</t>
+          <t>$-12.24</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4012.7</v>
+        <v>4010.3</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-4.34</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>2.81</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -647,8 +647,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n">
-        <v>22.65</v>
+      <c r="J3" s="4" t="n">
+        <v>21.95</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -659,36 +659,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3976.48</v>
+        <v>4017.04</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$4.31</t>
+          <t>+$1.19</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3985.6</v>
+        <v>4012.7</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+0.68%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-4.34</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -696,8 +696,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
-        <v>22.77</v>
+      <c r="J4" s="4" t="n">
+        <v>22.65</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -708,36 +708,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4060.55</v>
+        <v>3976.48</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$0.46</t>
+          <t>+$4.31</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4044</v>
+        <v>3985.6</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-16.55</v>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>9.119999999999999</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -745,8 +745,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
-        <v>21.84</v>
+      <c r="J5" s="4" t="n">
+        <v>22.77</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -757,36 +757,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4052.92</v>
+        <v>4060.55</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$5.21</t>
+          <t>+$0.46</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4061.1</v>
+        <v>4044</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+1.60%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-16.55</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -794,8 +794,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>22.12</v>
+      <c r="J6" s="4" t="n">
+        <v>21.84</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -806,36 +806,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4000.78</v>
+        <v>4052.92</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$5.21</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3997</v>
+        <v>4061.1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2.61%</t>
+          <t>+1.60%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>8.18</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -843,8 +843,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n">
-        <v>23.34</v>
+      <c r="J7" s="4" t="n">
+        <v>22.12</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -855,34 +855,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4119.29</v>
+        <v>4000.78</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4104.1</v>
+        <v>3997</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-2.61%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>-15.19</v>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
+        <v>-3.78</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -892,8 +892,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n">
-        <v>24.27</v>
+      <c r="J8" s="4" t="n">
+        <v>23.34</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -904,36 +904,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4123.38</v>
+        <v>4119.29</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4130.6</v>
+        <v>4104.1</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-15.19</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -941,8 +941,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="3" t="n">
-        <v>28.82</v>
+      <c r="J9" s="4" t="n">
+        <v>24.27</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -953,36 +953,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4077.4</v>
+        <v>4123.38</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4070.9</v>
+        <v>4130.6</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>7.22</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -990,8 +990,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="5" t="n">
-        <v>35.09</v>
+      <c r="J10" s="4" t="n">
+        <v>28.82</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1002,36 +1002,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4105.67</v>
+        <v>4077.4</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4145.3</v>
+        <v>4070.9</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>39.63</v>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-6.5</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1040,47 +1040,47 @@
         </is>
       </c>
       <c r="J11" s="5" t="n">
-        <v>33.16</v>
+        <v>35.09</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4165.04</v>
+        <v>4105.67</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4155.1</v>
+        <v>4145.3</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>-9.94</v>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>39.63</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1089,45 +1089,45 @@
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>31.24</v>
+        <v>33.16</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4123.77</v>
+        <v>4165.04</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4112.7</v>
+        <v>4155.1</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-11.07</v>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
+        <v>-9.94</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="J13" s="5" t="n">
-        <v>39.5</v>
+        <v>31.24</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1149,36 +1149,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4031.01</v>
+        <v>4123.77</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4068.3</v>
+        <v>4112.7</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-11.07</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1187,47 +1187,47 @@
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>47.28</v>
+        <v>39.5</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4007.41</v>
+        <v>4031.01</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4022.9</v>
+        <v>4068.3</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>15.49</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>37.29</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1236,43 +1236,43 @@
         </is>
       </c>
       <c r="J15" s="5" t="n">
-        <v>48.31</v>
+        <v>47.28</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4016.54</v>
+        <v>4007.41</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4022.3</v>
+        <v>4022.9</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>5.76</v>
+        <v>15.49</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>48</v>
+        <v>48.31</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1296,36 +1296,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4089.95</v>
+        <v>4016.54</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4078.7</v>
+        <v>4022.3</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-11.25</v>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>5.76</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="J17" s="5" t="n">
-        <v>46.99</v>
+        <v>48</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1345,36 +1345,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4026.57</v>
+        <v>4089.95</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4030.5</v>
+        <v>4078.7</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-11.25</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="J18" s="5" t="n">
-        <v>46.5</v>
+        <v>46.99</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1394,36 +1394,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3999.06</v>
+        <v>4026.57</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3990.3</v>
+        <v>4030.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-8.76</v>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>3.93</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>45.73</v>
+        <v>46.5</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1443,36 +1443,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4110.14</v>
+        <v>3999.06</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4129.9</v>
+        <v>3990.3</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>19.76</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-8.76</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>43.77</v>
+        <v>45.73</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1492,36 +1492,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4191.26</v>
+        <v>4110.14</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4181.9</v>
+        <v>4129.9</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.24%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>19.76</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>42.46</v>
+        <v>43.77</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1541,36 +1541,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4209.02</v>
+        <v>4191.26</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4224.1</v>
+        <v>4181.9</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>42.84</v>
+        <v>42.46</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1590,134 +1590,134 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4257.71</v>
+        <v>4209.02</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4358.9</v>
+        <v>4224.1</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>101.19</v>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
+        <v>15.08</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
         </is>
       </c>
       <c r="J23" s="5" t="n">
-        <v>37.86</v>
+        <v>42.84</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4331.14</v>
+        <v>4257.71</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$7.23</t>
+          <t>+$1.76</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4330.9</v>
+        <v>4358.9</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>101.19</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J24" s="5" t="n">
-        <v>31.5</v>
+        <v>37.86</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4309.03</v>
+        <v>4331.14</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$52.77</t>
+          <t>+$7.23</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4328</v>
+        <v>4330.9</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>18.97</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0.24</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="J25" s="5" t="n">
-        <v>30.25</v>
+        <v>31.5</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1737,36 +1737,36 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4218.71</v>
+        <v>4309.03</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-1.08</t>
+          <t>+$52.77</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4215</v>
+        <v>4328</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+3.05%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-3.71</v>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>18.97</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1774,8 +1774,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="3" t="n">
-        <v>29.98</v>
+      <c r="J26" s="5" t="n">
+        <v>30.25</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1786,34 +1786,34 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4210.69</v>
+        <v>4218.71</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$10.16</t>
+          <t>$-1.08</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4090.3</v>
+        <v>4215</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+3.05%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-120.39</v>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
+        <v>-3.71</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1823,57 +1823,57 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="3" t="n">
-        <v>22.73</v>
+      <c r="J27" s="4" t="n">
+        <v>29.98</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4071.28</v>
+        <v>4210.69</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-5.95</t>
+          <t>+$10.16</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4108.2</v>
+        <v>4090.3</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-3.56%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>36.92</v>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>12.14</v>
+        <v>-120.39</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>22.73</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1884,81 +1884,81 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4259.29</v>
+        <v>4071.28</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-4.41%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-5.95</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4260</v>
+        <v>4108.2</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>12.17</v>
+        <v>36.92</v>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>12.14</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4329.75</v>
+        <v>4259.29</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-2.37</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4335.9</v>
+        <v>4260</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>6.15</v>
+        <v>0.71</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1970,8 +1970,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="3" t="n">
-        <v>14.5</v>
+      <c r="J30" s="4" t="n">
+        <v>12.17</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1982,32 +1982,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4328.15</v>
+        <v>4329.75</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-3.29%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$7.90</t>
+          <t>$-2.37</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4337.1</v>
+        <v>4335.9</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3.10%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>8.949999999999999</v>
+        <v>6.15</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2019,8 +2019,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="3" t="n">
-        <v>16.4</v>
+      <c r="J31" s="4" t="n">
+        <v>14.5</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -50,14 +50,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-        <bgColor rgb="00C00000"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
       </patternFill>
     </fill>
     <fill>
@@ -105,10 +105,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -561,36 +561,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4077.87</v>
+        <v>4134.01</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$1.94</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4071.1</v>
+        <v>4146.9</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+1.52%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-6.77</v>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>12.89</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -598,8 +598,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>21.93</v>
+      <c r="J2" s="3" t="n">
+        <v>21.78</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -610,36 +610,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4007.49</v>
+        <v>4077.87</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>$-12.24</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4010.3</v>
+        <v>4071.1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-6.77</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -647,8 +647,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>21.95</v>
+      <c r="J3" s="3" t="n">
+        <v>21.93</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -659,36 +659,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4017.04</v>
+        <v>4007.49</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$1.19</t>
+          <t>$-12.24</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4012.7</v>
+        <v>4010.3</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-4.34</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>2.81</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -696,8 +696,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>22.65</v>
+      <c r="J4" s="3" t="n">
+        <v>21.95</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -708,36 +708,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3976.48</v>
+        <v>4017.04</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$4.31</t>
+          <t>+$1.19</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3985.6</v>
+        <v>4012.7</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+0.68%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-4.34</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -745,8 +745,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>22.77</v>
+      <c r="J5" s="3" t="n">
+        <v>22.65</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -757,36 +757,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4060.55</v>
+        <v>3976.48</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$0.46</t>
+          <t>+$4.31</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4044</v>
+        <v>3985.6</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-16.55</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>9.119999999999999</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -794,8 +794,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="4" t="n">
-        <v>21.84</v>
+      <c r="J6" s="3" t="n">
+        <v>22.77</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -806,36 +806,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4052.92</v>
+        <v>4060.55</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$5.21</t>
+          <t>+$0.46</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4061.1</v>
+        <v>4044</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+1.60%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-16.55</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -843,8 +843,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
-        <v>22.12</v>
+      <c r="J7" s="3" t="n">
+        <v>21.84</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -855,36 +855,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4000.78</v>
+        <v>4052.92</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$5.21</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3997</v>
+        <v>4061.1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2.61%</t>
+          <t>+1.60%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>8.18</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -892,8 +892,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n">
-        <v>23.34</v>
+      <c r="J8" s="3" t="n">
+        <v>22.12</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -904,34 +904,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4119.29</v>
+        <v>4000.78</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4104.1</v>
+        <v>3997</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-2.61%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>-15.19</v>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
+        <v>-3.78</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -941,8 +941,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
-        <v>24.27</v>
+      <c r="J9" s="3" t="n">
+        <v>23.34</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -953,36 +953,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4123.38</v>
+        <v>4119.29</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4130.6</v>
+        <v>4104.1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-15.19</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -990,8 +990,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n">
-        <v>28.82</v>
+      <c r="J10" s="3" t="n">
+        <v>24.27</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1002,36 +1002,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4077.4</v>
+        <v>4123.38</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4070.9</v>
+        <v>4130.6</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>7.22</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1039,8 +1039,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J11" s="5" t="n">
-        <v>35.09</v>
+      <c r="J11" s="3" t="n">
+        <v>28.82</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1051,36 +1051,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4105.67</v>
+        <v>4077.4</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4145.3</v>
+        <v>4070.9</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>39.63</v>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-6.5</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1089,47 +1089,47 @@
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>33.16</v>
+        <v>35.09</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4165.04</v>
+        <v>4105.67</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4155.1</v>
+        <v>4145.3</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-9.94</v>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>39.63</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1138,45 +1138,45 @@
         </is>
       </c>
       <c r="J13" s="5" t="n">
-        <v>31.24</v>
+        <v>33.16</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4123.77</v>
+        <v>4165.04</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4112.7</v>
+        <v>4155.1</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-11.07</v>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
+        <v>-9.94</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>39.5</v>
+        <v>31.24</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1198,36 +1198,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4031.01</v>
+        <v>4123.77</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4068.3</v>
+        <v>4112.7</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-11.07</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1236,47 +1236,47 @@
         </is>
       </c>
       <c r="J15" s="5" t="n">
-        <v>47.28</v>
+        <v>39.5</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4007.41</v>
+        <v>4031.01</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4022.9</v>
+        <v>4068.3</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>15.49</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>37.29</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1285,43 +1285,43 @@
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>48.31</v>
+        <v>47.28</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4016.54</v>
+        <v>4007.41</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4022.3</v>
+        <v>4022.9</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>5.76</v>
+        <v>15.49</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="J17" s="5" t="n">
-        <v>48</v>
+        <v>48.31</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1345,36 +1345,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4089.95</v>
+        <v>4016.54</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4078.7</v>
+        <v>4022.3</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-11.25</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>5.76</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="J18" s="5" t="n">
-        <v>46.99</v>
+        <v>48</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1394,36 +1394,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4026.57</v>
+        <v>4089.95</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4030.5</v>
+        <v>4078.7</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-11.25</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>46.5</v>
+        <v>46.99</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1443,36 +1443,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3999.06</v>
+        <v>4026.57</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3990.3</v>
+        <v>4030.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>-8.76</v>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>3.93</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>45.73</v>
+        <v>46.5</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1492,36 +1492,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4110.14</v>
+        <v>3999.06</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4129.9</v>
+        <v>3990.3</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>19.76</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-8.76</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>43.77</v>
+        <v>45.73</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1541,36 +1541,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4191.26</v>
+        <v>4110.14</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4181.9</v>
+        <v>4129.9</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.24%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>19.76</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>42.46</v>
+        <v>43.77</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1590,36 +1590,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4209.02</v>
+        <v>4191.26</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4224.1</v>
+        <v>4181.9</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="J23" s="5" t="n">
-        <v>42.84</v>
+        <v>42.46</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1639,134 +1639,134 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4257.71</v>
+        <v>4209.02</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4358.9</v>
+        <v>4224.1</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>101.19</v>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
+        <v>15.08</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
         </is>
       </c>
       <c r="J24" s="5" t="n">
-        <v>37.86</v>
+        <v>42.84</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4331.14</v>
+        <v>4257.71</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$7.23</t>
+          <t>+$1.76</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4330.9</v>
+        <v>4358.9</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>101.19</v>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J25" s="5" t="n">
-        <v>31.5</v>
+        <v>37.86</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4309.03</v>
+        <v>4331.14</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$52.77</t>
+          <t>+$7.23</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4328</v>
+        <v>4330.9</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>18.97</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0.24</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="J26" s="5" t="n">
-        <v>30.25</v>
+        <v>31.5</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1786,36 +1786,36 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4218.71</v>
+        <v>4309.03</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-1.08</t>
+          <t>+$52.77</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4215</v>
+        <v>4328</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+3.05%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-3.71</v>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>18.97</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1823,8 +1823,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n">
-        <v>29.98</v>
+      <c r="J27" s="5" t="n">
+        <v>30.25</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1835,34 +1835,34 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4210.69</v>
+        <v>4218.71</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$10.16</t>
+          <t>$-1.08</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4090.3</v>
+        <v>4215</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+3.05%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-120.39</v>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
+        <v>-3.71</v>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1872,57 +1872,57 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="4" t="n">
-        <v>22.73</v>
+      <c r="J28" s="3" t="n">
+        <v>29.98</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4071.28</v>
+        <v>4210.69</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-5.95</t>
+          <t>+$10.16</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4108.2</v>
+        <v>4090.3</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3.56%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>36.92</v>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>12.14</v>
+        <v>-120.39</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>22.73</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1933,81 +1933,81 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4259.29</v>
+        <v>4071.28</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-4.41%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-5.95</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4260</v>
+        <v>4108.2</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>12.17</v>
+        <v>36.92</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>12.14</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4329.75</v>
+        <v>4259.29</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-2.37</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4335.9</v>
+        <v>4260</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>6.15</v>
+        <v>0.71</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2019,8 +2019,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n">
-        <v>14.5</v>
+      <c r="J31" s="3" t="n">
+        <v>12.17</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -561,32 +561,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4134.01</v>
+        <v>4052.74</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$1.94</t>
+          <t>+$0.61</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4146.9</v>
+        <v>4070.8</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+1.86%</t>
+          <t>+0.60%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>12.89</v>
+        <v>18.06</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>21.78</v>
+        <v>21.42</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -610,32 +610,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4077.87</v>
+        <v>4049.43</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>$-10.76</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4071.1</v>
+        <v>4046.6</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+1.52%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-6.77</v>
+        <v>-2.83</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>21.93</v>
+        <v>20.01</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -659,32 +659,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4007.49</v>
+        <v>4130.11</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$-12.24</t>
+          <t>+$1.94</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4010.3</v>
+        <v>4146.9</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2.81</v>
+        <v>16.79</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>21.95</v>
+        <v>22.06</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -708,32 +708,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4017.04</v>
+        <v>4077.87</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$1.19</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4012.7</v>
+        <v>4071.1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-4.34</v>
+        <v>-6.77</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>22.65</v>
+        <v>21.93</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -757,32 +757,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3976.48</v>
+        <v>4007.49</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$4.31</t>
+          <t>$-12.24</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3985.6</v>
+        <v>4010.3</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>9.119999999999999</v>
+        <v>2.81</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>22.77</v>
+        <v>21.95</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -806,32 +806,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4060.55</v>
+        <v>4017.04</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$0.46</t>
+          <t>+$1.19</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4044</v>
+        <v>4012.7</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.68%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>-16.55</v>
+        <v>-4.34</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>21.84</v>
+        <v>22.65</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -855,32 +855,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4052.92</v>
+        <v>3976.48</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$5.21</t>
+          <t>+$4.31</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4061.1</v>
+        <v>3985.6</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+1.60%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>8.18</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>22.12</v>
+        <v>22.77</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -904,32 +904,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4000.78</v>
+        <v>4060.55</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$0.46</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3997</v>
+        <v>4044</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2.61%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>-3.78</v>
+        <v>-16.55</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>23.34</v>
+        <v>21.84</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -953,36 +953,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4119.29</v>
+        <v>4052.92</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>+$5.21</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4104.1</v>
+        <v>4061.1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>+1.60%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>-15.19</v>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>8.18</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>24.27</v>
+        <v>22.12</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1002,36 +1002,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4123.38</v>
+        <v>4000.78</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4130.6</v>
+        <v>3997</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>-2.61%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-3.78</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>28.82</v>
+        <v>23.34</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1051,32 +1051,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4077.4</v>
+        <v>4119.29</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4070.9</v>
+        <v>4104.1</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>-6.5</v>
+        <v>-15.19</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
@@ -1088,8 +1088,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>35.09</v>
+      <c r="J12" s="3" t="n">
+        <v>24.27</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1100,36 +1100,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4105.67</v>
+        <v>4123.38</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4145.3</v>
+        <v>4130.6</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>39.63</v>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>7.22</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1137,44 +1137,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J13" s="5" t="n">
-        <v>33.16</v>
+      <c r="J13" s="3" t="n">
+        <v>28.82</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4165.04</v>
+        <v>4077.4</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4155.1</v>
+        <v>4070.9</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-9.94</v>
+        <v>-6.5</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>31.24</v>
+        <v>35.09</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1198,36 +1198,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4123.77</v>
+        <v>4105.67</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4112.7</v>
+        <v>4145.3</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-11.07</v>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>39.63</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1236,47 +1236,47 @@
         </is>
       </c>
       <c r="J15" s="5" t="n">
-        <v>39.5</v>
+        <v>33.16</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4031.01</v>
+        <v>4165.04</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4068.3</v>
+        <v>4155.1</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-9.94</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1285,47 +1285,47 @@
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>47.28</v>
+        <v>31.24</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4007.41</v>
+        <v>4123.77</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4022.9</v>
+        <v>4112.7</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>15.49</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-11.07</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="J17" s="5" t="n">
-        <v>48.31</v>
+        <v>39.5</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1345,36 +1345,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4016.54</v>
+        <v>4031.01</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4022.3</v>
+        <v>4068.3</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>37.29</v>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1383,47 +1383,47 @@
         </is>
       </c>
       <c r="J18" s="5" t="n">
-        <v>48</v>
+        <v>47.28</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4089.95</v>
+        <v>4007.41</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4078.7</v>
+        <v>4022.9</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-11.25</v>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>15.49</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>46.99</v>
+        <v>48.31</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1443,32 +1443,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4026.57</v>
+        <v>4016.54</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4030.5</v>
+        <v>4022.3</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3.93</v>
+        <v>5.76</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>46.5</v>
+        <v>48</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1492,32 +1492,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3999.06</v>
+        <v>4089.95</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3990.3</v>
+        <v>4078.7</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-8.76</v>
+        <v>-11.25</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>45.73</v>
+        <v>46.99</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1541,32 +1541,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4110.14</v>
+        <v>4026.57</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4129.9</v>
+        <v>4030.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>19.76</v>
+        <v>3.93</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>43.77</v>
+        <v>46.5</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1590,32 +1590,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4191.26</v>
+        <v>3999.06</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4181.9</v>
+        <v>3990.3</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-9.359999999999999</v>
+        <v>-8.76</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="J23" s="5" t="n">
-        <v>42.46</v>
+        <v>45.73</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1639,32 +1639,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4209.02</v>
+        <v>4110.14</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4224.1</v>
+        <v>4129.9</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-1.24%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>15.08</v>
+        <v>19.76</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="J24" s="5" t="n">
-        <v>42.84</v>
+        <v>43.77</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1688,85 +1688,85 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4257.71</v>
+        <v>4191.26</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4358.9</v>
+        <v>4181.9</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>101.19</v>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
         </is>
       </c>
       <c r="J25" s="5" t="n">
-        <v>37.86</v>
+        <v>42.46</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4331.14</v>
+        <v>4209.02</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$7.23</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4330.9</v>
+        <v>4224.1</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>15.08</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="J26" s="5" t="n">
-        <v>31.5</v>
+        <v>42.84</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1786,81 +1786,81 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4309.03</v>
+        <v>4257.71</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$52.77</t>
+          <t>+$1.76</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4328</v>
+        <v>4358.9</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>18.97</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>101.19</v>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J27" s="5" t="n">
-        <v>30.25</v>
+        <v>37.86</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4218.71</v>
+        <v>4331.14</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-1.08</t>
+          <t>+$7.23</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4215</v>
+        <v>4330.9</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+3.05%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-3.71</v>
+        <v>-0.24</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
@@ -1872,8 +1872,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="3" t="n">
-        <v>29.98</v>
+      <c r="J28" s="5" t="n">
+        <v>31.5</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1884,36 +1884,36 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4210.69</v>
+        <v>4309.03</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$10.16</t>
+          <t>+$52.77</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4090.3</v>
+        <v>4328</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-120.39</v>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>18.97</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1921,97 +1921,97 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="3" t="n">
-        <v>22.73</v>
+      <c r="J29" s="5" t="n">
+        <v>30.25</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4071.28</v>
+        <v>4218.71</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-5.95</t>
+          <t>$-1.08</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4108.2</v>
+        <v>4215</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-3.56%</t>
+          <t>+3.05%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>36.92</v>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>12.14</v>
+        <v>-3.71</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>29.98</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4259.29</v>
+        <v>4210.69</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>+$10.16</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4260</v>
+        <v>4090.3</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-120.39</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2020,11 +2020,11 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>12.17</v>
+        <v>22.73</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -50,14 +50,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-        <bgColor rgb="00C00000"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -105,10 +105,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -561,36 +561,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4052.74</v>
+        <v>4076.6</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$0.61</t>
+          <t>+$43.44</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4070.8</v>
+        <v>4074.5</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.60%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>18.06</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-2.1</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -598,8 +598,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n">
-        <v>21.42</v>
+      <c r="J2" s="4" t="n">
+        <v>18.86</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -610,36 +610,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4049.43</v>
+        <v>4052.74</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>$-10.76</t>
+          <t>+$0.61</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4046.6</v>
+        <v>4067.6</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-2.83</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>14.86</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -647,8 +647,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n">
-        <v>20.01</v>
+      <c r="J3" s="4" t="n">
+        <v>21.19</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -659,36 +659,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4130.11</v>
+        <v>4049.43</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$1.94</t>
+          <t>$-10.76</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4146.9</v>
+        <v>4046.6</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+1.86%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>16.79</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-2.83</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -696,8 +696,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
-        <v>22.06</v>
+      <c r="J4" s="4" t="n">
+        <v>20.01</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -708,36 +708,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4077.87</v>
+        <v>4130.11</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$1.94</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4071.1</v>
+        <v>4146.9</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+1.52%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-6.77</v>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>16.79</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -745,8 +745,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
-        <v>21.93</v>
+      <c r="J5" s="4" t="n">
+        <v>22.06</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -757,36 +757,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4007.49</v>
+        <v>4077.87</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$-12.24</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4010.3</v>
+        <v>4071.1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-6.77</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -794,8 +794,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>21.95</v>
+      <c r="J6" s="4" t="n">
+        <v>21.93</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -806,36 +806,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4017.04</v>
+        <v>4007.49</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$1.19</t>
+          <t>$-12.24</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4012.7</v>
+        <v>4010.3</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>-4.34</v>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>2.81</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -843,8 +843,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n">
-        <v>22.65</v>
+      <c r="J7" s="4" t="n">
+        <v>21.95</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -855,36 +855,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3976.48</v>
+        <v>4017.04</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$4.31</t>
+          <t>+$1.19</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3985.6</v>
+        <v>4012.7</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+0.68%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-4.34</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -892,8 +892,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n">
-        <v>22.77</v>
+      <c r="J8" s="4" t="n">
+        <v>22.65</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -904,36 +904,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4060.55</v>
+        <v>3976.48</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$0.46</t>
+          <t>+$4.31</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4044</v>
+        <v>3985.6</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>-16.55</v>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>9.119999999999999</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -941,8 +941,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="3" t="n">
-        <v>21.84</v>
+      <c r="J9" s="4" t="n">
+        <v>22.77</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -953,36 +953,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4052.92</v>
+        <v>4060.55</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$5.21</t>
+          <t>+$0.46</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4061.1</v>
+        <v>4044</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+1.60%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-16.55</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -990,8 +990,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="3" t="n">
-        <v>22.12</v>
+      <c r="J10" s="4" t="n">
+        <v>21.84</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1002,36 +1002,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4000.78</v>
+        <v>4052.92</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$5.21</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3997</v>
+        <v>4061.1</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2.61%</t>
+          <t>+1.60%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>8.18</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1039,8 +1039,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J11" s="3" t="n">
-        <v>23.34</v>
+      <c r="J11" s="4" t="n">
+        <v>22.12</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1051,34 +1051,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4119.29</v>
+        <v>4000.78</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4104.1</v>
+        <v>3997</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-2.61%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>-15.19</v>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
+        <v>-3.78</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1088,8 +1088,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J12" s="3" t="n">
-        <v>24.27</v>
+      <c r="J12" s="4" t="n">
+        <v>23.34</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1100,36 +1100,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4123.38</v>
+        <v>4119.29</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4130.6</v>
+        <v>4104.1</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-15.19</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1137,8 +1137,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J13" s="3" t="n">
-        <v>28.82</v>
+      <c r="J13" s="4" t="n">
+        <v>24.27</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1149,36 +1149,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4077.4</v>
+        <v>4123.38</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4070.9</v>
+        <v>4130.6</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>7.22</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1186,8 +1186,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J14" s="5" t="n">
-        <v>35.09</v>
+      <c r="J14" s="4" t="n">
+        <v>28.82</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1198,36 +1198,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4105.67</v>
+        <v>4077.4</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4145.3</v>
+        <v>4070.9</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>39.63</v>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-6.5</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1236,47 +1236,47 @@
         </is>
       </c>
       <c r="J15" s="5" t="n">
-        <v>33.16</v>
+        <v>35.09</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4165.04</v>
+        <v>4105.67</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4155.1</v>
+        <v>4145.3</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-9.94</v>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>39.63</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1285,45 +1285,45 @@
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>31.24</v>
+        <v>33.16</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4123.77</v>
+        <v>4165.04</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4112.7</v>
+        <v>4155.1</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-11.07</v>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
+        <v>-9.94</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="J17" s="5" t="n">
-        <v>39.5</v>
+        <v>31.24</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1345,36 +1345,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4031.01</v>
+        <v>4123.77</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4068.3</v>
+        <v>4112.7</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-11.07</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1383,47 +1383,47 @@
         </is>
       </c>
       <c r="J18" s="5" t="n">
-        <v>47.28</v>
+        <v>39.5</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4007.41</v>
+        <v>4031.01</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4022.9</v>
+        <v>4068.3</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>15.49</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>37.29</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1432,43 +1432,43 @@
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>48.31</v>
+        <v>47.28</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4016.54</v>
+        <v>4007.41</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4022.3</v>
+        <v>4022.9</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>5.76</v>
+        <v>15.49</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>48</v>
+        <v>48.31</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1492,36 +1492,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4089.95</v>
+        <v>4016.54</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4078.7</v>
+        <v>4022.3</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-11.25</v>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>5.76</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>46.99</v>
+        <v>48</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1541,36 +1541,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4026.57</v>
+        <v>4089.95</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4030.5</v>
+        <v>4078.7</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-11.25</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>46.5</v>
+        <v>46.99</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1590,36 +1590,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3999.06</v>
+        <v>4026.57</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3990.3</v>
+        <v>4030.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-8.76</v>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>3.93</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="J23" s="5" t="n">
-        <v>45.73</v>
+        <v>46.5</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1639,36 +1639,36 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4110.14</v>
+        <v>3999.06</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4129.9</v>
+        <v>3990.3</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>19.76</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-8.76</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="J24" s="5" t="n">
-        <v>43.77</v>
+        <v>45.73</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1688,36 +1688,36 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4191.26</v>
+        <v>4110.14</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4181.9</v>
+        <v>4129.9</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.24%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>19.76</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="J25" s="5" t="n">
-        <v>42.46</v>
+        <v>43.77</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1737,36 +1737,36 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4209.02</v>
+        <v>4191.26</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4224.1</v>
+        <v>4181.9</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="J26" s="5" t="n">
-        <v>42.84</v>
+        <v>42.46</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1786,134 +1786,134 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4257.71</v>
+        <v>4209.02</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4358.9</v>
+        <v>4224.1</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>101.19</v>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
+        <v>15.08</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
         </is>
       </c>
       <c r="J27" s="5" t="n">
-        <v>37.86</v>
+        <v>42.84</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4331.14</v>
+        <v>4257.71</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$7.23</t>
+          <t>+$1.76</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4330.9</v>
+        <v>4358.9</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>101.19</v>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J28" s="5" t="n">
-        <v>31.5</v>
+        <v>37.86</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4309.03</v>
+        <v>4331.14</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$52.77</t>
+          <t>+$7.23</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4328</v>
+        <v>4330.9</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>18.97</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0.24</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="J29" s="5" t="n">
-        <v>30.25</v>
+        <v>31.5</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1933,36 +1933,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4218.71</v>
+        <v>4309.03</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-1.08</t>
+          <t>+$52.77</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4215</v>
+        <v>4328</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+3.05%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-3.71</v>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>18.97</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="J30" s="5" t="n">
-        <v>29.98</v>
+        <v>30.25</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1982,34 +1982,34 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4210.69</v>
+        <v>4218.71</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$10.16</t>
+          <t>$-1.08</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4090.3</v>
+        <v>4215</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+3.05%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>-120.39</v>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
+        <v>-3.71</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -2019,12 +2019,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="3" t="n">
-        <v>22.73</v>
+      <c r="J31" s="5" t="n">
+        <v>29.98</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -50,14 +50,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-        <bgColor rgb="00C00000"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
       </patternFill>
     </fill>
     <fill>
@@ -105,10 +105,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -561,36 +561,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4076.6</v>
+        <v>4028.54</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$43.44</t>
+          <t>+$2.81</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4074.5</v>
+        <v>4036.3</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>7.76</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -598,8 +598,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>18.86</v>
+      <c r="J2" s="3" t="n">
+        <v>16.27</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -610,36 +610,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4052.74</v>
+        <v>4076.6</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$0.61</t>
+          <t>+$43.44</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4067.6</v>
+        <v>4074.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>14.86</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-2.1</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -647,8 +647,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>21.19</v>
+      <c r="J3" s="3" t="n">
+        <v>18.86</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -659,36 +659,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4049.43</v>
+        <v>4052.74</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$-10.76</t>
+          <t>+$0.61</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4046.6</v>
+        <v>4067.6</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-2.83</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>14.86</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -696,8 +696,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>20.01</v>
+      <c r="J4" s="3" t="n">
+        <v>21.19</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -708,36 +708,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4130.11</v>
+        <v>4049.43</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$1.94</t>
+          <t>$-10.76</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4146.9</v>
+        <v>4046.6</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+1.86%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>16.79</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-2.83</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -745,8 +745,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>22.06</v>
+      <c r="J5" s="3" t="n">
+        <v>20.01</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -757,36 +757,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4077.87</v>
+        <v>4130.11</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$1.94</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4071.1</v>
+        <v>4146.9</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+1.52%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-6.77</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>16.79</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -794,8 +794,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="4" t="n">
-        <v>21.93</v>
+      <c r="J6" s="3" t="n">
+        <v>22.06</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -806,36 +806,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4007.49</v>
+        <v>4077.87</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$-12.24</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4010.3</v>
+        <v>4071.1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-6.77</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -843,8 +843,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
-        <v>21.95</v>
+      <c r="J7" s="3" t="n">
+        <v>21.93</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -855,36 +855,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4017.04</v>
+        <v>4007.49</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$1.19</t>
+          <t>$-12.24</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4012.7</v>
+        <v>4010.3</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>-4.34</v>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>2.81</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -892,8 +892,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n">
-        <v>22.65</v>
+      <c r="J8" s="3" t="n">
+        <v>21.95</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -904,36 +904,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3976.48</v>
+        <v>4017.04</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$4.31</t>
+          <t>+$1.19</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3985.6</v>
+        <v>4012.7</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+0.68%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-4.34</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -941,8 +941,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
-        <v>22.77</v>
+      <c r="J9" s="3" t="n">
+        <v>22.65</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -953,36 +953,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4060.55</v>
+        <v>3976.48</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$0.46</t>
+          <t>+$4.31</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4044</v>
+        <v>3985.6</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>-16.55</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>9.119999999999999</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -990,8 +990,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n">
-        <v>21.84</v>
+      <c r="J10" s="3" t="n">
+        <v>22.77</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1002,36 +1002,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4052.92</v>
+        <v>4060.55</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$5.21</t>
+          <t>+$0.46</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4061.1</v>
+        <v>4044</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+1.60%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-16.55</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1039,8 +1039,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n">
-        <v>22.12</v>
+      <c r="J11" s="3" t="n">
+        <v>21.84</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1051,36 +1051,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4000.78</v>
+        <v>4052.92</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$5.21</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3997</v>
+        <v>4061.1</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2.61%</t>
+          <t>+1.60%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>8.18</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1088,8 +1088,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J12" s="4" t="n">
-        <v>23.34</v>
+      <c r="J12" s="3" t="n">
+        <v>22.12</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1100,34 +1100,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4119.29</v>
+        <v>4000.78</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4104.1</v>
+        <v>3997</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-2.61%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-15.19</v>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
+        <v>-3.78</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1137,8 +1137,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J13" s="4" t="n">
-        <v>24.27</v>
+      <c r="J13" s="3" t="n">
+        <v>23.34</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1149,36 +1149,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4123.38</v>
+        <v>4119.29</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4130.6</v>
+        <v>4104.1</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-15.19</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1186,8 +1186,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J14" s="4" t="n">
-        <v>28.82</v>
+      <c r="J14" s="3" t="n">
+        <v>24.27</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1198,36 +1198,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4077.4</v>
+        <v>4123.38</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4070.9</v>
+        <v>4130.6</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>7.22</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1235,8 +1235,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J15" s="5" t="n">
-        <v>35.09</v>
+      <c r="J15" s="3" t="n">
+        <v>28.82</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1247,36 +1247,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4105.67</v>
+        <v>4077.4</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4145.3</v>
+        <v>4070.9</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>39.63</v>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-6.5</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1285,47 +1285,47 @@
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>33.16</v>
+        <v>35.09</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4165.04</v>
+        <v>4105.67</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4155.1</v>
+        <v>4145.3</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-9.94</v>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>39.63</v>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1334,45 +1334,45 @@
         </is>
       </c>
       <c r="J17" s="5" t="n">
-        <v>31.24</v>
+        <v>33.16</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4123.77</v>
+        <v>4165.04</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4112.7</v>
+        <v>4155.1</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-11.07</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
+        <v>-9.94</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="J18" s="5" t="n">
-        <v>39.5</v>
+        <v>31.24</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1394,36 +1394,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4031.01</v>
+        <v>4123.77</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4068.3</v>
+        <v>4112.7</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-11.07</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>47.28</v>
+        <v>39.5</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4007.41</v>
+        <v>4031.01</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4022.9</v>
+        <v>4068.3</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>15.49</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>37.29</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1481,43 +1481,43 @@
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>48.31</v>
+        <v>47.28</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4016.54</v>
+        <v>4007.41</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4022.3</v>
+        <v>4022.9</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>5.76</v>
+        <v>15.49</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>48</v>
+        <v>48.31</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1541,36 +1541,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4089.95</v>
+        <v>4016.54</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4078.7</v>
+        <v>4022.3</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-11.25</v>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>5.76</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>46.99</v>
+        <v>48</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1590,36 +1590,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4026.57</v>
+        <v>4089.95</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4030.5</v>
+        <v>4078.7</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-11.25</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="J23" s="5" t="n">
-        <v>46.5</v>
+        <v>46.99</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1639,36 +1639,36 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3999.06</v>
+        <v>4026.57</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3990.3</v>
+        <v>4030.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-8.76</v>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>3.93</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="J24" s="5" t="n">
-        <v>45.73</v>
+        <v>46.5</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1688,36 +1688,36 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4110.14</v>
+        <v>3999.06</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4129.9</v>
+        <v>3990.3</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>19.76</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-8.76</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="J25" s="5" t="n">
-        <v>43.77</v>
+        <v>45.73</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1737,36 +1737,36 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4191.26</v>
+        <v>4110.14</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4181.9</v>
+        <v>4129.9</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.24%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>19.76</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="J26" s="5" t="n">
-        <v>42.46</v>
+        <v>43.77</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1786,36 +1786,36 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4209.02</v>
+        <v>4191.26</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4224.1</v>
+        <v>4181.9</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="J27" s="5" t="n">
-        <v>42.84</v>
+        <v>42.46</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1835,134 +1835,134 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4257.71</v>
+        <v>4209.02</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4358.9</v>
+        <v>4224.1</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>101.19</v>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
+        <v>15.08</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
         </is>
       </c>
       <c r="J28" s="5" t="n">
-        <v>37.86</v>
+        <v>42.84</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4331.14</v>
+        <v>4257.71</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$7.23</t>
+          <t>+$1.76</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4330.9</v>
+        <v>4358.9</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>101.19</v>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J29" s="5" t="n">
-        <v>31.5</v>
+        <v>37.86</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4309.03</v>
+        <v>4331.14</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$52.77</t>
+          <t>+$7.23</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4328</v>
+        <v>4330.9</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>18.97</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0.24</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="J30" s="5" t="n">
-        <v>30.25</v>
+        <v>31.5</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1982,36 +1982,36 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4218.71</v>
+        <v>4309.03</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-1.08</t>
+          <t>+$52.77</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4215</v>
+        <v>4328</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+3.05%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>-3.71</v>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>18.97</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="J31" s="5" t="n">
-        <v>29.98</v>
+        <v>30.25</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -561,32 +561,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4028.54</v>
+        <v>4008.28</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>-0.50%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$2.81</t>
+          <t>+$1.59</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4036.3</v>
+        <v>4034.7</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7.76</v>
+        <v>26.42</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>16.27</v>
+        <v>16.62</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -610,36 +610,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4076.6</v>
+        <v>4028.54</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$43.44</t>
+          <t>+$2.81</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4074.5</v>
+        <v>4036.3</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>7.76</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>18.86</v>
+        <v>16.27</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -659,36 +659,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4052.74</v>
+        <v>4076.6</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$0.61</t>
+          <t>+$43.44</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4067.6</v>
+        <v>4074.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>14.86</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-2.1</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>21.19</v>
+        <v>18.86</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -708,36 +708,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4049.43</v>
+        <v>4052.74</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>$-10.76</t>
+          <t>+$0.61</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4046.6</v>
+        <v>4067.6</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-2.83</v>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>14.86</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>20.01</v>
+        <v>21.19</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -757,36 +757,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4130.11</v>
+        <v>4049.43</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$1.94</t>
+          <t>$-10.76</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4146.9</v>
+        <v>4046.6</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+1.86%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>16.79</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-2.83</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>22.06</v>
+        <v>20.01</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -806,36 +806,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4077.87</v>
+        <v>4130.11</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$1.94</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4071.1</v>
+        <v>4146.9</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+1.52%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>-6.77</v>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>16.79</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>21.93</v>
+        <v>22.06</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -855,36 +855,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4007.49</v>
+        <v>4077.87</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$-12.24</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4010.3</v>
+        <v>4071.1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-6.77</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>21.95</v>
+        <v>21.93</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -904,36 +904,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4017.04</v>
+        <v>4007.49</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$1.19</t>
+          <t>$-12.24</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4012.7</v>
+        <v>4010.3</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>-4.34</v>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>2.81</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>22.65</v>
+        <v>21.95</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -953,36 +953,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3976.48</v>
+        <v>4017.04</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$4.31</t>
+          <t>+$1.19</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3985.6</v>
+        <v>4012.7</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+0.68%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-4.34</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>22.77</v>
+        <v>22.65</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1002,36 +1002,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4060.55</v>
+        <v>3976.48</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$0.46</t>
+          <t>+$4.31</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4044</v>
+        <v>3985.6</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>-16.55</v>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>9.119999999999999</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>21.84</v>
+        <v>22.77</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1051,36 +1051,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4052.92</v>
+        <v>4060.55</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$5.21</t>
+          <t>+$0.46</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4061.1</v>
+        <v>4044</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+1.60%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-16.55</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>22.12</v>
+        <v>21.84</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1100,36 +1100,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4000.78</v>
+        <v>4052.92</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$5.21</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3997</v>
+        <v>4061.1</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2.61%</t>
+          <t>+1.60%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>8.18</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>23.34</v>
+        <v>22.12</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1149,32 +1149,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4119.29</v>
+        <v>4000.78</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4104.1</v>
+        <v>3997</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-2.61%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-15.19</v>
+        <v>-3.78</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>24.27</v>
+        <v>23.34</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1198,36 +1198,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4123.38</v>
+        <v>4119.29</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4130.6</v>
+        <v>4104.1</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-15.19</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>28.82</v>
+        <v>24.27</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1247,36 +1247,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4077.4</v>
+        <v>4123.38</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4070.9</v>
+        <v>4130.6</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>7.22</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1284,8 +1284,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J16" s="5" t="n">
-        <v>35.09</v>
+      <c r="J16" s="3" t="n">
+        <v>28.82</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1296,36 +1296,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4105.67</v>
+        <v>4077.4</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4145.3</v>
+        <v>4070.9</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>39.63</v>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-6.5</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1334,47 +1334,47 @@
         </is>
       </c>
       <c r="J17" s="5" t="n">
-        <v>33.16</v>
+        <v>35.09</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4165.04</v>
+        <v>4105.67</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4155.1</v>
+        <v>4145.3</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-9.94</v>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>39.63</v>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1383,43 +1383,43 @@
         </is>
       </c>
       <c r="J18" s="5" t="n">
-        <v>31.24</v>
+        <v>33.16</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4123.77</v>
+        <v>4165.04</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4112.7</v>
+        <v>4155.1</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-11.07</v>
+        <v>-9.94</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>39.5</v>
+        <v>31.24</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1443,36 +1443,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4031.01</v>
+        <v>4123.77</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4068.3</v>
+        <v>4112.7</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-11.07</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1481,47 +1481,47 @@
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>47.28</v>
+        <v>39.5</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4007.41</v>
+        <v>4031.01</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4022.9</v>
+        <v>4068.3</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>15.49</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>37.29</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1530,43 +1530,43 @@
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>48.31</v>
+        <v>47.28</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4016.54</v>
+        <v>4007.41</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4022.3</v>
+        <v>4022.9</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>5.76</v>
+        <v>15.49</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>48</v>
+        <v>48.31</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1590,36 +1590,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4089.95</v>
+        <v>4016.54</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4078.7</v>
+        <v>4022.3</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-11.25</v>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>5.76</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="J23" s="5" t="n">
-        <v>46.99</v>
+        <v>48</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1639,36 +1639,36 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4026.57</v>
+        <v>4089.95</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4030.5</v>
+        <v>4078.7</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-11.25</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="J24" s="5" t="n">
-        <v>46.5</v>
+        <v>46.99</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1688,36 +1688,36 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3999.06</v>
+        <v>4026.57</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3990.3</v>
+        <v>4030.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-8.76</v>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>3.93</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="J25" s="5" t="n">
-        <v>45.73</v>
+        <v>46.5</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1737,36 +1737,36 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4110.14</v>
+        <v>3999.06</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4129.9</v>
+        <v>3990.3</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>19.76</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-8.76</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="J26" s="5" t="n">
-        <v>43.77</v>
+        <v>45.73</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1786,36 +1786,36 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4191.26</v>
+        <v>4110.14</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4181.9</v>
+        <v>4129.9</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.24%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>19.76</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="J27" s="5" t="n">
-        <v>42.46</v>
+        <v>43.77</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1835,36 +1835,36 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4209.02</v>
+        <v>4191.26</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4224.1</v>
+        <v>4181.9</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="J28" s="5" t="n">
-        <v>42.84</v>
+        <v>42.46</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1884,134 +1884,134 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4257.71</v>
+        <v>4209.02</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4358.9</v>
+        <v>4224.1</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>101.19</v>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
+        <v>15.08</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
         </is>
       </c>
       <c r="J29" s="5" t="n">
-        <v>37.86</v>
+        <v>42.84</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4331.14</v>
+        <v>4257.71</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$7.23</t>
+          <t>+$1.76</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4330.9</v>
+        <v>4358.9</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>101.19</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J30" s="5" t="n">
-        <v>31.5</v>
+        <v>37.86</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4309.03</v>
+        <v>4331.14</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$52.77</t>
+          <t>+$7.23</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4328</v>
+        <v>4330.9</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>18.97</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0.24</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="J31" s="5" t="n">
-        <v>30.25</v>
+        <v>31.5</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -561,32 +561,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4008.28</v>
+        <v>4078.88</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-0.50%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$1.59</t>
+          <t>+$0.17</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4034.7</v>
+        <v>4100.1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+1.62%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>26.42</v>
+        <v>21.22</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>16.62</v>
+        <v>20.26</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -610,36 +610,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4028.54</v>
+        <v>4066.23</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$2.81</t>
+          <t>+$1.59</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4036.3</v>
+        <v>4034.7</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-31.53</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -648,47 +648,47 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>16.27</v>
+        <v>18.1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4076.6</v>
+        <v>4028.54</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$43.44</t>
+          <t>+$2.81</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4074.5</v>
+        <v>4036.3</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>7.76</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>18.86</v>
+        <v>16.27</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -708,36 +708,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4052.74</v>
+        <v>4076.6</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$0.61</t>
+          <t>+$43.44</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4067.6</v>
+        <v>4074.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>14.86</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-2.1</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>21.19</v>
+        <v>18.86</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -757,36 +757,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4049.43</v>
+        <v>4052.74</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$-10.76</t>
+          <t>+$0.61</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4046.6</v>
+        <v>4067.6</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-2.83</v>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>14.86</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>20.01</v>
+        <v>21.19</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -806,36 +806,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4130.11</v>
+        <v>4049.43</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$1.94</t>
+          <t>$-10.76</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4146.9</v>
+        <v>4046.6</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+1.86%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>16.79</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-2.83</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>22.06</v>
+        <v>20.01</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -855,36 +855,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4077.87</v>
+        <v>4130.11</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$1.94</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4071.1</v>
+        <v>4146.9</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+1.52%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>-6.77</v>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>16.79</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>21.93</v>
+        <v>22.06</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -904,36 +904,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4007.49</v>
+        <v>4077.87</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$-12.24</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4010.3</v>
+        <v>4071.1</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-6.77</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>21.95</v>
+        <v>21.93</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -953,36 +953,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4017.04</v>
+        <v>4007.49</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$1.19</t>
+          <t>$-12.24</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4012.7</v>
+        <v>4010.3</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>-4.34</v>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>2.81</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>22.65</v>
+        <v>21.95</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1002,36 +1002,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3976.48</v>
+        <v>4017.04</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$4.31</t>
+          <t>+$1.19</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3985.6</v>
+        <v>4012.7</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+0.68%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-4.34</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>22.77</v>
+        <v>22.65</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1051,36 +1051,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4060.55</v>
+        <v>3976.48</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$0.46</t>
+          <t>+$4.31</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4044</v>
+        <v>3985.6</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>-16.55</v>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>9.119999999999999</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>21.84</v>
+        <v>22.77</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1100,36 +1100,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4052.92</v>
+        <v>4060.55</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$5.21</t>
+          <t>+$0.46</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4061.1</v>
+        <v>4044</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+1.60%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-16.55</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>22.12</v>
+        <v>21.84</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1149,36 +1149,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4000.78</v>
+        <v>4052.92</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$5.21</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3997</v>
+        <v>4061.1</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-2.61%</t>
+          <t>+1.60%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>8.18</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>23.34</v>
+        <v>22.12</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1198,32 +1198,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4119.29</v>
+        <v>4000.78</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4104.1</v>
+        <v>3997</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-2.61%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-15.19</v>
+        <v>-3.78</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>24.27</v>
+        <v>23.34</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1247,36 +1247,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4123.38</v>
+        <v>4119.29</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4130.6</v>
+        <v>4104.1</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-15.19</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>28.82</v>
+        <v>24.27</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1296,36 +1296,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4077.4</v>
+        <v>4123.38</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4070.9</v>
+        <v>4130.6</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>7.22</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1333,8 +1333,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J17" s="5" t="n">
-        <v>35.09</v>
+      <c r="J17" s="3" t="n">
+        <v>28.82</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1345,36 +1345,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4105.67</v>
+        <v>4077.4</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4145.3</v>
+        <v>4070.9</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>39.63</v>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-6.5</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1383,47 +1383,47 @@
         </is>
       </c>
       <c r="J18" s="5" t="n">
-        <v>33.16</v>
+        <v>35.09</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4165.04</v>
+        <v>4105.67</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4155.1</v>
+        <v>4145.3</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-9.94</v>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>39.63</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1432,43 +1432,43 @@
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>31.24</v>
+        <v>33.16</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4123.77</v>
+        <v>4165.04</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4112.7</v>
+        <v>4155.1</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>-11.07</v>
+        <v>-9.94</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>39.5</v>
+        <v>31.24</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1492,36 +1492,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4031.01</v>
+        <v>4123.77</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4068.3</v>
+        <v>4112.7</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+        <v>-11.07</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1530,47 +1530,47 @@
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>47.28</v>
+        <v>39.5</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4007.41</v>
+        <v>4031.01</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4022.9</v>
+        <v>4068.3</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>15.49</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>37.29</v>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1579,43 +1579,43 @@
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>48.31</v>
+        <v>47.28</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4016.54</v>
+        <v>4007.41</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4022.3</v>
+        <v>4022.9</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>5.76</v>
+        <v>15.49</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="J23" s="5" t="n">
-        <v>48</v>
+        <v>48.31</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1639,36 +1639,36 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4089.95</v>
+        <v>4016.54</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4078.7</v>
+        <v>4022.3</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-11.25</v>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>5.76</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="J24" s="5" t="n">
-        <v>46.99</v>
+        <v>48</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1688,36 +1688,36 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4026.57</v>
+        <v>4089.95</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4030.5</v>
+        <v>4078.7</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-11.25</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="J25" s="5" t="n">
-        <v>46.5</v>
+        <v>46.99</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1737,36 +1737,36 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3999.06</v>
+        <v>4026.57</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3990.3</v>
+        <v>4030.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-8.76</v>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>3.93</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="J26" s="5" t="n">
-        <v>45.73</v>
+        <v>46.5</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1786,36 +1786,36 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4110.14</v>
+        <v>3999.06</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4129.9</v>
+        <v>3990.3</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>19.76</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-8.76</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="J27" s="5" t="n">
-        <v>43.77</v>
+        <v>45.73</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1835,36 +1835,36 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4191.26</v>
+        <v>4110.14</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4181.9</v>
+        <v>4129.9</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.24%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>19.76</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="J28" s="5" t="n">
-        <v>42.46</v>
+        <v>43.77</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1884,36 +1884,36 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4209.02</v>
+        <v>4191.26</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4224.1</v>
+        <v>4181.9</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="J29" s="5" t="n">
-        <v>42.84</v>
+        <v>42.46</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1933,98 +1933,98 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4257.71</v>
+        <v>4209.02</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4358.9</v>
+        <v>4224.1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>101.19</v>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
+        <v>15.08</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
         </is>
       </c>
       <c r="J30" s="5" t="n">
-        <v>37.86</v>
+        <v>42.84</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4331.14</v>
+        <v>4257.71</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$7.23</t>
+          <t>+$1.76</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4330.9</v>
+        <v>4358.9</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>101.19</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J31" s="5" t="n">
-        <v>31.5</v>
+        <v>37.86</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -50,6 +50,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
         <bgColor rgb="00E2EFDA"/>
       </patternFill>
@@ -64,18 +76,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,10 +105,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -117,7 +117,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -561,83 +561,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4078.88</v>
+        <v>4049.2</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$0.17</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4100.1</v>
+        <v>4109.9</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+1.62%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>21.22</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>20.26</v>
+        <v>60.7</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>22.27</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4066.23</v>
+        <v>4103.64</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$1.59</t>
+          <t>+$0.17</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4034.7</v>
+        <v>4100.1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+1.62%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-31.53</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
+        <v>-3.54</v>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -647,48 +647,48 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n">
-        <v>18.1</v>
+      <c r="J3" s="5" t="n">
+        <v>18.5</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4028.54</v>
+        <v>4066.23</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$2.81</t>
+          <t>+$1.59</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4036.3</v>
+        <v>4034.7</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-31.53</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -696,48 +696,48 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
-        <v>16.27</v>
+      <c r="J4" s="5" t="n">
+        <v>18.1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4076.6</v>
+        <v>4028.54</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$43.44</t>
+          <t>+$2.81</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4074.5</v>
+        <v>4036.3</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>7.76</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -745,8 +745,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
-        <v>18.86</v>
+      <c r="J5" s="5" t="n">
+        <v>16.27</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -757,36 +757,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4052.74</v>
+        <v>4076.6</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$0.61</t>
+          <t>+$43.44</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4067.6</v>
+        <v>4074.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>14.86</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-2.1</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -794,8 +794,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>21.19</v>
+      <c r="J6" s="5" t="n">
+        <v>18.86</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -806,36 +806,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4049.43</v>
+        <v>4052.74</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$-10.76</t>
+          <t>+$0.61</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4046.6</v>
+        <v>4067.6</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>-2.83</v>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>14.86</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -843,8 +843,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n">
-        <v>20.01</v>
+      <c r="J7" s="5" t="n">
+        <v>21.19</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -855,36 +855,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4130.11</v>
+        <v>4049.43</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$1.94</t>
+          <t>$-10.76</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4146.9</v>
+        <v>4046.6</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+1.86%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>16.79</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-2.83</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -892,8 +892,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n">
-        <v>22.06</v>
+      <c r="J8" s="5" t="n">
+        <v>20.01</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -904,36 +904,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4077.87</v>
+        <v>4130.11</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$1.94</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4071.1</v>
+        <v>4146.9</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+1.52%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>-6.77</v>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>16.79</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -941,8 +941,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="3" t="n">
-        <v>21.93</v>
+      <c r="J9" s="5" t="n">
+        <v>22.06</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -953,36 +953,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4007.49</v>
+        <v>4077.87</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-12.24</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4010.3</v>
+        <v>4071.1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-6.77</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -990,8 +990,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="3" t="n">
-        <v>21.95</v>
+      <c r="J10" s="5" t="n">
+        <v>21.93</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1002,36 +1002,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4017.04</v>
+        <v>4007.49</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$1.19</t>
+          <t>$-12.24</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4012.7</v>
+        <v>4010.3</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>-4.34</v>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>2.81</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1039,8 +1039,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J11" s="3" t="n">
-        <v>22.65</v>
+      <c r="J11" s="5" t="n">
+        <v>21.95</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1051,36 +1051,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3976.48</v>
+        <v>4017.04</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$4.31</t>
+          <t>+$1.19</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3985.6</v>
+        <v>4012.7</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+0.68%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-4.34</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1088,8 +1088,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J12" s="3" t="n">
-        <v>22.77</v>
+      <c r="J12" s="5" t="n">
+        <v>22.65</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1100,36 +1100,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4060.55</v>
+        <v>3976.48</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$0.46</t>
+          <t>+$4.31</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4044</v>
+        <v>3985.6</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-16.55</v>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>9.119999999999999</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1137,8 +1137,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J13" s="3" t="n">
-        <v>21.84</v>
+      <c r="J13" s="5" t="n">
+        <v>22.77</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1149,36 +1149,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4052.92</v>
+        <v>4060.55</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$5.21</t>
+          <t>+$0.46</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4061.1</v>
+        <v>4044</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+1.60%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-16.55</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1186,8 +1186,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J14" s="3" t="n">
-        <v>22.12</v>
+      <c r="J14" s="5" t="n">
+        <v>21.84</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1198,36 +1198,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4000.78</v>
+        <v>4052.92</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$5.21</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3997</v>
+        <v>4061.1</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2.61%</t>
+          <t>+1.60%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>8.18</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1235,8 +1235,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J15" s="3" t="n">
-        <v>23.34</v>
+      <c r="J15" s="5" t="n">
+        <v>22.12</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1247,34 +1247,34 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4119.29</v>
+        <v>4000.78</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4104.1</v>
+        <v>3997</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-2.61%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-15.19</v>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
+        <v>-3.78</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1284,8 +1284,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J16" s="3" t="n">
-        <v>24.27</v>
+      <c r="J16" s="5" t="n">
+        <v>23.34</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1296,36 +1296,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4123.38</v>
+        <v>4119.29</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4130.6</v>
+        <v>4104.1</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-15.19</v>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1333,8 +1333,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J17" s="3" t="n">
-        <v>28.82</v>
+      <c r="J17" s="5" t="n">
+        <v>24.27</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1345,36 +1345,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4077.4</v>
+        <v>4123.38</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4070.9</v>
+        <v>4130.6</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>7.22</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="J18" s="5" t="n">
-        <v>35.09</v>
+        <v>28.82</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1394,36 +1394,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4105.67</v>
+        <v>4077.4</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4145.3</v>
+        <v>4070.9</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>39.63</v>
+        <v>-6.5</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1431,48 +1431,48 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="5" t="n">
-        <v>33.16</v>
+      <c r="J19" s="7" t="n">
+        <v>35.09</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4165.04</v>
+        <v>4105.67</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4155.1</v>
+        <v>4145.3</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>-9.94</v>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>39.63</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1480,46 +1480,46 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J20" s="5" t="n">
-        <v>31.24</v>
+      <c r="J20" s="7" t="n">
+        <v>33.16</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4123.77</v>
+        <v>4165.04</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4112.7</v>
+        <v>4155.1</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-11.07</v>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
+        <v>-9.94</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>Backwardation (Extreme Demand)</t>
         </is>
@@ -1529,8 +1529,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J21" s="5" t="n">
-        <v>39.5</v>
+      <c r="J21" s="7" t="n">
+        <v>31.24</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1541,36 +1541,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4031.01</v>
+        <v>4123.77</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4068.3</v>
+        <v>4112.7</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>37.29</v>
+        <v>-11.07</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1578,48 +1578,48 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J22" s="5" t="n">
-        <v>47.28</v>
+      <c r="J22" s="7" t="n">
+        <v>39.5</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4007.41</v>
+        <v>4031.01</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4022.9</v>
+        <v>4068.3</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>15.49</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>37.29</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1627,44 +1627,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="5" t="n">
-        <v>48.31</v>
+      <c r="J23" s="7" t="n">
+        <v>47.28</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4016.54</v>
+        <v>4007.41</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4022.3</v>
+        <v>4022.9</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>5.76</v>
+        <v>15.49</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1676,8 +1676,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J24" s="5" t="n">
-        <v>48</v>
+      <c r="J24" s="7" t="n">
+        <v>48.31</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1688,36 +1688,36 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4089.95</v>
+        <v>4016.54</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4078.7</v>
+        <v>4022.3</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-11.25</v>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>5.76</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1725,8 +1725,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="5" t="n">
-        <v>46.99</v>
+      <c r="J25" s="7" t="n">
+        <v>48</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1737,36 +1737,36 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4026.57</v>
+        <v>4089.95</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4030.5</v>
+        <v>4078.7</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-11.25</v>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1774,8 +1774,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="5" t="n">
-        <v>46.5</v>
+      <c r="J26" s="7" t="n">
+        <v>46.99</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1786,36 +1786,36 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3999.06</v>
+        <v>4026.57</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3990.3</v>
+        <v>4030.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-8.76</v>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>3.93</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1823,8 +1823,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="5" t="n">
-        <v>45.73</v>
+      <c r="J27" s="7" t="n">
+        <v>46.5</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1835,36 +1835,36 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4110.14</v>
+        <v>3999.06</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4129.9</v>
+        <v>3990.3</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>19.76</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-8.76</v>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1872,8 +1872,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="5" t="n">
-        <v>43.77</v>
+      <c r="J28" s="7" t="n">
+        <v>45.73</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1884,36 +1884,36 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4191.26</v>
+        <v>4110.14</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4181.9</v>
+        <v>4129.9</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.24%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>19.76</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1921,8 +1921,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="5" t="n">
-        <v>42.46</v>
+      <c r="J29" s="7" t="n">
+        <v>43.77</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1933,36 +1933,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4209.02</v>
+        <v>4191.26</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4224.1</v>
+        <v>4181.9</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1970,8 +1970,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="5" t="n">
-        <v>42.84</v>
+      <c r="J30" s="7" t="n">
+        <v>42.46</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1982,49 +1982,49 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4257.71</v>
+        <v>4209.02</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4358.9</v>
+        <v>4224.1</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>101.19</v>
-      </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>37.86</v>
+        <v>15.08</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>42.84</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -565,11 +565,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4049.2</v>
+        <v>4047.07</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -578,15 +578,15 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4109.9</v>
+        <v>4103.7</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>60.7</v>
+        <v>56.63</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>22.27</v>
+        <v>21.98</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,14 +34,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="007F6000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -56,20 +50,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
         <bgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-        <bgColor rgb="00C00000"/>
       </patternFill>
     </fill>
     <fill>
@@ -97,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -108,16 +90,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -496,7 +472,7 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="39" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
@@ -565,11 +541,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4047.07</v>
+        <v>4044.36</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -578,28 +554,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4103.7</v>
+        <v>4098.6</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>56.63</v>
+        <v>54.24</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>21.98</v>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>17.8</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -627,19 +603,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4100.1</v>
+        <v>4160.6</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+1.62%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-3.54</v>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>56.96</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -647,12 +623,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="5" t="n">
-        <v>18.5</v>
+      <c r="J3" s="4" t="n">
+        <v>18.21</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -676,7 +652,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4034.7</v>
+        <v>4097</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -684,11 +660,11 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-31.53</v>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>30.77</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -696,8 +672,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="5" t="n">
-        <v>18.1</v>
+      <c r="J4" s="4" t="n">
+        <v>18.03</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -725,19 +701,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4036.3</v>
+        <v>4098.6</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>70.06</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -745,12 +721,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="5" t="n">
-        <v>16.27</v>
+      <c r="J5" s="4" t="n">
+        <v>16.18</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -774,19 +750,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4074.5</v>
+        <v>4136.4</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>59.8</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -794,12 +770,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="5" t="n">
-        <v>18.86</v>
+      <c r="J6" s="4" t="n">
+        <v>18.87</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -823,19 +799,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4067.6</v>
+        <v>4129.7</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>14.86</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>76.95999999999999</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -843,12 +819,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="5" t="n">
-        <v>21.19</v>
+      <c r="J7" s="4" t="n">
+        <v>21.15</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -872,19 +848,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4046.6</v>
+        <v>4108.8</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>-2.83</v>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>59.37</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -892,12 +868,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="5" t="n">
-        <v>20.01</v>
+      <c r="J8" s="4" t="n">
+        <v>19.94</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -921,19 +897,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4146.9</v>
+        <v>4210.3</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+1.86%</t>
+          <t>+1.84%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>16.79</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>80.19</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -941,12 +917,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="5" t="n">
-        <v>22.06</v>
+      <c r="J9" s="4" t="n">
+        <v>21.96</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -970,19 +946,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4071.1</v>
+        <v>4134.2</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+1.52%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>-6.77</v>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>56.33</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -990,12 +966,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="5" t="n">
-        <v>21.93</v>
+      <c r="J10" s="4" t="n">
+        <v>21.74</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -1019,19 +995,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4010.3</v>
+        <v>4073</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>65.51000000000001</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1039,12 +1015,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J11" s="5" t="n">
-        <v>21.95</v>
+      <c r="J11" s="4" t="n">
+        <v>21.72</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -1068,19 +1044,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4012.7</v>
+        <v>4075.8</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>-4.34</v>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>58.76</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1088,12 +1064,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>22.65</v>
+      <c r="J12" s="4" t="n">
+        <v>22.33</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -1117,19 +1093,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3985.6</v>
+        <v>4048.7</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>72.22</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1137,12 +1113,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J13" s="5" t="n">
-        <v>22.77</v>
+      <c r="J13" s="4" t="n">
+        <v>22.36</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -1166,19 +1142,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4044</v>
+        <v>4109.3</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-16.55</v>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>48.75</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1186,12 +1162,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J14" s="5" t="n">
-        <v>21.84</v>
+      <c r="J14" s="4" t="n">
+        <v>21.54</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -1215,19 +1191,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4061.1</v>
+        <v>4127.9</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+1.60%</t>
+          <t>+1.58%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>74.98</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1235,12 +1211,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J15" s="5" t="n">
-        <v>22.12</v>
+      <c r="J15" s="4" t="n">
+        <v>21.93</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -1264,19 +1240,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3997</v>
+        <v>4063.6</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2.61%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>62.82</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1284,12 +1260,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J16" s="5" t="n">
-        <v>23.34</v>
+      <c r="J16" s="4" t="n">
+        <v>22.96</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -1313,19 +1289,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4104.1</v>
+        <v>4173.6</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-0.66%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-15.19</v>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>54.31</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1333,12 +1309,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J17" s="5" t="n">
-        <v>24.27</v>
+      <c r="J17" s="4" t="n">
+        <v>24.16</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -1362,19 +1338,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4130.6</v>
+        <v>4201.4</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>+1.43%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>78.02</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1382,12 +1358,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J18" s="5" t="n">
-        <v>28.82</v>
+      <c r="J18" s="4" t="n">
+        <v>28.73</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -1411,19 +1387,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4070.9</v>
+        <v>4142.1</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>64.7</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1431,12 +1407,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="7" t="n">
-        <v>35.09</v>
+      <c r="J19" s="5" t="n">
+        <v>34.99</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1436,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4145.3</v>
+        <v>4218.3</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1468,7 +1444,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>39.63</v>
+        <v>112.63</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -1480,8 +1456,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J20" s="7" t="n">
-        <v>33.16</v>
+      <c r="J20" s="5" t="n">
+        <v>32.93</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1509,19 +1485,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4155.1</v>
+        <v>4228.6</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-9.94</v>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>63.56</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1529,12 +1505,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J21" s="7" t="n">
-        <v>31.24</v>
+      <c r="J21" s="5" t="n">
+        <v>31.11</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -1558,19 +1534,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4112.7</v>
+        <v>4186.6</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-11.07</v>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>62.83</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1578,12 +1554,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J22" s="7" t="n">
-        <v>39.5</v>
+      <c r="J22" s="5" t="n">
+        <v>39.51</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -1607,15 +1583,15 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4068.3</v>
+        <v>4142.9</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>37.29</v>
+        <v>111.89</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -1627,8 +1603,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="7" t="n">
-        <v>47.28</v>
+      <c r="J23" s="5" t="n">
+        <v>47.43</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1656,19 +1632,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4022.9</v>
+        <v>4098.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>15.49</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>91.09</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1676,12 +1652,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J24" s="7" t="n">
-        <v>48.31</v>
+      <c r="J24" s="5" t="n">
+        <v>48.29</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -1705,19 +1681,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4022.3</v>
+        <v>4098.8</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>82.26000000000001</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1725,12 +1701,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="7" t="n">
-        <v>48</v>
+      <c r="J25" s="5" t="n">
+        <v>48.18</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1730,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4078.7</v>
+        <v>4156.9</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1762,11 +1738,11 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-11.25</v>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>66.95</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1774,12 +1750,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="7" t="n">
-        <v>46.99</v>
+      <c r="J26" s="5" t="n">
+        <v>47.32</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -1803,19 +1779,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4030.5</v>
+        <v>4107.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>80.93000000000001</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1823,12 +1799,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="7" t="n">
-        <v>46.5</v>
+      <c r="J27" s="5" t="n">
+        <v>46.73</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -1852,19 +1828,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3990.3</v>
+        <v>4068.1</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>-3.39%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-8.76</v>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>69.04000000000001</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1872,12 +1848,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="7" t="n">
-        <v>45.73</v>
+      <c r="J28" s="5" t="n">
+        <v>46.06</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -1901,19 +1877,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4129.9</v>
+        <v>4210.9</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>19.76</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>100.76</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1921,12 +1897,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="7" t="n">
-        <v>43.77</v>
+      <c r="J29" s="5" t="n">
+        <v>43.81</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1926,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4181.9</v>
+        <v>4265.4</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -1958,11 +1934,11 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>74.14</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1970,12 +1946,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="7" t="n">
-        <v>42.46</v>
+      <c r="J30" s="5" t="n">
+        <v>42.64</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -1999,19 +1975,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4224.1</v>
+        <v>4308.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-3.07%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>99.48</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2019,12 +1995,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="7" t="n">
-        <v>42.84</v>
+      <c r="J31" s="5" t="n">
+        <v>43.1</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +34,14 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="007F6000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -60,6 +66,18 @@
         <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -79,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -94,6 +112,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -461,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -472,7 +496,7 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="39" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
@@ -2004,6 +2028,5615 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4257.71</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>-1.70%</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>+$1.76</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4444.8</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>+0.62%</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>187.09</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4331.14</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>+0.51%</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>+$7.23</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4417.3</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>86.16</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4309.03</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>+2.14%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>+$52.77</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4414.3</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>+2.65%</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>105.27</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4218.71</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>+0.19%</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>$-1.08</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4300.4</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>+3.03%</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>81.69</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4210.69</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>+3.42%</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>+$10.16</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4174</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>-0.49%</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>-36.69</v>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4071.28</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>-4.41%</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>$-5.95</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4194.5</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>-3.57%</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>123.22</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>4259.29</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>-1.63%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>+$3.24</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4349.6</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>-1.76%</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>90.31</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>4329.75</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>$-2.37</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4427.3</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>97.55</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4328.15</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>-3.29%</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>+$7.90</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4429</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>-3.09%</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>100.85</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4475.25</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>+0.92%</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>+$7.80</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>4570.4</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>+0.85%</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>95.15000000000001</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4434.3</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>-1.19%</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>+$3.39</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>4532</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>-1.17%</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>4487.78</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>$-3.86</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>4585.6</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>+0.29%</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>97.81999999999999</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4484.69</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>-1.22%</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>$-1.44</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>4572.2</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>-1.87%</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>87.51000000000001</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4540.28</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>+0.99%</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>+$1.89</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4659.5</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>+1.36%</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>119.22</v>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>4495.57</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>+0.88%</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>$-4.31</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>4597</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>+1.14%</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>101.43</v>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>4456.15</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>-1.14%</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>$-6.52</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>4545.1</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>-1.22%</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>88.95</v>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>4507.46</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>+$58.22</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>4601.2</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>-0.48%</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>93.73999999999999</v>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>4509.11</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>-0.75%</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>$-1.21</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>4623.4</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>-0.44%</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>114.29</v>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>4543.11</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>$-3.76</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>4643.6</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>+0.20%</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>100.49</v>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>4543.62</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>+1.38%</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>+$1.23</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>4634.4</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>+0.53%</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>90.78</v>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>4481.92</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>-1.84%</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>+$1.98</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>4610.1</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>-1.03%</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>128.18</v>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>4566.08</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>+0.58%</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>$-10.86</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4658.2</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>92.12</v>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4539.94</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>-2.41%</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>+$0.18</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>4662.2</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>-2.63%</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>122.26</v>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>4652.24</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>-0.78%</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>+$3.43</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4787.9</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>-0.47%</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>135.66</v>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>4688.75</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>$-3.60</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4810.3</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>+0.40%</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>121.55</v>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>4715.2</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>+$2.34</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>4790.9</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>-0.88%</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>4734.64</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>+0.40%</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>$-33.15</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4833.6</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>98.95999999999999</v>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>4715.83</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>$-8.63</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>4834.9</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>+0.40%</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>119.07</v>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>4687.08</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>-0.08%</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>+$7.02</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>4815.5</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>+0.36%</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>128.42</v>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>4690.82</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>+2.93%</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>+$3.16</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4798.2</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>+2.74%</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>4557.42</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>+0.74%</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4670.1</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>+0.76%</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>112.68</v>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>4523.72</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>-1.96%</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>+$18.71</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>4635.1</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>-2.37%</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>111.38</v>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>4614.08</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>-0.16%</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>+$4.06</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>4747.8</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>+0.34%</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>133.72</v>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>4621.53</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>+1.72%</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>+$1.89</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>4731.8</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>+1.50%</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>110.27</v>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>4543.37</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>-1.16%</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>$-3.14</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>4661.7</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>-1.02%</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>118.33</v>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>4596.87</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>-1.81%</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>+$3.24</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>4709.6</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>-1.82%</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>112.73</v>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>4681.73</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>-0.60%</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>$-12.44</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>4797</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>-0.99%</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>115.27</v>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>4710.12</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>+0.34%</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>+$12.00</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>4844.8</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>+0.34%</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>134.68</v>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>4694.36</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>-0.97%</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>+$4.60</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>4828.3</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>-0.62%</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>133.94</v>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>4740.15</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>+0.43%</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>$-0.84</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>4858.2</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>+0.71%</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>118.05</v>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>4720.07</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>-2.09%</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>+$0.62</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>4824.1</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>-2.26%</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>104.03</v>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>4820.58</v>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>$-56.03</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4935.4</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>-1.04%</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>114.82</v>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>4831.76</v>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>+0.86%</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>+$1.68</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>4987.3</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>+1.44%</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>155.54</v>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>30.87</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>4790.65</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>$-1.72</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>4916.6</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>-0.32%</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>125.95</v>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>4791.81</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>-1.03%</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>$-2.31</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>4932.6</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>140.79</v>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>4841.67</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>+2.09%</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>+$1.90</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>4960.6</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>+1.74%</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>118.93</v>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>39.82</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>4742.69</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>-0.14%</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>$-109.35</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>4876</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>-0.42%</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>133.31</v>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>4749.28</v>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>-0.31%</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>$-1.84</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>4896.4</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>-0.65%</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>147.12</v>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>50.95</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>4764.17</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>+0.94%</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>+$0.36</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>4928.3</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>+0.88%</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>164.13</v>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>4719.81</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>+0.38%</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>+$19.77</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>4885.4</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>+2.02%</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>165.59</v>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>68.06</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>4702.05</v>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>+1.13%</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>+$1.79</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>4788.9</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>86.84999999999999</v>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>67.61</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>4649.73</v>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>-0.62%</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>$-3.57</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>4788.9</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>+0.10%</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>139.17</v>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>64.22</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>4678.89</v>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>-1.68%</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>$-0.67</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>4784.1</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>-2.74%</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>105.21</v>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>65.06999999999999</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>4758.74</v>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>+1.92%</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>+$2.49</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>4919.1</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>+2.91%</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>160.36</v>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>61.51</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>4668.9</v>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>+3.50%</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>+$2.18</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>4780.2</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>+2.64%</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>61.02</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>4511.22</v>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>+0.39%</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>$-0.71</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>4657.4</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>+0.70%</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>146.18</v>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>61.83</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>4493.8</v>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>+2.65%</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>+$12.74</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>4624.8</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>+2.62%</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>131</v>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>66.98999999999999</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>4377.64</v>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>-2.84%</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>+$5.15</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>4506.7</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>-3.82%</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>129.06</v>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>68.39</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>4505.69</v>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>+0.32%</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>$-19.39</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>4685.7</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>+3.37%</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>180.01</v>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>65.34999999999999</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>4491.37</v>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>+$6.43</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>4532.8</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>-0.14%</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>41.43</v>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>55.61</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>4407.46</v>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>-1.85%</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>$-41.67</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>4539.3</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>-3.75%</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>131.84</v>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>52.06</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>4490.66</v>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>-3.43%</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>+$0.88</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>4716.2</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>-0.62%</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>225.54</v>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>4650.11</v>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>-3.50%</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>+$5.66</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>4745.4</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>-5.88%</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>95.29000000000001</v>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>4818.71</v>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>-3.74%</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>$-0.26</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>5041.7</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>-2.23%</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>222.99</v>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>34.38</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>5006.14</v>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>+$3.07</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>5156.7</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>+0.12%</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>150.56</v>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>5004.67</v>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>-0.29%</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>$-13.14</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>5150.3</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>-1.15%</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>145.63</v>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>34.78</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>5019</v>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>-1.19%</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>+$0.70</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>5210.4</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>-1.25%</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>191.4</v>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>34.04</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>5079.6</v>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>-1.87%</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>+$2.23</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>5276.4</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>-1.02%</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>196.8</v>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>35.66</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>5176.23</v>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>-0.30%</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>$-3.94</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>5330.9</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>-1.14%</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>154.67</v>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>5191.58</v>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>+1.03%</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>+$0.98</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>5392.5</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>+2.68%</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>200.92</v>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>33.19</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>5138.45</v>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>-0.64%</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>+$8.38</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>5251.9</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>-1.03%</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>113.45</v>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>5171.8</v>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>+1.76%</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>+$1.60</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>5306.8</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>+1.55%</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>135</v>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="n">
+        <v>27.41</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>5082.25</v>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>-1.13%</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>+$15.58</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>5225.6</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>-1.06%</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>143.35</v>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>5140.39</v>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>+1.03%</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>+$15.99</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>5281.6</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>+0.23%</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>141.21</v>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>5087.78</v>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>-4.39%</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>+$3.27</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>5269.7</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>-3.53%</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>181.92</v>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="n">
+        <v>26.89</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>5321.3</v>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>+0.80%</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>+$22.33</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>5462.6</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>+1.23%</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>141.3</v>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>5278.9</v>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>+1.83%</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>+$3.50</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>5396.2</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>+1.03%</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>5184.25</v>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>+0.39%</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>$-2.63</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>5341.1</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>-0.62%</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>156.85</v>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>5164.29</v>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>+0.42%</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>+$0.50</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>5374.2</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>+0.97%</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>209.91</v>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>5142.79</v>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>-1.62%</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>+$2.64</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>5322.8</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>-0.92%</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>180.01</v>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J111" s="5" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>5227.48</v>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>+2.36%</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>+$2.32</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>5372</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>+2.84%</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>144.52</v>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J112" s="4" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>5106.96</v>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>+2.22%</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>+$2.74</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>5223.4</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>+1.70%</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>116.44</v>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>35.59</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>4996.02</v>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>+0.38%</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>$-2.27</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>5136.1</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>-0.22%</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>140.08</v>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>44.31</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>4977.18</v>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>+2.03%</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>+$1.09</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>5147.3</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>+2.14%</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>170.12</v>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>46.23</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>4878.1</v>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>-3.25%</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>$-45.72</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>5039.4</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>-2.79%</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="n">
+        <v>46.39</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>5041.86</v>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>+2.44%</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>+$4.32</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>5183.8</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>+1.87%</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>141.94</v>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="n">
+        <v>57.41</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>4921.59</v>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>-3.19%</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>+$1.40</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>5088.4</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>-2.94%</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>166.81</v>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>5083.84</v>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>+1.18%</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>+$2.13</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>5242.5</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>+1.36%</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>158.66</v>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J119" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>5024.38</v>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>-0.71%</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>$-0.65</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>5172.2</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>-0.96%</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>147.82</v>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>64.01000000000001</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>5060.14</v>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>+1.88%</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>+$17.25</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>5222.1</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>+2.00%</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>161.96</v>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J121" s="5" t="n">
+        <v>63.42</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>4966.93</v>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>+3.92%</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>+$12.55</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>5119.8</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>+1.94%</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>152.87</v>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J122" s="5" t="n">
+        <v>63.27</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>4779.63</v>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>-3.71%</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>+$12.00</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>5022.3</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>-1.31%</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>242.67</v>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>4963.89</v>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>+0.39%</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>+$1.30</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>5089</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>+0.33%</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>125.11</v>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J124" s="5" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>4944.42</v>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>+6.13%</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>+$13.04</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>5072.5</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>+6.11%</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>128.08</v>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J125" s="5" t="n">
+        <v>49.09</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>4658.73</v>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>-4.75%</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>$-76.67</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>4780.4</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>-2.04%</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>121.67</v>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J126" s="5" t="n">
+        <v>48.95</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>4890.97</v>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>-8.99%</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>+$8.73</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>4880</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>-11.41%</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>-10.97</v>
+      </c>
+      <c r="H127" s="7" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J127" s="5" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>5373.91</v>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>-0.79%</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>+$5.87</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>5508.6</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>+0.25%</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>134.69</v>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J128" s="5" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>5416.79</v>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>+4.60%</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>+$0.28</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>5494.6</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>+4.32%</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>77.81</v>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J129" s="5" t="n">
+        <v>29.24</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>5178.46</v>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>+3.36%</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>+$3.14</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>5267.3</v>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>88.84</v>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J130" s="4" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>5010.31</v>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>+0.44%</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>+$20.73</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>5272.8</v>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>+2.18%</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>262.49</v>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J131" s="4" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>4988.56</v>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>+1.07%</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>+$5.34</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>5160.4</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>+1.44%</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>171.84</v>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J132" s="4" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>4935.8</v>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>+2.16%</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>+$0.94</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>5086.9</v>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>+1.59%</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>151.1</v>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J133" s="4" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>4831.51</v>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>+1.44%</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>+$0.31</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>5007.5</v>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>+1.51%</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>175.99</v>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>4762.99</v>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>+3.63%</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>+$75.81</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>4933</v>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>+3.65%</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>170.01</v>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>4596.18</v>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>-0.43%</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>+$1.80</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>4759.2</v>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>-0.60%</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>163.02</v>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>4615.95</v>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>-0.19%</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>+$6.28</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>4787.7</v>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>171.75</v>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>4624.8</v>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>+0.86%</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>+$3.59</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>4798.9</v>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>+0.81%</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>174.1</v>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>4585.44</v>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>-0.28%</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>+$5.33</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>4760.2</v>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>-0.37%</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>174.76</v>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>4598.46</v>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>+1.98%</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>+$9.47</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>4777.7</v>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>+2.49%</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>179.24</v>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>4509.27</v>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>+0.70%</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>+$1.86</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>4661.4</v>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>+0.90%</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>152.13</v>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>4477.84</v>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>+0.48%</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>$-0.03</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>4620</v>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>142.16</v>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>4456.26</v>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>+$0.08</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>4620.6</v>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>-0.76%</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>164.34</v>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>4494.61</v>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>+1.02%</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>$-0.07</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>4656.2</v>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>+1.04%</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>161.59</v>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>4449.11</v>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>+2.70%</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>+$28.96</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>4608.1</v>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>+2.76%</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>158.99</v>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>4332.17</v>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>4484.4</v>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>152.23</v>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>⚠️ MAJOR NEWS EVENT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -50,12 +50,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
         <bgColor rgb="00E2EFDA"/>
       </patternFill>
@@ -64,6 +58,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
@@ -105,13 +105,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -588,9 +588,9 @@
       <c r="G2" t="n">
         <v>54.24</v>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -598,12 +598,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="J2" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -637,9 +637,9 @@
       <c r="G3" t="n">
         <v>56.96</v>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -647,12 +647,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="J3" s="3" t="n">
         <v>18.21</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -686,9 +686,9 @@
       <c r="G4" t="n">
         <v>30.77</v>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -696,12 +696,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="J4" s="3" t="n">
         <v>18.03</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -735,9 +735,9 @@
       <c r="G5" t="n">
         <v>70.06</v>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J5" s="3" t="n">
         <v>16.18</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -784,9 +784,9 @@
       <c r="G6" t="n">
         <v>59.8</v>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J6" s="3" t="n">
         <v>18.87</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -833,9 +833,9 @@
       <c r="G7" t="n">
         <v>76.95999999999999</v>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="J7" s="3" t="n">
         <v>21.15</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -882,9 +882,9 @@
       <c r="G8" t="n">
         <v>59.37</v>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -892,12 +892,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="J8" s="3" t="n">
         <v>19.94</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -931,9 +931,9 @@
       <c r="G9" t="n">
         <v>80.19</v>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -941,12 +941,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="J9" s="3" t="n">
         <v>21.96</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -980,9 +980,9 @@
       <c r="G10" t="n">
         <v>56.33</v>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="J10" s="3" t="n">
         <v>21.74</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -1029,9 +1029,9 @@
       <c r="G11" t="n">
         <v>65.51000000000001</v>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="J11" s="3" t="n">
         <v>21.72</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -1078,9 +1078,9 @@
       <c r="G12" t="n">
         <v>58.76</v>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="J12" s="3" t="n">
         <v>22.33</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -1127,9 +1127,9 @@
       <c r="G13" t="n">
         <v>72.22</v>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1137,12 +1137,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="J13" s="3" t="n">
         <v>22.36</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -1176,9 +1176,9 @@
       <c r="G14" t="n">
         <v>48.75</v>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="J14" s="3" t="n">
         <v>21.54</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -1225,9 +1225,9 @@
       <c r="G15" t="n">
         <v>74.98</v>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="J15" s="3" t="n">
         <v>21.93</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -1274,9 +1274,9 @@
       <c r="G16" t="n">
         <v>62.82</v>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1284,12 +1284,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="J16" s="3" t="n">
         <v>22.96</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -1323,9 +1323,9 @@
       <c r="G17" t="n">
         <v>54.31</v>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="J17" s="3" t="n">
         <v>24.16</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -1372,9 +1372,9 @@
       <c r="G18" t="n">
         <v>78.02</v>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n">
+      <c r="J18" s="3" t="n">
         <v>28.73</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -1421,9 +1421,9 @@
       <c r="G19" t="n">
         <v>64.7</v>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="5" t="n">
+      <c r="J19" s="4" t="n">
         <v>34.99</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -1470,9 +1470,9 @@
       <c r="G20" t="n">
         <v>112.63</v>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J20" s="5" t="n">
+      <c r="J20" s="4" t="n">
         <v>32.93</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -1519,9 +1519,9 @@
       <c r="G21" t="n">
         <v>63.56</v>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1529,12 +1529,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J21" s="5" t="n">
+      <c r="J21" s="4" t="n">
         <v>31.11</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -1568,9 +1568,9 @@
       <c r="G22" t="n">
         <v>62.83</v>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J22" s="5" t="n">
+      <c r="J22" s="4" t="n">
         <v>39.51</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -1617,9 +1617,9 @@
       <c r="G23" t="n">
         <v>111.89</v>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1627,12 +1627,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="5" t="n">
+      <c r="J23" s="4" t="n">
         <v>47.43</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -1666,9 +1666,9 @@
       <c r="G24" t="n">
         <v>91.09</v>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J24" s="5" t="n">
+      <c r="J24" s="4" t="n">
         <v>48.29</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -1715,9 +1715,9 @@
       <c r="G25" t="n">
         <v>82.26000000000001</v>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="5" t="n">
+      <c r="J25" s="4" t="n">
         <v>48.18</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -1764,9 +1764,9 @@
       <c r="G26" t="n">
         <v>66.95</v>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="5" t="n">
+      <c r="J26" s="4" t="n">
         <v>47.32</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -1813,9 +1813,9 @@
       <c r="G27" t="n">
         <v>80.93000000000001</v>
       </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="5" t="n">
+      <c r="J27" s="4" t="n">
         <v>46.73</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -1862,9 +1862,9 @@
       <c r="G28" t="n">
         <v>69.04000000000001</v>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1872,12 +1872,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="5" t="n">
+      <c r="J28" s="4" t="n">
         <v>46.06</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -1911,9 +1911,9 @@
       <c r="G29" t="n">
         <v>100.76</v>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="5" t="n">
+      <c r="J29" s="4" t="n">
         <v>43.81</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -1960,9 +1960,9 @@
       <c r="G30" t="n">
         <v>74.14</v>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1970,12 +1970,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="5" t="n">
+      <c r="J30" s="4" t="n">
         <v>42.64</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -2009,9 +2009,9 @@
       <c r="G31" t="n">
         <v>99.48</v>
       </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="5" t="n">
+      <c r="J31" s="4" t="n">
         <v>43.1</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
       <c r="G32" t="n">
         <v>187.09</v>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>Contango (Extreme Oversupply / Glut)</t>
         </is>
@@ -2068,7 +2068,7 @@
           <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
-      <c r="J32" s="5" t="n">
+      <c r="J32" s="4" t="n">
         <v>38.11</v>
       </c>
       <c r="K32" t="inlineStr">
@@ -2107,9 +2107,9 @@
       <c r="G33" t="n">
         <v>86.16</v>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J33" s="5" t="n">
+      <c r="J33" s="4" t="n">
         <v>31.79</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -2156,9 +2156,9 @@
       <c r="G34" t="n">
         <v>105.27</v>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J34" s="5" t="n">
+      <c r="J34" s="4" t="n">
         <v>30.77</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -2205,9 +2205,9 @@
       <c r="G35" t="n">
         <v>81.69</v>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2215,12 +2215,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J35" s="5" t="n">
+      <c r="J35" s="4" t="n">
         <v>30.55</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J36" s="4" t="n">
+      <c r="J36" s="3" t="n">
         <v>23.08</v>
       </c>
       <c r="K36" t="inlineStr">
@@ -2303,9 +2303,9 @@
       <c r="G37" t="n">
         <v>123.22</v>
       </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2313,12 +2313,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J37" s="4" t="n">
+      <c r="J37" s="3" t="n">
         <v>12.35</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -2352,9 +2352,9 @@
       <c r="G38" t="n">
         <v>90.31</v>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J38" s="4" t="n">
+      <c r="J38" s="3" t="n">
         <v>12.67</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -2401,9 +2401,9 @@
       <c r="G39" t="n">
         <v>97.55</v>
       </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J39" s="4" t="n">
+      <c r="J39" s="3" t="n">
         <v>14.73</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -2450,9 +2450,9 @@
       <c r="G40" t="n">
         <v>100.85</v>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J40" s="4" t="n">
+      <c r="J40" s="3" t="n">
         <v>16.65</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -2499,9 +2499,9 @@
       <c r="G41" t="n">
         <v>95.15000000000001</v>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J41" s="4" t="n">
+      <c r="J41" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -2548,9 +2548,9 @@
       <c r="G42" t="n">
         <v>97.7</v>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2558,12 +2558,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J42" s="4" t="n">
+      <c r="J42" s="3" t="n">
         <v>18.03</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -2597,9 +2597,9 @@
       <c r="G43" t="n">
         <v>97.81999999999999</v>
       </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J43" s="4" t="n">
+      <c r="J43" s="3" t="n">
         <v>21.29</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -2646,9 +2646,9 @@
       <c r="G44" t="n">
         <v>87.51000000000001</v>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2656,12 +2656,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J44" s="4" t="n">
+      <c r="J44" s="3" t="n">
         <v>22.22</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -2695,9 +2695,9 @@
       <c r="G45" t="n">
         <v>119.22</v>
       </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J45" s="4" t="n">
+      <c r="J45" s="3" t="n">
         <v>21.39</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -2744,9 +2744,9 @@
       <c r="G46" t="n">
         <v>101.43</v>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J46" s="4" t="n">
+      <c r="J46" s="3" t="n">
         <v>20.79</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -2793,9 +2793,9 @@
       <c r="G47" t="n">
         <v>88.95</v>
       </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J47" s="4" t="n">
+      <c r="J47" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -2842,9 +2842,9 @@
       <c r="G48" t="n">
         <v>93.73999999999999</v>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J48" s="4" t="n">
+      <c r="J48" s="3" t="n">
         <v>21.43</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -2891,9 +2891,9 @@
       <c r="G49" t="n">
         <v>114.29</v>
       </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2901,12 +2901,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J49" s="4" t="n">
+      <c r="J49" s="3" t="n">
         <v>20.06</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -2940,9 +2940,9 @@
       <c r="G50" t="n">
         <v>100.49</v>
       </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J50" s="4" t="n">
+      <c r="J50" s="3" t="n">
         <v>20.67</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -2989,9 +2989,9 @@
       <c r="G51" t="n">
         <v>90.78</v>
       </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2999,12 +2999,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J51" s="4" t="n">
+      <c r="J51" s="3" t="n">
         <v>21.65</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -3038,9 +3038,9 @@
       <c r="G52" t="n">
         <v>128.18</v>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J52" s="4" t="n">
+      <c r="J52" s="3" t="n">
         <v>19.55</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -3087,9 +3087,9 @@
       <c r="G53" t="n">
         <v>92.12</v>
       </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J53" s="4" t="n">
+      <c r="J53" s="3" t="n">
         <v>17.38</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -3136,9 +3136,9 @@
       <c r="G54" t="n">
         <v>122.26</v>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J54" s="4" t="n">
+      <c r="J54" s="3" t="n">
         <v>15.41</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -3185,9 +3185,9 @@
       <c r="G55" t="n">
         <v>135.66</v>
       </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J55" s="4" t="n">
+      <c r="J55" s="3" t="n">
         <v>15.84</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -3234,9 +3234,9 @@
       <c r="G56" t="n">
         <v>121.55</v>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J56" s="4" t="n">
+      <c r="J56" s="3" t="n">
         <v>14.88</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -3283,9 +3283,9 @@
       <c r="G57" t="n">
         <v>75.7</v>
       </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J57" s="4" t="n">
+      <c r="J57" s="3" t="n">
         <v>12.74</v>
       </c>
       <c r="K57" t="inlineStr">
@@ -3332,9 +3332,9 @@
       <c r="G58" t="n">
         <v>98.95999999999999</v>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3342,12 +3342,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J58" s="4" t="n">
+      <c r="J58" s="3" t="n">
         <v>12.08</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -3381,9 +3381,9 @@
       <c r="G59" t="n">
         <v>119.07</v>
       </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J59" s="4" t="n">
+      <c r="J59" s="3" t="n">
         <v>11.42</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -3430,9 +3430,9 @@
       <c r="G60" t="n">
         <v>128.42</v>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3440,12 +3440,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J60" s="4" t="n">
+      <c r="J60" s="3" t="n">
         <v>13.66</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -3479,9 +3479,9 @@
       <c r="G61" t="n">
         <v>107.38</v>
       </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J61" s="4" t="n">
+      <c r="J61" s="3" t="n">
         <v>14.27</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -3528,9 +3528,9 @@
       <c r="G62" t="n">
         <v>112.68</v>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J62" s="4" t="n">
+      <c r="J62" s="3" t="n">
         <v>14.95</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -3577,9 +3577,9 @@
       <c r="G63" t="n">
         <v>111.38</v>
       </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J63" s="4" t="n">
+      <c r="J63" s="3" t="n">
         <v>16.42</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -3626,9 +3626,9 @@
       <c r="G64" t="n">
         <v>133.72</v>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3636,12 +3636,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J64" s="4" t="n">
+      <c r="J64" s="3" t="n">
         <v>15.85</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -3675,9 +3675,9 @@
       <c r="G65" t="n">
         <v>110.27</v>
       </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3685,12 +3685,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J65" s="4" t="n">
+      <c r="J65" s="3" t="n">
         <v>15.16</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -3724,9 +3724,9 @@
       <c r="G66" t="n">
         <v>118.33</v>
       </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J66" s="4" t="n">
+      <c r="J66" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -3773,9 +3773,9 @@
       <c r="G67" t="n">
         <v>112.73</v>
       </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3783,12 +3783,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J67" s="4" t="n">
+      <c r="J67" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -3822,9 +3822,9 @@
       <c r="G68" t="n">
         <v>115.27</v>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J68" s="4" t="n">
+      <c r="J68" s="3" t="n">
         <v>20.95</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -3871,9 +3871,9 @@
       <c r="G69" t="n">
         <v>134.68</v>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3881,12 +3881,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J69" s="4" t="n">
+      <c r="J69" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -3920,9 +3920,9 @@
       <c r="G70" t="n">
         <v>133.94</v>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3930,12 +3930,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J70" s="4" t="n">
+      <c r="J70" s="3" t="n">
         <v>25.67</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -3969,9 +3969,9 @@
       <c r="G71" t="n">
         <v>118.05</v>
       </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3979,12 +3979,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J71" s="4" t="n">
+      <c r="J71" s="3" t="n">
         <v>28.47</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4018,9 +4018,9 @@
       <c r="G72" t="n">
         <v>104.03</v>
       </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -4028,12 +4028,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J72" s="5" t="n">
+      <c r="J72" s="4" t="n">
         <v>30.98</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4067,9 +4067,9 @@
       <c r="G73" t="n">
         <v>114.82</v>
       </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -4077,12 +4077,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J73" s="5" t="n">
+      <c r="J73" s="4" t="n">
         <v>32.7</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4116,9 +4116,9 @@
       <c r="G74" t="n">
         <v>155.54</v>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J74" s="5" t="n">
+      <c r="J74" s="4" t="n">
         <v>30.87</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4165,9 +4165,9 @@
       <c r="G75" t="n">
         <v>125.95</v>
       </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J75" s="4" t="n">
+      <c r="J75" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4214,9 +4214,9 @@
       <c r="G76" t="n">
         <v>140.79</v>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -4224,12 +4224,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J76" s="5" t="n">
+      <c r="J76" s="4" t="n">
         <v>31.48</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4263,9 +4263,9 @@
       <c r="G77" t="n">
         <v>118.93</v>
       </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -4273,12 +4273,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J77" s="5" t="n">
+      <c r="J77" s="4" t="n">
         <v>39.82</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4312,9 +4312,9 @@
       <c r="G78" t="n">
         <v>133.31</v>
       </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J78" s="5" t="n">
+      <c r="J78" s="4" t="n">
         <v>45.25</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4361,9 +4361,9 @@
       <c r="G79" t="n">
         <v>147.12</v>
       </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -4371,12 +4371,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J79" s="5" t="n">
+      <c r="J79" s="4" t="n">
         <v>50.95</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4410,9 +4410,9 @@
       <c r="G80" t="n">
         <v>164.13</v>
       </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J80" s="5" t="n">
+      <c r="J80" s="4" t="n">
         <v>59.04</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4459,9 +4459,9 @@
       <c r="G81" t="n">
         <v>165.59</v>
       </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J81" s="5" t="n">
+      <c r="J81" s="4" t="n">
         <v>68.06</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4508,9 +4508,9 @@
       <c r="G82" t="n">
         <v>86.84999999999999</v>
       </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J82" s="5" t="n">
+      <c r="J82" s="4" t="n">
         <v>67.61</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4557,9 +4557,9 @@
       <c r="G83" t="n">
         <v>139.17</v>
       </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -4567,12 +4567,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J83" s="5" t="n">
+      <c r="J83" s="4" t="n">
         <v>64.22</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4606,9 +4606,9 @@
       <c r="G84" t="n">
         <v>105.21</v>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J84" s="5" t="n">
+      <c r="J84" s="4" t="n">
         <v>65.06999999999999</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4655,9 +4655,9 @@
       <c r="G85" t="n">
         <v>160.36</v>
       </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J85" s="5" t="n">
+      <c r="J85" s="4" t="n">
         <v>61.51</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4704,9 +4704,9 @@
       <c r="G86" t="n">
         <v>111.3</v>
       </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -4714,12 +4714,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J86" s="5" t="n">
+      <c r="J86" s="4" t="n">
         <v>61.02</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4753,9 +4753,9 @@
       <c r="G87" t="n">
         <v>146.18</v>
       </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J87" s="5" t="n">
+      <c r="J87" s="4" t="n">
         <v>61.83</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4802,9 +4802,9 @@
       <c r="G88" t="n">
         <v>131</v>
       </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J88" s="5" t="n">
+      <c r="J88" s="4" t="n">
         <v>66.98999999999999</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4851,9 +4851,9 @@
       <c r="G89" t="n">
         <v>129.06</v>
       </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J89" s="5" t="n">
+      <c r="J89" s="4" t="n">
         <v>68.39</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4900,9 +4900,9 @@
       <c r="G90" t="n">
         <v>180.01</v>
       </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J90" s="5" t="n">
+      <c r="J90" s="4" t="n">
         <v>65.34999999999999</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4949,9 +4949,9 @@
       <c r="G91" t="n">
         <v>41.43</v>
       </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -4959,7 +4959,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J91" s="5" t="n">
+      <c r="J91" s="4" t="n">
         <v>55.61</v>
       </c>
       <c r="K91" t="inlineStr">
@@ -4998,9 +4998,9 @@
       <c r="G92" t="n">
         <v>131.84</v>
       </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J92" s="5" t="n">
+      <c r="J92" s="4" t="n">
         <v>52.06</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5047,9 +5047,9 @@
       <c r="G93" t="n">
         <v>225.54</v>
       </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -5057,12 +5057,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J93" s="5" t="n">
+      <c r="J93" s="4" t="n">
         <v>48.26</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5096,9 +5096,9 @@
       <c r="G94" t="n">
         <v>95.29000000000001</v>
       </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J94" s="5" t="n">
+      <c r="J94" s="4" t="n">
         <v>40.68</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5145,22 +5145,22 @@
       <c r="G95" t="n">
         <v>222.99</v>
       </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I95" s="6" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J95" s="5" t="n">
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="n">
         <v>34.38</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5194,9 +5194,9 @@
       <c r="G96" t="n">
         <v>150.56</v>
       </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J96" s="5" t="n">
+      <c r="J96" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5243,9 +5243,9 @@
       <c r="G97" t="n">
         <v>145.63</v>
       </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J97" s="5" t="n">
+      <c r="J97" s="4" t="n">
         <v>34.78</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5292,9 +5292,9 @@
       <c r="G98" t="n">
         <v>191.4</v>
       </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J98" s="5" t="n">
+      <c r="J98" s="4" t="n">
         <v>34.04</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5341,9 +5341,9 @@
       <c r="G99" t="n">
         <v>196.8</v>
       </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J99" s="5" t="n">
+      <c r="J99" s="4" t="n">
         <v>35.66</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5390,9 +5390,9 @@
       <c r="G100" t="n">
         <v>154.67</v>
       </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -5400,12 +5400,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J100" s="5" t="n">
+      <c r="J100" s="4" t="n">
         <v>34.34</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5439,22 +5439,22 @@
       <c r="G101" t="n">
         <v>200.92</v>
       </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I101" s="6" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J101" s="5" t="n">
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="n">
         <v>33.19</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5488,9 +5488,9 @@
       <c r="G102" t="n">
         <v>113.45</v>
       </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J102" s="4" t="n">
+      <c r="J102" s="3" t="n">
         <v>27.57</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5537,9 +5537,9 @@
       <c r="G103" t="n">
         <v>135</v>
       </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -5547,12 +5547,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J103" s="4" t="n">
+      <c r="J103" s="3" t="n">
         <v>27.41</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5586,9 +5586,9 @@
       <c r="G104" t="n">
         <v>143.35</v>
       </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J104" s="4" t="n">
+      <c r="J104" s="3" t="n">
         <v>28.59</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5635,9 +5635,9 @@
       <c r="G105" t="n">
         <v>141.21</v>
       </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J105" s="5" t="n">
+      <c r="J105" s="4" t="n">
         <v>29.02</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5684,9 +5684,9 @@
       <c r="G106" t="n">
         <v>181.92</v>
       </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J106" s="4" t="n">
+      <c r="J106" s="3" t="n">
         <v>26.89</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5733,9 +5733,9 @@
       <c r="G107" t="n">
         <v>141.3</v>
       </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -5743,12 +5743,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J107" s="4" t="n">
+      <c r="J107" s="3" t="n">
         <v>25</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5782,9 +5782,9 @@
       <c r="G108" t="n">
         <v>117.3</v>
       </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J108" s="4" t="n">
+      <c r="J108" s="3" t="n">
         <v>23.93</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5831,9 +5831,9 @@
       <c r="G109" t="n">
         <v>156.85</v>
       </c>
-      <c r="H109" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J109" s="4" t="n">
+      <c r="J109" s="3" t="n">
         <v>27.52</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5880,9 +5880,9 @@
       <c r="G110" t="n">
         <v>209.91</v>
       </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -5890,12 +5890,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J110" s="5" t="n">
+      <c r="J110" s="4" t="n">
         <v>32.13</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5929,9 +5929,9 @@
       <c r="G111" t="n">
         <v>180.01</v>
       </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J111" s="5" t="n">
+      <c r="J111" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5978,9 +5978,9 @@
       <c r="G112" t="n">
         <v>144.52</v>
       </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J112" s="4" t="n">
+      <c r="J112" s="3" t="n">
         <v>28.13</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -6027,9 +6027,9 @@
       <c r="G113" t="n">
         <v>116.44</v>
       </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J113" s="5" t="n">
+      <c r="J113" s="4" t="n">
         <v>35.59</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -6076,9 +6076,9 @@
       <c r="G114" t="n">
         <v>140.08</v>
       </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -6086,12 +6086,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J114" s="5" t="n">
+      <c r="J114" s="4" t="n">
         <v>44.31</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -6125,9 +6125,9 @@
       <c r="G115" t="n">
         <v>170.12</v>
       </c>
-      <c r="H115" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J115" s="5" t="n">
+      <c r="J115" s="4" t="n">
         <v>46.23</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -6174,9 +6174,9 @@
       <c r="G116" t="n">
         <v>161.3</v>
       </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J116" s="5" t="n">
+      <c r="J116" s="4" t="n">
         <v>46.39</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -6223,9 +6223,9 @@
       <c r="G117" t="n">
         <v>141.94</v>
       </c>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J117" s="5" t="n">
+      <c r="J117" s="4" t="n">
         <v>57.41</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -6272,9 +6272,9 @@
       <c r="G118" t="n">
         <v>166.81</v>
       </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J118" s="5" t="n">
+      <c r="J118" s="4" t="n">
         <v>62.1</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -6321,9 +6321,9 @@
       <c r="G119" t="n">
         <v>158.66</v>
       </c>
-      <c r="H119" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J119" s="5" t="n">
+      <c r="J119" s="4" t="n">
         <v>63</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -6370,9 +6370,9 @@
       <c r="G120" t="n">
         <v>147.82</v>
       </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J120" s="5" t="n">
+      <c r="J120" s="4" t="n">
         <v>64.01000000000001</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -6419,9 +6419,9 @@
       <c r="G121" t="n">
         <v>161.96</v>
       </c>
-      <c r="H121" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J121" s="5" t="n">
+      <c r="J121" s="4" t="n">
         <v>63.42</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -6468,9 +6468,9 @@
       <c r="G122" t="n">
         <v>152.87</v>
       </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J122" s="5" t="n">
+      <c r="J122" s="4" t="n">
         <v>63.27</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -6517,9 +6517,9 @@
       <c r="G123" t="n">
         <v>242.67</v>
       </c>
-      <c r="H123" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J123" s="5" t="n">
+      <c r="J123" s="4" t="n">
         <v>57.48</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -6566,9 +6566,9 @@
       <c r="G124" t="n">
         <v>125.11</v>
       </c>
-      <c r="H124" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J124" s="5" t="n">
+      <c r="J124" s="4" t="n">
         <v>49.25</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -6615,9 +6615,9 @@
       <c r="G125" t="n">
         <v>128.08</v>
       </c>
-      <c r="H125" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
@@ -6625,12 +6625,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J125" s="5" t="n">
+      <c r="J125" s="4" t="n">
         <v>49.09</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -6664,9 +6664,9 @@
       <c r="G126" t="n">
         <v>121.67</v>
       </c>
-      <c r="H126" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J126" s="5" t="n">
+      <c r="J126" s="4" t="n">
         <v>48.95</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -6723,12 +6723,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J127" s="5" t="n">
+      <c r="J127" s="4" t="n">
         <v>41.41</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -6762,9 +6762,9 @@
       <c r="G128" t="n">
         <v>134.69</v>
       </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J128" s="5" t="n">
+      <c r="J128" s="4" t="n">
         <v>31.72</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -6811,9 +6811,9 @@
       <c r="G129" t="n">
         <v>77.81</v>
       </c>
-      <c r="H129" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -6821,12 +6821,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J129" s="5" t="n">
+      <c r="J129" s="4" t="n">
         <v>29.24</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -6860,9 +6860,9 @@
       <c r="G130" t="n">
         <v>88.84</v>
       </c>
-      <c r="H130" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J130" s="4" t="n">
+      <c r="J130" s="3" t="n">
         <v>28.65</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -6909,9 +6909,9 @@
       <c r="G131" t="n">
         <v>262.49</v>
       </c>
-      <c r="H131" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J131" s="4" t="n">
+      <c r="J131" s="3" t="n">
         <v>16.43</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -6958,9 +6958,9 @@
       <c r="G132" t="n">
         <v>171.84</v>
       </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J132" s="4" t="n">
+      <c r="J132" s="3" t="n">
         <v>10.44</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -7007,9 +7007,9 @@
       <c r="G133" t="n">
         <v>151.1</v>
       </c>
-      <c r="H133" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
@@ -7017,12 +7017,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J133" s="4" t="n">
+      <c r="J133" s="3" t="n">
         <v>8.960000000000001</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -7056,9 +7056,9 @@
       <c r="G134" t="n">
         <v>175.99</v>
       </c>
-      <c r="H134" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
@@ -7069,7 +7069,7 @@
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -7103,9 +7103,9 @@
       <c r="G135" t="n">
         <v>170.01</v>
       </c>
-      <c r="H135" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
@@ -7116,7 +7116,7 @@
       <c r="J135" s="2" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -7150,9 +7150,9 @@
       <c r="G136" t="n">
         <v>163.02</v>
       </c>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
@@ -7163,7 +7163,7 @@
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -7197,9 +7197,9 @@
       <c r="G137" t="n">
         <v>171.75</v>
       </c>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       <c r="J137" s="2" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -7244,9 +7244,9 @@
       <c r="G138" t="n">
         <v>174.1</v>
       </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
@@ -7257,7 +7257,7 @@
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -7291,9 +7291,9 @@
       <c r="G139" t="n">
         <v>174.76</v>
       </c>
-      <c r="H139" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
@@ -7304,7 +7304,7 @@
       <c r="J139" s="2" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -7338,9 +7338,9 @@
       <c r="G140" t="n">
         <v>179.24</v>
       </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -7351,7 +7351,7 @@
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -7385,9 +7385,9 @@
       <c r="G141" t="n">
         <v>152.13</v>
       </c>
-      <c r="H141" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       <c r="J141" s="2" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -7432,9 +7432,9 @@
       <c r="G142" t="n">
         <v>142.16</v>
       </c>
-      <c r="H142" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
@@ -7445,7 +7445,7 @@
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -7479,9 +7479,9 @@
       <c r="G143" t="n">
         <v>164.34</v>
       </c>
-      <c r="H143" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
@@ -7492,7 +7492,7 @@
       <c r="J143" s="2" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -7526,9 +7526,9 @@
       <c r="G144" t="n">
         <v>161.59</v>
       </c>
-      <c r="H144" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       <c r="J144" s="2" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -7573,9 +7573,9 @@
       <c r="G145" t="n">
         <v>158.99</v>
       </c>
-      <c r="H145" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
@@ -7586,7 +7586,7 @@
       <c r="J145" s="2" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -7620,9 +7620,9 @@
       <c r="G146" t="n">
         <v>152.23</v>
       </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       <c r="J146" s="2" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -578,15 +578,15 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4098.6</v>
+        <v>4110.9</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>54.24</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>17.8</v>
+        <v>18.29</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K146"/>
+  <dimension ref="A1:K147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -561,32 +561,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4044.36</v>
+        <v>4055.15</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$33.39</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4110.9</v>
+        <v>4156.4</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>66.54000000000001</v>
+        <v>101.25</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>18.29</v>
+        <v>19.9</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -610,32 +610,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4103.64</v>
+        <v>4044.36</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$0.17</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4160.6</v>
+        <v>4110.9</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>56.96</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>18.21</v>
+        <v>18.29</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -659,32 +659,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4066.23</v>
+        <v>4103.64</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$1.59</t>
+          <t>+$0.17</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4097</v>
+        <v>4160.6</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>30.77</v>
+        <v>56.96</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>18.03</v>
+        <v>18.21</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -708,32 +708,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4028.54</v>
+        <v>4066.23</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$2.81</t>
+          <t>+$1.59</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4098.6</v>
+        <v>4097</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>70.06</v>
+        <v>30.77</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>16.18</v>
+        <v>18.03</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -757,32 +757,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4076.6</v>
+        <v>4028.54</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$43.44</t>
+          <t>+$2.81</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4136.4</v>
+        <v>4098.6</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>59.8</v>
+        <v>70.06</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>18.87</v>
+        <v>16.18</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -806,32 +806,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4052.74</v>
+        <v>4076.6</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$0.61</t>
+          <t>+$43.44</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4129.7</v>
+        <v>4136.4</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>76.95999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>21.15</v>
+        <v>18.87</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -855,32 +855,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4049.43</v>
+        <v>4052.74</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$-10.76</t>
+          <t>+$0.61</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4108.8</v>
+        <v>4129.7</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>59.37</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>19.94</v>
+        <v>21.15</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -904,32 +904,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4130.11</v>
+        <v>4049.43</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$1.94</t>
+          <t>$-10.76</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4210.3</v>
+        <v>4108.8</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+1.84%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>80.19</v>
+        <v>59.37</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>21.96</v>
+        <v>19.94</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -953,32 +953,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4077.87</v>
+        <v>4130.11</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$1.94</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4134.2</v>
+        <v>4210.3</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+1.84%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>56.33</v>
+        <v>80.19</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>21.74</v>
+        <v>21.96</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1002,32 +1002,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4007.49</v>
+        <v>4077.87</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-12.24</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4073</v>
+        <v>4134.2</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>65.51000000000001</v>
+        <v>56.33</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>21.72</v>
+        <v>21.74</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1051,32 +1051,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4017.04</v>
+        <v>4007.49</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$1.19</t>
+          <t>$-12.24</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4075.8</v>
+        <v>4073</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>58.76</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>22.33</v>
+        <v>21.72</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1100,32 +1100,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3976.48</v>
+        <v>4017.04</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$4.31</t>
+          <t>+$1.19</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4048.7</v>
+        <v>4075.8</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>72.22</v>
+        <v>58.76</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>22.36</v>
+        <v>22.33</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1149,32 +1149,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4060.55</v>
+        <v>3976.48</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$0.46</t>
+          <t>+$4.31</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4109.3</v>
+        <v>4048.7</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>48.75</v>
+        <v>72.22</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>21.54</v>
+        <v>22.36</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1198,32 +1198,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4052.92</v>
+        <v>4060.55</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$5.21</t>
+          <t>+$0.46</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4127.9</v>
+        <v>4109.3</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+1.58%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>74.98</v>
+        <v>48.75</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>21.93</v>
+        <v>21.54</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1247,32 +1247,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4000.78</v>
+        <v>4052.92</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$5.21</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4063.6</v>
+        <v>4127.9</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>+1.58%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>62.82</v>
+        <v>74.98</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>22.96</v>
+        <v>21.93</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1296,32 +1296,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4119.29</v>
+        <v>4000.78</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4173.6</v>
+        <v>4063.6</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>54.31</v>
+        <v>62.82</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>24.16</v>
+        <v>22.96</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1345,32 +1345,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4123.38</v>
+        <v>4119.29</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4201.4</v>
+        <v>4173.6</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+1.43%</t>
+          <t>-0.66%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>78.02</v>
+        <v>54.31</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>28.73</v>
+        <v>24.16</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1394,32 +1394,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4077.4</v>
+        <v>4123.38</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4142.1</v>
+        <v>4201.4</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>+1.43%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>64.7</v>
+        <v>78.02</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1431,8 +1431,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n">
-        <v>34.99</v>
+      <c r="J19" s="3" t="n">
+        <v>28.73</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1443,32 +1443,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4105.67</v>
+        <v>4077.4</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4218.3</v>
+        <v>4142.1</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>112.63</v>
+        <v>64.7</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>32.93</v>
+        <v>34.99</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1492,32 +1492,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4165.04</v>
+        <v>4105.67</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4228.6</v>
+        <v>4218.3</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>63.56</v>
+        <v>112.63</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>31.11</v>
+        <v>32.93</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1541,32 +1541,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4123.77</v>
+        <v>4165.04</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4186.6</v>
+        <v>4228.6</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>62.83</v>
+        <v>63.56</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>39.51</v>
+        <v>31.11</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1590,32 +1590,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4031.01</v>
+        <v>4123.77</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4142.9</v>
+        <v>4186.6</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>111.89</v>
+        <v>62.83</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>47.43</v>
+        <v>39.51</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1639,32 +1639,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4007.41</v>
+        <v>4031.01</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4098.5</v>
+        <v>4142.9</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>91.09</v>
+        <v>111.89</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>48.29</v>
+        <v>47.43</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1688,32 +1688,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4016.54</v>
+        <v>4007.41</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4098.8</v>
+        <v>4098.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>82.26000000000001</v>
+        <v>91.09</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>48.18</v>
+        <v>48.29</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1737,32 +1737,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4089.95</v>
+        <v>4016.54</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4156.9</v>
+        <v>4098.8</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>66.95</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>47.32</v>
+        <v>48.18</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1786,32 +1786,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4026.57</v>
+        <v>4089.95</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4107.5</v>
+        <v>4156.9</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>80.93000000000001</v>
+        <v>66.95</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>46.73</v>
+        <v>47.32</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1835,32 +1835,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3999.06</v>
+        <v>4026.57</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4068.1</v>
+        <v>4107.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-3.39%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>69.04000000000001</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="J28" s="4" t="n">
-        <v>46.06</v>
+        <v>46.73</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1884,32 +1884,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4110.14</v>
+        <v>3999.06</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4210.9</v>
+        <v>4068.1</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-3.39%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>100.76</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="J29" s="4" t="n">
-        <v>43.81</v>
+        <v>46.06</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1933,32 +1933,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4191.26</v>
+        <v>4110.14</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4265.4</v>
+        <v>4210.9</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>74.14</v>
+        <v>100.76</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="J30" s="4" t="n">
-        <v>42.64</v>
+        <v>43.81</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1982,32 +1982,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4209.02</v>
+        <v>4191.26</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4308.5</v>
+        <v>4265.4</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>99.48</v>
+        <v>74.14</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="J31" s="4" t="n">
-        <v>43.1</v>
+        <v>42.64</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2031,130 +2031,130 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4257.71</v>
+        <v>4209.02</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4444.8</v>
+        <v>4308.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>-3.07%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>187.09</v>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
+        <v>99.48</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
         </is>
       </c>
       <c r="J32" s="4" t="n">
-        <v>38.11</v>
+        <v>43.1</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4331.14</v>
+        <v>4257.71</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+$7.23</t>
+          <t>+$1.76</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4417.3</v>
+        <v>4444.8</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>86.16</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>187.09</v>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>31.79</v>
+        <v>38.11</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4309.03</v>
+        <v>4331.14</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$52.77</t>
+          <t>+$7.23</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4414.3</v>
+        <v>4417.3</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>105.27</v>
+        <v>86.16</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="J34" s="4" t="n">
-        <v>30.77</v>
+        <v>31.79</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2178,32 +2178,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4218.71</v>
+        <v>4309.03</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>$-1.08</t>
+          <t>+$52.77</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4300.4</v>
+        <v>4414.3</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>81.69</v>
+        <v>105.27</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>30.55</v>
+        <v>30.77</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2227,36 +2227,36 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4210.69</v>
+        <v>4218.71</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$10.16</t>
+          <t>$-1.08</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4174</v>
+        <v>4300.4</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+3.03%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>-36.69</v>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>81.69</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2264,48 +2264,48 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J36" s="3" t="n">
-        <v>23.08</v>
+      <c r="J36" s="4" t="n">
+        <v>30.55</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4071.28</v>
+        <v>4210.69</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>$-5.95</t>
+          <t>+$10.16</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4194.5</v>
+        <v>4174</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3.57%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>123.22</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-36.69</v>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2314,43 +2314,43 @@
         </is>
       </c>
       <c r="J37" s="3" t="n">
-        <v>12.35</v>
+        <v>23.08</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4259.29</v>
+        <v>4071.28</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-4.41%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-5.95</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4349.6</v>
+        <v>4194.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>-3.57%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>90.31</v>
+        <v>123.22</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="J38" s="3" t="n">
-        <v>12.67</v>
+        <v>12.35</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2374,32 +2374,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4329.75</v>
+        <v>4259.29</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>$-2.37</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4427.3</v>
+        <v>4349.6</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>97.55</v>
+        <v>90.31</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="J39" s="3" t="n">
-        <v>14.73</v>
+        <v>12.67</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2423,32 +2423,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4328.15</v>
+        <v>4329.75</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>-3.29%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$7.90</t>
+          <t>$-2.37</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4429</v>
+        <v>4427.3</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>100.85</v>
+        <v>97.55</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="J40" s="3" t="n">
-        <v>16.65</v>
+        <v>14.73</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2472,32 +2472,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4475.25</v>
+        <v>4328.15</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-3.29%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$7.80</t>
+          <t>+$7.90</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4570.4</v>
+        <v>4429</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>95.15000000000001</v>
+        <v>100.85</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="J41" s="3" t="n">
-        <v>17.2</v>
+        <v>16.65</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2521,32 +2521,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4434.3</v>
+        <v>4475.25</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$3.39</t>
+          <t>+$7.80</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4532</v>
+        <v>4570.4</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>97.7</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="J42" s="3" t="n">
-        <v>18.03</v>
+        <v>17.2</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2570,32 +2570,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4487.78</v>
+        <v>4434.3</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>$-3.86</t>
+          <t>+$3.39</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4585.6</v>
+        <v>4532</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>97.81999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="J43" s="3" t="n">
-        <v>21.29</v>
+        <v>18.03</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2619,32 +2619,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4484.69</v>
+        <v>4487.78</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>$-1.44</t>
+          <t>$-3.86</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4572.2</v>
+        <v>4585.6</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>87.51000000000001</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="J44" s="3" t="n">
-        <v>22.22</v>
+        <v>21.29</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2668,32 +2668,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4540.28</v>
+        <v>4484.69</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$1.89</t>
+          <t>$-1.44</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4659.5</v>
+        <v>4572.2</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>119.22</v>
+        <v>87.51000000000001</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="J45" s="3" t="n">
-        <v>21.39</v>
+        <v>22.22</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2717,32 +2717,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4495.57</v>
+        <v>4540.28</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>$-4.31</t>
+          <t>+$1.89</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4597</v>
+        <v>4659.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>101.43</v>
+        <v>119.22</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="J46" s="3" t="n">
-        <v>20.79</v>
+        <v>21.39</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2766,32 +2766,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4456.15</v>
+        <v>4495.57</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>$-6.52</t>
+          <t>$-4.31</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4545.1</v>
+        <v>4597</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>88.95</v>
+        <v>101.43</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="J47" s="3" t="n">
-        <v>21.4</v>
+        <v>20.79</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2815,32 +2815,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4507.46</v>
+        <v>4456.15</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+$58.22</t>
+          <t>$-6.52</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4601.2</v>
+        <v>4545.1</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>93.73999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="J48" s="3" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2864,32 +2864,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4509.11</v>
+        <v>4507.46</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>$-1.21</t>
+          <t>+$58.22</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4623.4</v>
+        <v>4601.2</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>114.29</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="J49" s="3" t="n">
-        <v>20.06</v>
+        <v>21.43</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2913,32 +2913,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4543.11</v>
+        <v>4509.11</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.75%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>$-3.76</t>
+          <t>$-1.21</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4643.6</v>
+        <v>4623.4</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>100.49</v>
+        <v>114.29</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="J50" s="3" t="n">
-        <v>20.67</v>
+        <v>20.06</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2962,32 +2962,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4543.62</v>
+        <v>4543.11</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>$-3.76</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4634.4</v>
+        <v>4643.6</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>90.78</v>
+        <v>100.49</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="J51" s="3" t="n">
-        <v>21.65</v>
+        <v>20.67</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -3011,32 +3011,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4481.92</v>
+        <v>4543.62</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+$1.98</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4610.1</v>
+        <v>4634.4</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>128.18</v>
+        <v>90.78</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="J52" s="3" t="n">
-        <v>19.55</v>
+        <v>21.65</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3060,32 +3060,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4566.08</v>
+        <v>4481.92</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>$-10.86</t>
+          <t>+$1.98</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4658.2</v>
+        <v>4610.1</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>92.12</v>
+        <v>128.18</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="J53" s="3" t="n">
-        <v>17.38</v>
+        <v>19.55</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3109,32 +3109,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4539.94</v>
+        <v>4566.08</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+$0.18</t>
+          <t>$-10.86</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4662.2</v>
+        <v>4658.2</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>122.26</v>
+        <v>92.12</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="J54" s="3" t="n">
-        <v>15.41</v>
+        <v>17.38</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3158,32 +3158,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4652.24</v>
+        <v>4539.94</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$0.18</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4787.9</v>
+        <v>4662.2</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-2.63%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>135.66</v>
+        <v>122.26</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="J55" s="3" t="n">
-        <v>15.84</v>
+        <v>15.41</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3207,32 +3207,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4688.75</v>
+        <v>4652.24</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>$-3.60</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4810.3</v>
+        <v>4787.9</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>121.55</v>
+        <v>135.66</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="J56" s="3" t="n">
-        <v>14.88</v>
+        <v>15.84</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3256,32 +3256,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4715.2</v>
+        <v>4688.75</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>+$2.34</t>
+          <t>$-3.60</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4790.9</v>
+        <v>4810.3</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>75.7</v>
+        <v>121.55</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3294,43 +3294,43 @@
         </is>
       </c>
       <c r="J57" s="3" t="n">
-        <v>12.74</v>
+        <v>14.88</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4734.64</v>
+        <v>4715.2</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>$-33.15</t>
+          <t>+$2.34</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4833.6</v>
+        <v>4790.9</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>98.95999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3343,43 +3343,43 @@
         </is>
       </c>
       <c r="J58" s="3" t="n">
-        <v>12.08</v>
+        <v>12.74</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4715.83</v>
+        <v>4734.64</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>$-8.63</t>
+          <t>$-33.15</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4834.9</v>
+        <v>4833.6</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>119.07</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="J59" s="3" t="n">
-        <v>11.42</v>
+        <v>12.08</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -3403,32 +3403,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4687.08</v>
+        <v>4715.83</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>+$7.02</t>
+          <t>$-8.63</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4815.5</v>
+        <v>4834.9</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>128.42</v>
+        <v>119.07</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="J60" s="3" t="n">
-        <v>13.66</v>
+        <v>11.42</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -3452,32 +3452,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4690.82</v>
+        <v>4687.08</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>+2.93%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>+$3.16</t>
+          <t>+$7.02</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4798.2</v>
+        <v>4815.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>+2.74%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>107.38</v>
+        <v>128.42</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="J61" s="3" t="n">
-        <v>14.27</v>
+        <v>13.66</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -3501,32 +3501,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4557.42</v>
+        <v>4690.82</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>+0.74%</t>
+          <t>+2.93%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>+$3.16</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4670.1</v>
+        <v>4798.2</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>+2.74%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>112.68</v>
+        <v>107.38</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="J62" s="3" t="n">
-        <v>14.95</v>
+        <v>14.27</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -3550,32 +3550,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4523.72</v>
+        <v>4557.42</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>+0.74%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>+$18.71</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4635.1</v>
+        <v>4670.1</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>+0.76%</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>111.38</v>
+        <v>112.68</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="J63" s="3" t="n">
-        <v>16.42</v>
+        <v>14.95</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -3599,32 +3599,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4614.08</v>
+        <v>4523.72</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>+$4.06</t>
+          <t>+$18.71</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4747.8</v>
+        <v>4635.1</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-2.37%</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>133.72</v>
+        <v>111.38</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="J64" s="3" t="n">
-        <v>15.85</v>
+        <v>16.42</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -3648,32 +3648,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4621.53</v>
+        <v>4614.08</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>+$1.89</t>
+          <t>+$4.06</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4731.8</v>
+        <v>4747.8</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>110.27</v>
+        <v>133.72</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="J65" s="3" t="n">
-        <v>15.16</v>
+        <v>15.85</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -3697,32 +3697,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4543.37</v>
+        <v>4621.53</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>$-3.14</t>
+          <t>+$1.89</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4661.7</v>
+        <v>4731.8</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>118.33</v>
+        <v>110.27</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="J66" s="3" t="n">
-        <v>15.8</v>
+        <v>15.16</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -3746,32 +3746,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4596.87</v>
+        <v>4543.37</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-3.14</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4709.6</v>
+        <v>4661.7</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>112.73</v>
+        <v>118.33</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="J67" s="3" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -3795,32 +3795,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4681.73</v>
+        <v>4596.87</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>$-12.44</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4797</v>
+        <v>4709.6</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>-0.99%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>115.27</v>
+        <v>112.73</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="J68" s="3" t="n">
-        <v>20.95</v>
+        <v>15.5</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -3844,32 +3844,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4710.12</v>
+        <v>4681.73</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>+$12.00</t>
+          <t>$-12.44</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4844.8</v>
+        <v>4797</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>134.68</v>
+        <v>115.27</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="J69" s="3" t="n">
-        <v>23.3</v>
+        <v>20.95</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -3893,32 +3893,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>4694.36</v>
+        <v>4710.12</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>+$4.60</t>
+          <t>+$12.00</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4828.3</v>
+        <v>4844.8</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>133.94</v>
+        <v>134.68</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="J70" s="3" t="n">
-        <v>25.67</v>
+        <v>23.3</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -3942,32 +3942,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4740.15</v>
+        <v>4694.36</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>$-0.84</t>
+          <t>+$4.60</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4858.2</v>
+        <v>4828.3</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>118.05</v>
+        <v>133.94</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="J71" s="3" t="n">
-        <v>28.47</v>
+        <v>25.67</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -3991,32 +3991,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4720.07</v>
+        <v>4740.15</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>-2.09%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>+$0.62</t>
+          <t>$-0.84</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4824.1</v>
+        <v>4858.2</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>-2.26%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>104.03</v>
+        <v>118.05</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -4028,8 +4028,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J72" s="4" t="n">
-        <v>30.98</v>
+      <c r="J72" s="3" t="n">
+        <v>28.47</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -4040,32 +4040,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4820.58</v>
+        <v>4720.07</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>$-56.03</t>
+          <t>+$0.62</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4935.4</v>
+        <v>4824.1</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>-1.04%</t>
+          <t>-2.26%</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>114.82</v>
+        <v>104.03</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="J73" s="4" t="n">
-        <v>32.7</v>
+        <v>30.98</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -4089,32 +4089,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>4831.76</v>
+        <v>4820.58</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>+$1.68</t>
+          <t>$-56.03</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4987.3</v>
+        <v>4935.4</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>-1.04%</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>155.54</v>
+        <v>114.82</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="J74" s="4" t="n">
-        <v>30.87</v>
+        <v>32.7</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -4138,32 +4138,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4790.65</v>
+        <v>4831.76</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>$-1.72</t>
+          <t>+$1.68</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4916.6</v>
+        <v>4987.3</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>125.95</v>
+        <v>155.54</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -4175,8 +4175,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J75" s="3" t="n">
-        <v>28.9</v>
+      <c r="J75" s="4" t="n">
+        <v>30.87</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -4187,32 +4187,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4791.81</v>
+        <v>4790.65</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>$-1.72</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4932.6</v>
+        <v>4916.6</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>140.79</v>
+        <v>125.95</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="J76" s="4" t="n">
-        <v>31.48</v>
+        <v>28.9</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -4236,32 +4236,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>4841.67</v>
+        <v>4791.81</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>+2.09%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>+$1.90</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4960.6</v>
+        <v>4932.6</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>+1.74%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>118.93</v>
+        <v>140.79</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>39.82</v>
+        <v>31.48</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -4285,32 +4285,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>4742.69</v>
+        <v>4841.67</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+2.09%</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>$-109.35</t>
+          <t>+$1.90</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4876</v>
+        <v>4960.6</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+1.74%</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>133.31</v>
+        <v>118.93</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="J78" s="4" t="n">
-        <v>45.25</v>
+        <v>39.82</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -4334,32 +4334,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>4749.28</v>
+        <v>4742.69</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>$-1.84</t>
+          <t>$-109.35</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4896.4</v>
+        <v>4876</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>147.12</v>
+        <v>133.31</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="J79" s="4" t="n">
-        <v>50.95</v>
+        <v>45.25</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -4383,32 +4383,32 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>4764.17</v>
+        <v>4749.28</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>+$0.36</t>
+          <t>$-1.84</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4928.3</v>
+        <v>4896.4</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>164.13</v>
+        <v>147.12</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="J80" s="4" t="n">
-        <v>59.04</v>
+        <v>50.95</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -4432,32 +4432,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4719.81</v>
+        <v>4764.17</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>+$19.77</t>
+          <t>+$0.36</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4885.4</v>
+        <v>4928.3</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>+2.02%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>165.59</v>
+        <v>164.13</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="J81" s="4" t="n">
-        <v>68.06</v>
+        <v>59.04</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -4481,32 +4481,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>4702.05</v>
+        <v>4719.81</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>+$1.79</t>
+          <t>+$19.77</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4788.9</v>
+        <v>4885.4</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+2.02%</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>86.84999999999999</v>
+        <v>165.59</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         </is>
       </c>
       <c r="J82" s="4" t="n">
-        <v>67.61</v>
+        <v>68.06</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -4530,20 +4530,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4649.73</v>
+        <v>4702.05</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>$-3.57</t>
+          <t>+$1.79</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -4551,11 +4551,11 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>139.17</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="J83" s="4" t="n">
-        <v>64.22</v>
+        <v>67.61</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -4579,32 +4579,32 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>4678.89</v>
+        <v>4649.73</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>$-0.67</t>
+          <t>$-3.57</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4784.1</v>
+        <v>4788.9</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>-2.74%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>105.21</v>
+        <v>139.17</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="J84" s="4" t="n">
-        <v>65.06999999999999</v>
+        <v>64.22</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -4628,32 +4628,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4758.74</v>
+        <v>4678.89</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>+$2.49</t>
+          <t>$-0.67</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4919.1</v>
+        <v>4784.1</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>+2.91%</t>
+          <t>-2.74%</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>160.36</v>
+        <v>105.21</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         </is>
       </c>
       <c r="J85" s="4" t="n">
-        <v>61.51</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -4677,32 +4677,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4668.9</v>
+        <v>4758.74</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>+3.50%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>+$2.18</t>
+          <t>+$2.49</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4780.2</v>
+        <v>4919.1</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>+2.64%</t>
+          <t>+2.91%</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>111.3</v>
+        <v>160.36</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="J86" s="4" t="n">
-        <v>61.02</v>
+        <v>61.51</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -4726,32 +4726,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>4511.22</v>
+        <v>4668.9</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+3.50%</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>$-0.71</t>
+          <t>+$2.18</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4657.4</v>
+        <v>4780.2</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+2.64%</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>146.18</v>
+        <v>111.3</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="J87" s="4" t="n">
-        <v>61.83</v>
+        <v>61.02</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -4775,32 +4775,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>4493.8</v>
+        <v>4511.22</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>+$12.74</t>
+          <t>$-0.71</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4624.8</v>
+        <v>4657.4</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>+2.62%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>131</v>
+        <v>146.18</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="J88" s="4" t="n">
-        <v>66.98999999999999</v>
+        <v>61.83</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -4824,32 +4824,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>4377.64</v>
+        <v>4493.8</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>+$5.15</t>
+          <t>+$12.74</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4506.7</v>
+        <v>4624.8</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>-3.82%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>129.06</v>
+        <v>131</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         </is>
       </c>
       <c r="J89" s="4" t="n">
-        <v>68.39</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -4873,32 +4873,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>4505.69</v>
+        <v>4377.64</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>$-19.39</t>
+          <t>+$5.15</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4685.7</v>
+        <v>4506.7</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>+3.37%</t>
+          <t>-3.82%</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>180.01</v>
+        <v>129.06</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="J90" s="4" t="n">
-        <v>65.34999999999999</v>
+        <v>68.39</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -4922,32 +4922,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>4491.37</v>
+        <v>4505.69</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>+$6.43</t>
+          <t>$-19.39</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4532.8</v>
+        <v>4685.7</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+3.37%</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>41.43</v>
+        <v>180.01</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4960,43 +4960,43 @@
         </is>
       </c>
       <c r="J91" s="4" t="n">
-        <v>55.61</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>4407.46</v>
+        <v>4491.37</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>$-41.67</t>
+          <t>+$6.43</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4539.3</v>
+        <v>4532.8</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>131.84</v>
+        <v>41.43</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -5009,43 +5009,43 @@
         </is>
       </c>
       <c r="J92" s="4" t="n">
-        <v>52.06</v>
+        <v>55.61</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>4490.66</v>
+        <v>4407.46</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>-3.43%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>+$0.88</t>
+          <t>$-41.67</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4716.2</v>
+        <v>4539.3</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>-3.75%</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>225.54</v>
+        <v>131.84</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="J93" s="4" t="n">
-        <v>48.26</v>
+        <v>52.06</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -5069,32 +5069,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>4650.11</v>
+        <v>4490.66</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>-3.50%</t>
+          <t>-3.43%</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>+$5.66</t>
+          <t>+$0.88</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4745.4</v>
+        <v>4716.2</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>-5.88%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>95.29000000000001</v>
+        <v>225.54</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="J94" s="4" t="n">
-        <v>40.68</v>
+        <v>48.26</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -5118,32 +5118,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>4818.71</v>
+        <v>4650.11</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>-3.74%</t>
+          <t>-3.50%</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>$-0.26</t>
+          <t>+$5.66</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5041.7</v>
+        <v>4745.4</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>-2.23%</t>
+          <t>-5.88%</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>222.99</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         </is>
       </c>
       <c r="J95" s="4" t="n">
-        <v>34.38</v>
+        <v>40.68</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -5167,32 +5167,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>5006.14</v>
+        <v>4818.71</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-3.74%</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>+$3.07</t>
+          <t>$-0.26</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5156.7</v>
+        <v>5041.7</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-2.23%</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>150.56</v>
+        <v>222.99</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="J96" s="4" t="n">
-        <v>33</v>
+        <v>34.38</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -5216,32 +5216,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>5004.67</v>
+        <v>5006.14</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>$-13.14</t>
+          <t>+$3.07</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5150.3</v>
+        <v>5156.7</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>145.63</v>
+        <v>150.56</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="J97" s="4" t="n">
-        <v>34.78</v>
+        <v>33</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -5265,32 +5265,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>5019</v>
+        <v>5004.67</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>+$0.70</t>
+          <t>$-13.14</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5210.4</v>
+        <v>5150.3</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>-1.25%</t>
+          <t>-1.15%</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>191.4</v>
+        <v>145.63</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="J98" s="4" t="n">
-        <v>34.04</v>
+        <v>34.78</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -5314,32 +5314,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>5079.6</v>
+        <v>5019</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>+$2.23</t>
+          <t>+$0.70</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5276.4</v>
+        <v>5210.4</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>-1.25%</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>196.8</v>
+        <v>191.4</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         </is>
       </c>
       <c r="J99" s="4" t="n">
-        <v>35.66</v>
+        <v>34.04</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -5363,32 +5363,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>5176.23</v>
+        <v>5079.6</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>$-3.94</t>
+          <t>+$2.23</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5330.9</v>
+        <v>5276.4</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>154.67</v>
+        <v>196.8</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="J100" s="4" t="n">
-        <v>34.34</v>
+        <v>35.66</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -5412,32 +5412,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>5191.58</v>
+        <v>5176.23</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>+$0.98</t>
+          <t>$-3.94</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5392.5</v>
+        <v>5330.9</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>200.92</v>
+        <v>154.67</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="J101" s="4" t="n">
-        <v>33.19</v>
+        <v>34.34</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -5461,32 +5461,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>5138.45</v>
+        <v>5191.58</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>+$8.38</t>
+          <t>+$0.98</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5251.9</v>
+        <v>5392.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>113.45</v>
+        <v>200.92</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -5498,8 +5498,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J102" s="3" t="n">
-        <v>27.57</v>
+      <c r="J102" s="4" t="n">
+        <v>33.19</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -5510,32 +5510,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>5171.8</v>
+        <v>5138.45</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>+$1.60</t>
+          <t>+$8.38</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5306.8</v>
+        <v>5251.9</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>135</v>
+        <v>113.45</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         </is>
       </c>
       <c r="J103" s="3" t="n">
-        <v>27.41</v>
+        <v>27.57</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -5559,32 +5559,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>5082.25</v>
+        <v>5171.8</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>+$15.58</t>
+          <t>+$1.60</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5225.6</v>
+        <v>5306.8</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>143.35</v>
+        <v>135</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="J104" s="3" t="n">
-        <v>28.59</v>
+        <v>27.41</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -5608,32 +5608,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>5140.39</v>
+        <v>5082.25</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>+$15.99</t>
+          <t>+$15.58</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5281.6</v>
+        <v>5225.6</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-1.06%</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>141.21</v>
+        <v>143.35</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -5645,8 +5645,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J105" s="4" t="n">
-        <v>29.02</v>
+      <c r="J105" s="3" t="n">
+        <v>28.59</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -5657,32 +5657,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>5087.78</v>
+        <v>5140.39</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>-4.39%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>+$3.27</t>
+          <t>+$15.99</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5269.7</v>
+        <v>5281.6</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>-3.53%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>181.92</v>
+        <v>141.21</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -5694,8 +5694,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J106" s="3" t="n">
-        <v>26.89</v>
+      <c r="J106" s="4" t="n">
+        <v>29.02</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -5706,32 +5706,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>5321.3</v>
+        <v>5087.78</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>+0.80%</t>
+          <t>-4.39%</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>+$22.33</t>
+          <t>+$3.27</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5462.6</v>
+        <v>5269.7</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-3.53%</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>141.3</v>
+        <v>181.92</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="J107" s="3" t="n">
-        <v>25</v>
+        <v>26.89</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -5755,32 +5755,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>5278.9</v>
+        <v>5321.3</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>+1.83%</t>
+          <t>+0.80%</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>+$3.50</t>
+          <t>+$22.33</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5396.2</v>
+        <v>5462.6</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>117.3</v>
+        <v>141.3</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="J108" s="3" t="n">
-        <v>23.93</v>
+        <v>25</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -5804,32 +5804,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>5184.25</v>
+        <v>5278.9</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+1.83%</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>$-2.63</t>
+          <t>+$3.50</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5341.1</v>
+        <v>5396.2</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>156.85</v>
+        <v>117.3</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         </is>
       </c>
       <c r="J109" s="3" t="n">
-        <v>27.52</v>
+        <v>23.93</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -5853,32 +5853,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>5164.29</v>
+        <v>5184.25</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>+$0.50</t>
+          <t>$-2.63</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5374.2</v>
+        <v>5341.1</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>209.91</v>
+        <v>156.85</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5890,8 +5890,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J110" s="4" t="n">
-        <v>32.13</v>
+      <c r="J110" s="3" t="n">
+        <v>27.52</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -5902,32 +5902,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>5142.79</v>
+        <v>5164.29</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>-1.62%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>+$2.64</t>
+          <t>+$0.50</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5322.8</v>
+        <v>5374.2</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>180.01</v>
+        <v>209.91</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         </is>
       </c>
       <c r="J111" s="4" t="n">
-        <v>30.2</v>
+        <v>32.13</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -5951,32 +5951,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>5227.48</v>
+        <v>5142.79</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>+2.36%</t>
+          <t>-1.62%</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>+$2.32</t>
+          <t>+$2.64</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5372</v>
+        <v>5322.8</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>144.52</v>
+        <v>180.01</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5988,8 +5988,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J112" s="3" t="n">
-        <v>28.13</v>
+      <c r="J112" s="4" t="n">
+        <v>30.2</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -6000,32 +6000,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>5106.96</v>
+        <v>5227.48</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>+2.22%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>+$2.74</t>
+          <t>+$2.32</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5223.4</v>
+        <v>5372</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>+1.70%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>116.44</v>
+        <v>144.52</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -6037,8 +6037,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J113" s="4" t="n">
-        <v>35.59</v>
+      <c r="J113" s="3" t="n">
+        <v>28.13</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -6049,32 +6049,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>4996.02</v>
+        <v>5106.96</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+2.22%</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>$-2.27</t>
+          <t>+$2.74</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5136.1</v>
+        <v>5223.4</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+1.70%</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>140.08</v>
+        <v>116.44</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="J114" s="4" t="n">
-        <v>44.31</v>
+        <v>35.59</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -6098,32 +6098,32 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>4977.18</v>
+        <v>4996.02</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>+2.03%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>+$1.09</t>
+          <t>$-2.27</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5147.3</v>
+        <v>5136.1</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>170.12</v>
+        <v>140.08</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="J115" s="4" t="n">
-        <v>46.23</v>
+        <v>44.31</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -6147,32 +6147,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>4878.1</v>
+        <v>4977.18</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>-3.25%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>$-45.72</t>
+          <t>+$1.09</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5039.4</v>
+        <v>5147.3</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>-2.79%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>161.3</v>
+        <v>170.12</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="J116" s="4" t="n">
-        <v>46.39</v>
+        <v>46.23</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -6196,32 +6196,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>5041.86</v>
+        <v>4878.1</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>+2.44%</t>
+          <t>-3.25%</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>+$4.32</t>
+          <t>$-45.72</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5183.8</v>
+        <v>5039.4</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>+1.87%</t>
+          <t>-2.79%</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>141.94</v>
+        <v>161.3</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         </is>
       </c>
       <c r="J117" s="4" t="n">
-        <v>57.41</v>
+        <v>46.39</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -6245,32 +6245,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>4921.59</v>
+        <v>5041.86</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>-3.19%</t>
+          <t>+2.44%</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>+$1.40</t>
+          <t>+$4.32</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5088.4</v>
+        <v>5183.8</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>-2.94%</t>
+          <t>+1.87%</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>166.81</v>
+        <v>141.94</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="J118" s="4" t="n">
-        <v>62.1</v>
+        <v>57.41</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -6294,32 +6294,32 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>5083.84</v>
+        <v>4921.59</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>+1.18%</t>
+          <t>-3.19%</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>+$2.13</t>
+          <t>+$1.40</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5242.5</v>
+        <v>5088.4</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-2.94%</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>158.66</v>
+        <v>166.81</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         </is>
       </c>
       <c r="J119" s="4" t="n">
-        <v>63</v>
+        <v>62.1</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -6343,32 +6343,32 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>5024.38</v>
+        <v>5083.84</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>+1.18%</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>$-0.65</t>
+          <t>+$2.13</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5172.2</v>
+        <v>5242.5</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>147.82</v>
+        <v>158.66</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="J120" s="4" t="n">
-        <v>64.01000000000001</v>
+        <v>63</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -6392,32 +6392,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>5060.14</v>
+        <v>5024.38</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>+1.88%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>+$17.25</t>
+          <t>$-0.65</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5222.1</v>
+        <v>5172.2</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>+2.00%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>161.96</v>
+        <v>147.82</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="J121" s="4" t="n">
-        <v>63.42</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -6441,32 +6441,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>4966.93</v>
+        <v>5060.14</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>+3.92%</t>
+          <t>+1.88%</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>+$12.55</t>
+          <t>+$17.25</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5119.8</v>
+        <v>5222.1</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>+1.94%</t>
+          <t>+2.00%</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>152.87</v>
+        <v>161.96</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="J122" s="4" t="n">
-        <v>63.27</v>
+        <v>63.42</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -6490,32 +6490,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>4779.63</v>
+        <v>4966.93</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>-3.71%</t>
+          <t>+3.92%</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>+$12.00</t>
+          <t>+$12.55</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5022.3</v>
+        <v>5119.8</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>+1.94%</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>242.67</v>
+        <v>152.87</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="J123" s="4" t="n">
-        <v>57.48</v>
+        <v>63.27</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -6539,32 +6539,32 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>4963.89</v>
+        <v>4779.63</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-3.71%</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>+$1.30</t>
+          <t>+$12.00</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5089</v>
+        <v>5022.3</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>125.11</v>
+        <v>242.67</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="J124" s="4" t="n">
-        <v>49.25</v>
+        <v>57.48</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -6588,32 +6588,32 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>4944.42</v>
+        <v>4963.89</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>+6.13%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>+$13.04</t>
+          <t>+$1.30</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5072.5</v>
+        <v>5089</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>+6.11%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>128.08</v>
+        <v>125.11</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         </is>
       </c>
       <c r="J125" s="4" t="n">
-        <v>49.09</v>
+        <v>49.25</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -6637,32 +6637,32 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>4658.73</v>
+        <v>4944.42</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>-4.75%</t>
+          <t>+6.13%</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>$-76.67</t>
+          <t>+$13.04</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4780.4</v>
+        <v>5072.5</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>+6.11%</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>121.67</v>
+        <v>128.08</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         </is>
       </c>
       <c r="J126" s="4" t="n">
-        <v>48.95</v>
+        <v>49.09</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -6686,36 +6686,36 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>4890.97</v>
+        <v>4658.73</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>-8.99%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>+$8.73</t>
+          <t>$-76.67</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4880</v>
+        <v>4780.4</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>-11.41%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>-10.97</v>
-      </c>
-      <c r="H127" s="7" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>121.67</v>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
@@ -6724,47 +6724,47 @@
         </is>
       </c>
       <c r="J127" s="4" t="n">
-        <v>41.41</v>
+        <v>48.95</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>5373.91</v>
+        <v>4890.97</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-8.99%</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>+$5.87</t>
+          <t>+$8.73</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5508.6</v>
+        <v>4880</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-11.41%</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>134.69</v>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-10.97</v>
+      </c>
+      <c r="H128" s="7" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
@@ -6773,43 +6773,43 @@
         </is>
       </c>
       <c r="J128" s="4" t="n">
-        <v>31.72</v>
+        <v>41.41</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>5416.79</v>
+        <v>5373.91</v>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>+4.60%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>+$5.87</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5494.6</v>
+        <v>5508.6</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>+4.32%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>77.81</v>
+        <v>134.69</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="J129" s="4" t="n">
-        <v>29.24</v>
+        <v>31.72</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -6833,32 +6833,32 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>5178.46</v>
+        <v>5416.79</v>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>+3.36%</t>
+          <t>+4.60%</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>+$3.14</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5267.3</v>
+        <v>5494.6</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+4.32%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>88.84</v>
+        <v>77.81</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -6870,8 +6870,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J130" s="3" t="n">
-        <v>28.65</v>
+      <c r="J130" s="4" t="n">
+        <v>29.24</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -6882,32 +6882,32 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>5010.31</v>
+        <v>5178.46</v>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+3.36%</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>+$20.73</t>
+          <t>+$3.14</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5272.8</v>
+        <v>5267.3</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>262.49</v>
+        <v>88.84</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         </is>
       </c>
       <c r="J131" s="3" t="n">
-        <v>16.43</v>
+        <v>28.65</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -6931,32 +6931,32 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>4988.56</v>
+        <v>5010.31</v>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>+1.07%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>+$5.34</t>
+          <t>+$20.73</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5160.4</v>
+        <v>5272.8</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+2.18%</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>171.84</v>
+        <v>262.49</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         </is>
       </c>
       <c r="J132" s="3" t="n">
-        <v>10.44</v>
+        <v>16.43</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -6980,32 +6980,32 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>4935.8</v>
+        <v>4988.56</v>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>+$0.94</t>
+          <t>+$5.34</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5086.9</v>
+        <v>5160.4</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>+1.59%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>151.1</v>
+        <v>171.84</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="J133" s="3" t="n">
-        <v>8.960000000000001</v>
+        <v>10.44</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -7029,32 +7029,32 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>4831.51</v>
+        <v>4935.8</v>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+2.16%</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>+$0.31</t>
+          <t>+$0.94</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5007.5</v>
+        <v>5086.9</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>+1.51%</t>
+          <t>+1.59%</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>175.99</v>
+        <v>151.1</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -7066,7 +7066,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J134" s="2" t="inlineStr"/>
+      <c r="J134" s="3" t="n">
+        <v>8.960000000000001</v>
+      </c>
       <c r="K134" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -7076,32 +7078,32 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>4762.99</v>
+        <v>4831.51</v>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>+3.63%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>+$75.81</t>
+          <t>+$0.31</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4933</v>
+        <v>5007.5</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>+3.65%</t>
+          <t>+1.51%</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>170.01</v>
+        <v>175.99</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -7123,32 +7125,32 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>4596.18</v>
+        <v>4762.99</v>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+3.63%</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>+$1.80</t>
+          <t>+$75.81</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4759.2</v>
+        <v>4933</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>+3.65%</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>163.02</v>
+        <v>170.01</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -7170,32 +7172,32 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>4615.95</v>
+        <v>4596.18</v>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>+$6.28</t>
+          <t>+$1.80</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4787.7</v>
+        <v>4759.2</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>171.75</v>
+        <v>163.02</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -7217,32 +7219,32 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>4624.8</v>
+        <v>4615.95</v>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>+$3.59</t>
+          <t>+$6.28</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4798.9</v>
+        <v>4787.7</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>174.1</v>
+        <v>171.75</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -7264,32 +7266,32 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>4585.44</v>
+        <v>4624.8</v>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>+$5.33</t>
+          <t>+$3.59</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4760.2</v>
+        <v>4798.9</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>174.76</v>
+        <v>174.1</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -7311,32 +7313,32 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>4598.46</v>
+        <v>4585.44</v>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>+1.98%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>+$9.47</t>
+          <t>+$5.33</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4777.7</v>
+        <v>4760.2</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>+2.49%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>179.24</v>
+        <v>174.76</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -7358,32 +7360,32 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>4509.27</v>
+        <v>4598.46</v>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>+$1.86</t>
+          <t>+$9.47</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4661.4</v>
+        <v>4777.7</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>+0.90%</t>
+          <t>+2.49%</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>152.13</v>
+        <v>179.24</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -7405,32 +7407,32 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>4477.84</v>
+        <v>4509.27</v>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>$-0.03</t>
+          <t>+$1.86</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4620</v>
+        <v>4661.4</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.90%</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>142.16</v>
+        <v>152.13</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -7452,32 +7454,32 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>4456.26</v>
+        <v>4477.84</v>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>+$0.08</t>
+          <t>$-0.03</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4620.6</v>
+        <v>4620</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>-0.76%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>164.34</v>
+        <v>142.16</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -7499,32 +7501,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>4494.61</v>
+        <v>4456.26</v>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.85%</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>$-0.07</t>
+          <t>+$0.08</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4656.2</v>
+        <v>4620.6</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>-0.76%</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>161.59</v>
+        <v>164.34</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -7546,32 +7548,32 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>4449.11</v>
+        <v>4494.61</v>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>+2.70%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>+$28.96</t>
+          <t>$-0.07</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4608.1</v>
+        <v>4656.2</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>+2.76%</t>
+          <t>+1.04%</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>158.99</v>
+        <v>161.59</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -7593,32 +7595,32 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>4332.17</v>
+        <v>4449.11</v>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.70%</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+$28.96</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4484.4</v>
+        <v>4608.1</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.76%</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>152.23</v>
+        <v>158.99</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -7632,6 +7634,53 @@
       </c>
       <c r="J146" s="2" t="inlineStr"/>
       <c r="K146" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>4332.17</v>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>4484.4</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>152.23</v>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -50,6 +50,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
         <bgColor rgb="00E2EFDA"/>
       </patternFill>
@@ -58,18 +70,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -105,16 +105,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K147"/>
+  <dimension ref="A1:K148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -561,81 +561,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4055.15</v>
+        <v>4097.29</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+1.04%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$33.39</t>
+          <t>+$22.75</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4156.4</v>
+        <v>4339</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>+4.39%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>101.25</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>19.9</v>
+        <v>241.71</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>28.06</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4044.36</v>
+        <v>4055.15</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$33.39</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4110.9</v>
+        <v>4156.4</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>66.54000000000001</v>
+        <v>101.25</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -647,8 +647,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n">
-        <v>18.29</v>
+      <c r="J3" s="5" t="n">
+        <v>19.9</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -659,32 +659,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4103.64</v>
+        <v>4044.36</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$0.17</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4160.6</v>
+        <v>4110.9</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>56.96</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -696,8 +696,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
-        <v>18.21</v>
+      <c r="J4" s="5" t="n">
+        <v>18.29</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -708,32 +708,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4066.23</v>
+        <v>4103.64</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$1.59</t>
+          <t>+$0.17</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4097</v>
+        <v>4160.6</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>30.77</v>
+        <v>56.96</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -745,8 +745,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
-        <v>18.03</v>
+      <c r="J5" s="5" t="n">
+        <v>18.21</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -757,32 +757,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4028.54</v>
+        <v>4066.23</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$2.81</t>
+          <t>+$1.59</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4098.6</v>
+        <v>4097</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>70.06</v>
+        <v>30.77</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -794,8 +794,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>16.18</v>
+      <c r="J6" s="5" t="n">
+        <v>18.03</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -806,32 +806,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4076.6</v>
+        <v>4028.54</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$43.44</t>
+          <t>+$2.81</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4136.4</v>
+        <v>4098.6</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>59.8</v>
+        <v>70.06</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -843,8 +843,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n">
-        <v>18.87</v>
+      <c r="J7" s="5" t="n">
+        <v>16.18</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -855,32 +855,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4052.74</v>
+        <v>4076.6</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$0.61</t>
+          <t>+$43.44</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4129.7</v>
+        <v>4136.4</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>76.95999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -892,8 +892,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n">
-        <v>21.15</v>
+      <c r="J8" s="5" t="n">
+        <v>18.87</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -904,32 +904,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4049.43</v>
+        <v>4052.74</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$-10.76</t>
+          <t>+$0.61</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4108.8</v>
+        <v>4129.7</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>59.37</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -941,8 +941,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="3" t="n">
-        <v>19.94</v>
+      <c r="J9" s="5" t="n">
+        <v>21.15</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -953,32 +953,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4130.11</v>
+        <v>4049.43</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$1.94</t>
+          <t>$-10.76</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4210.3</v>
+        <v>4108.8</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+1.84%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>80.19</v>
+        <v>59.37</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -990,8 +990,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="3" t="n">
-        <v>21.96</v>
+      <c r="J10" s="5" t="n">
+        <v>19.94</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1002,32 +1002,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4077.87</v>
+        <v>4130.11</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$1.94</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4134.2</v>
+        <v>4210.3</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+1.84%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>56.33</v>
+        <v>80.19</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1039,8 +1039,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J11" s="3" t="n">
-        <v>21.74</v>
+      <c r="J11" s="5" t="n">
+        <v>21.96</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1051,32 +1051,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4007.49</v>
+        <v>4077.87</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-12.24</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4073</v>
+        <v>4134.2</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>65.51000000000001</v>
+        <v>56.33</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1088,8 +1088,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J12" s="3" t="n">
-        <v>21.72</v>
+      <c r="J12" s="5" t="n">
+        <v>21.74</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1100,32 +1100,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4017.04</v>
+        <v>4007.49</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$1.19</t>
+          <t>$-12.24</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4075.8</v>
+        <v>4073</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>58.76</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1137,8 +1137,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J13" s="3" t="n">
-        <v>22.33</v>
+      <c r="J13" s="5" t="n">
+        <v>21.72</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1149,32 +1149,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3976.48</v>
+        <v>4017.04</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$4.31</t>
+          <t>+$1.19</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4048.7</v>
+        <v>4075.8</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>72.22</v>
+        <v>58.76</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1186,8 +1186,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J14" s="3" t="n">
-        <v>22.36</v>
+      <c r="J14" s="5" t="n">
+        <v>22.33</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1198,32 +1198,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4060.55</v>
+        <v>3976.48</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$0.46</t>
+          <t>+$4.31</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4109.3</v>
+        <v>4048.7</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>48.75</v>
+        <v>72.22</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1235,8 +1235,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J15" s="3" t="n">
-        <v>21.54</v>
+      <c r="J15" s="5" t="n">
+        <v>22.36</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1247,32 +1247,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4052.92</v>
+        <v>4060.55</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$5.21</t>
+          <t>+$0.46</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4127.9</v>
+        <v>4109.3</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+1.58%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>74.98</v>
+        <v>48.75</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1284,8 +1284,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J16" s="3" t="n">
-        <v>21.93</v>
+      <c r="J16" s="5" t="n">
+        <v>21.54</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1296,32 +1296,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4000.78</v>
+        <v>4052.92</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$5.21</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4063.6</v>
+        <v>4127.9</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>+1.58%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>62.82</v>
+        <v>74.98</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1333,8 +1333,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J17" s="3" t="n">
-        <v>22.96</v>
+      <c r="J17" s="5" t="n">
+        <v>21.93</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1345,32 +1345,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4119.29</v>
+        <v>4000.78</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4173.6</v>
+        <v>4063.6</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>54.31</v>
+        <v>62.82</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1382,8 +1382,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J18" s="3" t="n">
-        <v>24.16</v>
+      <c r="J18" s="5" t="n">
+        <v>22.96</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1394,32 +1394,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4123.38</v>
+        <v>4119.29</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4201.4</v>
+        <v>4173.6</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+1.43%</t>
+          <t>-0.66%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>78.02</v>
+        <v>54.31</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1431,8 +1431,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="3" t="n">
-        <v>28.73</v>
+      <c r="J19" s="5" t="n">
+        <v>24.16</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1443,32 +1443,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4077.4</v>
+        <v>4123.38</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4142.1</v>
+        <v>4201.4</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>+1.43%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>64.7</v>
+        <v>78.02</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1480,8 +1480,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J20" s="4" t="n">
-        <v>34.99</v>
+      <c r="J20" s="5" t="n">
+        <v>28.73</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1492,32 +1492,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4105.67</v>
+        <v>4077.4</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4218.3</v>
+        <v>4142.1</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>112.63</v>
+        <v>64.7</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1529,8 +1529,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n">
-        <v>32.93</v>
+      <c r="J21" s="6" t="n">
+        <v>34.99</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1541,32 +1541,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4165.04</v>
+        <v>4105.67</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4228.6</v>
+        <v>4218.3</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>63.56</v>
+        <v>112.63</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1578,8 +1578,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J22" s="4" t="n">
-        <v>31.11</v>
+      <c r="J22" s="6" t="n">
+        <v>32.93</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1590,32 +1590,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4123.77</v>
+        <v>4165.04</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4186.6</v>
+        <v>4228.6</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>62.83</v>
+        <v>63.56</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1627,8 +1627,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n">
-        <v>39.51</v>
+      <c r="J23" s="6" t="n">
+        <v>31.11</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1639,32 +1639,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4031.01</v>
+        <v>4123.77</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4142.9</v>
+        <v>4186.6</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>111.89</v>
+        <v>62.83</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1676,8 +1676,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J24" s="4" t="n">
-        <v>47.43</v>
+      <c r="J24" s="6" t="n">
+        <v>39.51</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1688,32 +1688,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4007.41</v>
+        <v>4031.01</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4098.5</v>
+        <v>4142.9</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>91.09</v>
+        <v>111.89</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1725,8 +1725,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n">
-        <v>48.29</v>
+      <c r="J25" s="6" t="n">
+        <v>47.43</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1737,32 +1737,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4016.54</v>
+        <v>4007.41</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4098.8</v>
+        <v>4098.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>82.26000000000001</v>
+        <v>91.09</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1774,8 +1774,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n">
-        <v>48.18</v>
+      <c r="J26" s="6" t="n">
+        <v>48.29</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1786,32 +1786,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4089.95</v>
+        <v>4016.54</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4156.9</v>
+        <v>4098.8</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>66.95</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1823,8 +1823,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n">
-        <v>47.32</v>
+      <c r="J27" s="6" t="n">
+        <v>48.18</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1835,32 +1835,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4026.57</v>
+        <v>4089.95</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4107.5</v>
+        <v>4156.9</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>80.93000000000001</v>
+        <v>66.95</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1872,8 +1872,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="4" t="n">
-        <v>46.73</v>
+      <c r="J28" s="6" t="n">
+        <v>47.32</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1884,32 +1884,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3999.06</v>
+        <v>4026.57</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4068.1</v>
+        <v>4107.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3.39%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>69.04000000000001</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1921,8 +1921,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n">
-        <v>46.06</v>
+      <c r="J29" s="6" t="n">
+        <v>46.73</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1933,32 +1933,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4110.14</v>
+        <v>3999.06</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4210.9</v>
+        <v>4068.1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-3.39%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>100.76</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1970,8 +1970,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n">
-        <v>43.81</v>
+      <c r="J30" s="6" t="n">
+        <v>46.06</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1982,32 +1982,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4191.26</v>
+        <v>4110.14</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4265.4</v>
+        <v>4210.9</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>74.14</v>
+        <v>100.76</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2019,8 +2019,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n">
-        <v>42.64</v>
+      <c r="J31" s="6" t="n">
+        <v>43.81</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2031,32 +2031,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4209.02</v>
+        <v>4191.26</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4308.5</v>
+        <v>4265.4</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>99.48</v>
+        <v>74.14</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2068,8 +2068,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J32" s="4" t="n">
-        <v>43.1</v>
+      <c r="J32" s="6" t="n">
+        <v>42.64</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2080,130 +2080,130 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4257.71</v>
+        <v>4209.02</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4444.8</v>
+        <v>4308.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>-3.07%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>187.09</v>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>38.11</v>
+        <v>99.48</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>43.1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4331.14</v>
+        <v>4257.71</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$7.23</t>
+          <t>+$1.76</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4417.3</v>
+        <v>4444.8</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>86.16</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>31.79</v>
+        <v>187.09</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>38.11</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4309.03</v>
+        <v>4331.14</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$52.77</t>
+          <t>+$7.23</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4414.3</v>
+        <v>4417.3</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>105.27</v>
+        <v>86.16</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2215,8 +2215,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J35" s="4" t="n">
-        <v>30.77</v>
+      <c r="J35" s="6" t="n">
+        <v>31.79</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2227,32 +2227,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4218.71</v>
+        <v>4309.03</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>$-1.08</t>
+          <t>+$52.77</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4300.4</v>
+        <v>4414.3</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>81.69</v>
+        <v>105.27</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2264,8 +2264,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J36" s="4" t="n">
-        <v>30.55</v>
+      <c r="J36" s="6" t="n">
+        <v>30.77</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2276,36 +2276,36 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4210.69</v>
+        <v>4218.71</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$10.16</t>
+          <t>$-1.08</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4174</v>
+        <v>4300.4</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+3.03%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>-36.69</v>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>81.69</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2313,48 +2313,48 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J37" s="3" t="n">
-        <v>23.08</v>
+      <c r="J37" s="6" t="n">
+        <v>30.55</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4071.28</v>
+        <v>4210.69</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>$-5.95</t>
+          <t>+$10.16</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4194.5</v>
+        <v>4174</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-3.57%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>123.22</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-36.69</v>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2362,44 +2362,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J38" s="3" t="n">
-        <v>12.35</v>
+      <c r="J38" s="5" t="n">
+        <v>23.08</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4259.29</v>
+        <v>4071.28</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-4.41%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-5.95</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4349.6</v>
+        <v>4194.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>-3.57%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>90.31</v>
+        <v>123.22</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2411,8 +2411,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J39" s="3" t="n">
-        <v>12.67</v>
+      <c r="J39" s="5" t="n">
+        <v>12.35</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2423,32 +2423,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4329.75</v>
+        <v>4259.29</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$-2.37</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4427.3</v>
+        <v>4349.6</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>97.55</v>
+        <v>90.31</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2460,8 +2460,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J40" s="3" t="n">
-        <v>14.73</v>
+      <c r="J40" s="5" t="n">
+        <v>12.67</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2472,32 +2472,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4328.15</v>
+        <v>4329.75</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-3.29%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$7.90</t>
+          <t>$-2.37</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4429</v>
+        <v>4427.3</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>100.85</v>
+        <v>97.55</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2509,8 +2509,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J41" s="3" t="n">
-        <v>16.65</v>
+      <c r="J41" s="5" t="n">
+        <v>14.73</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2521,32 +2521,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4475.25</v>
+        <v>4328.15</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-3.29%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$7.80</t>
+          <t>+$7.90</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4570.4</v>
+        <v>4429</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>95.15000000000001</v>
+        <v>100.85</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2558,8 +2558,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J42" s="3" t="n">
-        <v>17.2</v>
+      <c r="J42" s="5" t="n">
+        <v>16.65</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2570,32 +2570,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4434.3</v>
+        <v>4475.25</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$3.39</t>
+          <t>+$7.80</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4532</v>
+        <v>4570.4</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>97.7</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2607,8 +2607,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J43" s="3" t="n">
-        <v>18.03</v>
+      <c r="J43" s="5" t="n">
+        <v>17.2</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2619,32 +2619,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4487.78</v>
+        <v>4434.3</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>$-3.86</t>
+          <t>+$3.39</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4585.6</v>
+        <v>4532</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>97.81999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2656,8 +2656,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J44" s="3" t="n">
-        <v>21.29</v>
+      <c r="J44" s="5" t="n">
+        <v>18.03</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2668,32 +2668,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4484.69</v>
+        <v>4487.78</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>$-1.44</t>
+          <t>$-3.86</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4572.2</v>
+        <v>4585.6</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>87.51000000000001</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2705,8 +2705,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J45" s="3" t="n">
-        <v>22.22</v>
+      <c r="J45" s="5" t="n">
+        <v>21.29</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2717,32 +2717,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4540.28</v>
+        <v>4484.69</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$1.89</t>
+          <t>$-1.44</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4659.5</v>
+        <v>4572.2</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>119.22</v>
+        <v>87.51000000000001</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2754,8 +2754,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J46" s="3" t="n">
-        <v>21.39</v>
+      <c r="J46" s="5" t="n">
+        <v>22.22</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2766,32 +2766,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4495.57</v>
+        <v>4540.28</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>$-4.31</t>
+          <t>+$1.89</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4597</v>
+        <v>4659.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>101.43</v>
+        <v>119.22</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2803,8 +2803,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J47" s="3" t="n">
-        <v>20.79</v>
+      <c r="J47" s="5" t="n">
+        <v>21.39</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2815,32 +2815,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4456.15</v>
+        <v>4495.57</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>$-6.52</t>
+          <t>$-4.31</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4545.1</v>
+        <v>4597</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>88.95</v>
+        <v>101.43</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2852,8 +2852,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J48" s="3" t="n">
-        <v>21.4</v>
+      <c r="J48" s="5" t="n">
+        <v>20.79</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2864,32 +2864,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4507.46</v>
+        <v>4456.15</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+$58.22</t>
+          <t>$-6.52</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4601.2</v>
+        <v>4545.1</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>93.73999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2901,8 +2901,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J49" s="3" t="n">
-        <v>21.43</v>
+      <c r="J49" s="5" t="n">
+        <v>21.4</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2913,32 +2913,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4509.11</v>
+        <v>4507.46</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>$-1.21</t>
+          <t>+$58.22</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4623.4</v>
+        <v>4601.2</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>114.29</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2950,8 +2950,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J50" s="3" t="n">
-        <v>20.06</v>
+      <c r="J50" s="5" t="n">
+        <v>21.43</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2962,32 +2962,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4543.11</v>
+        <v>4509.11</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.75%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>$-3.76</t>
+          <t>$-1.21</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4643.6</v>
+        <v>4623.4</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>100.49</v>
+        <v>114.29</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2999,8 +2999,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J51" s="3" t="n">
-        <v>20.67</v>
+      <c r="J51" s="5" t="n">
+        <v>20.06</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -3011,32 +3011,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4543.62</v>
+        <v>4543.11</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>$-3.76</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4634.4</v>
+        <v>4643.6</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>90.78</v>
+        <v>100.49</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3048,8 +3048,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J52" s="3" t="n">
-        <v>21.65</v>
+      <c r="J52" s="5" t="n">
+        <v>20.67</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3060,32 +3060,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4481.92</v>
+        <v>4543.62</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>+$1.98</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4610.1</v>
+        <v>4634.4</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>128.18</v>
+        <v>90.78</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3097,8 +3097,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J53" s="3" t="n">
-        <v>19.55</v>
+      <c r="J53" s="5" t="n">
+        <v>21.65</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3109,32 +3109,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4566.08</v>
+        <v>4481.92</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>$-10.86</t>
+          <t>+$1.98</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4658.2</v>
+        <v>4610.1</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>92.12</v>
+        <v>128.18</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3146,8 +3146,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J54" s="3" t="n">
-        <v>17.38</v>
+      <c r="J54" s="5" t="n">
+        <v>19.55</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3158,32 +3158,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4539.94</v>
+        <v>4566.08</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+$0.18</t>
+          <t>$-10.86</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4662.2</v>
+        <v>4658.2</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>122.26</v>
+        <v>92.12</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3195,8 +3195,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J55" s="3" t="n">
-        <v>15.41</v>
+      <c r="J55" s="5" t="n">
+        <v>17.38</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3207,32 +3207,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4652.24</v>
+        <v>4539.94</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$0.18</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4787.9</v>
+        <v>4662.2</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-2.63%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>135.66</v>
+        <v>122.26</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3244,8 +3244,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J56" s="3" t="n">
-        <v>15.84</v>
+      <c r="J56" s="5" t="n">
+        <v>15.41</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3256,32 +3256,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4688.75</v>
+        <v>4652.24</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>$-3.60</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4810.3</v>
+        <v>4787.9</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>121.55</v>
+        <v>135.66</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3293,8 +3293,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J57" s="3" t="n">
-        <v>14.88</v>
+      <c r="J57" s="5" t="n">
+        <v>15.84</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -3305,32 +3305,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4715.2</v>
+        <v>4688.75</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>+$2.34</t>
+          <t>$-3.60</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4790.9</v>
+        <v>4810.3</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>75.7</v>
+        <v>121.55</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3342,44 +3342,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J58" s="3" t="n">
-        <v>12.74</v>
+      <c r="J58" s="5" t="n">
+        <v>14.88</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4734.64</v>
+        <v>4715.2</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>$-33.15</t>
+          <t>+$2.34</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4833.6</v>
+        <v>4790.9</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>98.95999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3391,44 +3391,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J59" s="3" t="n">
-        <v>12.08</v>
+      <c r="J59" s="5" t="n">
+        <v>12.74</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4715.83</v>
+        <v>4734.64</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>$-8.63</t>
+          <t>$-33.15</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4834.9</v>
+        <v>4833.6</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>119.07</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3440,8 +3440,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J60" s="3" t="n">
-        <v>11.42</v>
+      <c r="J60" s="5" t="n">
+        <v>12.08</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -3452,32 +3452,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4687.08</v>
+        <v>4715.83</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>+$7.02</t>
+          <t>$-8.63</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4815.5</v>
+        <v>4834.9</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>128.42</v>
+        <v>119.07</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3489,8 +3489,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J61" s="3" t="n">
-        <v>13.66</v>
+      <c r="J61" s="5" t="n">
+        <v>11.42</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -3501,32 +3501,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4690.82</v>
+        <v>4687.08</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>+2.93%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>+$3.16</t>
+          <t>+$7.02</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4798.2</v>
+        <v>4815.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>+2.74%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>107.38</v>
+        <v>128.42</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3538,8 +3538,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J62" s="3" t="n">
-        <v>14.27</v>
+      <c r="J62" s="5" t="n">
+        <v>13.66</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -3550,32 +3550,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4557.42</v>
+        <v>4690.82</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>+0.74%</t>
+          <t>+2.93%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>+$3.16</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4670.1</v>
+        <v>4798.2</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>+2.74%</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>112.68</v>
+        <v>107.38</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3587,8 +3587,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J63" s="3" t="n">
-        <v>14.95</v>
+      <c r="J63" s="5" t="n">
+        <v>14.27</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -3599,32 +3599,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4523.72</v>
+        <v>4557.42</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>+0.74%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>+$18.71</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4635.1</v>
+        <v>4670.1</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>+0.76%</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>111.38</v>
+        <v>112.68</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3636,8 +3636,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J64" s="3" t="n">
-        <v>16.42</v>
+      <c r="J64" s="5" t="n">
+        <v>14.95</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -3648,32 +3648,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4614.08</v>
+        <v>4523.72</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>+$4.06</t>
+          <t>+$18.71</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4747.8</v>
+        <v>4635.1</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-2.37%</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>133.72</v>
+        <v>111.38</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3685,8 +3685,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J65" s="3" t="n">
-        <v>15.85</v>
+      <c r="J65" s="5" t="n">
+        <v>16.42</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -3697,32 +3697,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4621.53</v>
+        <v>4614.08</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>+$1.89</t>
+          <t>+$4.06</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4731.8</v>
+        <v>4747.8</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>110.27</v>
+        <v>133.72</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3734,8 +3734,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J66" s="3" t="n">
-        <v>15.16</v>
+      <c r="J66" s="5" t="n">
+        <v>15.85</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -3746,32 +3746,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4543.37</v>
+        <v>4621.53</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>$-3.14</t>
+          <t>+$1.89</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4661.7</v>
+        <v>4731.8</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>118.33</v>
+        <v>110.27</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3783,8 +3783,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J67" s="3" t="n">
-        <v>15.8</v>
+      <c r="J67" s="5" t="n">
+        <v>15.16</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -3795,32 +3795,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4596.87</v>
+        <v>4543.37</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-3.14</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4709.6</v>
+        <v>4661.7</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>112.73</v>
+        <v>118.33</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3832,8 +3832,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J68" s="3" t="n">
-        <v>15.5</v>
+      <c r="J68" s="5" t="n">
+        <v>15.8</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -3844,32 +3844,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4681.73</v>
+        <v>4596.87</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>$-12.44</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4797</v>
+        <v>4709.6</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>-0.99%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>115.27</v>
+        <v>112.73</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3881,8 +3881,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J69" s="3" t="n">
-        <v>20.95</v>
+      <c r="J69" s="5" t="n">
+        <v>15.5</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -3893,32 +3893,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>4710.12</v>
+        <v>4681.73</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>+$12.00</t>
+          <t>$-12.44</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4844.8</v>
+        <v>4797</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>134.68</v>
+        <v>115.27</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3930,8 +3930,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J70" s="3" t="n">
-        <v>23.3</v>
+      <c r="J70" s="5" t="n">
+        <v>20.95</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -3942,32 +3942,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4694.36</v>
+        <v>4710.12</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>+$4.60</t>
+          <t>+$12.00</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4828.3</v>
+        <v>4844.8</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>133.94</v>
+        <v>134.68</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3979,8 +3979,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J71" s="3" t="n">
-        <v>25.67</v>
+      <c r="J71" s="5" t="n">
+        <v>23.3</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -3991,32 +3991,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4740.15</v>
+        <v>4694.36</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>$-0.84</t>
+          <t>+$4.60</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4858.2</v>
+        <v>4828.3</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>118.05</v>
+        <v>133.94</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -4028,8 +4028,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J72" s="3" t="n">
-        <v>28.47</v>
+      <c r="J72" s="5" t="n">
+        <v>25.67</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -4040,32 +4040,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4720.07</v>
+        <v>4740.15</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>-2.09%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>+$0.62</t>
+          <t>$-0.84</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4824.1</v>
+        <v>4858.2</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>-2.26%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>104.03</v>
+        <v>118.05</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -4077,8 +4077,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J73" s="4" t="n">
-        <v>30.98</v>
+      <c r="J73" s="5" t="n">
+        <v>28.47</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -4089,32 +4089,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>4820.58</v>
+        <v>4720.07</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>$-56.03</t>
+          <t>+$0.62</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4935.4</v>
+        <v>4824.1</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>-1.04%</t>
+          <t>-2.26%</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>114.82</v>
+        <v>104.03</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -4126,8 +4126,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J74" s="4" t="n">
-        <v>32.7</v>
+      <c r="J74" s="6" t="n">
+        <v>30.98</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -4138,32 +4138,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4831.76</v>
+        <v>4820.58</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>+$1.68</t>
+          <t>$-56.03</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4987.3</v>
+        <v>4935.4</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>-1.04%</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>155.54</v>
+        <v>114.82</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -4175,8 +4175,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J75" s="4" t="n">
-        <v>30.87</v>
+      <c r="J75" s="6" t="n">
+        <v>32.7</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -4187,32 +4187,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4790.65</v>
+        <v>4831.76</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>$-1.72</t>
+          <t>+$1.68</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4916.6</v>
+        <v>4987.3</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>125.95</v>
+        <v>155.54</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -4224,8 +4224,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J76" s="4" t="n">
-        <v>28.9</v>
+      <c r="J76" s="6" t="n">
+        <v>30.87</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -4236,32 +4236,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>4791.81</v>
+        <v>4790.65</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>$-1.72</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4932.6</v>
+        <v>4916.6</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>140.79</v>
+        <v>125.95</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -4273,8 +4273,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J77" s="4" t="n">
-        <v>31.48</v>
+      <c r="J77" s="6" t="n">
+        <v>28.9</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -4285,32 +4285,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>4841.67</v>
+        <v>4791.81</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>+2.09%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>+$1.90</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4960.6</v>
+        <v>4932.6</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>+1.74%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>118.93</v>
+        <v>140.79</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -4322,8 +4322,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J78" s="4" t="n">
-        <v>39.82</v>
+      <c r="J78" s="6" t="n">
+        <v>31.48</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -4334,32 +4334,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>4742.69</v>
+        <v>4841.67</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+2.09%</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>$-109.35</t>
+          <t>+$1.90</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4876</v>
+        <v>4960.6</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+1.74%</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>133.31</v>
+        <v>118.93</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -4371,8 +4371,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J79" s="4" t="n">
-        <v>45.25</v>
+      <c r="J79" s="6" t="n">
+        <v>39.82</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -4383,32 +4383,32 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>4749.28</v>
+        <v>4742.69</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>$-1.84</t>
+          <t>$-109.35</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4896.4</v>
+        <v>4876</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>147.12</v>
+        <v>133.31</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -4420,8 +4420,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J80" s="4" t="n">
-        <v>50.95</v>
+      <c r="J80" s="6" t="n">
+        <v>45.25</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -4432,32 +4432,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4764.17</v>
+        <v>4749.28</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>+$0.36</t>
+          <t>$-1.84</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4928.3</v>
+        <v>4896.4</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>164.13</v>
+        <v>147.12</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -4469,8 +4469,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J81" s="4" t="n">
-        <v>59.04</v>
+      <c r="J81" s="6" t="n">
+        <v>50.95</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -4481,32 +4481,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>4719.81</v>
+        <v>4764.17</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>+$19.77</t>
+          <t>+$0.36</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4885.4</v>
+        <v>4928.3</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>+2.02%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>165.59</v>
+        <v>164.13</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -4518,8 +4518,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J82" s="4" t="n">
-        <v>68.06</v>
+      <c r="J82" s="6" t="n">
+        <v>59.04</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -4530,32 +4530,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4702.05</v>
+        <v>4719.81</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>+$1.79</t>
+          <t>+$19.77</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4788.9</v>
+        <v>4885.4</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+2.02%</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>86.84999999999999</v>
+        <v>165.59</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -4567,8 +4567,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J83" s="4" t="n">
-        <v>67.61</v>
+      <c r="J83" s="6" t="n">
+        <v>68.06</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -4579,20 +4579,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>4649.73</v>
+        <v>4702.05</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>$-3.57</t>
+          <t>+$1.79</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -4600,11 +4600,11 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>139.17</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -4616,8 +4616,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J84" s="4" t="n">
-        <v>64.22</v>
+      <c r="J84" s="6" t="n">
+        <v>67.61</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -4628,32 +4628,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4678.89</v>
+        <v>4649.73</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>$-0.67</t>
+          <t>$-3.57</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4784.1</v>
+        <v>4788.9</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>-2.74%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>105.21</v>
+        <v>139.17</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -4665,8 +4665,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J85" s="4" t="n">
-        <v>65.06999999999999</v>
+      <c r="J85" s="6" t="n">
+        <v>64.22</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -4677,32 +4677,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4758.74</v>
+        <v>4678.89</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>+$2.49</t>
+          <t>$-0.67</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4919.1</v>
+        <v>4784.1</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>+2.91%</t>
+          <t>-2.74%</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>160.36</v>
+        <v>105.21</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4714,8 +4714,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J86" s="4" t="n">
-        <v>61.51</v>
+      <c r="J86" s="6" t="n">
+        <v>65.06999999999999</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -4726,32 +4726,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>4668.9</v>
+        <v>4758.74</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>+3.50%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>+$2.18</t>
+          <t>+$2.49</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4780.2</v>
+        <v>4919.1</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>+2.64%</t>
+          <t>+2.91%</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>111.3</v>
+        <v>160.36</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4763,8 +4763,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J87" s="4" t="n">
-        <v>61.02</v>
+      <c r="J87" s="6" t="n">
+        <v>61.51</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -4775,32 +4775,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>4511.22</v>
+        <v>4668.9</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+3.50%</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>$-0.71</t>
+          <t>+$2.18</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4657.4</v>
+        <v>4780.2</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+2.64%</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>146.18</v>
+        <v>111.3</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4812,8 +4812,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J88" s="4" t="n">
-        <v>61.83</v>
+      <c r="J88" s="6" t="n">
+        <v>61.02</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -4824,32 +4824,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>4493.8</v>
+        <v>4511.22</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>+$12.74</t>
+          <t>$-0.71</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4624.8</v>
+        <v>4657.4</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>+2.62%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>131</v>
+        <v>146.18</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4861,8 +4861,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J89" s="4" t="n">
-        <v>66.98999999999999</v>
+      <c r="J89" s="6" t="n">
+        <v>61.83</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -4873,32 +4873,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>4377.64</v>
+        <v>4493.8</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>+$5.15</t>
+          <t>+$12.74</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4506.7</v>
+        <v>4624.8</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>-3.82%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>129.06</v>
+        <v>131</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4910,8 +4910,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J90" s="4" t="n">
-        <v>68.39</v>
+      <c r="J90" s="6" t="n">
+        <v>66.98999999999999</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -4922,32 +4922,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>4505.69</v>
+        <v>4377.64</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>$-19.39</t>
+          <t>+$5.15</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4685.7</v>
+        <v>4506.7</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>+3.37%</t>
+          <t>-3.82%</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>180.01</v>
+        <v>129.06</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4959,8 +4959,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J91" s="4" t="n">
-        <v>65.34999999999999</v>
+      <c r="J91" s="6" t="n">
+        <v>68.39</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -4971,32 +4971,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>4491.37</v>
+        <v>4505.69</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>+$6.43</t>
+          <t>$-19.39</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4532.8</v>
+        <v>4685.7</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+3.37%</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>41.43</v>
+        <v>180.01</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -5008,44 +5008,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J92" s="4" t="n">
-        <v>55.61</v>
+      <c r="J92" s="6" t="n">
+        <v>65.34999999999999</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>4407.46</v>
+        <v>4491.37</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>$-41.67</t>
+          <t>+$6.43</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4539.3</v>
+        <v>4532.8</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>131.84</v>
+        <v>41.43</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -5057,44 +5057,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J93" s="4" t="n">
-        <v>52.06</v>
+      <c r="J93" s="6" t="n">
+        <v>55.61</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>4490.66</v>
+        <v>4407.46</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>-3.43%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>+$0.88</t>
+          <t>$-41.67</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4716.2</v>
+        <v>4539.3</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>-3.75%</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>225.54</v>
+        <v>131.84</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -5106,8 +5106,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J94" s="4" t="n">
-        <v>48.26</v>
+      <c r="J94" s="6" t="n">
+        <v>52.06</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -5118,32 +5118,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>4650.11</v>
+        <v>4490.66</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>-3.50%</t>
+          <t>-3.43%</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>+$5.66</t>
+          <t>+$0.88</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4745.4</v>
+        <v>4716.2</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>-5.88%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>95.29000000000001</v>
+        <v>225.54</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -5155,8 +5155,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J95" s="4" t="n">
-        <v>40.68</v>
+      <c r="J95" s="6" t="n">
+        <v>48.26</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -5167,32 +5167,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>4818.71</v>
+        <v>4650.11</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>-3.74%</t>
+          <t>-3.50%</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>$-0.26</t>
+          <t>+$5.66</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5041.7</v>
+        <v>4745.4</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>-2.23%</t>
+          <t>-5.88%</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>222.99</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -5204,8 +5204,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J96" s="4" t="n">
-        <v>34.38</v>
+      <c r="J96" s="6" t="n">
+        <v>40.68</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -5216,32 +5216,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>5006.14</v>
+        <v>4818.71</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-3.74%</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>+$3.07</t>
+          <t>$-0.26</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5156.7</v>
+        <v>5041.7</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-2.23%</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>150.56</v>
+        <v>222.99</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -5253,8 +5253,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J97" s="4" t="n">
-        <v>33</v>
+      <c r="J97" s="6" t="n">
+        <v>34.38</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -5265,32 +5265,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>5004.67</v>
+        <v>5006.14</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>$-13.14</t>
+          <t>+$3.07</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5150.3</v>
+        <v>5156.7</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>145.63</v>
+        <v>150.56</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -5302,8 +5302,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J98" s="4" t="n">
-        <v>34.78</v>
+      <c r="J98" s="6" t="n">
+        <v>33</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -5314,32 +5314,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>5019</v>
+        <v>5004.67</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>+$0.70</t>
+          <t>$-13.14</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5210.4</v>
+        <v>5150.3</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>-1.25%</t>
+          <t>-1.15%</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>191.4</v>
+        <v>145.63</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -5351,8 +5351,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J99" s="4" t="n">
-        <v>34.04</v>
+      <c r="J99" s="6" t="n">
+        <v>34.78</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -5363,32 +5363,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>5079.6</v>
+        <v>5019</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>+$2.23</t>
+          <t>+$0.70</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5276.4</v>
+        <v>5210.4</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>-1.25%</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>196.8</v>
+        <v>191.4</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -5400,8 +5400,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J100" s="4" t="n">
-        <v>35.66</v>
+      <c r="J100" s="6" t="n">
+        <v>34.04</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -5412,32 +5412,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>5176.23</v>
+        <v>5079.6</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>$-3.94</t>
+          <t>+$2.23</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5330.9</v>
+        <v>5276.4</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>154.67</v>
+        <v>196.8</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -5449,8 +5449,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J101" s="4" t="n">
-        <v>34.34</v>
+      <c r="J101" s="6" t="n">
+        <v>35.66</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -5461,32 +5461,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>5191.58</v>
+        <v>5176.23</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>+$0.98</t>
+          <t>$-3.94</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5392.5</v>
+        <v>5330.9</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>200.92</v>
+        <v>154.67</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -5498,8 +5498,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J102" s="4" t="n">
-        <v>33.19</v>
+      <c r="J102" s="6" t="n">
+        <v>34.34</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -5510,32 +5510,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>5138.45</v>
+        <v>5191.58</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>+$8.38</t>
+          <t>+$0.98</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5251.9</v>
+        <v>5392.5</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>113.45</v>
+        <v>200.92</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -5547,8 +5547,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J103" s="3" t="n">
-        <v>27.57</v>
+      <c r="J103" s="6" t="n">
+        <v>33.19</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -5559,32 +5559,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>5171.8</v>
+        <v>5138.45</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>+$1.60</t>
+          <t>+$8.38</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5306.8</v>
+        <v>5251.9</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>135</v>
+        <v>113.45</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -5596,8 +5596,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J104" s="3" t="n">
-        <v>27.41</v>
+      <c r="J104" s="5" t="n">
+        <v>27.57</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -5608,32 +5608,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>5082.25</v>
+        <v>5171.8</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>+$15.58</t>
+          <t>+$1.60</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5225.6</v>
+        <v>5306.8</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>143.35</v>
+        <v>135</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -5645,8 +5645,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J105" s="3" t="n">
-        <v>28.59</v>
+      <c r="J105" s="5" t="n">
+        <v>27.41</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -5657,32 +5657,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>5140.39</v>
+        <v>5082.25</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>+$15.99</t>
+          <t>+$15.58</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5281.6</v>
+        <v>5225.6</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-1.06%</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>141.21</v>
+        <v>143.35</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -5694,8 +5694,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J106" s="4" t="n">
-        <v>29.02</v>
+      <c r="J106" s="5" t="n">
+        <v>28.59</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -5706,32 +5706,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>5087.78</v>
+        <v>5140.39</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>-4.39%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>+$3.27</t>
+          <t>+$15.99</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5269.7</v>
+        <v>5281.6</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>-3.53%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>181.92</v>
+        <v>141.21</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -5743,8 +5743,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J107" s="3" t="n">
-        <v>26.89</v>
+      <c r="J107" s="6" t="n">
+        <v>29.02</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -5755,32 +5755,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>5321.3</v>
+        <v>5087.78</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>+0.80%</t>
+          <t>-4.39%</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>+$22.33</t>
+          <t>+$3.27</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5462.6</v>
+        <v>5269.7</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-3.53%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>141.3</v>
+        <v>181.92</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -5792,8 +5792,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J108" s="3" t="n">
-        <v>25</v>
+      <c r="J108" s="5" t="n">
+        <v>26.89</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -5804,32 +5804,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>5278.9</v>
+        <v>5321.3</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>+1.83%</t>
+          <t>+0.80%</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>+$3.50</t>
+          <t>+$22.33</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5396.2</v>
+        <v>5462.6</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>117.3</v>
+        <v>141.3</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -5841,8 +5841,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J109" s="3" t="n">
-        <v>23.93</v>
+      <c r="J109" s="5" t="n">
+        <v>25</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -5853,32 +5853,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>5184.25</v>
+        <v>5278.9</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+1.83%</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>$-2.63</t>
+          <t>+$3.50</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5341.1</v>
+        <v>5396.2</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>156.85</v>
+        <v>117.3</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5890,8 +5890,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J110" s="3" t="n">
-        <v>27.52</v>
+      <c r="J110" s="5" t="n">
+        <v>23.93</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -5902,32 +5902,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>5164.29</v>
+        <v>5184.25</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>+$0.50</t>
+          <t>$-2.63</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5374.2</v>
+        <v>5341.1</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>209.91</v>
+        <v>156.85</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5939,8 +5939,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J111" s="4" t="n">
-        <v>32.13</v>
+      <c r="J111" s="5" t="n">
+        <v>27.52</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -5951,32 +5951,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>5142.79</v>
+        <v>5164.29</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>-1.62%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>+$2.64</t>
+          <t>+$0.50</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5322.8</v>
+        <v>5374.2</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>180.01</v>
+        <v>209.91</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5988,8 +5988,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J112" s="4" t="n">
-        <v>30.2</v>
+      <c r="J112" s="6" t="n">
+        <v>32.13</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -6000,32 +6000,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>5227.48</v>
+        <v>5142.79</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>+2.36%</t>
+          <t>-1.62%</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>+$2.32</t>
+          <t>+$2.64</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5372</v>
+        <v>5322.8</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>144.52</v>
+        <v>180.01</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -6037,8 +6037,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J113" s="3" t="n">
-        <v>28.13</v>
+      <c r="J113" s="6" t="n">
+        <v>30.2</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -6049,32 +6049,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>5106.96</v>
+        <v>5227.48</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>+2.22%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>+$2.74</t>
+          <t>+$2.32</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5223.4</v>
+        <v>5372</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>+1.70%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>116.44</v>
+        <v>144.52</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -6086,8 +6086,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J114" s="4" t="n">
-        <v>35.59</v>
+      <c r="J114" s="5" t="n">
+        <v>28.13</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -6098,32 +6098,32 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>4996.02</v>
+        <v>5106.96</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+2.22%</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>$-2.27</t>
+          <t>+$2.74</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5136.1</v>
+        <v>5223.4</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+1.70%</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>140.08</v>
+        <v>116.44</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -6135,8 +6135,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J115" s="4" t="n">
-        <v>44.31</v>
+      <c r="J115" s="6" t="n">
+        <v>35.59</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -6147,32 +6147,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>4977.18</v>
+        <v>4996.02</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>+2.03%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>+$1.09</t>
+          <t>$-2.27</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5147.3</v>
+        <v>5136.1</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>170.12</v>
+        <v>140.08</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -6184,8 +6184,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J116" s="4" t="n">
-        <v>46.23</v>
+      <c r="J116" s="6" t="n">
+        <v>44.31</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -6196,32 +6196,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>4878.1</v>
+        <v>4977.18</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>-3.25%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>$-45.72</t>
+          <t>+$1.09</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5039.4</v>
+        <v>5147.3</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>-2.79%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>161.3</v>
+        <v>170.12</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -6233,8 +6233,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J117" s="4" t="n">
-        <v>46.39</v>
+      <c r="J117" s="6" t="n">
+        <v>46.23</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -6245,32 +6245,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>5041.86</v>
+        <v>4878.1</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>+2.44%</t>
+          <t>-3.25%</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>+$4.32</t>
+          <t>$-45.72</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5183.8</v>
+        <v>5039.4</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>+1.87%</t>
+          <t>-2.79%</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>141.94</v>
+        <v>161.3</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -6282,8 +6282,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J118" s="4" t="n">
-        <v>57.41</v>
+      <c r="J118" s="6" t="n">
+        <v>46.39</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -6294,32 +6294,32 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>4921.59</v>
+        <v>5041.86</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>-3.19%</t>
+          <t>+2.44%</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>+$1.40</t>
+          <t>+$4.32</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5088.4</v>
+        <v>5183.8</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>-2.94%</t>
+          <t>+1.87%</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>166.81</v>
+        <v>141.94</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -6331,8 +6331,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J119" s="4" t="n">
-        <v>62.1</v>
+      <c r="J119" s="6" t="n">
+        <v>57.41</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -6343,32 +6343,32 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>5083.84</v>
+        <v>4921.59</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>+1.18%</t>
+          <t>-3.19%</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>+$2.13</t>
+          <t>+$1.40</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5242.5</v>
+        <v>5088.4</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-2.94%</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>158.66</v>
+        <v>166.81</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -6380,8 +6380,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J120" s="4" t="n">
-        <v>63</v>
+      <c r="J120" s="6" t="n">
+        <v>62.1</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -6392,32 +6392,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>5024.38</v>
+        <v>5083.84</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>+1.18%</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>$-0.65</t>
+          <t>+$2.13</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5172.2</v>
+        <v>5242.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>147.82</v>
+        <v>158.66</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -6429,8 +6429,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J121" s="4" t="n">
-        <v>64.01000000000001</v>
+      <c r="J121" s="6" t="n">
+        <v>63</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -6441,32 +6441,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>5060.14</v>
+        <v>5024.38</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>+1.88%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>+$17.25</t>
+          <t>$-0.65</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5222.1</v>
+        <v>5172.2</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>+2.00%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>161.96</v>
+        <v>147.82</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -6478,8 +6478,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J122" s="4" t="n">
-        <v>63.42</v>
+      <c r="J122" s="6" t="n">
+        <v>64.01000000000001</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -6490,32 +6490,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>4966.93</v>
+        <v>5060.14</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>+3.92%</t>
+          <t>+1.88%</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>+$12.55</t>
+          <t>+$17.25</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5119.8</v>
+        <v>5222.1</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>+1.94%</t>
+          <t>+2.00%</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>152.87</v>
+        <v>161.96</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -6527,8 +6527,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J123" s="4" t="n">
-        <v>63.27</v>
+      <c r="J123" s="6" t="n">
+        <v>63.42</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -6539,32 +6539,32 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>4779.63</v>
+        <v>4966.93</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>-3.71%</t>
+          <t>+3.92%</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>+$12.00</t>
+          <t>+$12.55</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5022.3</v>
+        <v>5119.8</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>+1.94%</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>242.67</v>
+        <v>152.87</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -6576,8 +6576,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J124" s="4" t="n">
-        <v>57.48</v>
+      <c r="J124" s="6" t="n">
+        <v>63.27</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -6588,32 +6588,32 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>4963.89</v>
+        <v>4779.63</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-3.71%</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>+$1.30</t>
+          <t>+$12.00</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5089</v>
+        <v>5022.3</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>125.11</v>
+        <v>242.67</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -6625,8 +6625,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J125" s="4" t="n">
-        <v>49.25</v>
+      <c r="J125" s="6" t="n">
+        <v>57.48</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -6637,32 +6637,32 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>4944.42</v>
+        <v>4963.89</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>+6.13%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>+$13.04</t>
+          <t>+$1.30</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5072.5</v>
+        <v>5089</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>+6.11%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>128.08</v>
+        <v>125.11</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -6674,8 +6674,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J126" s="4" t="n">
-        <v>49.09</v>
+      <c r="J126" s="6" t="n">
+        <v>49.25</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -6686,32 +6686,32 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>4658.73</v>
+        <v>4944.42</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>-4.75%</t>
+          <t>+6.13%</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>$-76.67</t>
+          <t>+$13.04</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4780.4</v>
+        <v>5072.5</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>+6.11%</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>121.67</v>
+        <v>128.08</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -6723,8 +6723,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J127" s="4" t="n">
-        <v>48.95</v>
+      <c r="J127" s="6" t="n">
+        <v>49.09</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -6735,36 +6735,36 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>4890.97</v>
+        <v>4658.73</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>-8.99%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>+$8.73</t>
+          <t>$-76.67</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4880</v>
+        <v>4780.4</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>-11.41%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>-10.97</v>
-      </c>
-      <c r="H128" s="7" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>121.67</v>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
@@ -6772,48 +6772,48 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J128" s="4" t="n">
-        <v>41.41</v>
+      <c r="J128" s="6" t="n">
+        <v>48.95</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>5373.91</v>
+        <v>4890.97</v>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-8.99%</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>+$5.87</t>
+          <t>+$8.73</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5508.6</v>
+        <v>4880</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-11.41%</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>134.69</v>
-      </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-10.97</v>
+      </c>
+      <c r="H129" s="7" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -6821,44 +6821,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J129" s="4" t="n">
-        <v>31.72</v>
+      <c r="J129" s="6" t="n">
+        <v>41.41</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>5416.79</v>
+        <v>5373.91</v>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>+4.60%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>+$5.87</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5494.6</v>
+        <v>5508.6</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>+4.32%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>77.81</v>
+        <v>134.69</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -6870,8 +6870,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J130" s="4" t="n">
-        <v>29.24</v>
+      <c r="J130" s="6" t="n">
+        <v>31.72</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -6882,32 +6882,32 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>5178.46</v>
+        <v>5416.79</v>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>+3.36%</t>
+          <t>+4.60%</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>+$3.14</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5267.3</v>
+        <v>5494.6</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+4.32%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>88.84</v>
+        <v>77.81</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -6919,8 +6919,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J131" s="3" t="n">
-        <v>28.65</v>
+      <c r="J131" s="6" t="n">
+        <v>29.24</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -6931,32 +6931,32 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>5010.31</v>
+        <v>5178.46</v>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+3.36%</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>+$20.73</t>
+          <t>+$3.14</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5272.8</v>
+        <v>5267.3</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>262.49</v>
+        <v>88.84</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -6968,8 +6968,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J132" s="3" t="n">
-        <v>16.43</v>
+      <c r="J132" s="5" t="n">
+        <v>28.65</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -6980,32 +6980,32 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>4988.56</v>
+        <v>5010.31</v>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>+1.07%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>+$5.34</t>
+          <t>+$20.73</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5160.4</v>
+        <v>5272.8</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+2.18%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>171.84</v>
+        <v>262.49</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -7017,8 +7017,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J133" s="3" t="n">
-        <v>10.44</v>
+      <c r="J133" s="5" t="n">
+        <v>16.43</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -7029,32 +7029,32 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>4935.8</v>
+        <v>4988.56</v>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>+$0.94</t>
+          <t>+$5.34</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5086.9</v>
+        <v>5160.4</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>+1.59%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>151.1</v>
+        <v>171.84</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -7066,8 +7066,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J134" s="3" t="n">
-        <v>8.960000000000001</v>
+      <c r="J134" s="5" t="n">
+        <v>10.44</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -7078,32 +7078,32 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>4831.51</v>
+        <v>4935.8</v>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+2.16%</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>+$0.31</t>
+          <t>+$0.94</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5007.5</v>
+        <v>5086.9</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>+1.51%</t>
+          <t>+1.59%</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>175.99</v>
+        <v>151.1</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -7115,7 +7115,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J135" s="2" t="inlineStr"/>
+      <c r="J135" s="5" t="n">
+        <v>8.960000000000001</v>
+      </c>
       <c r="K135" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -7125,32 +7127,32 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>4762.99</v>
+        <v>4831.51</v>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>+3.63%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>+$75.81</t>
+          <t>+$0.31</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4933</v>
+        <v>5007.5</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>+3.65%</t>
+          <t>+1.51%</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>170.01</v>
+        <v>175.99</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -7172,32 +7174,32 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>4596.18</v>
+        <v>4762.99</v>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+3.63%</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>+$1.80</t>
+          <t>+$75.81</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4759.2</v>
+        <v>4933</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>+3.65%</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>163.02</v>
+        <v>170.01</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -7219,32 +7221,32 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>4615.95</v>
+        <v>4596.18</v>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>+$6.28</t>
+          <t>+$1.80</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4787.7</v>
+        <v>4759.2</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>171.75</v>
+        <v>163.02</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -7266,32 +7268,32 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>4624.8</v>
+        <v>4615.95</v>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>+$3.59</t>
+          <t>+$6.28</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4798.9</v>
+        <v>4787.7</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>174.1</v>
+        <v>171.75</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -7313,32 +7315,32 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>4585.44</v>
+        <v>4624.8</v>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>+$5.33</t>
+          <t>+$3.59</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4760.2</v>
+        <v>4798.9</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>174.76</v>
+        <v>174.1</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -7360,32 +7362,32 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>4598.46</v>
+        <v>4585.44</v>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>+1.98%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>+$9.47</t>
+          <t>+$5.33</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4777.7</v>
+        <v>4760.2</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>+2.49%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>179.24</v>
+        <v>174.76</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -7407,32 +7409,32 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>4509.27</v>
+        <v>4598.46</v>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>+$1.86</t>
+          <t>+$9.47</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4661.4</v>
+        <v>4777.7</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>+0.90%</t>
+          <t>+2.49%</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>152.13</v>
+        <v>179.24</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -7454,32 +7456,32 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>4477.84</v>
+        <v>4509.27</v>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>$-0.03</t>
+          <t>+$1.86</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4620</v>
+        <v>4661.4</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.90%</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>142.16</v>
+        <v>152.13</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -7501,32 +7503,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>4456.26</v>
+        <v>4477.84</v>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>+$0.08</t>
+          <t>$-0.03</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4620.6</v>
+        <v>4620</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>-0.76%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>164.34</v>
+        <v>142.16</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -7548,32 +7550,32 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>4494.61</v>
+        <v>4456.26</v>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.85%</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>$-0.07</t>
+          <t>+$0.08</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4656.2</v>
+        <v>4620.6</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>-0.76%</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>161.59</v>
+        <v>164.34</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -7595,32 +7597,32 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>4449.11</v>
+        <v>4494.61</v>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>+2.70%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>+$28.96</t>
+          <t>$-0.07</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4608.1</v>
+        <v>4656.2</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>+2.76%</t>
+          <t>+1.04%</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>158.99</v>
+        <v>161.59</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -7642,32 +7644,32 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>4332.17</v>
+        <v>4449.11</v>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.70%</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+$28.96</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4484.4</v>
+        <v>4608.1</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.76%</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>152.23</v>
+        <v>158.99</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -7681,6 +7683,53 @@
       </c>
       <c r="J147" s="2" t="inlineStr"/>
       <c r="K147" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>4332.17</v>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>4484.4</v>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>152.23</v>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -50,6 +50,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
       </patternFill>
@@ -64,12 +70,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
         <bgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -105,13 +105,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K148"/>
+  <dimension ref="A1:K149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -561,130 +561,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4097.29</v>
+        <v>4273.01</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>+4.29%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$22.75</t>
+          <t>+$151.16</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4339</v>
+        <v>4298.3</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+4.39%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>241.71</v>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>28.06</v>
+        <v>25.29</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>41.84</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4055.15</v>
+        <v>4097.29</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+1.04%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$33.39</t>
+          <t>+$22.75</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4156.4</v>
+        <v>4339</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>+4.39%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>101.25</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>19.9</v>
+        <v>241.71</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>28.06</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4044.36</v>
+        <v>4055.15</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$33.39</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4110.9</v>
+        <v>4156.4</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>66.54000000000001</v>
+        <v>101.25</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -696,8 +696,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="5" t="n">
-        <v>18.29</v>
+      <c r="J4" s="6" t="n">
+        <v>19.9</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -708,32 +708,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4103.64</v>
+        <v>4044.36</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$0.17</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4160.6</v>
+        <v>4110.9</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>56.96</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -745,8 +745,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="5" t="n">
-        <v>18.21</v>
+      <c r="J5" s="6" t="n">
+        <v>18.29</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -757,32 +757,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4066.23</v>
+        <v>4103.64</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$1.59</t>
+          <t>+$0.17</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4097</v>
+        <v>4160.6</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>30.77</v>
+        <v>56.96</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -794,8 +794,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="5" t="n">
-        <v>18.03</v>
+      <c r="J6" s="6" t="n">
+        <v>18.21</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -806,32 +806,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4028.54</v>
+        <v>4066.23</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$2.81</t>
+          <t>+$1.59</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4098.6</v>
+        <v>4097</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>70.06</v>
+        <v>30.77</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -843,8 +843,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="5" t="n">
-        <v>16.18</v>
+      <c r="J7" s="6" t="n">
+        <v>18.03</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -855,32 +855,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4076.6</v>
+        <v>4028.54</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$43.44</t>
+          <t>+$2.81</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4136.4</v>
+        <v>4098.6</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>59.8</v>
+        <v>70.06</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -892,8 +892,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="5" t="n">
-        <v>18.87</v>
+      <c r="J8" s="6" t="n">
+        <v>16.18</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -904,32 +904,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4052.74</v>
+        <v>4076.6</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$0.61</t>
+          <t>+$43.44</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4129.7</v>
+        <v>4136.4</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>76.95999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -941,8 +941,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="5" t="n">
-        <v>21.15</v>
+      <c r="J9" s="6" t="n">
+        <v>18.87</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -953,32 +953,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4049.43</v>
+        <v>4052.74</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$-10.76</t>
+          <t>+$0.61</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4108.8</v>
+        <v>4129.7</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>59.37</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -990,8 +990,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="5" t="n">
-        <v>19.94</v>
+      <c r="J10" s="6" t="n">
+        <v>21.15</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1002,32 +1002,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4130.11</v>
+        <v>4049.43</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$1.94</t>
+          <t>$-10.76</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4210.3</v>
+        <v>4108.8</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+1.84%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>80.19</v>
+        <v>59.37</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1039,8 +1039,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J11" s="5" t="n">
-        <v>21.96</v>
+      <c r="J11" s="6" t="n">
+        <v>19.94</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1051,32 +1051,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4077.87</v>
+        <v>4130.11</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$1.94</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4134.2</v>
+        <v>4210.3</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+1.84%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>56.33</v>
+        <v>80.19</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1088,8 +1088,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>21.74</v>
+      <c r="J12" s="6" t="n">
+        <v>21.96</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1100,32 +1100,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4007.49</v>
+        <v>4077.87</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-12.24</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4073</v>
+        <v>4134.2</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>65.51000000000001</v>
+        <v>56.33</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1137,8 +1137,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J13" s="5" t="n">
-        <v>21.72</v>
+      <c r="J13" s="6" t="n">
+        <v>21.74</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1149,32 +1149,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4017.04</v>
+        <v>4007.49</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$1.19</t>
+          <t>$-12.24</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4075.8</v>
+        <v>4073</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>58.76</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1186,8 +1186,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J14" s="5" t="n">
-        <v>22.33</v>
+      <c r="J14" s="6" t="n">
+        <v>21.72</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1198,32 +1198,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3976.48</v>
+        <v>4017.04</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$4.31</t>
+          <t>+$1.19</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4048.7</v>
+        <v>4075.8</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>72.22</v>
+        <v>58.76</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1235,8 +1235,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J15" s="5" t="n">
-        <v>22.36</v>
+      <c r="J15" s="6" t="n">
+        <v>22.33</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1247,32 +1247,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4060.55</v>
+        <v>3976.48</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$0.46</t>
+          <t>+$4.31</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4109.3</v>
+        <v>4048.7</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>48.75</v>
+        <v>72.22</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1284,8 +1284,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J16" s="5" t="n">
-        <v>21.54</v>
+      <c r="J16" s="6" t="n">
+        <v>22.36</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1296,32 +1296,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4052.92</v>
+        <v>4060.55</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$5.21</t>
+          <t>+$0.46</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4127.9</v>
+        <v>4109.3</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+1.58%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>74.98</v>
+        <v>48.75</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1333,8 +1333,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J17" s="5" t="n">
-        <v>21.93</v>
+      <c r="J17" s="6" t="n">
+        <v>21.54</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1345,32 +1345,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4000.78</v>
+        <v>4052.92</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$5.21</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4063.6</v>
+        <v>4127.9</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>+1.58%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>62.82</v>
+        <v>74.98</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1382,8 +1382,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J18" s="5" t="n">
-        <v>22.96</v>
+      <c r="J18" s="6" t="n">
+        <v>21.93</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1394,32 +1394,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4119.29</v>
+        <v>4000.78</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4173.6</v>
+        <v>4063.6</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>54.31</v>
+        <v>62.82</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1431,8 +1431,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="5" t="n">
-        <v>24.16</v>
+      <c r="J19" s="6" t="n">
+        <v>22.96</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1443,32 +1443,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4123.38</v>
+        <v>4119.29</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4201.4</v>
+        <v>4173.6</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+1.43%</t>
+          <t>-0.66%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>78.02</v>
+        <v>54.31</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1480,8 +1480,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J20" s="5" t="n">
-        <v>28.73</v>
+      <c r="J20" s="6" t="n">
+        <v>24.16</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1492,32 +1492,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4077.4</v>
+        <v>4123.38</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4142.1</v>
+        <v>4201.4</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>+1.43%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>64.7</v>
+        <v>78.02</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="J21" s="6" t="n">
-        <v>34.99</v>
+        <v>28.73</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1541,32 +1541,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4105.67</v>
+        <v>4077.4</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4218.3</v>
+        <v>4142.1</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>112.63</v>
+        <v>64.7</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1578,8 +1578,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J22" s="6" t="n">
-        <v>32.93</v>
+      <c r="J22" s="3" t="n">
+        <v>34.99</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1590,32 +1590,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4165.04</v>
+        <v>4105.67</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4228.6</v>
+        <v>4218.3</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>63.56</v>
+        <v>112.63</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1627,8 +1627,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="6" t="n">
-        <v>31.11</v>
+      <c r="J23" s="3" t="n">
+        <v>32.93</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1639,32 +1639,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4123.77</v>
+        <v>4165.04</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4186.6</v>
+        <v>4228.6</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>62.83</v>
+        <v>63.56</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1676,8 +1676,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J24" s="6" t="n">
-        <v>39.51</v>
+      <c r="J24" s="3" t="n">
+        <v>31.11</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1688,32 +1688,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4031.01</v>
+        <v>4123.77</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4142.9</v>
+        <v>4186.6</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>111.89</v>
+        <v>62.83</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1725,8 +1725,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="6" t="n">
-        <v>47.43</v>
+      <c r="J25" s="3" t="n">
+        <v>39.51</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1737,32 +1737,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4007.41</v>
+        <v>4031.01</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4098.5</v>
+        <v>4142.9</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>91.09</v>
+        <v>111.89</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1774,8 +1774,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="6" t="n">
-        <v>48.29</v>
+      <c r="J26" s="3" t="n">
+        <v>47.43</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1786,32 +1786,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4016.54</v>
+        <v>4007.41</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4098.8</v>
+        <v>4098.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>82.26000000000001</v>
+        <v>91.09</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1823,8 +1823,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="6" t="n">
-        <v>48.18</v>
+      <c r="J27" s="3" t="n">
+        <v>48.29</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1835,32 +1835,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4089.95</v>
+        <v>4016.54</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4156.9</v>
+        <v>4098.8</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>66.95</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1872,8 +1872,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="6" t="n">
-        <v>47.32</v>
+      <c r="J28" s="3" t="n">
+        <v>48.18</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1884,32 +1884,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4026.57</v>
+        <v>4089.95</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4107.5</v>
+        <v>4156.9</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>80.93000000000001</v>
+        <v>66.95</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1921,8 +1921,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="6" t="n">
-        <v>46.73</v>
+      <c r="J29" s="3" t="n">
+        <v>47.32</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1933,32 +1933,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3999.06</v>
+        <v>4026.57</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4068.1</v>
+        <v>4107.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-3.39%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>69.04000000000001</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1970,8 +1970,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="6" t="n">
-        <v>46.06</v>
+      <c r="J30" s="3" t="n">
+        <v>46.73</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1982,32 +1982,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4110.14</v>
+        <v>3999.06</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4210.9</v>
+        <v>4068.1</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-3.39%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>100.76</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2019,8 +2019,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="6" t="n">
-        <v>43.81</v>
+      <c r="J31" s="3" t="n">
+        <v>46.06</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2031,32 +2031,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4191.26</v>
+        <v>4110.14</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4265.4</v>
+        <v>4210.9</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>74.14</v>
+        <v>100.76</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2068,8 +2068,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J32" s="6" t="n">
-        <v>42.64</v>
+      <c r="J32" s="3" t="n">
+        <v>43.81</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2080,32 +2080,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4209.02</v>
+        <v>4191.26</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4308.5</v>
+        <v>4265.4</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>99.48</v>
+        <v>74.14</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2117,8 +2117,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J33" s="6" t="n">
-        <v>43.1</v>
+      <c r="J33" s="3" t="n">
+        <v>42.64</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2129,130 +2129,130 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4257.71</v>
+        <v>4209.02</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4444.8</v>
+        <v>4308.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>-3.07%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>187.09</v>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J34" s="6" t="n">
-        <v>38.11</v>
+        <v>99.48</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>43.1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4331.14</v>
+        <v>4257.71</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$7.23</t>
+          <t>+$1.76</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4417.3</v>
+        <v>4444.8</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>86.16</v>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
-        </is>
-      </c>
-      <c r="J35" s="6" t="n">
-        <v>31.79</v>
+        <v>187.09</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>38.11</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4309.03</v>
+        <v>4331.14</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$52.77</t>
+          <t>+$7.23</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4414.3</v>
+        <v>4417.3</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>105.27</v>
+        <v>86.16</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2264,8 +2264,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J36" s="6" t="n">
-        <v>30.77</v>
+      <c r="J36" s="3" t="n">
+        <v>31.79</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2276,32 +2276,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4218.71</v>
+        <v>4309.03</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>$-1.08</t>
+          <t>+$52.77</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4300.4</v>
+        <v>4414.3</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>81.69</v>
+        <v>105.27</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2313,8 +2313,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J37" s="6" t="n">
-        <v>30.55</v>
+      <c r="J37" s="3" t="n">
+        <v>30.77</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2325,36 +2325,36 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4210.69</v>
+        <v>4218.71</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$10.16</t>
+          <t>$-1.08</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4174</v>
+        <v>4300.4</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+3.03%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>-36.69</v>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>81.69</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2362,48 +2362,48 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J38" s="5" t="n">
-        <v>23.08</v>
+      <c r="J38" s="3" t="n">
+        <v>30.55</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4071.28</v>
+        <v>4210.69</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>$-5.95</t>
+          <t>+$10.16</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4194.5</v>
+        <v>4174</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-3.57%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>123.22</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-36.69</v>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2411,44 +2411,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J39" s="5" t="n">
-        <v>12.35</v>
+      <c r="J39" s="6" t="n">
+        <v>23.08</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4259.29</v>
+        <v>4071.28</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-4.41%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-5.95</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4349.6</v>
+        <v>4194.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>-3.57%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>90.31</v>
+        <v>123.22</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2460,8 +2460,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J40" s="5" t="n">
-        <v>12.67</v>
+      <c r="J40" s="6" t="n">
+        <v>12.35</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2472,32 +2472,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4329.75</v>
+        <v>4259.29</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>$-2.37</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4427.3</v>
+        <v>4349.6</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>97.55</v>
+        <v>90.31</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2509,8 +2509,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J41" s="5" t="n">
-        <v>14.73</v>
+      <c r="J41" s="6" t="n">
+        <v>12.67</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2521,32 +2521,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4328.15</v>
+        <v>4329.75</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>-3.29%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$7.90</t>
+          <t>$-2.37</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4429</v>
+        <v>4427.3</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>100.85</v>
+        <v>97.55</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2558,8 +2558,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J42" s="5" t="n">
-        <v>16.65</v>
+      <c r="J42" s="6" t="n">
+        <v>14.73</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2570,32 +2570,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4475.25</v>
+        <v>4328.15</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-3.29%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$7.80</t>
+          <t>+$7.90</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4570.4</v>
+        <v>4429</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>95.15000000000001</v>
+        <v>100.85</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2607,8 +2607,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J43" s="5" t="n">
-        <v>17.2</v>
+      <c r="J43" s="6" t="n">
+        <v>16.65</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2619,32 +2619,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4434.3</v>
+        <v>4475.25</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$3.39</t>
+          <t>+$7.80</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4532</v>
+        <v>4570.4</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>97.7</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2656,8 +2656,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J44" s="5" t="n">
-        <v>18.03</v>
+      <c r="J44" s="6" t="n">
+        <v>17.2</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2668,32 +2668,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4487.78</v>
+        <v>4434.3</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>$-3.86</t>
+          <t>+$3.39</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4585.6</v>
+        <v>4532</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>97.81999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2705,8 +2705,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J45" s="5" t="n">
-        <v>21.29</v>
+      <c r="J45" s="6" t="n">
+        <v>18.03</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2717,32 +2717,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4484.69</v>
+        <v>4487.78</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>$-1.44</t>
+          <t>$-3.86</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4572.2</v>
+        <v>4585.6</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>87.51000000000001</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2754,8 +2754,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J46" s="5" t="n">
-        <v>22.22</v>
+      <c r="J46" s="6" t="n">
+        <v>21.29</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2766,32 +2766,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4540.28</v>
+        <v>4484.69</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+$1.89</t>
+          <t>$-1.44</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4659.5</v>
+        <v>4572.2</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>119.22</v>
+        <v>87.51000000000001</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2803,8 +2803,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J47" s="5" t="n">
-        <v>21.39</v>
+      <c r="J47" s="6" t="n">
+        <v>22.22</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2815,32 +2815,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4495.57</v>
+        <v>4540.28</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>$-4.31</t>
+          <t>+$1.89</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4597</v>
+        <v>4659.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>101.43</v>
+        <v>119.22</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2852,8 +2852,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J48" s="5" t="n">
-        <v>20.79</v>
+      <c r="J48" s="6" t="n">
+        <v>21.39</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2864,32 +2864,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4456.15</v>
+        <v>4495.57</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>$-6.52</t>
+          <t>$-4.31</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4545.1</v>
+        <v>4597</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>88.95</v>
+        <v>101.43</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2901,8 +2901,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J49" s="5" t="n">
-        <v>21.4</v>
+      <c r="J49" s="6" t="n">
+        <v>20.79</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2913,32 +2913,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4507.46</v>
+        <v>4456.15</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>+$58.22</t>
+          <t>$-6.52</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4601.2</v>
+        <v>4545.1</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>93.73999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2950,8 +2950,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J50" s="5" t="n">
-        <v>21.43</v>
+      <c r="J50" s="6" t="n">
+        <v>21.4</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2962,32 +2962,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4509.11</v>
+        <v>4507.46</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>$-1.21</t>
+          <t>+$58.22</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4623.4</v>
+        <v>4601.2</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>114.29</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2999,8 +2999,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J51" s="5" t="n">
-        <v>20.06</v>
+      <c r="J51" s="6" t="n">
+        <v>21.43</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -3011,32 +3011,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4543.11</v>
+        <v>4509.11</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.75%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>$-3.76</t>
+          <t>$-1.21</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4643.6</v>
+        <v>4623.4</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>100.49</v>
+        <v>114.29</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3048,8 +3048,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J52" s="5" t="n">
-        <v>20.67</v>
+      <c r="J52" s="6" t="n">
+        <v>20.06</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3060,32 +3060,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4543.62</v>
+        <v>4543.11</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>$-3.76</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4634.4</v>
+        <v>4643.6</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>90.78</v>
+        <v>100.49</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3097,8 +3097,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J53" s="5" t="n">
-        <v>21.65</v>
+      <c r="J53" s="6" t="n">
+        <v>20.67</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3109,32 +3109,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4481.92</v>
+        <v>4543.62</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+$1.98</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4610.1</v>
+        <v>4634.4</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>128.18</v>
+        <v>90.78</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3146,8 +3146,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J54" s="5" t="n">
-        <v>19.55</v>
+      <c r="J54" s="6" t="n">
+        <v>21.65</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3158,32 +3158,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4566.08</v>
+        <v>4481.92</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>$-10.86</t>
+          <t>+$1.98</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4658.2</v>
+        <v>4610.1</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>92.12</v>
+        <v>128.18</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3195,8 +3195,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J55" s="5" t="n">
-        <v>17.38</v>
+      <c r="J55" s="6" t="n">
+        <v>19.55</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3207,32 +3207,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4539.94</v>
+        <v>4566.08</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>+$0.18</t>
+          <t>$-10.86</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4662.2</v>
+        <v>4658.2</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>122.26</v>
+        <v>92.12</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3244,8 +3244,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J56" s="5" t="n">
-        <v>15.41</v>
+      <c r="J56" s="6" t="n">
+        <v>17.38</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3256,32 +3256,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4652.24</v>
+        <v>4539.94</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$0.18</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4787.9</v>
+        <v>4662.2</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-2.63%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>135.66</v>
+        <v>122.26</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3293,8 +3293,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J57" s="5" t="n">
-        <v>15.84</v>
+      <c r="J57" s="6" t="n">
+        <v>15.41</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -3305,32 +3305,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4688.75</v>
+        <v>4652.24</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>$-3.60</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4810.3</v>
+        <v>4787.9</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>121.55</v>
+        <v>135.66</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3342,8 +3342,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J58" s="5" t="n">
-        <v>14.88</v>
+      <c r="J58" s="6" t="n">
+        <v>15.84</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -3354,32 +3354,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4715.2</v>
+        <v>4688.75</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>+$2.34</t>
+          <t>$-3.60</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4790.9</v>
+        <v>4810.3</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>75.7</v>
+        <v>121.55</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3391,44 +3391,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J59" s="5" t="n">
-        <v>12.74</v>
+      <c r="J59" s="6" t="n">
+        <v>14.88</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4734.64</v>
+        <v>4715.2</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>$-33.15</t>
+          <t>+$2.34</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4833.6</v>
+        <v>4790.9</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>98.95999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3440,44 +3440,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J60" s="5" t="n">
-        <v>12.08</v>
+      <c r="J60" s="6" t="n">
+        <v>12.74</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4715.83</v>
+        <v>4734.64</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>$-8.63</t>
+          <t>$-33.15</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4834.9</v>
+        <v>4833.6</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>119.07</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3489,8 +3489,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J61" s="5" t="n">
-        <v>11.42</v>
+      <c r="J61" s="6" t="n">
+        <v>12.08</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -3501,32 +3501,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4687.08</v>
+        <v>4715.83</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>+$7.02</t>
+          <t>$-8.63</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4815.5</v>
+        <v>4834.9</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>128.42</v>
+        <v>119.07</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3538,8 +3538,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J62" s="5" t="n">
-        <v>13.66</v>
+      <c r="J62" s="6" t="n">
+        <v>11.42</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -3550,32 +3550,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4690.82</v>
+        <v>4687.08</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>+2.93%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>+$3.16</t>
+          <t>+$7.02</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4798.2</v>
+        <v>4815.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>+2.74%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>107.38</v>
+        <v>128.42</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3587,8 +3587,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J63" s="5" t="n">
-        <v>14.27</v>
+      <c r="J63" s="6" t="n">
+        <v>13.66</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -3599,32 +3599,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4557.42</v>
+        <v>4690.82</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>+0.74%</t>
+          <t>+2.93%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>+$3.16</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4670.1</v>
+        <v>4798.2</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>+2.74%</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>112.68</v>
+        <v>107.38</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3636,8 +3636,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J64" s="5" t="n">
-        <v>14.95</v>
+      <c r="J64" s="6" t="n">
+        <v>14.27</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -3648,32 +3648,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4523.72</v>
+        <v>4557.42</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>+0.74%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>+$18.71</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4635.1</v>
+        <v>4670.1</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>+0.76%</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>111.38</v>
+        <v>112.68</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3685,8 +3685,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J65" s="5" t="n">
-        <v>16.42</v>
+      <c r="J65" s="6" t="n">
+        <v>14.95</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -3697,32 +3697,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4614.08</v>
+        <v>4523.72</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>+$4.06</t>
+          <t>+$18.71</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4747.8</v>
+        <v>4635.1</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-2.37%</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>133.72</v>
+        <v>111.38</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3734,8 +3734,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J66" s="5" t="n">
-        <v>15.85</v>
+      <c r="J66" s="6" t="n">
+        <v>16.42</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -3746,32 +3746,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4621.53</v>
+        <v>4614.08</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>+$1.89</t>
+          <t>+$4.06</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4731.8</v>
+        <v>4747.8</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>110.27</v>
+        <v>133.72</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3783,8 +3783,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J67" s="5" t="n">
-        <v>15.16</v>
+      <c r="J67" s="6" t="n">
+        <v>15.85</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -3795,32 +3795,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4543.37</v>
+        <v>4621.53</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>$-3.14</t>
+          <t>+$1.89</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4661.7</v>
+        <v>4731.8</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>118.33</v>
+        <v>110.27</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3832,8 +3832,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J68" s="5" t="n">
-        <v>15.8</v>
+      <c r="J68" s="6" t="n">
+        <v>15.16</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -3844,32 +3844,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4596.87</v>
+        <v>4543.37</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-3.14</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4709.6</v>
+        <v>4661.7</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>112.73</v>
+        <v>118.33</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3881,8 +3881,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J69" s="5" t="n">
-        <v>15.5</v>
+      <c r="J69" s="6" t="n">
+        <v>15.8</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -3893,32 +3893,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>4681.73</v>
+        <v>4596.87</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>$-12.44</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4797</v>
+        <v>4709.6</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>-0.99%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>115.27</v>
+        <v>112.73</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3930,8 +3930,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J70" s="5" t="n">
-        <v>20.95</v>
+      <c r="J70" s="6" t="n">
+        <v>15.5</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -3942,32 +3942,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4710.12</v>
+        <v>4681.73</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>+$12.00</t>
+          <t>$-12.44</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4844.8</v>
+        <v>4797</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>134.68</v>
+        <v>115.27</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3979,8 +3979,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J71" s="5" t="n">
-        <v>23.3</v>
+      <c r="J71" s="6" t="n">
+        <v>20.95</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -3991,32 +3991,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4694.36</v>
+        <v>4710.12</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>+$4.60</t>
+          <t>+$12.00</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4828.3</v>
+        <v>4844.8</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>133.94</v>
+        <v>134.68</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -4028,8 +4028,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J72" s="5" t="n">
-        <v>25.67</v>
+      <c r="J72" s="6" t="n">
+        <v>23.3</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -4040,32 +4040,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4740.15</v>
+        <v>4694.36</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>$-0.84</t>
+          <t>+$4.60</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4858.2</v>
+        <v>4828.3</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>118.05</v>
+        <v>133.94</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -4077,8 +4077,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J73" s="5" t="n">
-        <v>28.47</v>
+      <c r="J73" s="6" t="n">
+        <v>25.67</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -4089,32 +4089,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>4720.07</v>
+        <v>4740.15</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>-2.09%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>+$0.62</t>
+          <t>$-0.84</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4824.1</v>
+        <v>4858.2</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>-2.26%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>104.03</v>
+        <v>118.05</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="J74" s="6" t="n">
-        <v>30.98</v>
+        <v>28.47</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -4138,32 +4138,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4820.58</v>
+        <v>4720.07</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>$-56.03</t>
+          <t>+$0.62</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4935.4</v>
+        <v>4824.1</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>-1.04%</t>
+          <t>-2.26%</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>114.82</v>
+        <v>104.03</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -4175,8 +4175,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J75" s="6" t="n">
-        <v>32.7</v>
+      <c r="J75" s="3" t="n">
+        <v>30.98</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -4187,32 +4187,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4831.76</v>
+        <v>4820.58</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>+$1.68</t>
+          <t>$-56.03</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4987.3</v>
+        <v>4935.4</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>-1.04%</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>155.54</v>
+        <v>114.82</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -4224,8 +4224,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J76" s="6" t="n">
-        <v>30.87</v>
+      <c r="J76" s="3" t="n">
+        <v>32.7</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -4236,32 +4236,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>4790.65</v>
+        <v>4831.76</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>$-1.72</t>
+          <t>+$1.68</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4916.6</v>
+        <v>4987.3</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>125.95</v>
+        <v>155.54</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -4273,8 +4273,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J77" s="6" t="n">
-        <v>28.9</v>
+      <c r="J77" s="3" t="n">
+        <v>30.87</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -4285,32 +4285,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>4791.81</v>
+        <v>4790.65</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>$-1.72</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4932.6</v>
+        <v>4916.6</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>140.79</v>
+        <v>125.95</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -4322,8 +4322,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J78" s="6" t="n">
-        <v>31.48</v>
+      <c r="J78" s="3" t="n">
+        <v>28.9</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -4334,32 +4334,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>4841.67</v>
+        <v>4791.81</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>+2.09%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>+$1.90</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4960.6</v>
+        <v>4932.6</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>+1.74%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>118.93</v>
+        <v>140.79</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -4371,8 +4371,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J79" s="6" t="n">
-        <v>39.82</v>
+      <c r="J79" s="3" t="n">
+        <v>31.48</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -4383,32 +4383,32 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>4742.69</v>
+        <v>4841.67</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+2.09%</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>$-109.35</t>
+          <t>+$1.90</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4876</v>
+        <v>4960.6</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+1.74%</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>133.31</v>
+        <v>118.93</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -4420,8 +4420,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J80" s="6" t="n">
-        <v>45.25</v>
+      <c r="J80" s="3" t="n">
+        <v>39.82</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -4432,32 +4432,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4749.28</v>
+        <v>4742.69</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>$-1.84</t>
+          <t>$-109.35</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4896.4</v>
+        <v>4876</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>147.12</v>
+        <v>133.31</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -4469,8 +4469,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J81" s="6" t="n">
-        <v>50.95</v>
+      <c r="J81" s="3" t="n">
+        <v>45.25</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -4481,32 +4481,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>4764.17</v>
+        <v>4749.28</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>+$0.36</t>
+          <t>$-1.84</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4928.3</v>
+        <v>4896.4</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>164.13</v>
+        <v>147.12</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -4518,8 +4518,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J82" s="6" t="n">
-        <v>59.04</v>
+      <c r="J82" s="3" t="n">
+        <v>50.95</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -4530,32 +4530,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4719.81</v>
+        <v>4764.17</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>+$19.77</t>
+          <t>+$0.36</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4885.4</v>
+        <v>4928.3</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>+2.02%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>165.59</v>
+        <v>164.13</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -4567,8 +4567,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J83" s="6" t="n">
-        <v>68.06</v>
+      <c r="J83" s="3" t="n">
+        <v>59.04</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -4579,32 +4579,32 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>4702.05</v>
+        <v>4719.81</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>+$1.79</t>
+          <t>+$19.77</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4788.9</v>
+        <v>4885.4</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+2.02%</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>86.84999999999999</v>
+        <v>165.59</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -4616,8 +4616,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J84" s="6" t="n">
-        <v>67.61</v>
+      <c r="J84" s="3" t="n">
+        <v>68.06</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -4628,20 +4628,20 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4649.73</v>
+        <v>4702.05</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>$-3.57</t>
+          <t>+$1.79</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -4649,11 +4649,11 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>139.17</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -4665,8 +4665,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J85" s="6" t="n">
-        <v>64.22</v>
+      <c r="J85" s="3" t="n">
+        <v>67.61</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -4677,32 +4677,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4678.89</v>
+        <v>4649.73</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>$-0.67</t>
+          <t>$-3.57</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4784.1</v>
+        <v>4788.9</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>-2.74%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>105.21</v>
+        <v>139.17</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4714,8 +4714,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J86" s="6" t="n">
-        <v>65.06999999999999</v>
+      <c r="J86" s="3" t="n">
+        <v>64.22</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -4726,32 +4726,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>4758.74</v>
+        <v>4678.89</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>+$2.49</t>
+          <t>$-0.67</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4919.1</v>
+        <v>4784.1</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>+2.91%</t>
+          <t>-2.74%</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>160.36</v>
+        <v>105.21</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4763,8 +4763,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J87" s="6" t="n">
-        <v>61.51</v>
+      <c r="J87" s="3" t="n">
+        <v>65.06999999999999</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -4775,32 +4775,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>4668.9</v>
+        <v>4758.74</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>+3.50%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>+$2.18</t>
+          <t>+$2.49</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4780.2</v>
+        <v>4919.1</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>+2.64%</t>
+          <t>+2.91%</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>111.3</v>
+        <v>160.36</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4812,8 +4812,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J88" s="6" t="n">
-        <v>61.02</v>
+      <c r="J88" s="3" t="n">
+        <v>61.51</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -4824,32 +4824,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>4511.22</v>
+        <v>4668.9</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+3.50%</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>$-0.71</t>
+          <t>+$2.18</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4657.4</v>
+        <v>4780.2</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+2.64%</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>146.18</v>
+        <v>111.3</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4861,8 +4861,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J89" s="6" t="n">
-        <v>61.83</v>
+      <c r="J89" s="3" t="n">
+        <v>61.02</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -4873,32 +4873,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>4493.8</v>
+        <v>4511.22</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>+$12.74</t>
+          <t>$-0.71</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4624.8</v>
+        <v>4657.4</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>+2.62%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>131</v>
+        <v>146.18</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4910,8 +4910,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J90" s="6" t="n">
-        <v>66.98999999999999</v>
+      <c r="J90" s="3" t="n">
+        <v>61.83</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -4922,32 +4922,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>4377.64</v>
+        <v>4493.8</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>+$5.15</t>
+          <t>+$12.74</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4506.7</v>
+        <v>4624.8</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>-3.82%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>129.06</v>
+        <v>131</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4959,8 +4959,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J91" s="6" t="n">
-        <v>68.39</v>
+      <c r="J91" s="3" t="n">
+        <v>66.98999999999999</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -4971,32 +4971,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>4505.69</v>
+        <v>4377.64</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>$-19.39</t>
+          <t>+$5.15</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4685.7</v>
+        <v>4506.7</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>+3.37%</t>
+          <t>-3.82%</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>180.01</v>
+        <v>129.06</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -5008,8 +5008,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J92" s="6" t="n">
-        <v>65.34999999999999</v>
+      <c r="J92" s="3" t="n">
+        <v>68.39</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -5020,32 +5020,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>4491.37</v>
+        <v>4505.69</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>+$6.43</t>
+          <t>$-19.39</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4532.8</v>
+        <v>4685.7</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+3.37%</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>41.43</v>
+        <v>180.01</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -5057,44 +5057,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J93" s="6" t="n">
-        <v>55.61</v>
+      <c r="J93" s="3" t="n">
+        <v>65.34999999999999</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>4407.46</v>
+        <v>4491.37</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>$-41.67</t>
+          <t>+$6.43</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4539.3</v>
+        <v>4532.8</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>131.84</v>
+        <v>41.43</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -5106,44 +5106,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J94" s="6" t="n">
-        <v>52.06</v>
+      <c r="J94" s="3" t="n">
+        <v>55.61</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>4490.66</v>
+        <v>4407.46</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>-3.43%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>+$0.88</t>
+          <t>$-41.67</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4716.2</v>
+        <v>4539.3</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>-3.75%</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>225.54</v>
+        <v>131.84</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -5155,8 +5155,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J95" s="6" t="n">
-        <v>48.26</v>
+      <c r="J95" s="3" t="n">
+        <v>52.06</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -5167,32 +5167,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>4650.11</v>
+        <v>4490.66</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>-3.50%</t>
+          <t>-3.43%</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>+$5.66</t>
+          <t>+$0.88</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4745.4</v>
+        <v>4716.2</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>-5.88%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>95.29000000000001</v>
+        <v>225.54</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -5204,8 +5204,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J96" s="6" t="n">
-        <v>40.68</v>
+      <c r="J96" s="3" t="n">
+        <v>48.26</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -5216,32 +5216,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>4818.71</v>
+        <v>4650.11</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>-3.74%</t>
+          <t>-3.50%</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>$-0.26</t>
+          <t>+$5.66</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5041.7</v>
+        <v>4745.4</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>-2.23%</t>
+          <t>-5.88%</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>222.99</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -5253,8 +5253,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J97" s="6" t="n">
-        <v>34.38</v>
+      <c r="J97" s="3" t="n">
+        <v>40.68</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -5265,32 +5265,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>5006.14</v>
+        <v>4818.71</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-3.74%</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>+$3.07</t>
+          <t>$-0.26</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5156.7</v>
+        <v>5041.7</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-2.23%</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>150.56</v>
+        <v>222.99</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -5302,8 +5302,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J98" s="6" t="n">
-        <v>33</v>
+      <c r="J98" s="3" t="n">
+        <v>34.38</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -5314,32 +5314,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>5004.67</v>
+        <v>5006.14</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>$-13.14</t>
+          <t>+$3.07</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5150.3</v>
+        <v>5156.7</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>145.63</v>
+        <v>150.56</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -5351,8 +5351,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J99" s="6" t="n">
-        <v>34.78</v>
+      <c r="J99" s="3" t="n">
+        <v>33</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -5363,32 +5363,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>5019</v>
+        <v>5004.67</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>+$0.70</t>
+          <t>$-13.14</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5210.4</v>
+        <v>5150.3</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>-1.25%</t>
+          <t>-1.15%</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>191.4</v>
+        <v>145.63</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -5400,8 +5400,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J100" s="6" t="n">
-        <v>34.04</v>
+      <c r="J100" s="3" t="n">
+        <v>34.78</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -5412,32 +5412,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>5079.6</v>
+        <v>5019</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>+$2.23</t>
+          <t>+$0.70</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5276.4</v>
+        <v>5210.4</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>-1.25%</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>196.8</v>
+        <v>191.4</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -5449,8 +5449,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J101" s="6" t="n">
-        <v>35.66</v>
+      <c r="J101" s="3" t="n">
+        <v>34.04</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -5461,32 +5461,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>5176.23</v>
+        <v>5079.6</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>$-3.94</t>
+          <t>+$2.23</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5330.9</v>
+        <v>5276.4</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>154.67</v>
+        <v>196.8</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -5498,8 +5498,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J102" s="6" t="n">
-        <v>34.34</v>
+      <c r="J102" s="3" t="n">
+        <v>35.66</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -5510,32 +5510,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>5191.58</v>
+        <v>5176.23</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>+$0.98</t>
+          <t>$-3.94</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5392.5</v>
+        <v>5330.9</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>200.92</v>
+        <v>154.67</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -5547,8 +5547,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J103" s="6" t="n">
-        <v>33.19</v>
+      <c r="J103" s="3" t="n">
+        <v>34.34</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -5559,32 +5559,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>5138.45</v>
+        <v>5191.58</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>+$8.38</t>
+          <t>+$0.98</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5251.9</v>
+        <v>5392.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>113.45</v>
+        <v>200.92</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -5596,8 +5596,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J104" s="5" t="n">
-        <v>27.57</v>
+      <c r="J104" s="3" t="n">
+        <v>33.19</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -5608,32 +5608,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>5171.8</v>
+        <v>5138.45</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>+$1.60</t>
+          <t>+$8.38</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5306.8</v>
+        <v>5251.9</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>135</v>
+        <v>113.45</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -5645,8 +5645,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J105" s="5" t="n">
-        <v>27.41</v>
+      <c r="J105" s="6" t="n">
+        <v>27.57</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -5657,32 +5657,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>5082.25</v>
+        <v>5171.8</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>+$15.58</t>
+          <t>+$1.60</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5225.6</v>
+        <v>5306.8</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>143.35</v>
+        <v>135</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -5694,8 +5694,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J106" s="5" t="n">
-        <v>28.59</v>
+      <c r="J106" s="6" t="n">
+        <v>27.41</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -5706,32 +5706,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>5140.39</v>
+        <v>5082.25</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>+$15.99</t>
+          <t>+$15.58</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5281.6</v>
+        <v>5225.6</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-1.06%</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>141.21</v>
+        <v>143.35</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="J107" s="6" t="n">
-        <v>29.02</v>
+        <v>28.59</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -5755,32 +5755,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>5087.78</v>
+        <v>5140.39</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>-4.39%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>+$3.27</t>
+          <t>+$15.99</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5269.7</v>
+        <v>5281.6</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>-3.53%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>181.92</v>
+        <v>141.21</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -5792,8 +5792,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J108" s="5" t="n">
-        <v>26.89</v>
+      <c r="J108" s="3" t="n">
+        <v>29.02</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -5804,32 +5804,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>5321.3</v>
+        <v>5087.78</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>+0.80%</t>
+          <t>-4.39%</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>+$22.33</t>
+          <t>+$3.27</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5462.6</v>
+        <v>5269.7</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-3.53%</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>141.3</v>
+        <v>181.92</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -5841,8 +5841,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J109" s="5" t="n">
-        <v>25</v>
+      <c r="J109" s="6" t="n">
+        <v>26.89</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -5853,32 +5853,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>5278.9</v>
+        <v>5321.3</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>+1.83%</t>
+          <t>+0.80%</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>+$3.50</t>
+          <t>+$22.33</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5396.2</v>
+        <v>5462.6</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>117.3</v>
+        <v>141.3</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5890,8 +5890,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J110" s="5" t="n">
-        <v>23.93</v>
+      <c r="J110" s="6" t="n">
+        <v>25</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -5902,32 +5902,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>5184.25</v>
+        <v>5278.9</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+1.83%</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>$-2.63</t>
+          <t>+$3.50</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5341.1</v>
+        <v>5396.2</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>156.85</v>
+        <v>117.3</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5939,8 +5939,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J111" s="5" t="n">
-        <v>27.52</v>
+      <c r="J111" s="6" t="n">
+        <v>23.93</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -5951,32 +5951,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>5164.29</v>
+        <v>5184.25</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>+$0.50</t>
+          <t>$-2.63</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5374.2</v>
+        <v>5341.1</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>209.91</v>
+        <v>156.85</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="J112" s="6" t="n">
-        <v>32.13</v>
+        <v>27.52</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -6000,32 +6000,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>5142.79</v>
+        <v>5164.29</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>-1.62%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>+$2.64</t>
+          <t>+$0.50</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5322.8</v>
+        <v>5374.2</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>180.01</v>
+        <v>209.91</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -6037,8 +6037,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J113" s="6" t="n">
-        <v>30.2</v>
+      <c r="J113" s="3" t="n">
+        <v>32.13</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -6049,32 +6049,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>5227.48</v>
+        <v>5142.79</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>+2.36%</t>
+          <t>-1.62%</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>+$2.32</t>
+          <t>+$2.64</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5372</v>
+        <v>5322.8</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>144.52</v>
+        <v>180.01</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -6086,8 +6086,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J114" s="5" t="n">
-        <v>28.13</v>
+      <c r="J114" s="3" t="n">
+        <v>30.2</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -6098,32 +6098,32 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>5106.96</v>
+        <v>5227.48</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>+2.22%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>+$2.74</t>
+          <t>+$2.32</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5223.4</v>
+        <v>5372</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>+1.70%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>116.44</v>
+        <v>144.52</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="J115" s="6" t="n">
-        <v>35.59</v>
+        <v>28.13</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -6147,32 +6147,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>4996.02</v>
+        <v>5106.96</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+2.22%</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>$-2.27</t>
+          <t>+$2.74</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5136.1</v>
+        <v>5223.4</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+1.70%</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>140.08</v>
+        <v>116.44</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -6184,8 +6184,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J116" s="6" t="n">
-        <v>44.31</v>
+      <c r="J116" s="3" t="n">
+        <v>35.59</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -6196,32 +6196,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>4977.18</v>
+        <v>4996.02</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>+2.03%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>+$1.09</t>
+          <t>$-2.27</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5147.3</v>
+        <v>5136.1</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>170.12</v>
+        <v>140.08</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -6233,8 +6233,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J117" s="6" t="n">
-        <v>46.23</v>
+      <c r="J117" s="3" t="n">
+        <v>44.31</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -6245,32 +6245,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>4878.1</v>
+        <v>4977.18</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>-3.25%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>$-45.72</t>
+          <t>+$1.09</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5039.4</v>
+        <v>5147.3</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>-2.79%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>161.3</v>
+        <v>170.12</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -6282,8 +6282,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J118" s="6" t="n">
-        <v>46.39</v>
+      <c r="J118" s="3" t="n">
+        <v>46.23</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -6294,32 +6294,32 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>5041.86</v>
+        <v>4878.1</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>+2.44%</t>
+          <t>-3.25%</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>+$4.32</t>
+          <t>$-45.72</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5183.8</v>
+        <v>5039.4</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>+1.87%</t>
+          <t>-2.79%</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>141.94</v>
+        <v>161.3</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -6331,8 +6331,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J119" s="6" t="n">
-        <v>57.41</v>
+      <c r="J119" s="3" t="n">
+        <v>46.39</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -6343,32 +6343,32 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>4921.59</v>
+        <v>5041.86</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>-3.19%</t>
+          <t>+2.44%</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>+$1.40</t>
+          <t>+$4.32</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5088.4</v>
+        <v>5183.8</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>-2.94%</t>
+          <t>+1.87%</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>166.81</v>
+        <v>141.94</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -6380,8 +6380,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J120" s="6" t="n">
-        <v>62.1</v>
+      <c r="J120" s="3" t="n">
+        <v>57.41</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -6392,32 +6392,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>5083.84</v>
+        <v>4921.59</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>+1.18%</t>
+          <t>-3.19%</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>+$2.13</t>
+          <t>+$1.40</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5242.5</v>
+        <v>5088.4</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-2.94%</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>158.66</v>
+        <v>166.81</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -6429,8 +6429,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J121" s="6" t="n">
-        <v>63</v>
+      <c r="J121" s="3" t="n">
+        <v>62.1</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -6441,32 +6441,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>5024.38</v>
+        <v>5083.84</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>+1.18%</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>$-0.65</t>
+          <t>+$2.13</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5172.2</v>
+        <v>5242.5</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>147.82</v>
+        <v>158.66</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -6478,8 +6478,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J122" s="6" t="n">
-        <v>64.01000000000001</v>
+      <c r="J122" s="3" t="n">
+        <v>63</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -6490,32 +6490,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>5060.14</v>
+        <v>5024.38</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>+1.88%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>+$17.25</t>
+          <t>$-0.65</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5222.1</v>
+        <v>5172.2</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>+2.00%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>161.96</v>
+        <v>147.82</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -6527,8 +6527,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J123" s="6" t="n">
-        <v>63.42</v>
+      <c r="J123" s="3" t="n">
+        <v>64.01000000000001</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -6539,32 +6539,32 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>4966.93</v>
+        <v>5060.14</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>+3.92%</t>
+          <t>+1.88%</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>+$12.55</t>
+          <t>+$17.25</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5119.8</v>
+        <v>5222.1</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>+1.94%</t>
+          <t>+2.00%</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>152.87</v>
+        <v>161.96</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -6576,8 +6576,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J124" s="6" t="n">
-        <v>63.27</v>
+      <c r="J124" s="3" t="n">
+        <v>63.42</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -6588,32 +6588,32 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>4779.63</v>
+        <v>4966.93</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>-3.71%</t>
+          <t>+3.92%</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>+$12.00</t>
+          <t>+$12.55</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5022.3</v>
+        <v>5119.8</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>+1.94%</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>242.67</v>
+        <v>152.87</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -6625,8 +6625,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J125" s="6" t="n">
-        <v>57.48</v>
+      <c r="J125" s="3" t="n">
+        <v>63.27</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -6637,32 +6637,32 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>4963.89</v>
+        <v>4779.63</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-3.71%</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>+$1.30</t>
+          <t>+$12.00</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5089</v>
+        <v>5022.3</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>125.11</v>
+        <v>242.67</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -6674,8 +6674,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J126" s="6" t="n">
-        <v>49.25</v>
+      <c r="J126" s="3" t="n">
+        <v>57.48</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -6686,32 +6686,32 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>4944.42</v>
+        <v>4963.89</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>+6.13%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>+$13.04</t>
+          <t>+$1.30</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5072.5</v>
+        <v>5089</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>+6.11%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>128.08</v>
+        <v>125.11</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -6723,8 +6723,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J127" s="6" t="n">
-        <v>49.09</v>
+      <c r="J127" s="3" t="n">
+        <v>49.25</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -6735,32 +6735,32 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>4658.73</v>
+        <v>4944.42</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>-4.75%</t>
+          <t>+6.13%</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>$-76.67</t>
+          <t>+$13.04</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4780.4</v>
+        <v>5072.5</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>+6.11%</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>121.67</v>
+        <v>128.08</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -6772,8 +6772,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J128" s="6" t="n">
-        <v>48.95</v>
+      <c r="J128" s="3" t="n">
+        <v>49.09</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -6784,36 +6784,36 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>4890.97</v>
+        <v>4658.73</v>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>-8.99%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>+$8.73</t>
+          <t>$-76.67</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4880</v>
+        <v>4780.4</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>-11.41%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>-10.97</v>
-      </c>
-      <c r="H129" s="7" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>121.67</v>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -6821,48 +6821,48 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J129" s="6" t="n">
-        <v>41.41</v>
+      <c r="J129" s="3" t="n">
+        <v>48.95</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>5373.91</v>
+        <v>4890.97</v>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-8.99%</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>+$5.87</t>
+          <t>+$8.73</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5508.6</v>
+        <v>4880</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-11.41%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>134.69</v>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-10.97</v>
+      </c>
+      <c r="H130" s="7" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
@@ -6870,44 +6870,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J130" s="6" t="n">
-        <v>31.72</v>
+      <c r="J130" s="3" t="n">
+        <v>41.41</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>5416.79</v>
+        <v>5373.91</v>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>+4.60%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>+$5.87</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5494.6</v>
+        <v>5508.6</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>+4.32%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>77.81</v>
+        <v>134.69</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -6919,8 +6919,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J131" s="6" t="n">
-        <v>29.24</v>
+      <c r="J131" s="3" t="n">
+        <v>31.72</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -6931,32 +6931,32 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>5178.46</v>
+        <v>5416.79</v>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>+3.36%</t>
+          <t>+4.60%</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>+$3.14</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5267.3</v>
+        <v>5494.6</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+4.32%</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>88.84</v>
+        <v>77.81</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -6968,8 +6968,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J132" s="5" t="n">
-        <v>28.65</v>
+      <c r="J132" s="3" t="n">
+        <v>29.24</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -6980,32 +6980,32 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>5010.31</v>
+        <v>5178.46</v>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+3.36%</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>+$20.73</t>
+          <t>+$3.14</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5272.8</v>
+        <v>5267.3</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>262.49</v>
+        <v>88.84</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -7017,8 +7017,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J133" s="5" t="n">
-        <v>16.43</v>
+      <c r="J133" s="6" t="n">
+        <v>28.65</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -7029,32 +7029,32 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>4988.56</v>
+        <v>5010.31</v>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>+1.07%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>+$5.34</t>
+          <t>+$20.73</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5160.4</v>
+        <v>5272.8</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+2.18%</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>171.84</v>
+        <v>262.49</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -7066,8 +7066,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J134" s="5" t="n">
-        <v>10.44</v>
+      <c r="J134" s="6" t="n">
+        <v>16.43</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -7078,32 +7078,32 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>4935.8</v>
+        <v>4988.56</v>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>+$0.94</t>
+          <t>+$5.34</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5086.9</v>
+        <v>5160.4</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>+1.59%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>151.1</v>
+        <v>171.84</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -7115,8 +7115,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J135" s="5" t="n">
-        <v>8.960000000000001</v>
+      <c r="J135" s="6" t="n">
+        <v>10.44</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -7127,32 +7127,32 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>4831.51</v>
+        <v>4935.8</v>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+2.16%</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>+$0.31</t>
+          <t>+$0.94</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5007.5</v>
+        <v>5086.9</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>+1.51%</t>
+          <t>+1.59%</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>175.99</v>
+        <v>151.1</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -7164,7 +7164,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J136" s="2" t="inlineStr"/>
+      <c r="J136" s="6" t="n">
+        <v>8.960000000000001</v>
+      </c>
       <c r="K136" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -7174,32 +7176,32 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>4762.99</v>
+        <v>4831.51</v>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>+3.63%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>+$75.81</t>
+          <t>+$0.31</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4933</v>
+        <v>5007.5</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>+3.65%</t>
+          <t>+1.51%</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>170.01</v>
+        <v>175.99</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -7221,32 +7223,32 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>4596.18</v>
+        <v>4762.99</v>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+3.63%</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>+$1.80</t>
+          <t>+$75.81</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4759.2</v>
+        <v>4933</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>+3.65%</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>163.02</v>
+        <v>170.01</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -7268,32 +7270,32 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>4615.95</v>
+        <v>4596.18</v>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>+$6.28</t>
+          <t>+$1.80</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4787.7</v>
+        <v>4759.2</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>171.75</v>
+        <v>163.02</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -7315,32 +7317,32 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>4624.8</v>
+        <v>4615.95</v>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>+$3.59</t>
+          <t>+$6.28</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4798.9</v>
+        <v>4787.7</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>174.1</v>
+        <v>171.75</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -7362,32 +7364,32 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>4585.44</v>
+        <v>4624.8</v>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>+$5.33</t>
+          <t>+$3.59</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4760.2</v>
+        <v>4798.9</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>174.76</v>
+        <v>174.1</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -7409,32 +7411,32 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>4598.46</v>
+        <v>4585.44</v>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>+1.98%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>+$9.47</t>
+          <t>+$5.33</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4777.7</v>
+        <v>4760.2</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>+2.49%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>179.24</v>
+        <v>174.76</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -7456,32 +7458,32 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>4509.27</v>
+        <v>4598.46</v>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>+$1.86</t>
+          <t>+$9.47</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4661.4</v>
+        <v>4777.7</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>+0.90%</t>
+          <t>+2.49%</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>152.13</v>
+        <v>179.24</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -7503,32 +7505,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>4477.84</v>
+        <v>4509.27</v>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>$-0.03</t>
+          <t>+$1.86</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4620</v>
+        <v>4661.4</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.90%</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>142.16</v>
+        <v>152.13</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -7550,32 +7552,32 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>4456.26</v>
+        <v>4477.84</v>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>+$0.08</t>
+          <t>$-0.03</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4620.6</v>
+        <v>4620</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>-0.76%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>164.34</v>
+        <v>142.16</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -7597,32 +7599,32 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>4494.61</v>
+        <v>4456.26</v>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.85%</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>$-0.07</t>
+          <t>+$0.08</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4656.2</v>
+        <v>4620.6</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>-0.76%</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>161.59</v>
+        <v>164.34</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -7644,32 +7646,32 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>4449.11</v>
+        <v>4494.61</v>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>+2.70%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>+$28.96</t>
+          <t>$-0.07</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4608.1</v>
+        <v>4656.2</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>+2.76%</t>
+          <t>+1.04%</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>158.99</v>
+        <v>161.59</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -7691,32 +7693,32 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>4332.17</v>
+        <v>4449.11</v>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.70%</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+$28.96</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4484.4</v>
+        <v>4608.1</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.76%</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>152.23</v>
+        <v>158.99</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -7730,6 +7732,53 @@
       </c>
       <c r="J148" s="2" t="inlineStr"/>
       <c r="K148" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>4332.17</v>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>4484.4</v>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>152.23</v>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K149"/>
+  <dimension ref="A1:K150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -561,32 +561,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4273.01</v>
+        <v>4341.84</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+4.29%</t>
+          <t>+1.61%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$151.16</t>
+          <t>$-34.98</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4298.3</v>
+        <v>4399.7</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>25.29</v>
+        <v>57.86</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>41.84</v>
+        <v>43.2</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -610,130 +610,130 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4097.29</v>
+        <v>4273.01</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>+4.29%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$22.75</t>
+          <t>+$151.16</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4339</v>
+        <v>4298.3</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+4.39%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>241.71</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="n">
-        <v>28.06</v>
+        <v>25.29</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>41.84</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4055.15</v>
+        <v>4097.29</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+1.04%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$33.39</t>
+          <t>+$22.75</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4156.4</v>
+        <v>4339</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>+4.39%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>101.25</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>241.71</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J4" s="6" t="n">
-        <v>19.9</v>
+        <v>28.06</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4044.36</v>
+        <v>4055.15</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$33.39</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4110.9</v>
+        <v>4156.4</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>66.54000000000001</v>
+        <v>101.25</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>18.29</v>
+        <v>19.9</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -757,32 +757,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4103.64</v>
+        <v>4044.36</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$0.17</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4160.6</v>
+        <v>4110.9</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>56.96</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>18.21</v>
+        <v>18.29</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -806,32 +806,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4066.23</v>
+        <v>4103.64</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$1.59</t>
+          <t>+$0.17</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4097</v>
+        <v>4160.6</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>30.77</v>
+        <v>56.96</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="J7" s="6" t="n">
-        <v>18.03</v>
+        <v>18.21</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -855,32 +855,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4028.54</v>
+        <v>4066.23</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$2.81</t>
+          <t>+$1.59</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4098.6</v>
+        <v>4097</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>70.06</v>
+        <v>30.77</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="J8" s="6" t="n">
-        <v>16.18</v>
+        <v>18.03</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -904,32 +904,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4076.6</v>
+        <v>4028.54</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$43.44</t>
+          <t>+$2.81</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4136.4</v>
+        <v>4098.6</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>59.8</v>
+        <v>70.06</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="J9" s="6" t="n">
-        <v>18.87</v>
+        <v>16.18</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -953,32 +953,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4052.74</v>
+        <v>4076.6</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$0.61</t>
+          <t>+$43.44</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4129.7</v>
+        <v>4136.4</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>76.95999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="J10" s="6" t="n">
-        <v>21.15</v>
+        <v>18.87</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1002,32 +1002,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4049.43</v>
+        <v>4052.74</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>$-10.76</t>
+          <t>+$0.61</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4108.8</v>
+        <v>4129.7</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>59.37</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="J11" s="6" t="n">
-        <v>19.94</v>
+        <v>21.15</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1051,32 +1051,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4130.11</v>
+        <v>4049.43</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$1.94</t>
+          <t>$-10.76</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4210.3</v>
+        <v>4108.8</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+1.84%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>80.19</v>
+        <v>59.37</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="J12" s="6" t="n">
-        <v>21.96</v>
+        <v>19.94</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1100,32 +1100,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4077.87</v>
+        <v>4130.11</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$1.94</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4134.2</v>
+        <v>4210.3</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+1.84%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>56.33</v>
+        <v>80.19</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="J13" s="6" t="n">
-        <v>21.74</v>
+        <v>21.96</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1149,32 +1149,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4007.49</v>
+        <v>4077.87</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-12.24</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4073</v>
+        <v>4134.2</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>65.51000000000001</v>
+        <v>56.33</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="J14" s="6" t="n">
-        <v>21.72</v>
+        <v>21.74</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1198,32 +1198,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4017.04</v>
+        <v>4007.49</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$1.19</t>
+          <t>$-12.24</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4075.8</v>
+        <v>4073</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>58.76</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="J15" s="6" t="n">
-        <v>22.33</v>
+        <v>21.72</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1247,32 +1247,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3976.48</v>
+        <v>4017.04</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$4.31</t>
+          <t>+$1.19</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4048.7</v>
+        <v>4075.8</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>72.22</v>
+        <v>58.76</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>22.36</v>
+        <v>22.33</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1296,32 +1296,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4060.55</v>
+        <v>3976.48</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$0.46</t>
+          <t>+$4.31</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4109.3</v>
+        <v>4048.7</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>48.75</v>
+        <v>72.22</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="J17" s="6" t="n">
-        <v>21.54</v>
+        <v>22.36</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1345,32 +1345,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4052.92</v>
+        <v>4060.55</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$5.21</t>
+          <t>+$0.46</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4127.9</v>
+        <v>4109.3</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+1.58%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>74.98</v>
+        <v>48.75</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="J18" s="6" t="n">
-        <v>21.93</v>
+        <v>21.54</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1394,32 +1394,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4000.78</v>
+        <v>4052.92</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$5.21</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4063.6</v>
+        <v>4127.9</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>+1.58%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>62.82</v>
+        <v>74.98</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="J19" s="6" t="n">
-        <v>22.96</v>
+        <v>21.93</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1443,32 +1443,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4119.29</v>
+        <v>4000.78</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4173.6</v>
+        <v>4063.6</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>54.31</v>
+        <v>62.82</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="J20" s="6" t="n">
-        <v>24.16</v>
+        <v>22.96</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1492,32 +1492,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4123.38</v>
+        <v>4119.29</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4201.4</v>
+        <v>4173.6</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+1.43%</t>
+          <t>-0.66%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>78.02</v>
+        <v>54.31</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="J21" s="6" t="n">
-        <v>28.73</v>
+        <v>24.16</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1541,32 +1541,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4077.4</v>
+        <v>4123.38</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4142.1</v>
+        <v>4201.4</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>+1.43%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>64.7</v>
+        <v>78.02</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1578,8 +1578,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J22" s="3" t="n">
-        <v>34.99</v>
+      <c r="J22" s="6" t="n">
+        <v>28.73</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1590,32 +1590,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4105.67</v>
+        <v>4077.4</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4218.3</v>
+        <v>4142.1</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>112.63</v>
+        <v>64.7</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>32.93</v>
+        <v>34.99</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1639,32 +1639,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4165.04</v>
+        <v>4105.67</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4228.6</v>
+        <v>4218.3</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>63.56</v>
+        <v>112.63</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>31.11</v>
+        <v>32.93</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1688,32 +1688,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4123.77</v>
+        <v>4165.04</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4186.6</v>
+        <v>4228.6</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>62.83</v>
+        <v>63.56</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>39.51</v>
+        <v>31.11</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1737,32 +1737,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4031.01</v>
+        <v>4123.77</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4142.9</v>
+        <v>4186.6</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>111.89</v>
+        <v>62.83</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>47.43</v>
+        <v>39.51</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1786,32 +1786,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4007.41</v>
+        <v>4031.01</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4098.5</v>
+        <v>4142.9</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>91.09</v>
+        <v>111.89</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>48.29</v>
+        <v>47.43</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1835,32 +1835,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4016.54</v>
+        <v>4007.41</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4098.8</v>
+        <v>4098.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>82.26000000000001</v>
+        <v>91.09</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>48.18</v>
+        <v>48.29</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1884,32 +1884,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4089.95</v>
+        <v>4016.54</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4156.9</v>
+        <v>4098.8</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>66.95</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>47.32</v>
+        <v>48.18</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1933,32 +1933,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4026.57</v>
+        <v>4089.95</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4107.5</v>
+        <v>4156.9</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>80.93000000000001</v>
+        <v>66.95</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>46.73</v>
+        <v>47.32</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1982,32 +1982,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3999.06</v>
+        <v>4026.57</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4068.1</v>
+        <v>4107.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3.39%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>69.04000000000001</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>46.06</v>
+        <v>46.73</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2031,32 +2031,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4110.14</v>
+        <v>3999.06</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4210.9</v>
+        <v>4068.1</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-3.39%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>100.76</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>43.81</v>
+        <v>46.06</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2080,32 +2080,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4191.26</v>
+        <v>4110.14</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4265.4</v>
+        <v>4210.9</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>74.14</v>
+        <v>100.76</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>42.64</v>
+        <v>43.81</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2129,32 +2129,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4209.02</v>
+        <v>4191.26</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4308.5</v>
+        <v>4265.4</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>99.48</v>
+        <v>74.14</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>43.1</v>
+        <v>42.64</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2178,130 +2178,130 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4257.71</v>
+        <v>4209.02</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4444.8</v>
+        <v>4308.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>-3.07%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>187.09</v>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
+        <v>99.48</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
         </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>38.11</v>
+        <v>43.1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4331.14</v>
+        <v>4257.71</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$7.23</t>
+          <t>+$1.76</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4417.3</v>
+        <v>4444.8</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>86.16</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>187.09</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>31.79</v>
+        <v>38.11</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4309.03</v>
+        <v>4331.14</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$52.77</t>
+          <t>+$7.23</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4414.3</v>
+        <v>4417.3</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>105.27</v>
+        <v>86.16</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="J37" s="3" t="n">
-        <v>30.77</v>
+        <v>31.79</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2325,32 +2325,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4218.71</v>
+        <v>4309.03</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>$-1.08</t>
+          <t>+$52.77</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4300.4</v>
+        <v>4414.3</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>81.69</v>
+        <v>105.27</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="J38" s="3" t="n">
-        <v>30.55</v>
+        <v>30.77</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2374,36 +2374,36 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4210.69</v>
+        <v>4218.71</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$10.16</t>
+          <t>$-1.08</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4174</v>
+        <v>4300.4</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+3.03%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>-36.69</v>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>81.69</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2411,48 +2411,48 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J39" s="6" t="n">
-        <v>23.08</v>
+      <c r="J39" s="3" t="n">
+        <v>30.55</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4071.28</v>
+        <v>4210.69</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$-5.95</t>
+          <t>+$10.16</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4194.5</v>
+        <v>4174</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>-3.57%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>123.22</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-36.69</v>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2461,43 +2461,43 @@
         </is>
       </c>
       <c r="J40" s="6" t="n">
-        <v>12.35</v>
+        <v>23.08</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4259.29</v>
+        <v>4071.28</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-4.41%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-5.95</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4349.6</v>
+        <v>4194.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>-3.57%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>90.31</v>
+        <v>123.22</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="J41" s="6" t="n">
-        <v>12.67</v>
+        <v>12.35</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2521,32 +2521,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4329.75</v>
+        <v>4259.29</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>$-2.37</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4427.3</v>
+        <v>4349.6</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>97.55</v>
+        <v>90.31</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="J42" s="6" t="n">
-        <v>14.73</v>
+        <v>12.67</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2570,32 +2570,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4328.15</v>
+        <v>4329.75</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>-3.29%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$7.90</t>
+          <t>$-2.37</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4429</v>
+        <v>4427.3</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>100.85</v>
+        <v>97.55</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="J43" s="6" t="n">
-        <v>16.65</v>
+        <v>14.73</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2619,32 +2619,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4475.25</v>
+        <v>4328.15</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-3.29%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$7.80</t>
+          <t>+$7.90</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4570.4</v>
+        <v>4429</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>95.15000000000001</v>
+        <v>100.85</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="J44" s="6" t="n">
-        <v>17.2</v>
+        <v>16.65</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2668,32 +2668,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4434.3</v>
+        <v>4475.25</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$3.39</t>
+          <t>+$7.80</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4532</v>
+        <v>4570.4</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>97.7</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="J45" s="6" t="n">
-        <v>18.03</v>
+        <v>17.2</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2717,32 +2717,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4487.78</v>
+        <v>4434.3</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>$-3.86</t>
+          <t>+$3.39</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4585.6</v>
+        <v>4532</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>97.81999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="J46" s="6" t="n">
-        <v>21.29</v>
+        <v>18.03</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2766,32 +2766,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4484.69</v>
+        <v>4487.78</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>$-1.44</t>
+          <t>$-3.86</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4572.2</v>
+        <v>4585.6</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>87.51000000000001</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="J47" s="6" t="n">
-        <v>22.22</v>
+        <v>21.29</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2815,32 +2815,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4540.28</v>
+        <v>4484.69</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+$1.89</t>
+          <t>$-1.44</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4659.5</v>
+        <v>4572.2</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>119.22</v>
+        <v>87.51000000000001</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="J48" s="6" t="n">
-        <v>21.39</v>
+        <v>22.22</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2864,32 +2864,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4495.57</v>
+        <v>4540.28</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>$-4.31</t>
+          <t>+$1.89</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4597</v>
+        <v>4659.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>101.43</v>
+        <v>119.22</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="J49" s="6" t="n">
-        <v>20.79</v>
+        <v>21.39</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2913,32 +2913,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4456.15</v>
+        <v>4495.57</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>$-6.52</t>
+          <t>$-4.31</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4545.1</v>
+        <v>4597</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>88.95</v>
+        <v>101.43</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="J50" s="6" t="n">
-        <v>21.4</v>
+        <v>20.79</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2962,32 +2962,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4507.46</v>
+        <v>4456.15</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+$58.22</t>
+          <t>$-6.52</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4601.2</v>
+        <v>4545.1</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>93.73999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="J51" s="6" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -3011,32 +3011,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4509.11</v>
+        <v>4507.46</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>$-1.21</t>
+          <t>+$58.22</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4623.4</v>
+        <v>4601.2</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>114.29</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="J52" s="6" t="n">
-        <v>20.06</v>
+        <v>21.43</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3060,32 +3060,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4543.11</v>
+        <v>4509.11</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.75%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>$-3.76</t>
+          <t>$-1.21</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4643.6</v>
+        <v>4623.4</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>100.49</v>
+        <v>114.29</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="J53" s="6" t="n">
-        <v>20.67</v>
+        <v>20.06</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3109,32 +3109,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4543.62</v>
+        <v>4543.11</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>$-3.76</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4634.4</v>
+        <v>4643.6</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>90.78</v>
+        <v>100.49</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="J54" s="6" t="n">
-        <v>21.65</v>
+        <v>20.67</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3158,32 +3158,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4481.92</v>
+        <v>4543.62</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+$1.98</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4610.1</v>
+        <v>4634.4</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>128.18</v>
+        <v>90.78</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="J55" s="6" t="n">
-        <v>19.55</v>
+        <v>21.65</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3207,32 +3207,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4566.08</v>
+        <v>4481.92</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>$-10.86</t>
+          <t>+$1.98</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4658.2</v>
+        <v>4610.1</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>92.12</v>
+        <v>128.18</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="J56" s="6" t="n">
-        <v>17.38</v>
+        <v>19.55</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3256,32 +3256,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4539.94</v>
+        <v>4566.08</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>+$0.18</t>
+          <t>$-10.86</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4662.2</v>
+        <v>4658.2</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>122.26</v>
+        <v>92.12</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="J57" s="6" t="n">
-        <v>15.41</v>
+        <v>17.38</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -3305,32 +3305,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4652.24</v>
+        <v>4539.94</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$0.18</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4787.9</v>
+        <v>4662.2</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-2.63%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>135.66</v>
+        <v>122.26</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="J58" s="6" t="n">
-        <v>15.84</v>
+        <v>15.41</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -3354,32 +3354,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4688.75</v>
+        <v>4652.24</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>$-3.60</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4810.3</v>
+        <v>4787.9</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>121.55</v>
+        <v>135.66</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="J59" s="6" t="n">
-        <v>14.88</v>
+        <v>15.84</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -3403,32 +3403,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4715.2</v>
+        <v>4688.75</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>+$2.34</t>
+          <t>$-3.60</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4790.9</v>
+        <v>4810.3</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>75.7</v>
+        <v>121.55</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3441,43 +3441,43 @@
         </is>
       </c>
       <c r="J60" s="6" t="n">
-        <v>12.74</v>
+        <v>14.88</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4734.64</v>
+        <v>4715.2</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>$-33.15</t>
+          <t>+$2.34</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4833.6</v>
+        <v>4790.9</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>98.95999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3490,43 +3490,43 @@
         </is>
       </c>
       <c r="J61" s="6" t="n">
-        <v>12.08</v>
+        <v>12.74</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4715.83</v>
+        <v>4734.64</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>$-8.63</t>
+          <t>$-33.15</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4834.9</v>
+        <v>4833.6</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>119.07</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="J62" s="6" t="n">
-        <v>11.42</v>
+        <v>12.08</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -3550,32 +3550,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4687.08</v>
+        <v>4715.83</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>+$7.02</t>
+          <t>$-8.63</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4815.5</v>
+        <v>4834.9</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>128.42</v>
+        <v>119.07</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="J63" s="6" t="n">
-        <v>13.66</v>
+        <v>11.42</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -3599,32 +3599,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4690.82</v>
+        <v>4687.08</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>+2.93%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>+$3.16</t>
+          <t>+$7.02</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4798.2</v>
+        <v>4815.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>+2.74%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>107.38</v>
+        <v>128.42</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="J64" s="6" t="n">
-        <v>14.27</v>
+        <v>13.66</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -3648,32 +3648,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4557.42</v>
+        <v>4690.82</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>+0.74%</t>
+          <t>+2.93%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>+$3.16</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4670.1</v>
+        <v>4798.2</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>+2.74%</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>112.68</v>
+        <v>107.38</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="J65" s="6" t="n">
-        <v>14.95</v>
+        <v>14.27</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -3697,32 +3697,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4523.72</v>
+        <v>4557.42</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>+0.74%</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>+$18.71</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4635.1</v>
+        <v>4670.1</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>+0.76%</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>111.38</v>
+        <v>112.68</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="J66" s="6" t="n">
-        <v>16.42</v>
+        <v>14.95</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -3746,32 +3746,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4614.08</v>
+        <v>4523.72</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>+$4.06</t>
+          <t>+$18.71</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4747.8</v>
+        <v>4635.1</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-2.37%</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>133.72</v>
+        <v>111.38</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="J67" s="6" t="n">
-        <v>15.85</v>
+        <v>16.42</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -3795,32 +3795,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4621.53</v>
+        <v>4614.08</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>+$1.89</t>
+          <t>+$4.06</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4731.8</v>
+        <v>4747.8</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>110.27</v>
+        <v>133.72</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="J68" s="6" t="n">
-        <v>15.16</v>
+        <v>15.85</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -3844,32 +3844,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4543.37</v>
+        <v>4621.53</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>$-3.14</t>
+          <t>+$1.89</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4661.7</v>
+        <v>4731.8</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>118.33</v>
+        <v>110.27</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="J69" s="6" t="n">
-        <v>15.8</v>
+        <v>15.16</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -3893,32 +3893,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>4596.87</v>
+        <v>4543.37</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-3.14</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4709.6</v>
+        <v>4661.7</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>112.73</v>
+        <v>118.33</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="J70" s="6" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -3942,32 +3942,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4681.73</v>
+        <v>4596.87</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>$-12.44</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4797</v>
+        <v>4709.6</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>-0.99%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>115.27</v>
+        <v>112.73</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="J71" s="6" t="n">
-        <v>20.95</v>
+        <v>15.5</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -3991,32 +3991,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4710.12</v>
+        <v>4681.73</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>+$12.00</t>
+          <t>$-12.44</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4844.8</v>
+        <v>4797</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>134.68</v>
+        <v>115.27</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="J72" s="6" t="n">
-        <v>23.3</v>
+        <v>20.95</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -4040,32 +4040,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4694.36</v>
+        <v>4710.12</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>+$4.60</t>
+          <t>+$12.00</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4828.3</v>
+        <v>4844.8</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>133.94</v>
+        <v>134.68</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="J73" s="6" t="n">
-        <v>25.67</v>
+        <v>23.3</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -4089,32 +4089,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>4740.15</v>
+        <v>4694.36</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>$-0.84</t>
+          <t>+$4.60</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4858.2</v>
+        <v>4828.3</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>118.05</v>
+        <v>133.94</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="J74" s="6" t="n">
-        <v>28.47</v>
+        <v>25.67</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -4138,32 +4138,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4720.07</v>
+        <v>4740.15</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>-2.09%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>+$0.62</t>
+          <t>$-0.84</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4824.1</v>
+        <v>4858.2</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>-2.26%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>104.03</v>
+        <v>118.05</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -4175,8 +4175,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J75" s="3" t="n">
-        <v>30.98</v>
+      <c r="J75" s="6" t="n">
+        <v>28.47</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -4187,32 +4187,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4820.58</v>
+        <v>4720.07</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>$-56.03</t>
+          <t>+$0.62</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4935.4</v>
+        <v>4824.1</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>-1.04%</t>
+          <t>-2.26%</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>114.82</v>
+        <v>104.03</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="J76" s="3" t="n">
-        <v>32.7</v>
+        <v>30.98</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -4236,32 +4236,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>4831.76</v>
+        <v>4820.58</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>+$1.68</t>
+          <t>$-56.03</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4987.3</v>
+        <v>4935.4</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>-1.04%</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>155.54</v>
+        <v>114.82</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="J77" s="3" t="n">
-        <v>30.87</v>
+        <v>32.7</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -4285,32 +4285,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>4790.65</v>
+        <v>4831.76</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>$-1.72</t>
+          <t>+$1.68</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4916.6</v>
+        <v>4987.3</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>125.95</v>
+        <v>155.54</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="J78" s="3" t="n">
-        <v>28.9</v>
+        <v>30.87</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -4334,32 +4334,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>4791.81</v>
+        <v>4790.65</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>$-1.72</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4932.6</v>
+        <v>4916.6</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>140.79</v>
+        <v>125.95</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -4371,8 +4371,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J79" s="3" t="n">
-        <v>31.48</v>
+      <c r="J79" s="6" t="n">
+        <v>28.9</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -4383,32 +4383,32 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>4841.67</v>
+        <v>4791.81</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>+2.09%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>+$1.90</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4960.6</v>
+        <v>4932.6</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>+1.74%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>118.93</v>
+        <v>140.79</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="J80" s="3" t="n">
-        <v>39.82</v>
+        <v>31.48</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -4432,32 +4432,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4742.69</v>
+        <v>4841.67</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+2.09%</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>$-109.35</t>
+          <t>+$1.90</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4876</v>
+        <v>4960.6</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+1.74%</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>133.31</v>
+        <v>118.93</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="J81" s="3" t="n">
-        <v>45.25</v>
+        <v>39.82</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -4481,32 +4481,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>4749.28</v>
+        <v>4742.69</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>$-1.84</t>
+          <t>$-109.35</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4896.4</v>
+        <v>4876</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>147.12</v>
+        <v>133.31</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         </is>
       </c>
       <c r="J82" s="3" t="n">
-        <v>50.95</v>
+        <v>45.25</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -4530,32 +4530,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4764.17</v>
+        <v>4749.28</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>+$0.36</t>
+          <t>$-1.84</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4928.3</v>
+        <v>4896.4</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>164.13</v>
+        <v>147.12</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="J83" s="3" t="n">
-        <v>59.04</v>
+        <v>50.95</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -4579,32 +4579,32 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>4719.81</v>
+        <v>4764.17</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>+$19.77</t>
+          <t>+$0.36</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4885.4</v>
+        <v>4928.3</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>+2.02%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>165.59</v>
+        <v>164.13</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="J84" s="3" t="n">
-        <v>68.06</v>
+        <v>59.04</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -4628,32 +4628,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4702.05</v>
+        <v>4719.81</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>+$1.79</t>
+          <t>+$19.77</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4788.9</v>
+        <v>4885.4</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+2.02%</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>86.84999999999999</v>
+        <v>165.59</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         </is>
       </c>
       <c r="J85" s="3" t="n">
-        <v>67.61</v>
+        <v>68.06</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -4677,20 +4677,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4649.73</v>
+        <v>4702.05</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>$-3.57</t>
+          <t>+$1.79</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -4698,11 +4698,11 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>139.17</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="J86" s="3" t="n">
-        <v>64.22</v>
+        <v>67.61</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -4726,32 +4726,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>4678.89</v>
+        <v>4649.73</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>$-0.67</t>
+          <t>$-3.57</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4784.1</v>
+        <v>4788.9</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>-2.74%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>105.21</v>
+        <v>139.17</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="J87" s="3" t="n">
-        <v>65.06999999999999</v>
+        <v>64.22</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -4775,32 +4775,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>4758.74</v>
+        <v>4678.89</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>+$2.49</t>
+          <t>$-0.67</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4919.1</v>
+        <v>4784.1</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>+2.91%</t>
+          <t>-2.74%</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>160.36</v>
+        <v>105.21</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="J88" s="3" t="n">
-        <v>61.51</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -4824,32 +4824,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>4668.9</v>
+        <v>4758.74</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>+3.50%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>+$2.18</t>
+          <t>+$2.49</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4780.2</v>
+        <v>4919.1</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>+2.64%</t>
+          <t>+2.91%</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>111.3</v>
+        <v>160.36</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         </is>
       </c>
       <c r="J89" s="3" t="n">
-        <v>61.02</v>
+        <v>61.51</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -4873,32 +4873,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>4511.22</v>
+        <v>4668.9</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+3.50%</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>$-0.71</t>
+          <t>+$2.18</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4657.4</v>
+        <v>4780.2</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+2.64%</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>146.18</v>
+        <v>111.3</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="J90" s="3" t="n">
-        <v>61.83</v>
+        <v>61.02</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -4922,32 +4922,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>4493.8</v>
+        <v>4511.22</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>+$12.74</t>
+          <t>$-0.71</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4624.8</v>
+        <v>4657.4</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>+2.62%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>131</v>
+        <v>146.18</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="J91" s="3" t="n">
-        <v>66.98999999999999</v>
+        <v>61.83</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -4971,32 +4971,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>4377.64</v>
+        <v>4493.8</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>+$5.15</t>
+          <t>+$12.74</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4506.7</v>
+        <v>4624.8</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>-3.82%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>129.06</v>
+        <v>131</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="J92" s="3" t="n">
-        <v>68.39</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -5020,32 +5020,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>4505.69</v>
+        <v>4377.64</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>$-19.39</t>
+          <t>+$5.15</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4685.7</v>
+        <v>4506.7</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>+3.37%</t>
+          <t>-3.82%</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>180.01</v>
+        <v>129.06</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="J93" s="3" t="n">
-        <v>65.34999999999999</v>
+        <v>68.39</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -5069,32 +5069,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>4491.37</v>
+        <v>4505.69</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>+$6.43</t>
+          <t>$-19.39</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4532.8</v>
+        <v>4685.7</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+3.37%</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>41.43</v>
+        <v>180.01</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -5107,43 +5107,43 @@
         </is>
       </c>
       <c r="J94" s="3" t="n">
-        <v>55.61</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>4407.46</v>
+        <v>4491.37</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>$-41.67</t>
+          <t>+$6.43</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4539.3</v>
+        <v>4532.8</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>131.84</v>
+        <v>41.43</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -5156,43 +5156,43 @@
         </is>
       </c>
       <c r="J95" s="3" t="n">
-        <v>52.06</v>
+        <v>55.61</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>4490.66</v>
+        <v>4407.46</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>-3.43%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>+$0.88</t>
+          <t>$-41.67</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4716.2</v>
+        <v>4539.3</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>-3.75%</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>225.54</v>
+        <v>131.84</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="J96" s="3" t="n">
-        <v>48.26</v>
+        <v>52.06</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -5216,32 +5216,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>4650.11</v>
+        <v>4490.66</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>-3.50%</t>
+          <t>-3.43%</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>+$5.66</t>
+          <t>+$0.88</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4745.4</v>
+        <v>4716.2</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>-5.88%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>95.29000000000001</v>
+        <v>225.54</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="J97" s="3" t="n">
-        <v>40.68</v>
+        <v>48.26</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -5265,32 +5265,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>4818.71</v>
+        <v>4650.11</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>-3.74%</t>
+          <t>-3.50%</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>$-0.26</t>
+          <t>+$5.66</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5041.7</v>
+        <v>4745.4</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>-2.23%</t>
+          <t>-5.88%</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>222.99</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="J98" s="3" t="n">
-        <v>34.38</v>
+        <v>40.68</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -5314,32 +5314,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>5006.14</v>
+        <v>4818.71</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-3.74%</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>+$3.07</t>
+          <t>$-0.26</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5156.7</v>
+        <v>5041.7</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-2.23%</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>150.56</v>
+        <v>222.99</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         </is>
       </c>
       <c r="J99" s="3" t="n">
-        <v>33</v>
+        <v>34.38</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -5363,32 +5363,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>5004.67</v>
+        <v>5006.14</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>$-13.14</t>
+          <t>+$3.07</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5150.3</v>
+        <v>5156.7</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>145.63</v>
+        <v>150.56</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="J100" s="3" t="n">
-        <v>34.78</v>
+        <v>33</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -5412,32 +5412,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>5019</v>
+        <v>5004.67</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>+$0.70</t>
+          <t>$-13.14</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5210.4</v>
+        <v>5150.3</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>-1.25%</t>
+          <t>-1.15%</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>191.4</v>
+        <v>145.63</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="J101" s="3" t="n">
-        <v>34.04</v>
+        <v>34.78</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -5461,32 +5461,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>5079.6</v>
+        <v>5019</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>+$2.23</t>
+          <t>+$0.70</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5276.4</v>
+        <v>5210.4</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>-1.25%</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>196.8</v>
+        <v>191.4</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="J102" s="3" t="n">
-        <v>35.66</v>
+        <v>34.04</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -5510,32 +5510,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>5176.23</v>
+        <v>5079.6</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>$-3.94</t>
+          <t>+$2.23</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5330.9</v>
+        <v>5276.4</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>154.67</v>
+        <v>196.8</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         </is>
       </c>
       <c r="J103" s="3" t="n">
-        <v>34.34</v>
+        <v>35.66</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -5559,32 +5559,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>5191.58</v>
+        <v>5176.23</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>+$0.98</t>
+          <t>$-3.94</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5392.5</v>
+        <v>5330.9</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>200.92</v>
+        <v>154.67</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="J104" s="3" t="n">
-        <v>33.19</v>
+        <v>34.34</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -5608,32 +5608,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>5138.45</v>
+        <v>5191.58</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>+$8.38</t>
+          <t>+$0.98</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5251.9</v>
+        <v>5392.5</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>113.45</v>
+        <v>200.92</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -5645,8 +5645,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J105" s="6" t="n">
-        <v>27.57</v>
+      <c r="J105" s="3" t="n">
+        <v>33.19</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -5657,32 +5657,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>5171.8</v>
+        <v>5138.45</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>+$1.60</t>
+          <t>+$8.38</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5306.8</v>
+        <v>5251.9</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>135</v>
+        <v>113.45</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="J106" s="6" t="n">
-        <v>27.41</v>
+        <v>27.57</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -5706,32 +5706,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>5082.25</v>
+        <v>5171.8</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>+$15.58</t>
+          <t>+$1.60</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5225.6</v>
+        <v>5306.8</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>143.35</v>
+        <v>135</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="J107" s="6" t="n">
-        <v>28.59</v>
+        <v>27.41</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -5755,32 +5755,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>5140.39</v>
+        <v>5082.25</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>+$15.99</t>
+          <t>+$15.58</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5281.6</v>
+        <v>5225.6</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-1.06%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>141.21</v>
+        <v>143.35</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -5792,8 +5792,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J108" s="3" t="n">
-        <v>29.02</v>
+      <c r="J108" s="6" t="n">
+        <v>28.59</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -5804,32 +5804,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>5087.78</v>
+        <v>5140.39</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>-4.39%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>+$3.27</t>
+          <t>+$15.99</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5269.7</v>
+        <v>5281.6</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>-3.53%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>181.92</v>
+        <v>141.21</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -5841,8 +5841,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J109" s="6" t="n">
-        <v>26.89</v>
+      <c r="J109" s="3" t="n">
+        <v>29.02</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -5853,32 +5853,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>5321.3</v>
+        <v>5087.78</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>+0.80%</t>
+          <t>-4.39%</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>+$22.33</t>
+          <t>+$3.27</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5462.6</v>
+        <v>5269.7</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-3.53%</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>141.3</v>
+        <v>181.92</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="J110" s="6" t="n">
-        <v>25</v>
+        <v>26.89</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -5902,32 +5902,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>5278.9</v>
+        <v>5321.3</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>+1.83%</t>
+          <t>+0.80%</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>+$3.50</t>
+          <t>+$22.33</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5396.2</v>
+        <v>5462.6</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>117.3</v>
+        <v>141.3</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         </is>
       </c>
       <c r="J111" s="6" t="n">
-        <v>23.93</v>
+        <v>25</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -5951,32 +5951,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>5184.25</v>
+        <v>5278.9</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+1.83%</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>$-2.63</t>
+          <t>+$3.50</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5341.1</v>
+        <v>5396.2</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>156.85</v>
+        <v>117.3</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="J112" s="6" t="n">
-        <v>27.52</v>
+        <v>23.93</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -6000,32 +6000,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>5164.29</v>
+        <v>5184.25</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>+$0.50</t>
+          <t>$-2.63</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5374.2</v>
+        <v>5341.1</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>209.91</v>
+        <v>156.85</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -6037,8 +6037,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J113" s="3" t="n">
-        <v>32.13</v>
+      <c r="J113" s="6" t="n">
+        <v>27.52</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -6049,32 +6049,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>5142.79</v>
+        <v>5164.29</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>-1.62%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>+$2.64</t>
+          <t>+$0.50</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5322.8</v>
+        <v>5374.2</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>180.01</v>
+        <v>209.91</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="J114" s="3" t="n">
-        <v>30.2</v>
+        <v>32.13</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -6098,32 +6098,32 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>5227.48</v>
+        <v>5142.79</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>+2.36%</t>
+          <t>-1.62%</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>+$2.32</t>
+          <t>+$2.64</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5372</v>
+        <v>5322.8</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>144.52</v>
+        <v>180.01</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -6135,8 +6135,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J115" s="6" t="n">
-        <v>28.13</v>
+      <c r="J115" s="3" t="n">
+        <v>30.2</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -6147,32 +6147,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>5106.96</v>
+        <v>5227.48</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>+2.22%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>+$2.74</t>
+          <t>+$2.32</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5223.4</v>
+        <v>5372</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>+1.70%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>116.44</v>
+        <v>144.52</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -6184,8 +6184,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J116" s="3" t="n">
-        <v>35.59</v>
+      <c r="J116" s="6" t="n">
+        <v>28.13</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -6196,32 +6196,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>4996.02</v>
+        <v>5106.96</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+2.22%</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>$-2.27</t>
+          <t>+$2.74</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5136.1</v>
+        <v>5223.4</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+1.70%</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>140.08</v>
+        <v>116.44</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         </is>
       </c>
       <c r="J117" s="3" t="n">
-        <v>44.31</v>
+        <v>35.59</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -6245,32 +6245,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>4977.18</v>
+        <v>4996.02</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>+2.03%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>+$1.09</t>
+          <t>$-2.27</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5147.3</v>
+        <v>5136.1</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>170.12</v>
+        <v>140.08</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="J118" s="3" t="n">
-        <v>46.23</v>
+        <v>44.31</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -6294,32 +6294,32 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>4878.1</v>
+        <v>4977.18</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>-3.25%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>$-45.72</t>
+          <t>+$1.09</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5039.4</v>
+        <v>5147.3</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>-2.79%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>161.3</v>
+        <v>170.12</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         </is>
       </c>
       <c r="J119" s="3" t="n">
-        <v>46.39</v>
+        <v>46.23</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -6343,32 +6343,32 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>5041.86</v>
+        <v>4878.1</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>+2.44%</t>
+          <t>-3.25%</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>+$4.32</t>
+          <t>$-45.72</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5183.8</v>
+        <v>5039.4</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>+1.87%</t>
+          <t>-2.79%</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>141.94</v>
+        <v>161.3</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="J120" s="3" t="n">
-        <v>57.41</v>
+        <v>46.39</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -6392,32 +6392,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>4921.59</v>
+        <v>5041.86</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>-3.19%</t>
+          <t>+2.44%</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>+$1.40</t>
+          <t>+$4.32</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5088.4</v>
+        <v>5183.8</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>-2.94%</t>
+          <t>+1.87%</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>166.81</v>
+        <v>141.94</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="J121" s="3" t="n">
-        <v>62.1</v>
+        <v>57.41</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -6441,32 +6441,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>5083.84</v>
+        <v>4921.59</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>+1.18%</t>
+          <t>-3.19%</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>+$2.13</t>
+          <t>+$1.40</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5242.5</v>
+        <v>5088.4</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-2.94%</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>158.66</v>
+        <v>166.81</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="J122" s="3" t="n">
-        <v>63</v>
+        <v>62.1</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -6490,32 +6490,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>5024.38</v>
+        <v>5083.84</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>+1.18%</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>$-0.65</t>
+          <t>+$2.13</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5172.2</v>
+        <v>5242.5</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>147.82</v>
+        <v>158.66</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="J123" s="3" t="n">
-        <v>64.01000000000001</v>
+        <v>63</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -6539,32 +6539,32 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>5060.14</v>
+        <v>5024.38</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>+1.88%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>+$17.25</t>
+          <t>$-0.65</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5222.1</v>
+        <v>5172.2</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>+2.00%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>161.96</v>
+        <v>147.82</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="J124" s="3" t="n">
-        <v>63.42</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -6588,32 +6588,32 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>4966.93</v>
+        <v>5060.14</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>+3.92%</t>
+          <t>+1.88%</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>+$12.55</t>
+          <t>+$17.25</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5119.8</v>
+        <v>5222.1</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>+1.94%</t>
+          <t>+2.00%</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>152.87</v>
+        <v>161.96</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         </is>
       </c>
       <c r="J125" s="3" t="n">
-        <v>63.27</v>
+        <v>63.42</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -6637,32 +6637,32 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>4779.63</v>
+        <v>4966.93</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>-3.71%</t>
+          <t>+3.92%</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>+$12.00</t>
+          <t>+$12.55</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5022.3</v>
+        <v>5119.8</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>+1.94%</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>242.67</v>
+        <v>152.87</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         </is>
       </c>
       <c r="J126" s="3" t="n">
-        <v>57.48</v>
+        <v>63.27</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -6686,32 +6686,32 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>4963.89</v>
+        <v>4779.63</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-3.71%</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>+$1.30</t>
+          <t>+$12.00</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5089</v>
+        <v>5022.3</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>125.11</v>
+        <v>242.67</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         </is>
       </c>
       <c r="J127" s="3" t="n">
-        <v>49.25</v>
+        <v>57.48</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -6735,32 +6735,32 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>4944.42</v>
+        <v>4963.89</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>+6.13%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>+$13.04</t>
+          <t>+$1.30</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5072.5</v>
+        <v>5089</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>+6.11%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>128.08</v>
+        <v>125.11</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         </is>
       </c>
       <c r="J128" s="3" t="n">
-        <v>49.09</v>
+        <v>49.25</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -6784,32 +6784,32 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>4658.73</v>
+        <v>4944.42</v>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>-4.75%</t>
+          <t>+6.13%</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>$-76.67</t>
+          <t>+$13.04</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4780.4</v>
+        <v>5072.5</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>+6.11%</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>121.67</v>
+        <v>128.08</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="J129" s="3" t="n">
-        <v>48.95</v>
+        <v>49.09</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -6833,36 +6833,36 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>4890.97</v>
+        <v>4658.73</v>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>-8.99%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>+$8.73</t>
+          <t>$-76.67</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4880</v>
+        <v>4780.4</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>-11.41%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>-10.97</v>
-      </c>
-      <c r="H130" s="7" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>121.67</v>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
@@ -6871,47 +6871,47 @@
         </is>
       </c>
       <c r="J130" s="3" t="n">
-        <v>41.41</v>
+        <v>48.95</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>5373.91</v>
+        <v>4890.97</v>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-8.99%</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>+$5.87</t>
+          <t>+$8.73</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5508.6</v>
+        <v>4880</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-11.41%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>134.69</v>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-10.97</v>
+      </c>
+      <c r="H131" s="7" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
@@ -6920,43 +6920,43 @@
         </is>
       </c>
       <c r="J131" s="3" t="n">
-        <v>31.72</v>
+        <v>41.41</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>5416.79</v>
+        <v>5373.91</v>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>+4.60%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>+$5.87</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5494.6</v>
+        <v>5508.6</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>+4.32%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>77.81</v>
+        <v>134.69</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         </is>
       </c>
       <c r="J132" s="3" t="n">
-        <v>29.24</v>
+        <v>31.72</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -6980,32 +6980,32 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>5178.46</v>
+        <v>5416.79</v>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>+3.36%</t>
+          <t>+4.60%</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>+$3.14</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5267.3</v>
+        <v>5494.6</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+4.32%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>88.84</v>
+        <v>77.81</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -7017,8 +7017,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J133" s="6" t="n">
-        <v>28.65</v>
+      <c r="J133" s="3" t="n">
+        <v>29.24</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -7029,32 +7029,32 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>5010.31</v>
+        <v>5178.46</v>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+3.36%</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>+$20.73</t>
+          <t>+$3.14</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5272.8</v>
+        <v>5267.3</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>262.49</v>
+        <v>88.84</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         </is>
       </c>
       <c r="J134" s="6" t="n">
-        <v>16.43</v>
+        <v>28.65</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -7078,32 +7078,32 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>4988.56</v>
+        <v>5010.31</v>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>+1.07%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>+$5.34</t>
+          <t>+$20.73</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5160.4</v>
+        <v>5272.8</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+2.18%</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>171.84</v>
+        <v>262.49</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         </is>
       </c>
       <c r="J135" s="6" t="n">
-        <v>10.44</v>
+        <v>16.43</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -7127,32 +7127,32 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>4935.8</v>
+        <v>4988.56</v>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>+$0.94</t>
+          <t>+$5.34</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5086.9</v>
+        <v>5160.4</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>+1.59%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>151.1</v>
+        <v>171.84</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="J136" s="6" t="n">
-        <v>8.960000000000001</v>
+        <v>10.44</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -7176,32 +7176,32 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>4831.51</v>
+        <v>4935.8</v>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+2.16%</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>+$0.31</t>
+          <t>+$0.94</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5007.5</v>
+        <v>5086.9</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>+1.51%</t>
+          <t>+1.59%</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>175.99</v>
+        <v>151.1</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -7213,7 +7213,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J137" s="2" t="inlineStr"/>
+      <c r="J137" s="6" t="n">
+        <v>8.960000000000001</v>
+      </c>
       <c r="K137" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -7223,32 +7225,32 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>4762.99</v>
+        <v>4831.51</v>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>+3.63%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>+$75.81</t>
+          <t>+$0.31</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4933</v>
+        <v>5007.5</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>+3.65%</t>
+          <t>+1.51%</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>170.01</v>
+        <v>175.99</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -7270,32 +7272,32 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>4596.18</v>
+        <v>4762.99</v>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+3.63%</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>+$1.80</t>
+          <t>+$75.81</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4759.2</v>
+        <v>4933</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>+3.65%</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>163.02</v>
+        <v>170.01</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -7317,32 +7319,32 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>4615.95</v>
+        <v>4596.18</v>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>+$6.28</t>
+          <t>+$1.80</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4787.7</v>
+        <v>4759.2</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>171.75</v>
+        <v>163.02</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -7364,32 +7366,32 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>4624.8</v>
+        <v>4615.95</v>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>+$3.59</t>
+          <t>+$6.28</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4798.9</v>
+        <v>4787.7</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>174.1</v>
+        <v>171.75</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -7411,32 +7413,32 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>4585.44</v>
+        <v>4624.8</v>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>+$5.33</t>
+          <t>+$3.59</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4760.2</v>
+        <v>4798.9</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>174.76</v>
+        <v>174.1</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -7458,32 +7460,32 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>4598.46</v>
+        <v>4585.44</v>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>+1.98%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>+$9.47</t>
+          <t>+$5.33</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4777.7</v>
+        <v>4760.2</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>+2.49%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>179.24</v>
+        <v>174.76</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -7505,32 +7507,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>4509.27</v>
+        <v>4598.46</v>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>+$1.86</t>
+          <t>+$9.47</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4661.4</v>
+        <v>4777.7</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>+0.90%</t>
+          <t>+2.49%</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>152.13</v>
+        <v>179.24</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -7552,32 +7554,32 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>4477.84</v>
+        <v>4509.27</v>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>$-0.03</t>
+          <t>+$1.86</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4620</v>
+        <v>4661.4</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.90%</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>142.16</v>
+        <v>152.13</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -7599,32 +7601,32 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>4456.26</v>
+        <v>4477.84</v>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>+$0.08</t>
+          <t>$-0.03</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4620.6</v>
+        <v>4620</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>-0.76%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>164.34</v>
+        <v>142.16</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -7646,32 +7648,32 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>4494.61</v>
+        <v>4456.26</v>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.85%</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>$-0.07</t>
+          <t>+$0.08</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4656.2</v>
+        <v>4620.6</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>-0.76%</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>161.59</v>
+        <v>164.34</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -7693,32 +7695,32 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>4449.11</v>
+        <v>4494.61</v>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>+2.70%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>+$28.96</t>
+          <t>$-0.07</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4608.1</v>
+        <v>4656.2</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>+2.76%</t>
+          <t>+1.04%</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>158.99</v>
+        <v>161.59</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -7740,32 +7742,32 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>4332.17</v>
+        <v>4449.11</v>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.70%</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+$28.96</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4484.4</v>
+        <v>4608.1</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.76%</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>152.23</v>
+        <v>158.99</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -7779,6 +7781,53 @@
       </c>
       <c r="J149" s="2" t="inlineStr"/>
       <c r="K149" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>4332.17</v>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>4484.4</v>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>152.23</v>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -578,15 +578,15 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4399.7</v>
+        <v>4461</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+2.36%</t>
+          <t>+3.79%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>57.86</v>
+        <v>119.16</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>43.2</v>
+        <v>47.58</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K150"/>
+  <dimension ref="A1:K151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -561,32 +561,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4341.84</v>
+        <v>4404</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+1.61%</t>
+          <t>+1.43%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>$-34.98</t>
+          <t>+$47.82</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4461</v>
+        <v>4458.5</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+3.79%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>119.16</v>
+        <v>54.5</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>47.58</v>
+        <v>51.72</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -610,32 +610,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4273.01</v>
+        <v>4341.84</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+4.29%</t>
+          <t>+1.61%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$151.16</t>
+          <t>$-34.98</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4298.3</v>
+        <v>4461</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>+3.79%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>25.29</v>
+        <v>119.16</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>41.84</v>
+        <v>47.58</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -659,130 +659,130 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4097.29</v>
+        <v>4273.01</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>+4.29%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$22.75</t>
+          <t>+$151.16</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4339</v>
+        <v>4298.3</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+4.39%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>241.71</v>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>28.06</v>
+        <v>25.29</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>41.84</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4055.15</v>
+        <v>4097.29</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+1.04%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$33.39</t>
+          <t>+$22.75</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4156.4</v>
+        <v>4339</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>+4.39%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>101.25</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>241.71</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>19.9</v>
+        <v>28.06</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4044.36</v>
+        <v>4055.15</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$33.39</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4110.9</v>
+        <v>4156.4</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>66.54000000000001</v>
+        <v>101.25</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>18.29</v>
+        <v>19.9</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -806,32 +806,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4103.64</v>
+        <v>4044.36</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$0.17</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4160.6</v>
+        <v>4110.9</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>56.96</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="J7" s="6" t="n">
-        <v>18.21</v>
+        <v>18.29</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -855,32 +855,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4066.23</v>
+        <v>4103.64</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$1.59</t>
+          <t>+$0.17</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4097</v>
+        <v>4160.6</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>30.77</v>
+        <v>56.96</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="J8" s="6" t="n">
-        <v>18.03</v>
+        <v>18.21</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -904,32 +904,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4028.54</v>
+        <v>4066.23</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$2.81</t>
+          <t>+$1.59</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4098.6</v>
+        <v>4097</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>70.06</v>
+        <v>30.77</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="J9" s="6" t="n">
-        <v>16.18</v>
+        <v>18.03</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -953,32 +953,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4076.6</v>
+        <v>4028.54</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$43.44</t>
+          <t>+$2.81</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4136.4</v>
+        <v>4098.6</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>59.8</v>
+        <v>70.06</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="J10" s="6" t="n">
-        <v>18.87</v>
+        <v>16.18</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1002,32 +1002,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4052.74</v>
+        <v>4076.6</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$0.61</t>
+          <t>+$43.44</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4129.7</v>
+        <v>4136.4</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>76.95999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="J11" s="6" t="n">
-        <v>21.15</v>
+        <v>18.87</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1051,32 +1051,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4049.43</v>
+        <v>4052.74</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$-10.76</t>
+          <t>+$0.61</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4108.8</v>
+        <v>4129.7</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>59.37</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="J12" s="6" t="n">
-        <v>19.94</v>
+        <v>21.15</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1100,32 +1100,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4130.11</v>
+        <v>4049.43</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$1.94</t>
+          <t>$-10.76</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4210.3</v>
+        <v>4108.8</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+1.84%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>80.19</v>
+        <v>59.37</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="J13" s="6" t="n">
-        <v>21.96</v>
+        <v>19.94</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1149,32 +1149,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4077.87</v>
+        <v>4130.11</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$1.94</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4134.2</v>
+        <v>4210.3</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+1.84%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>56.33</v>
+        <v>80.19</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="J14" s="6" t="n">
-        <v>21.74</v>
+        <v>21.96</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1198,32 +1198,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4007.49</v>
+        <v>4077.87</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-12.24</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4073</v>
+        <v>4134.2</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>65.51000000000001</v>
+        <v>56.33</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="J15" s="6" t="n">
-        <v>21.72</v>
+        <v>21.74</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1247,32 +1247,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4017.04</v>
+        <v>4007.49</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$1.19</t>
+          <t>$-12.24</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4075.8</v>
+        <v>4073</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>58.76</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>22.33</v>
+        <v>21.72</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1296,32 +1296,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3976.48</v>
+        <v>4017.04</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$4.31</t>
+          <t>+$1.19</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4048.7</v>
+        <v>4075.8</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>72.22</v>
+        <v>58.76</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="J17" s="6" t="n">
-        <v>22.36</v>
+        <v>22.33</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1345,32 +1345,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4060.55</v>
+        <v>3976.48</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$0.46</t>
+          <t>+$4.31</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4109.3</v>
+        <v>4048.7</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>48.75</v>
+        <v>72.22</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="J18" s="6" t="n">
-        <v>21.54</v>
+        <v>22.36</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1394,32 +1394,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4052.92</v>
+        <v>4060.55</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$5.21</t>
+          <t>+$0.46</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4127.9</v>
+        <v>4109.3</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+1.58%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>74.98</v>
+        <v>48.75</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="J19" s="6" t="n">
-        <v>21.93</v>
+        <v>21.54</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1443,32 +1443,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4000.78</v>
+        <v>4052.92</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$5.21</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4063.6</v>
+        <v>4127.9</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>+1.58%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>62.82</v>
+        <v>74.98</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="J20" s="6" t="n">
-        <v>22.96</v>
+        <v>21.93</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1492,32 +1492,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4119.29</v>
+        <v>4000.78</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4173.6</v>
+        <v>4063.6</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>54.31</v>
+        <v>62.82</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="J21" s="6" t="n">
-        <v>24.16</v>
+        <v>22.96</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1541,32 +1541,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4123.38</v>
+        <v>4119.29</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4201.4</v>
+        <v>4173.6</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+1.43%</t>
+          <t>-0.66%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>78.02</v>
+        <v>54.31</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="J22" s="6" t="n">
-        <v>28.73</v>
+        <v>24.16</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1590,32 +1590,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4077.4</v>
+        <v>4123.38</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4142.1</v>
+        <v>4201.4</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>+1.43%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>64.7</v>
+        <v>78.02</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1627,8 +1627,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="3" t="n">
-        <v>34.99</v>
+      <c r="J23" s="6" t="n">
+        <v>28.73</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1639,32 +1639,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4105.67</v>
+        <v>4077.4</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4218.3</v>
+        <v>4142.1</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>112.63</v>
+        <v>64.7</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>32.93</v>
+        <v>34.99</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1688,32 +1688,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4165.04</v>
+        <v>4105.67</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4228.6</v>
+        <v>4218.3</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>63.56</v>
+        <v>112.63</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>31.11</v>
+        <v>32.93</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1737,32 +1737,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4123.77</v>
+        <v>4165.04</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4186.6</v>
+        <v>4228.6</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>62.83</v>
+        <v>63.56</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>39.51</v>
+        <v>31.11</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1786,32 +1786,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4031.01</v>
+        <v>4123.77</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4142.9</v>
+        <v>4186.6</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>111.89</v>
+        <v>62.83</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>47.43</v>
+        <v>39.51</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1835,32 +1835,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4007.41</v>
+        <v>4031.01</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4098.5</v>
+        <v>4142.9</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>91.09</v>
+        <v>111.89</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>48.29</v>
+        <v>47.43</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1884,32 +1884,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4016.54</v>
+        <v>4007.41</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4098.8</v>
+        <v>4098.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>82.26000000000001</v>
+        <v>91.09</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>48.18</v>
+        <v>48.29</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1933,32 +1933,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4089.95</v>
+        <v>4016.54</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4156.9</v>
+        <v>4098.8</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>66.95</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>47.32</v>
+        <v>48.18</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1982,32 +1982,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4026.57</v>
+        <v>4089.95</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4107.5</v>
+        <v>4156.9</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>80.93000000000001</v>
+        <v>66.95</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>46.73</v>
+        <v>47.32</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2031,32 +2031,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3999.06</v>
+        <v>4026.57</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4068.1</v>
+        <v>4107.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-3.39%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>69.04000000000001</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>46.06</v>
+        <v>46.73</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2080,32 +2080,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4110.14</v>
+        <v>3999.06</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4210.9</v>
+        <v>4068.1</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-3.39%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>100.76</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>43.81</v>
+        <v>46.06</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2129,32 +2129,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4191.26</v>
+        <v>4110.14</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4265.4</v>
+        <v>4210.9</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>74.14</v>
+        <v>100.76</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>42.64</v>
+        <v>43.81</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2178,32 +2178,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4209.02</v>
+        <v>4191.26</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4308.5</v>
+        <v>4265.4</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>99.48</v>
+        <v>74.14</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>43.1</v>
+        <v>42.64</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2227,130 +2227,130 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4257.71</v>
+        <v>4209.02</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4444.8</v>
+        <v>4308.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>-3.07%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>187.09</v>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
+        <v>99.48</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>38.11</v>
+        <v>43.1</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4331.14</v>
+        <v>4257.71</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$7.23</t>
+          <t>+$1.76</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4417.3</v>
+        <v>4444.8</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>86.16</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>187.09</v>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J37" s="3" t="n">
-        <v>31.79</v>
+        <v>38.11</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4309.03</v>
+        <v>4331.14</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$52.77</t>
+          <t>+$7.23</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4414.3</v>
+        <v>4417.3</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>105.27</v>
+        <v>86.16</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="J38" s="3" t="n">
-        <v>30.77</v>
+        <v>31.79</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2374,32 +2374,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4218.71</v>
+        <v>4309.03</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>$-1.08</t>
+          <t>+$52.77</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4300.4</v>
+        <v>4414.3</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>81.69</v>
+        <v>105.27</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="J39" s="3" t="n">
-        <v>30.55</v>
+        <v>30.77</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2423,36 +2423,36 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4210.69</v>
+        <v>4218.71</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$10.16</t>
+          <t>$-1.08</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4174</v>
+        <v>4300.4</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+3.03%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>-36.69</v>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>81.69</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2460,48 +2460,48 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J40" s="6" t="n">
-        <v>23.08</v>
+      <c r="J40" s="3" t="n">
+        <v>30.55</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4071.28</v>
+        <v>4210.69</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>$-5.95</t>
+          <t>+$10.16</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4194.5</v>
+        <v>4174</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-3.57%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>123.22</v>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-36.69</v>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2510,43 +2510,43 @@
         </is>
       </c>
       <c r="J41" s="6" t="n">
-        <v>12.35</v>
+        <v>23.08</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4259.29</v>
+        <v>4071.28</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-4.41%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-5.95</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4349.6</v>
+        <v>4194.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>-3.57%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>90.31</v>
+        <v>123.22</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="J42" s="6" t="n">
-        <v>12.67</v>
+        <v>12.35</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2570,32 +2570,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4329.75</v>
+        <v>4259.29</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>$-2.37</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4427.3</v>
+        <v>4349.6</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>97.55</v>
+        <v>90.31</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="J43" s="6" t="n">
-        <v>14.73</v>
+        <v>12.67</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2619,32 +2619,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4328.15</v>
+        <v>4329.75</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>-3.29%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$7.90</t>
+          <t>$-2.37</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4429</v>
+        <v>4427.3</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>100.85</v>
+        <v>97.55</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="J44" s="6" t="n">
-        <v>16.65</v>
+        <v>14.73</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2668,32 +2668,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4475.25</v>
+        <v>4328.15</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-3.29%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$7.80</t>
+          <t>+$7.90</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4570.4</v>
+        <v>4429</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>95.15000000000001</v>
+        <v>100.85</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="J45" s="6" t="n">
-        <v>17.2</v>
+        <v>16.65</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2717,32 +2717,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4434.3</v>
+        <v>4475.25</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$3.39</t>
+          <t>+$7.80</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4532</v>
+        <v>4570.4</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>97.7</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="J46" s="6" t="n">
-        <v>18.03</v>
+        <v>17.2</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2766,32 +2766,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4487.78</v>
+        <v>4434.3</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>$-3.86</t>
+          <t>+$3.39</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4585.6</v>
+        <v>4532</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>97.81999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="J47" s="6" t="n">
-        <v>21.29</v>
+        <v>18.03</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2815,32 +2815,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4484.69</v>
+        <v>4487.78</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>$-1.44</t>
+          <t>$-3.86</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4572.2</v>
+        <v>4585.6</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>87.51000000000001</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="J48" s="6" t="n">
-        <v>22.22</v>
+        <v>21.29</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2864,32 +2864,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4540.28</v>
+        <v>4484.69</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+$1.89</t>
+          <t>$-1.44</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4659.5</v>
+        <v>4572.2</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>119.22</v>
+        <v>87.51000000000001</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="J49" s="6" t="n">
-        <v>21.39</v>
+        <v>22.22</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2913,32 +2913,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4495.57</v>
+        <v>4540.28</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>$-4.31</t>
+          <t>+$1.89</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4597</v>
+        <v>4659.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>101.43</v>
+        <v>119.22</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="J50" s="6" t="n">
-        <v>20.79</v>
+        <v>21.39</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2962,32 +2962,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4456.15</v>
+        <v>4495.57</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>$-6.52</t>
+          <t>$-4.31</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4545.1</v>
+        <v>4597</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>88.95</v>
+        <v>101.43</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="J51" s="6" t="n">
-        <v>21.4</v>
+        <v>20.79</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -3011,32 +3011,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4507.46</v>
+        <v>4456.15</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+$58.22</t>
+          <t>$-6.52</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4601.2</v>
+        <v>4545.1</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>93.73999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="J52" s="6" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3060,32 +3060,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4509.11</v>
+        <v>4507.46</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>$-1.21</t>
+          <t>+$58.22</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4623.4</v>
+        <v>4601.2</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>114.29</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="J53" s="6" t="n">
-        <v>20.06</v>
+        <v>21.43</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3109,32 +3109,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4543.11</v>
+        <v>4509.11</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.75%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>$-3.76</t>
+          <t>$-1.21</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4643.6</v>
+        <v>4623.4</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>100.49</v>
+        <v>114.29</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="J54" s="6" t="n">
-        <v>20.67</v>
+        <v>20.06</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3158,32 +3158,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4543.62</v>
+        <v>4543.11</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>$-3.76</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4634.4</v>
+        <v>4643.6</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>90.78</v>
+        <v>100.49</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="J55" s="6" t="n">
-        <v>21.65</v>
+        <v>20.67</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3207,32 +3207,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4481.92</v>
+        <v>4543.62</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>+$1.98</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4610.1</v>
+        <v>4634.4</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>128.18</v>
+        <v>90.78</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="J56" s="6" t="n">
-        <v>19.55</v>
+        <v>21.65</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3256,32 +3256,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4566.08</v>
+        <v>4481.92</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>$-10.86</t>
+          <t>+$1.98</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4658.2</v>
+        <v>4610.1</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>92.12</v>
+        <v>128.18</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="J57" s="6" t="n">
-        <v>17.38</v>
+        <v>19.55</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -3305,32 +3305,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4539.94</v>
+        <v>4566.08</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>+$0.18</t>
+          <t>$-10.86</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4662.2</v>
+        <v>4658.2</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>122.26</v>
+        <v>92.12</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="J58" s="6" t="n">
-        <v>15.41</v>
+        <v>17.38</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -3354,32 +3354,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4652.24</v>
+        <v>4539.94</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$0.18</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4787.9</v>
+        <v>4662.2</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-2.63%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>135.66</v>
+        <v>122.26</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="J59" s="6" t="n">
-        <v>15.84</v>
+        <v>15.41</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -3403,32 +3403,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4688.75</v>
+        <v>4652.24</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>$-3.60</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4810.3</v>
+        <v>4787.9</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>121.55</v>
+        <v>135.66</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="J60" s="6" t="n">
-        <v>14.88</v>
+        <v>15.84</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -3452,32 +3452,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4715.2</v>
+        <v>4688.75</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>+$2.34</t>
+          <t>$-3.60</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4790.9</v>
+        <v>4810.3</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>75.7</v>
+        <v>121.55</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3490,43 +3490,43 @@
         </is>
       </c>
       <c r="J61" s="6" t="n">
-        <v>12.74</v>
+        <v>14.88</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4734.64</v>
+        <v>4715.2</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>$-33.15</t>
+          <t>+$2.34</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4833.6</v>
+        <v>4790.9</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>98.95999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3539,43 +3539,43 @@
         </is>
       </c>
       <c r="J62" s="6" t="n">
-        <v>12.08</v>
+        <v>12.74</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4715.83</v>
+        <v>4734.64</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>$-8.63</t>
+          <t>$-33.15</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4834.9</v>
+        <v>4833.6</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>119.07</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="J63" s="6" t="n">
-        <v>11.42</v>
+        <v>12.08</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -3599,32 +3599,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4687.08</v>
+        <v>4715.83</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>+$7.02</t>
+          <t>$-8.63</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4815.5</v>
+        <v>4834.9</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>128.42</v>
+        <v>119.07</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="J64" s="6" t="n">
-        <v>13.66</v>
+        <v>11.42</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -3648,32 +3648,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4690.82</v>
+        <v>4687.08</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>+2.93%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>+$3.16</t>
+          <t>+$7.02</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4798.2</v>
+        <v>4815.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>+2.74%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>107.38</v>
+        <v>128.42</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="J65" s="6" t="n">
-        <v>14.27</v>
+        <v>13.66</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -3697,32 +3697,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4557.42</v>
+        <v>4690.82</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>+0.74%</t>
+          <t>+2.93%</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>+$3.16</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4670.1</v>
+        <v>4798.2</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>+2.74%</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>112.68</v>
+        <v>107.38</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="J66" s="6" t="n">
-        <v>14.95</v>
+        <v>14.27</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -3746,32 +3746,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4523.72</v>
+        <v>4557.42</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>+0.74%</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>+$18.71</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4635.1</v>
+        <v>4670.1</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>+0.76%</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>111.38</v>
+        <v>112.68</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="J67" s="6" t="n">
-        <v>16.42</v>
+        <v>14.95</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -3795,32 +3795,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4614.08</v>
+        <v>4523.72</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>+$4.06</t>
+          <t>+$18.71</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4747.8</v>
+        <v>4635.1</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-2.37%</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>133.72</v>
+        <v>111.38</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="J68" s="6" t="n">
-        <v>15.85</v>
+        <v>16.42</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -3844,32 +3844,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4621.53</v>
+        <v>4614.08</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>+$1.89</t>
+          <t>+$4.06</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4731.8</v>
+        <v>4747.8</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>110.27</v>
+        <v>133.72</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="J69" s="6" t="n">
-        <v>15.16</v>
+        <v>15.85</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -3893,32 +3893,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>4543.37</v>
+        <v>4621.53</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>$-3.14</t>
+          <t>+$1.89</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4661.7</v>
+        <v>4731.8</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>118.33</v>
+        <v>110.27</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="J70" s="6" t="n">
-        <v>15.8</v>
+        <v>15.16</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -3942,32 +3942,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4596.87</v>
+        <v>4543.37</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-3.14</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4709.6</v>
+        <v>4661.7</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>112.73</v>
+        <v>118.33</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="J71" s="6" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -3991,32 +3991,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4681.73</v>
+        <v>4596.87</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>$-12.44</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4797</v>
+        <v>4709.6</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>-0.99%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>115.27</v>
+        <v>112.73</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="J72" s="6" t="n">
-        <v>20.95</v>
+        <v>15.5</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -4040,32 +4040,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4710.12</v>
+        <v>4681.73</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>+$12.00</t>
+          <t>$-12.44</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4844.8</v>
+        <v>4797</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>134.68</v>
+        <v>115.27</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="J73" s="6" t="n">
-        <v>23.3</v>
+        <v>20.95</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -4089,32 +4089,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>4694.36</v>
+        <v>4710.12</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>+$4.60</t>
+          <t>+$12.00</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4828.3</v>
+        <v>4844.8</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>133.94</v>
+        <v>134.68</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="J74" s="6" t="n">
-        <v>25.67</v>
+        <v>23.3</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -4138,32 +4138,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4740.15</v>
+        <v>4694.36</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>$-0.84</t>
+          <t>+$4.60</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4858.2</v>
+        <v>4828.3</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>118.05</v>
+        <v>133.94</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="J75" s="6" t="n">
-        <v>28.47</v>
+        <v>25.67</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -4187,32 +4187,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4720.07</v>
+        <v>4740.15</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>-2.09%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>+$0.62</t>
+          <t>$-0.84</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4824.1</v>
+        <v>4858.2</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>-2.26%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>104.03</v>
+        <v>118.05</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -4224,8 +4224,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J76" s="3" t="n">
-        <v>30.98</v>
+      <c r="J76" s="6" t="n">
+        <v>28.47</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -4236,32 +4236,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>4820.58</v>
+        <v>4720.07</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>$-56.03</t>
+          <t>+$0.62</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4935.4</v>
+        <v>4824.1</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>-1.04%</t>
+          <t>-2.26%</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>114.82</v>
+        <v>104.03</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="J77" s="3" t="n">
-        <v>32.7</v>
+        <v>30.98</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -4285,32 +4285,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>4831.76</v>
+        <v>4820.58</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>+$1.68</t>
+          <t>$-56.03</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4987.3</v>
+        <v>4935.4</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>-1.04%</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>155.54</v>
+        <v>114.82</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="J78" s="3" t="n">
-        <v>30.87</v>
+        <v>32.7</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -4334,32 +4334,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>4790.65</v>
+        <v>4831.76</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>$-1.72</t>
+          <t>+$1.68</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4916.6</v>
+        <v>4987.3</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>125.95</v>
+        <v>155.54</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -4371,8 +4371,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J79" s="6" t="n">
-        <v>28.9</v>
+      <c r="J79" s="3" t="n">
+        <v>30.87</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -4383,32 +4383,32 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>4791.81</v>
+        <v>4790.65</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>$-1.72</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4932.6</v>
+        <v>4916.6</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>140.79</v>
+        <v>125.95</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -4420,8 +4420,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J80" s="3" t="n">
-        <v>31.48</v>
+      <c r="J80" s="6" t="n">
+        <v>28.9</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -4432,32 +4432,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4841.67</v>
+        <v>4791.81</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>+2.09%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>+$1.90</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4960.6</v>
+        <v>4932.6</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>+1.74%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>118.93</v>
+        <v>140.79</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="J81" s="3" t="n">
-        <v>39.82</v>
+        <v>31.48</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -4481,32 +4481,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>4742.69</v>
+        <v>4841.67</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+2.09%</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>$-109.35</t>
+          <t>+$1.90</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4876</v>
+        <v>4960.6</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+1.74%</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>133.31</v>
+        <v>118.93</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         </is>
       </c>
       <c r="J82" s="3" t="n">
-        <v>45.25</v>
+        <v>39.82</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -4530,32 +4530,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4749.28</v>
+        <v>4742.69</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>$-1.84</t>
+          <t>$-109.35</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4896.4</v>
+        <v>4876</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>147.12</v>
+        <v>133.31</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="J83" s="3" t="n">
-        <v>50.95</v>
+        <v>45.25</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -4579,32 +4579,32 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>4764.17</v>
+        <v>4749.28</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>+$0.36</t>
+          <t>$-1.84</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4928.3</v>
+        <v>4896.4</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>164.13</v>
+        <v>147.12</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="J84" s="3" t="n">
-        <v>59.04</v>
+        <v>50.95</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -4628,32 +4628,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4719.81</v>
+        <v>4764.17</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>+$19.77</t>
+          <t>+$0.36</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4885.4</v>
+        <v>4928.3</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>+2.02%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>165.59</v>
+        <v>164.13</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         </is>
       </c>
       <c r="J85" s="3" t="n">
-        <v>68.06</v>
+        <v>59.04</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -4677,32 +4677,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4702.05</v>
+        <v>4719.81</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>+$1.79</t>
+          <t>+$19.77</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4788.9</v>
+        <v>4885.4</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+2.02%</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>86.84999999999999</v>
+        <v>165.59</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="J86" s="3" t="n">
-        <v>67.61</v>
+        <v>68.06</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -4726,20 +4726,20 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>4649.73</v>
+        <v>4702.05</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>$-3.57</t>
+          <t>+$1.79</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -4747,11 +4747,11 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>139.17</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="J87" s="3" t="n">
-        <v>64.22</v>
+        <v>67.61</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -4775,32 +4775,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>4678.89</v>
+        <v>4649.73</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>$-0.67</t>
+          <t>$-3.57</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4784.1</v>
+        <v>4788.9</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>-2.74%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>105.21</v>
+        <v>139.17</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="J88" s="3" t="n">
-        <v>65.06999999999999</v>
+        <v>64.22</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -4824,32 +4824,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>4758.74</v>
+        <v>4678.89</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>+$2.49</t>
+          <t>$-0.67</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4919.1</v>
+        <v>4784.1</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>+2.91%</t>
+          <t>-2.74%</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>160.36</v>
+        <v>105.21</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         </is>
       </c>
       <c r="J89" s="3" t="n">
-        <v>61.51</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -4873,32 +4873,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>4668.9</v>
+        <v>4758.74</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>+3.50%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>+$2.18</t>
+          <t>+$2.49</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4780.2</v>
+        <v>4919.1</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>+2.64%</t>
+          <t>+2.91%</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>111.3</v>
+        <v>160.36</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="J90" s="3" t="n">
-        <v>61.02</v>
+        <v>61.51</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -4922,32 +4922,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>4511.22</v>
+        <v>4668.9</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+3.50%</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>$-0.71</t>
+          <t>+$2.18</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4657.4</v>
+        <v>4780.2</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+2.64%</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>146.18</v>
+        <v>111.3</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="J91" s="3" t="n">
-        <v>61.83</v>
+        <v>61.02</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -4971,32 +4971,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>4493.8</v>
+        <v>4511.22</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>+$12.74</t>
+          <t>$-0.71</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4624.8</v>
+        <v>4657.4</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>+2.62%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>131</v>
+        <v>146.18</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="J92" s="3" t="n">
-        <v>66.98999999999999</v>
+        <v>61.83</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -5020,32 +5020,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>4377.64</v>
+        <v>4493.8</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>+$5.15</t>
+          <t>+$12.74</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4506.7</v>
+        <v>4624.8</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>-3.82%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>129.06</v>
+        <v>131</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="J93" s="3" t="n">
-        <v>68.39</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -5069,32 +5069,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>4505.69</v>
+        <v>4377.64</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>$-19.39</t>
+          <t>+$5.15</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4685.7</v>
+        <v>4506.7</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>+3.37%</t>
+          <t>-3.82%</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>180.01</v>
+        <v>129.06</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="J94" s="3" t="n">
-        <v>65.34999999999999</v>
+        <v>68.39</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -5118,32 +5118,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>4491.37</v>
+        <v>4505.69</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>+$6.43</t>
+          <t>$-19.39</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4532.8</v>
+        <v>4685.7</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+3.37%</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>41.43</v>
+        <v>180.01</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -5156,43 +5156,43 @@
         </is>
       </c>
       <c r="J95" s="3" t="n">
-        <v>55.61</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>4407.46</v>
+        <v>4491.37</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>$-41.67</t>
+          <t>+$6.43</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4539.3</v>
+        <v>4532.8</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>131.84</v>
+        <v>41.43</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -5205,43 +5205,43 @@
         </is>
       </c>
       <c r="J96" s="3" t="n">
-        <v>52.06</v>
+        <v>55.61</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>4490.66</v>
+        <v>4407.46</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>-3.43%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>+$0.88</t>
+          <t>$-41.67</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4716.2</v>
+        <v>4539.3</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>-3.75%</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>225.54</v>
+        <v>131.84</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="J97" s="3" t="n">
-        <v>48.26</v>
+        <v>52.06</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -5265,32 +5265,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>4650.11</v>
+        <v>4490.66</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>-3.50%</t>
+          <t>-3.43%</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>+$5.66</t>
+          <t>+$0.88</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4745.4</v>
+        <v>4716.2</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>-5.88%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>95.29000000000001</v>
+        <v>225.54</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="J98" s="3" t="n">
-        <v>40.68</v>
+        <v>48.26</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -5314,32 +5314,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>4818.71</v>
+        <v>4650.11</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>-3.74%</t>
+          <t>-3.50%</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>$-0.26</t>
+          <t>+$5.66</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5041.7</v>
+        <v>4745.4</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>-2.23%</t>
+          <t>-5.88%</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>222.99</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         </is>
       </c>
       <c r="J99" s="3" t="n">
-        <v>34.38</v>
+        <v>40.68</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -5363,32 +5363,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>5006.14</v>
+        <v>4818.71</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-3.74%</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>+$3.07</t>
+          <t>$-0.26</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5156.7</v>
+        <v>5041.7</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-2.23%</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>150.56</v>
+        <v>222.99</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="J100" s="3" t="n">
-        <v>33</v>
+        <v>34.38</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -5412,32 +5412,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>5004.67</v>
+        <v>5006.14</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>$-13.14</t>
+          <t>+$3.07</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5150.3</v>
+        <v>5156.7</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>145.63</v>
+        <v>150.56</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="J101" s="3" t="n">
-        <v>34.78</v>
+        <v>33</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -5461,32 +5461,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>5019</v>
+        <v>5004.67</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>+$0.70</t>
+          <t>$-13.14</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5210.4</v>
+        <v>5150.3</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>-1.25%</t>
+          <t>-1.15%</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>191.4</v>
+        <v>145.63</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="J102" s="3" t="n">
-        <v>34.04</v>
+        <v>34.78</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -5510,32 +5510,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>5079.6</v>
+        <v>5019</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>+$2.23</t>
+          <t>+$0.70</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5276.4</v>
+        <v>5210.4</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>-1.25%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>196.8</v>
+        <v>191.4</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         </is>
       </c>
       <c r="J103" s="3" t="n">
-        <v>35.66</v>
+        <v>34.04</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -5559,32 +5559,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>5176.23</v>
+        <v>5079.6</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>$-3.94</t>
+          <t>+$2.23</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5330.9</v>
+        <v>5276.4</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>154.67</v>
+        <v>196.8</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="J104" s="3" t="n">
-        <v>34.34</v>
+        <v>35.66</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -5608,32 +5608,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>5191.58</v>
+        <v>5176.23</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>+$0.98</t>
+          <t>$-3.94</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5392.5</v>
+        <v>5330.9</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>200.92</v>
+        <v>154.67</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="J105" s="3" t="n">
-        <v>33.19</v>
+        <v>34.34</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -5657,32 +5657,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>5138.45</v>
+        <v>5191.58</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>+$8.38</t>
+          <t>+$0.98</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5251.9</v>
+        <v>5392.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>113.45</v>
+        <v>200.92</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -5694,8 +5694,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J106" s="6" t="n">
-        <v>27.57</v>
+      <c r="J106" s="3" t="n">
+        <v>33.19</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -5706,32 +5706,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>5171.8</v>
+        <v>5138.45</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>+$1.60</t>
+          <t>+$8.38</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5306.8</v>
+        <v>5251.9</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>135</v>
+        <v>113.45</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="J107" s="6" t="n">
-        <v>27.41</v>
+        <v>27.57</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -5755,32 +5755,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>5082.25</v>
+        <v>5171.8</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>+$15.58</t>
+          <t>+$1.60</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5225.6</v>
+        <v>5306.8</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>143.35</v>
+        <v>135</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="J108" s="6" t="n">
-        <v>28.59</v>
+        <v>27.41</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -5804,32 +5804,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>5140.39</v>
+        <v>5082.25</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>+$15.99</t>
+          <t>+$15.58</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5281.6</v>
+        <v>5225.6</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-1.06%</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>141.21</v>
+        <v>143.35</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -5841,8 +5841,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J109" s="3" t="n">
-        <v>29.02</v>
+      <c r="J109" s="6" t="n">
+        <v>28.59</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -5853,32 +5853,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>5087.78</v>
+        <v>5140.39</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>-4.39%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>+$3.27</t>
+          <t>+$15.99</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5269.7</v>
+        <v>5281.6</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>-3.53%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>181.92</v>
+        <v>141.21</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="J110" s="6" t="n">
-        <v>26.89</v>
+        <v>29.02</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -5902,32 +5902,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>5321.3</v>
+        <v>5087.78</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>+0.80%</t>
+          <t>-4.39%</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>+$22.33</t>
+          <t>+$3.27</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5462.6</v>
+        <v>5269.7</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-3.53%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>141.3</v>
+        <v>181.92</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         </is>
       </c>
       <c r="J111" s="6" t="n">
-        <v>25</v>
+        <v>26.89</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -5951,32 +5951,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>5278.9</v>
+        <v>5321.3</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>+1.83%</t>
+          <t>+0.80%</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>+$3.50</t>
+          <t>+$22.33</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5396.2</v>
+        <v>5462.6</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>117.3</v>
+        <v>141.3</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="J112" s="6" t="n">
-        <v>23.93</v>
+        <v>25</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -6000,32 +6000,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>5184.25</v>
+        <v>5278.9</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+1.83%</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>$-2.63</t>
+          <t>+$3.50</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5341.1</v>
+        <v>5396.2</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>156.85</v>
+        <v>117.3</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="J113" s="6" t="n">
-        <v>27.52</v>
+        <v>23.93</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -6049,32 +6049,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>5164.29</v>
+        <v>5184.25</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>+$0.50</t>
+          <t>$-2.63</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5374.2</v>
+        <v>5341.1</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>209.91</v>
+        <v>156.85</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -6086,8 +6086,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J114" s="3" t="n">
-        <v>32.13</v>
+      <c r="J114" s="6" t="n">
+        <v>27.52</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -6098,32 +6098,32 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>5142.79</v>
+        <v>5164.29</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>-1.62%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>+$2.64</t>
+          <t>+$0.50</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5322.8</v>
+        <v>5374.2</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>180.01</v>
+        <v>209.91</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="J115" s="3" t="n">
-        <v>30.2</v>
+        <v>32.13</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -6147,32 +6147,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>5227.48</v>
+        <v>5142.79</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>+2.36%</t>
+          <t>-1.62%</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>+$2.32</t>
+          <t>+$2.64</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5372</v>
+        <v>5322.8</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>144.52</v>
+        <v>180.01</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -6184,8 +6184,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J116" s="6" t="n">
-        <v>28.13</v>
+      <c r="J116" s="3" t="n">
+        <v>30.2</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -6196,32 +6196,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>5106.96</v>
+        <v>5227.48</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>+2.22%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>+$2.74</t>
+          <t>+$2.32</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5223.4</v>
+        <v>5372</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>+1.70%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>116.44</v>
+        <v>144.52</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -6233,8 +6233,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J117" s="3" t="n">
-        <v>35.59</v>
+      <c r="J117" s="6" t="n">
+        <v>28.13</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -6245,32 +6245,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>4996.02</v>
+        <v>5106.96</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+2.22%</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>$-2.27</t>
+          <t>+$2.74</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5136.1</v>
+        <v>5223.4</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+1.70%</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>140.08</v>
+        <v>116.44</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="J118" s="3" t="n">
-        <v>44.31</v>
+        <v>35.59</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -6294,32 +6294,32 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>4977.18</v>
+        <v>4996.02</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>+2.03%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>+$1.09</t>
+          <t>$-2.27</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5147.3</v>
+        <v>5136.1</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>170.12</v>
+        <v>140.08</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         </is>
       </c>
       <c r="J119" s="3" t="n">
-        <v>46.23</v>
+        <v>44.31</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -6343,32 +6343,32 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>4878.1</v>
+        <v>4977.18</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>-3.25%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>$-45.72</t>
+          <t>+$1.09</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5039.4</v>
+        <v>5147.3</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>-2.79%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>161.3</v>
+        <v>170.12</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="J120" s="3" t="n">
-        <v>46.39</v>
+        <v>46.23</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -6392,32 +6392,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>5041.86</v>
+        <v>4878.1</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>+2.44%</t>
+          <t>-3.25%</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>+$4.32</t>
+          <t>$-45.72</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5183.8</v>
+        <v>5039.4</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>+1.87%</t>
+          <t>-2.79%</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>141.94</v>
+        <v>161.3</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="J121" s="3" t="n">
-        <v>57.41</v>
+        <v>46.39</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -6441,32 +6441,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>4921.59</v>
+        <v>5041.86</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>-3.19%</t>
+          <t>+2.44%</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>+$1.40</t>
+          <t>+$4.32</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5088.4</v>
+        <v>5183.8</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>-2.94%</t>
+          <t>+1.87%</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>166.81</v>
+        <v>141.94</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="J122" s="3" t="n">
-        <v>62.1</v>
+        <v>57.41</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -6490,32 +6490,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>5083.84</v>
+        <v>4921.59</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>+1.18%</t>
+          <t>-3.19%</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>+$2.13</t>
+          <t>+$1.40</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5242.5</v>
+        <v>5088.4</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-2.94%</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>158.66</v>
+        <v>166.81</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="J123" s="3" t="n">
-        <v>63</v>
+        <v>62.1</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -6539,32 +6539,32 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>5024.38</v>
+        <v>5083.84</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>+1.18%</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>$-0.65</t>
+          <t>+$2.13</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5172.2</v>
+        <v>5242.5</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>147.82</v>
+        <v>158.66</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="J124" s="3" t="n">
-        <v>64.01000000000001</v>
+        <v>63</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -6588,32 +6588,32 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>5060.14</v>
+        <v>5024.38</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>+1.88%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>+$17.25</t>
+          <t>$-0.65</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5222.1</v>
+        <v>5172.2</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>+2.00%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>161.96</v>
+        <v>147.82</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         </is>
       </c>
       <c r="J125" s="3" t="n">
-        <v>63.42</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -6637,32 +6637,32 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>4966.93</v>
+        <v>5060.14</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>+3.92%</t>
+          <t>+1.88%</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>+$12.55</t>
+          <t>+$17.25</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5119.8</v>
+        <v>5222.1</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>+1.94%</t>
+          <t>+2.00%</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>152.87</v>
+        <v>161.96</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         </is>
       </c>
       <c r="J126" s="3" t="n">
-        <v>63.27</v>
+        <v>63.42</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -6686,32 +6686,32 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>4779.63</v>
+        <v>4966.93</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>-3.71%</t>
+          <t>+3.92%</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>+$12.00</t>
+          <t>+$12.55</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5022.3</v>
+        <v>5119.8</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>+1.94%</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>242.67</v>
+        <v>152.87</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         </is>
       </c>
       <c r="J127" s="3" t="n">
-        <v>57.48</v>
+        <v>63.27</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -6735,32 +6735,32 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>4963.89</v>
+        <v>4779.63</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-3.71%</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>+$1.30</t>
+          <t>+$12.00</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5089</v>
+        <v>5022.3</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>125.11</v>
+        <v>242.67</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         </is>
       </c>
       <c r="J128" s="3" t="n">
-        <v>49.25</v>
+        <v>57.48</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -6784,32 +6784,32 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>4944.42</v>
+        <v>4963.89</v>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>+6.13%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>+$13.04</t>
+          <t>+$1.30</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5072.5</v>
+        <v>5089</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>+6.11%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>128.08</v>
+        <v>125.11</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="J129" s="3" t="n">
-        <v>49.09</v>
+        <v>49.25</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -6833,32 +6833,32 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>4658.73</v>
+        <v>4944.42</v>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>-4.75%</t>
+          <t>+6.13%</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>$-76.67</t>
+          <t>+$13.04</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4780.4</v>
+        <v>5072.5</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>+6.11%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>121.67</v>
+        <v>128.08</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="J130" s="3" t="n">
-        <v>48.95</v>
+        <v>49.09</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -6882,36 +6882,36 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>4890.97</v>
+        <v>4658.73</v>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>-8.99%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>+$8.73</t>
+          <t>$-76.67</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4880</v>
+        <v>4780.4</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>-11.41%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>-10.97</v>
-      </c>
-      <c r="H131" s="7" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>121.67</v>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
@@ -6920,47 +6920,47 @@
         </is>
       </c>
       <c r="J131" s="3" t="n">
-        <v>41.41</v>
+        <v>48.95</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>5373.91</v>
+        <v>4890.97</v>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-8.99%</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>+$5.87</t>
+          <t>+$8.73</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5508.6</v>
+        <v>4880</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-11.41%</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>134.69</v>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-10.97</v>
+      </c>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
@@ -6969,43 +6969,43 @@
         </is>
       </c>
       <c r="J132" s="3" t="n">
-        <v>31.72</v>
+        <v>41.41</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>5416.79</v>
+        <v>5373.91</v>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>+4.60%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>+$5.87</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5494.6</v>
+        <v>5508.6</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>+4.32%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>77.81</v>
+        <v>134.69</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="J133" s="3" t="n">
-        <v>29.24</v>
+        <v>31.72</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -7029,32 +7029,32 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>5178.46</v>
+        <v>5416.79</v>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>+3.36%</t>
+          <t>+4.60%</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>+$3.14</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5267.3</v>
+        <v>5494.6</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+4.32%</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>88.84</v>
+        <v>77.81</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -7066,8 +7066,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J134" s="6" t="n">
-        <v>28.65</v>
+      <c r="J134" s="3" t="n">
+        <v>29.24</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -7078,32 +7078,32 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>5010.31</v>
+        <v>5178.46</v>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+3.36%</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>+$20.73</t>
+          <t>+$3.14</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5272.8</v>
+        <v>5267.3</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>262.49</v>
+        <v>88.84</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         </is>
       </c>
       <c r="J135" s="6" t="n">
-        <v>16.43</v>
+        <v>28.65</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -7127,32 +7127,32 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>4988.56</v>
+        <v>5010.31</v>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>+1.07%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>+$5.34</t>
+          <t>+$20.73</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5160.4</v>
+        <v>5272.8</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+2.18%</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>171.84</v>
+        <v>262.49</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="J136" s="6" t="n">
-        <v>10.44</v>
+        <v>16.43</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -7176,32 +7176,32 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>4935.8</v>
+        <v>4988.56</v>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>+$0.94</t>
+          <t>+$5.34</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5086.9</v>
+        <v>5160.4</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>+1.59%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>151.1</v>
+        <v>171.84</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="J137" s="6" t="n">
-        <v>8.960000000000001</v>
+        <v>10.44</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -7225,32 +7225,32 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>4831.51</v>
+        <v>4935.8</v>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+2.16%</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>+$0.31</t>
+          <t>+$0.94</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5007.5</v>
+        <v>5086.9</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>+1.51%</t>
+          <t>+1.59%</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>175.99</v>
+        <v>151.1</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -7262,7 +7262,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J138" s="2" t="inlineStr"/>
+      <c r="J138" s="6" t="n">
+        <v>8.960000000000001</v>
+      </c>
       <c r="K138" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -7272,32 +7274,32 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>4762.99</v>
+        <v>4831.51</v>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>+3.63%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>+$75.81</t>
+          <t>+$0.31</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4933</v>
+        <v>5007.5</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>+3.65%</t>
+          <t>+1.51%</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>170.01</v>
+        <v>175.99</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -7319,32 +7321,32 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>4596.18</v>
+        <v>4762.99</v>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+3.63%</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>+$1.80</t>
+          <t>+$75.81</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4759.2</v>
+        <v>4933</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>+3.65%</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>163.02</v>
+        <v>170.01</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -7366,32 +7368,32 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>4615.95</v>
+        <v>4596.18</v>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>+$6.28</t>
+          <t>+$1.80</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4787.7</v>
+        <v>4759.2</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>171.75</v>
+        <v>163.02</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -7413,32 +7415,32 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>4624.8</v>
+        <v>4615.95</v>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>+$3.59</t>
+          <t>+$6.28</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4798.9</v>
+        <v>4787.7</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>174.1</v>
+        <v>171.75</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -7460,32 +7462,32 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>4585.44</v>
+        <v>4624.8</v>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>+$5.33</t>
+          <t>+$3.59</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4760.2</v>
+        <v>4798.9</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>174.76</v>
+        <v>174.1</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -7507,32 +7509,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>4598.46</v>
+        <v>4585.44</v>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>+1.98%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>+$9.47</t>
+          <t>+$5.33</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4777.7</v>
+        <v>4760.2</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>+2.49%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>179.24</v>
+        <v>174.76</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -7554,32 +7556,32 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>4509.27</v>
+        <v>4598.46</v>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>+$1.86</t>
+          <t>+$9.47</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4661.4</v>
+        <v>4777.7</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>+0.90%</t>
+          <t>+2.49%</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>152.13</v>
+        <v>179.24</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -7601,32 +7603,32 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>4477.84</v>
+        <v>4509.27</v>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>$-0.03</t>
+          <t>+$1.86</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4620</v>
+        <v>4661.4</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.90%</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>142.16</v>
+        <v>152.13</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -7648,32 +7650,32 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>4456.26</v>
+        <v>4477.84</v>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>+$0.08</t>
+          <t>$-0.03</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4620.6</v>
+        <v>4620</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>-0.76%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>164.34</v>
+        <v>142.16</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -7695,32 +7697,32 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>4494.61</v>
+        <v>4456.26</v>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.85%</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>$-0.07</t>
+          <t>+$0.08</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4656.2</v>
+        <v>4620.6</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>-0.76%</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>161.59</v>
+        <v>164.34</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -7742,32 +7744,32 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>4449.11</v>
+        <v>4494.61</v>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>+2.70%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>+$28.96</t>
+          <t>$-0.07</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4608.1</v>
+        <v>4656.2</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>+2.76%</t>
+          <t>+1.04%</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>158.99</v>
+        <v>161.59</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -7789,32 +7791,32 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>4332.17</v>
+        <v>4449.11</v>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.70%</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+$28.96</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4484.4</v>
+        <v>4608.1</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.76%</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>152.23</v>
+        <v>158.99</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -7828,6 +7830,53 @@
       </c>
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>4332.17</v>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>4484.4</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>152.23</v>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -50,6 +50,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
       </patternFill>
@@ -70,12 +76,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
         <bgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-        <bgColor rgb="00C00000"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,19 +105,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K151"/>
+  <dimension ref="A1:K152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -561,36 +561,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4404</v>
+        <v>4402.09</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+1.43%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+$47.82</t>
+          <t>$-31.56</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4458.5</v>
+        <v>4390.3</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.53%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-11.79</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -598,8 +598,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n">
-        <v>51.72</v>
+      <c r="J2" s="4" t="n">
+        <v>55.8</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -610,32 +610,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4341.84</v>
+        <v>4404</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+1.61%</t>
+          <t>+1.43%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>$-34.98</t>
+          <t>+$47.82</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4461</v>
+        <v>4458.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+3.79%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>119.16</v>
+        <v>54.5</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -647,8 +647,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n">
-        <v>47.58</v>
+      <c r="J3" s="4" t="n">
+        <v>51.72</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -659,32 +659,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4273.01</v>
+        <v>4341.84</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+4.29%</t>
+          <t>+1.61%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$151.16</t>
+          <t>$-34.98</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4298.3</v>
+        <v>4461</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>+3.79%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>25.29</v>
+        <v>119.16</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -696,8 +696,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
-        <v>41.84</v>
+      <c r="J4" s="4" t="n">
+        <v>47.58</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -708,130 +708,130 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4097.29</v>
+        <v>4273.01</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>+4.29%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$22.75</t>
+          <t>+$151.16</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4339</v>
+        <v>4298.3</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+4.39%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>241.71</v>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>28.06</v>
+        <v>25.29</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>41.84</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4055.15</v>
+        <v>4097.29</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+1.04%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$33.39</t>
+          <t>+$22.75</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4156.4</v>
+        <v>4339</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>+4.39%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>101.25</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>19.9</v>
+        <v>241.71</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>28.06</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4044.36</v>
+        <v>4055.15</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$33.39</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4110.9</v>
+        <v>4156.4</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>66.54000000000001</v>
+        <v>101.25</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -843,8 +843,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>18.29</v>
+      <c r="J7" s="7" t="n">
+        <v>19.9</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -855,32 +855,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4103.64</v>
+        <v>4044.36</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$0.17</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4160.6</v>
+        <v>4110.9</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>56.96</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -892,8 +892,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="6" t="n">
-        <v>18.21</v>
+      <c r="J8" s="7" t="n">
+        <v>18.29</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -904,32 +904,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4066.23</v>
+        <v>4103.64</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$1.59</t>
+          <t>+$0.17</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4097</v>
+        <v>4160.6</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>30.77</v>
+        <v>56.96</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -941,8 +941,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>18.03</v>
+      <c r="J9" s="7" t="n">
+        <v>18.21</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -953,32 +953,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4028.54</v>
+        <v>4066.23</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$2.81</t>
+          <t>+$1.59</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4098.6</v>
+        <v>4097</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>70.06</v>
+        <v>30.77</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -990,8 +990,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="6" t="n">
-        <v>16.18</v>
+      <c r="J10" s="7" t="n">
+        <v>18.03</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1002,32 +1002,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4076.6</v>
+        <v>4028.54</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$43.44</t>
+          <t>+$2.81</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4136.4</v>
+        <v>4098.6</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>59.8</v>
+        <v>70.06</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1039,8 +1039,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>18.87</v>
+      <c r="J11" s="7" t="n">
+        <v>16.18</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1051,32 +1051,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4052.74</v>
+        <v>4076.6</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$0.61</t>
+          <t>+$43.44</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4129.7</v>
+        <v>4136.4</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>76.95999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1088,8 +1088,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J12" s="6" t="n">
-        <v>21.15</v>
+      <c r="J12" s="7" t="n">
+        <v>18.87</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1100,32 +1100,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4049.43</v>
+        <v>4052.74</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$-10.76</t>
+          <t>+$0.61</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4108.8</v>
+        <v>4129.7</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>59.37</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1137,8 +1137,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J13" s="6" t="n">
-        <v>19.94</v>
+      <c r="J13" s="7" t="n">
+        <v>21.15</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1149,32 +1149,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4130.11</v>
+        <v>4049.43</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$1.94</t>
+          <t>$-10.76</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4210.3</v>
+        <v>4108.8</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+1.84%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>80.19</v>
+        <v>59.37</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1186,8 +1186,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J14" s="6" t="n">
-        <v>21.96</v>
+      <c r="J14" s="7" t="n">
+        <v>19.94</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1198,32 +1198,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4077.87</v>
+        <v>4130.11</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$1.94</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4134.2</v>
+        <v>4210.3</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+1.84%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>56.33</v>
+        <v>80.19</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1235,8 +1235,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J15" s="6" t="n">
-        <v>21.74</v>
+      <c r="J15" s="7" t="n">
+        <v>21.96</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1247,32 +1247,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4007.49</v>
+        <v>4077.87</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$-12.24</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4073</v>
+        <v>4134.2</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>65.51000000000001</v>
+        <v>56.33</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1284,8 +1284,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J16" s="6" t="n">
-        <v>21.72</v>
+      <c r="J16" s="7" t="n">
+        <v>21.74</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1296,32 +1296,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4017.04</v>
+        <v>4007.49</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$1.19</t>
+          <t>$-12.24</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4075.8</v>
+        <v>4073</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>58.76</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1333,8 +1333,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J17" s="6" t="n">
-        <v>22.33</v>
+      <c r="J17" s="7" t="n">
+        <v>21.72</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1345,32 +1345,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3976.48</v>
+        <v>4017.04</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$4.31</t>
+          <t>+$1.19</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4048.7</v>
+        <v>4075.8</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>72.22</v>
+        <v>58.76</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1382,8 +1382,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J18" s="6" t="n">
-        <v>22.36</v>
+      <c r="J18" s="7" t="n">
+        <v>22.33</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1394,32 +1394,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4060.55</v>
+        <v>3976.48</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$0.46</t>
+          <t>+$4.31</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4109.3</v>
+        <v>4048.7</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>48.75</v>
+        <v>72.22</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1431,8 +1431,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="6" t="n">
-        <v>21.54</v>
+      <c r="J19" s="7" t="n">
+        <v>22.36</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1443,32 +1443,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4052.92</v>
+        <v>4060.55</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$5.21</t>
+          <t>+$0.46</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4127.9</v>
+        <v>4109.3</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+1.58%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>74.98</v>
+        <v>48.75</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1480,8 +1480,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J20" s="6" t="n">
-        <v>21.93</v>
+      <c r="J20" s="7" t="n">
+        <v>21.54</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1492,32 +1492,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4000.78</v>
+        <v>4052.92</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$5.21</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4063.6</v>
+        <v>4127.9</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>+1.58%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>62.82</v>
+        <v>74.98</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1529,8 +1529,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J21" s="6" t="n">
-        <v>22.96</v>
+      <c r="J21" s="7" t="n">
+        <v>21.93</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1541,32 +1541,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4119.29</v>
+        <v>4000.78</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4173.6</v>
+        <v>4063.6</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>54.31</v>
+        <v>62.82</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1578,8 +1578,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J22" s="6" t="n">
-        <v>24.16</v>
+      <c r="J22" s="7" t="n">
+        <v>22.96</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1590,32 +1590,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4123.38</v>
+        <v>4119.29</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4201.4</v>
+        <v>4173.6</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+1.43%</t>
+          <t>-0.66%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>78.02</v>
+        <v>54.31</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1627,8 +1627,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="6" t="n">
-        <v>28.73</v>
+      <c r="J23" s="7" t="n">
+        <v>24.16</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1639,32 +1639,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4077.4</v>
+        <v>4123.38</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4142.1</v>
+        <v>4201.4</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>+1.43%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>64.7</v>
+        <v>78.02</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1676,8 +1676,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J24" s="3" t="n">
-        <v>34.99</v>
+      <c r="J24" s="7" t="n">
+        <v>28.73</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1688,32 +1688,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4105.67</v>
+        <v>4077.4</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4218.3</v>
+        <v>4142.1</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>112.63</v>
+        <v>64.7</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1725,8 +1725,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="3" t="n">
-        <v>32.93</v>
+      <c r="J25" s="4" t="n">
+        <v>34.99</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1737,32 +1737,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4165.04</v>
+        <v>4105.67</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4228.6</v>
+        <v>4218.3</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>63.56</v>
+        <v>112.63</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1774,8 +1774,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="3" t="n">
-        <v>31.11</v>
+      <c r="J26" s="4" t="n">
+        <v>32.93</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1786,32 +1786,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4123.77</v>
+        <v>4165.04</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4186.6</v>
+        <v>4228.6</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>62.83</v>
+        <v>63.56</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1823,8 +1823,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="3" t="n">
-        <v>39.51</v>
+      <c r="J27" s="4" t="n">
+        <v>31.11</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1835,32 +1835,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4031.01</v>
+        <v>4123.77</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4142.9</v>
+        <v>4186.6</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>111.89</v>
+        <v>62.83</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1872,8 +1872,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="3" t="n">
-        <v>47.43</v>
+      <c r="J28" s="4" t="n">
+        <v>39.51</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1884,32 +1884,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4007.41</v>
+        <v>4031.01</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4098.5</v>
+        <v>4142.9</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>91.09</v>
+        <v>111.89</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1921,8 +1921,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="3" t="n">
-        <v>48.29</v>
+      <c r="J29" s="4" t="n">
+        <v>47.43</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1933,32 +1933,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4016.54</v>
+        <v>4007.41</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4098.8</v>
+        <v>4098.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>82.26000000000001</v>
+        <v>91.09</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1970,8 +1970,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="3" t="n">
-        <v>48.18</v>
+      <c r="J30" s="4" t="n">
+        <v>48.29</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1982,32 +1982,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4089.95</v>
+        <v>4016.54</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4156.9</v>
+        <v>4098.8</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>66.95</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2019,8 +2019,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="3" t="n">
-        <v>47.32</v>
+      <c r="J31" s="4" t="n">
+        <v>48.18</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2031,32 +2031,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4026.57</v>
+        <v>4089.95</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4107.5</v>
+        <v>4156.9</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>80.93000000000001</v>
+        <v>66.95</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2068,8 +2068,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J32" s="3" t="n">
-        <v>46.73</v>
+      <c r="J32" s="4" t="n">
+        <v>47.32</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2080,32 +2080,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3999.06</v>
+        <v>4026.57</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4068.1</v>
+        <v>4107.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3.39%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>69.04000000000001</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2117,8 +2117,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J33" s="3" t="n">
-        <v>46.06</v>
+      <c r="J33" s="4" t="n">
+        <v>46.73</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2129,32 +2129,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4110.14</v>
+        <v>3999.06</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4210.9</v>
+        <v>4068.1</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-3.39%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>100.76</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2166,8 +2166,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J34" s="3" t="n">
-        <v>43.81</v>
+      <c r="J34" s="4" t="n">
+        <v>46.06</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2178,32 +2178,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4191.26</v>
+        <v>4110.14</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4265.4</v>
+        <v>4210.9</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>74.14</v>
+        <v>100.76</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2215,8 +2215,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J35" s="3" t="n">
-        <v>42.64</v>
+      <c r="J35" s="4" t="n">
+        <v>43.81</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2227,32 +2227,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4209.02</v>
+        <v>4191.26</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4308.5</v>
+        <v>4265.4</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>99.48</v>
+        <v>74.14</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2264,8 +2264,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J36" s="3" t="n">
-        <v>43.1</v>
+      <c r="J36" s="4" t="n">
+        <v>42.64</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2276,130 +2276,130 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4257.71</v>
+        <v>4209.02</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4444.8</v>
+        <v>4308.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>-3.07%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>187.09</v>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>38.11</v>
+        <v>99.48</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>43.1</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4331.14</v>
+        <v>4257.71</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$7.23</t>
+          <t>+$1.76</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4417.3</v>
+        <v>4444.8</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>86.16</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>31.79</v>
+        <v>187.09</v>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>38.11</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4309.03</v>
+        <v>4331.14</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$52.77</t>
+          <t>+$7.23</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4414.3</v>
+        <v>4417.3</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>105.27</v>
+        <v>86.16</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2411,8 +2411,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J39" s="3" t="n">
-        <v>30.77</v>
+      <c r="J39" s="4" t="n">
+        <v>31.79</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2423,32 +2423,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4218.71</v>
+        <v>4309.03</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$-1.08</t>
+          <t>+$52.77</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4300.4</v>
+        <v>4414.3</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>81.69</v>
+        <v>105.27</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2460,8 +2460,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J40" s="3" t="n">
-        <v>30.55</v>
+      <c r="J40" s="4" t="n">
+        <v>30.77</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2472,36 +2472,36 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4210.69</v>
+        <v>4218.71</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+$10.16</t>
+          <t>$-1.08</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4174</v>
+        <v>4300.4</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+3.03%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>-36.69</v>
-      </c>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>81.69</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2509,48 +2509,48 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J41" s="6" t="n">
-        <v>23.08</v>
+      <c r="J41" s="4" t="n">
+        <v>30.55</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4071.28</v>
+        <v>4210.69</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>$-5.95</t>
+          <t>+$10.16</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4194.5</v>
+        <v>4174</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-3.57%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>123.22</v>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-36.69</v>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2558,44 +2558,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J42" s="6" t="n">
-        <v>12.35</v>
+      <c r="J42" s="7" t="n">
+        <v>23.08</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4259.29</v>
+        <v>4071.28</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-4.41%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-5.95</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4349.6</v>
+        <v>4194.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>-3.57%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>90.31</v>
+        <v>123.22</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2607,8 +2607,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J43" s="6" t="n">
-        <v>12.67</v>
+      <c r="J43" s="7" t="n">
+        <v>12.35</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2619,32 +2619,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4329.75</v>
+        <v>4259.29</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>$-2.37</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4427.3</v>
+        <v>4349.6</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>97.55</v>
+        <v>90.31</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2656,8 +2656,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J44" s="6" t="n">
-        <v>14.73</v>
+      <c r="J44" s="7" t="n">
+        <v>12.67</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2668,32 +2668,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4328.15</v>
+        <v>4329.75</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>-3.29%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+$7.90</t>
+          <t>$-2.37</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4429</v>
+        <v>4427.3</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>100.85</v>
+        <v>97.55</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2705,8 +2705,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J45" s="6" t="n">
-        <v>16.65</v>
+      <c r="J45" s="7" t="n">
+        <v>14.73</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2717,32 +2717,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4475.25</v>
+        <v>4328.15</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-3.29%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$7.80</t>
+          <t>+$7.90</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4570.4</v>
+        <v>4429</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>95.15000000000001</v>
+        <v>100.85</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2754,8 +2754,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J46" s="6" t="n">
-        <v>17.2</v>
+      <c r="J46" s="7" t="n">
+        <v>16.65</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2766,32 +2766,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4434.3</v>
+        <v>4475.25</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+$3.39</t>
+          <t>+$7.80</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4532</v>
+        <v>4570.4</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>97.7</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2803,8 +2803,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J47" s="6" t="n">
-        <v>18.03</v>
+      <c r="J47" s="7" t="n">
+        <v>17.2</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2815,32 +2815,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4487.78</v>
+        <v>4434.3</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>$-3.86</t>
+          <t>+$3.39</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4585.6</v>
+        <v>4532</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>97.81999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2852,8 +2852,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J48" s="6" t="n">
-        <v>21.29</v>
+      <c r="J48" s="7" t="n">
+        <v>18.03</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2864,32 +2864,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4484.69</v>
+        <v>4487.78</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>$-1.44</t>
+          <t>$-3.86</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4572.2</v>
+        <v>4585.6</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>87.51000000000001</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2901,8 +2901,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J49" s="6" t="n">
-        <v>22.22</v>
+      <c r="J49" s="7" t="n">
+        <v>21.29</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2913,32 +2913,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4540.28</v>
+        <v>4484.69</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>+$1.89</t>
+          <t>$-1.44</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4659.5</v>
+        <v>4572.2</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>119.22</v>
+        <v>87.51000000000001</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2950,8 +2950,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J50" s="6" t="n">
-        <v>21.39</v>
+      <c r="J50" s="7" t="n">
+        <v>22.22</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2962,32 +2962,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4495.57</v>
+        <v>4540.28</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>$-4.31</t>
+          <t>+$1.89</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4597</v>
+        <v>4659.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>101.43</v>
+        <v>119.22</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2999,8 +2999,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J51" s="6" t="n">
-        <v>20.79</v>
+      <c r="J51" s="7" t="n">
+        <v>21.39</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -3011,32 +3011,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4456.15</v>
+        <v>4495.57</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>$-6.52</t>
+          <t>$-4.31</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4545.1</v>
+        <v>4597</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>88.95</v>
+        <v>101.43</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3048,8 +3048,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J52" s="6" t="n">
-        <v>21.4</v>
+      <c r="J52" s="7" t="n">
+        <v>20.79</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3060,32 +3060,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4507.46</v>
+        <v>4456.15</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>+$58.22</t>
+          <t>$-6.52</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4601.2</v>
+        <v>4545.1</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>93.73999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3097,8 +3097,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J53" s="6" t="n">
-        <v>21.43</v>
+      <c r="J53" s="7" t="n">
+        <v>21.4</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3109,32 +3109,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4509.11</v>
+        <v>4507.46</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>$-1.21</t>
+          <t>+$58.22</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4623.4</v>
+        <v>4601.2</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>114.29</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3146,8 +3146,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J54" s="6" t="n">
-        <v>20.06</v>
+      <c r="J54" s="7" t="n">
+        <v>21.43</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3158,32 +3158,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4543.11</v>
+        <v>4509.11</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.75%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>$-3.76</t>
+          <t>$-1.21</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4643.6</v>
+        <v>4623.4</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>100.49</v>
+        <v>114.29</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3195,8 +3195,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J55" s="6" t="n">
-        <v>20.67</v>
+      <c r="J55" s="7" t="n">
+        <v>20.06</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3207,32 +3207,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4543.62</v>
+        <v>4543.11</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>$-3.76</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4634.4</v>
+        <v>4643.6</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>90.78</v>
+        <v>100.49</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3244,8 +3244,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J56" s="6" t="n">
-        <v>21.65</v>
+      <c r="J56" s="7" t="n">
+        <v>20.67</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3256,32 +3256,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4481.92</v>
+        <v>4543.62</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>+$1.98</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4610.1</v>
+        <v>4634.4</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>128.18</v>
+        <v>90.78</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3293,8 +3293,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J57" s="6" t="n">
-        <v>19.55</v>
+      <c r="J57" s="7" t="n">
+        <v>21.65</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -3305,32 +3305,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4566.08</v>
+        <v>4481.92</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>$-10.86</t>
+          <t>+$1.98</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4658.2</v>
+        <v>4610.1</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>92.12</v>
+        <v>128.18</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3342,8 +3342,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J58" s="6" t="n">
-        <v>17.38</v>
+      <c r="J58" s="7" t="n">
+        <v>19.55</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -3354,32 +3354,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4539.94</v>
+        <v>4566.08</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>+$0.18</t>
+          <t>$-10.86</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4662.2</v>
+        <v>4658.2</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>122.26</v>
+        <v>92.12</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3391,8 +3391,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J59" s="6" t="n">
-        <v>15.41</v>
+      <c r="J59" s="7" t="n">
+        <v>17.38</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -3403,32 +3403,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4652.24</v>
+        <v>4539.94</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$0.18</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4787.9</v>
+        <v>4662.2</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-2.63%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>135.66</v>
+        <v>122.26</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3440,8 +3440,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J60" s="6" t="n">
-        <v>15.84</v>
+      <c r="J60" s="7" t="n">
+        <v>15.41</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -3452,32 +3452,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4688.75</v>
+        <v>4652.24</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>$-3.60</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4810.3</v>
+        <v>4787.9</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>121.55</v>
+        <v>135.66</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3489,8 +3489,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J61" s="6" t="n">
-        <v>14.88</v>
+      <c r="J61" s="7" t="n">
+        <v>15.84</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -3501,32 +3501,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4715.2</v>
+        <v>4688.75</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>+$2.34</t>
+          <t>$-3.60</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4790.9</v>
+        <v>4810.3</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>75.7</v>
+        <v>121.55</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3538,44 +3538,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J62" s="6" t="n">
-        <v>12.74</v>
+      <c r="J62" s="7" t="n">
+        <v>14.88</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4734.64</v>
+        <v>4715.2</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>$-33.15</t>
+          <t>+$2.34</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4833.6</v>
+        <v>4790.9</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>98.95999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3587,44 +3587,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J63" s="6" t="n">
-        <v>12.08</v>
+      <c r="J63" s="7" t="n">
+        <v>12.74</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4715.83</v>
+        <v>4734.64</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>$-8.63</t>
+          <t>$-33.15</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4834.9</v>
+        <v>4833.6</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>119.07</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3636,8 +3636,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J64" s="6" t="n">
-        <v>11.42</v>
+      <c r="J64" s="7" t="n">
+        <v>12.08</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -3648,32 +3648,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4687.08</v>
+        <v>4715.83</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>+$7.02</t>
+          <t>$-8.63</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4815.5</v>
+        <v>4834.9</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>128.42</v>
+        <v>119.07</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3685,8 +3685,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J65" s="6" t="n">
-        <v>13.66</v>
+      <c r="J65" s="7" t="n">
+        <v>11.42</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -3697,32 +3697,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4690.82</v>
+        <v>4687.08</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>+2.93%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>+$3.16</t>
+          <t>+$7.02</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4798.2</v>
+        <v>4815.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>+2.74%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>107.38</v>
+        <v>128.42</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3734,8 +3734,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J66" s="6" t="n">
-        <v>14.27</v>
+      <c r="J66" s="7" t="n">
+        <v>13.66</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -3746,32 +3746,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4557.42</v>
+        <v>4690.82</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>+0.74%</t>
+          <t>+2.93%</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>+$3.16</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4670.1</v>
+        <v>4798.2</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>+2.74%</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>112.68</v>
+        <v>107.38</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3783,8 +3783,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J67" s="6" t="n">
-        <v>14.95</v>
+      <c r="J67" s="7" t="n">
+        <v>14.27</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -3795,32 +3795,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4523.72</v>
+        <v>4557.42</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>+0.74%</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>+$18.71</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4635.1</v>
+        <v>4670.1</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>+0.76%</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>111.38</v>
+        <v>112.68</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3832,8 +3832,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J68" s="6" t="n">
-        <v>16.42</v>
+      <c r="J68" s="7" t="n">
+        <v>14.95</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -3844,32 +3844,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4614.08</v>
+        <v>4523.72</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>+$4.06</t>
+          <t>+$18.71</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4747.8</v>
+        <v>4635.1</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-2.37%</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>133.72</v>
+        <v>111.38</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3881,8 +3881,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J69" s="6" t="n">
-        <v>15.85</v>
+      <c r="J69" s="7" t="n">
+        <v>16.42</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -3893,32 +3893,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>4621.53</v>
+        <v>4614.08</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>+$1.89</t>
+          <t>+$4.06</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4731.8</v>
+        <v>4747.8</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>110.27</v>
+        <v>133.72</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3930,8 +3930,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J70" s="6" t="n">
-        <v>15.16</v>
+      <c r="J70" s="7" t="n">
+        <v>15.85</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -3942,32 +3942,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4543.37</v>
+        <v>4621.53</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>$-3.14</t>
+          <t>+$1.89</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4661.7</v>
+        <v>4731.8</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>118.33</v>
+        <v>110.27</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3979,8 +3979,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J71" s="6" t="n">
-        <v>15.8</v>
+      <c r="J71" s="7" t="n">
+        <v>15.16</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -3991,32 +3991,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4596.87</v>
+        <v>4543.37</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-3.14</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4709.6</v>
+        <v>4661.7</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>112.73</v>
+        <v>118.33</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -4028,8 +4028,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J72" s="6" t="n">
-        <v>15.5</v>
+      <c r="J72" s="7" t="n">
+        <v>15.8</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -4040,32 +4040,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4681.73</v>
+        <v>4596.87</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>$-12.44</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4797</v>
+        <v>4709.6</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>-0.99%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>115.27</v>
+        <v>112.73</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -4077,8 +4077,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J73" s="6" t="n">
-        <v>20.95</v>
+      <c r="J73" s="7" t="n">
+        <v>15.5</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -4089,32 +4089,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>4710.12</v>
+        <v>4681.73</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>+$12.00</t>
+          <t>$-12.44</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4844.8</v>
+        <v>4797</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>134.68</v>
+        <v>115.27</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -4126,8 +4126,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J74" s="6" t="n">
-        <v>23.3</v>
+      <c r="J74" s="7" t="n">
+        <v>20.95</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -4138,32 +4138,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4694.36</v>
+        <v>4710.12</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>+$4.60</t>
+          <t>+$12.00</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4828.3</v>
+        <v>4844.8</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>133.94</v>
+        <v>134.68</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -4175,8 +4175,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J75" s="6" t="n">
-        <v>25.67</v>
+      <c r="J75" s="7" t="n">
+        <v>23.3</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -4187,32 +4187,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4740.15</v>
+        <v>4694.36</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>$-0.84</t>
+          <t>+$4.60</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4858.2</v>
+        <v>4828.3</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>118.05</v>
+        <v>133.94</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -4224,8 +4224,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J76" s="6" t="n">
-        <v>28.47</v>
+      <c r="J76" s="7" t="n">
+        <v>25.67</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -4236,32 +4236,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>4720.07</v>
+        <v>4740.15</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>-2.09%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>+$0.62</t>
+          <t>$-0.84</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4824.1</v>
+        <v>4858.2</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>-2.26%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>104.03</v>
+        <v>118.05</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -4273,8 +4273,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J77" s="3" t="n">
-        <v>30.98</v>
+      <c r="J77" s="7" t="n">
+        <v>28.47</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -4285,32 +4285,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>4820.58</v>
+        <v>4720.07</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>$-56.03</t>
+          <t>+$0.62</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4935.4</v>
+        <v>4824.1</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>-1.04%</t>
+          <t>-2.26%</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>114.82</v>
+        <v>104.03</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -4322,8 +4322,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J78" s="3" t="n">
-        <v>32.7</v>
+      <c r="J78" s="4" t="n">
+        <v>30.98</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -4334,32 +4334,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>4831.76</v>
+        <v>4820.58</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>+$1.68</t>
+          <t>$-56.03</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4987.3</v>
+        <v>4935.4</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>-1.04%</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>155.54</v>
+        <v>114.82</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -4371,8 +4371,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J79" s="3" t="n">
-        <v>30.87</v>
+      <c r="J79" s="4" t="n">
+        <v>32.7</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -4383,32 +4383,32 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>4790.65</v>
+        <v>4831.76</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>$-1.72</t>
+          <t>+$1.68</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4916.6</v>
+        <v>4987.3</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>125.95</v>
+        <v>155.54</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -4420,8 +4420,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J80" s="6" t="n">
-        <v>28.9</v>
+      <c r="J80" s="4" t="n">
+        <v>30.87</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -4432,32 +4432,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4791.81</v>
+        <v>4790.65</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>$-1.72</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4932.6</v>
+        <v>4916.6</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>140.79</v>
+        <v>125.95</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -4469,8 +4469,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J81" s="3" t="n">
-        <v>31.48</v>
+      <c r="J81" s="7" t="n">
+        <v>28.9</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -4481,32 +4481,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>4841.67</v>
+        <v>4791.81</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>+2.09%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>+$1.90</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4960.6</v>
+        <v>4932.6</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>+1.74%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>118.93</v>
+        <v>140.79</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -4518,8 +4518,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J82" s="3" t="n">
-        <v>39.82</v>
+      <c r="J82" s="4" t="n">
+        <v>31.48</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -4530,32 +4530,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4742.69</v>
+        <v>4841.67</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+2.09%</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>$-109.35</t>
+          <t>+$1.90</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4876</v>
+        <v>4960.6</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+1.74%</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>133.31</v>
+        <v>118.93</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -4567,8 +4567,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J83" s="3" t="n">
-        <v>45.25</v>
+      <c r="J83" s="4" t="n">
+        <v>39.82</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -4579,32 +4579,32 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>4749.28</v>
+        <v>4742.69</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>$-1.84</t>
+          <t>$-109.35</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4896.4</v>
+        <v>4876</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>147.12</v>
+        <v>133.31</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -4616,8 +4616,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J84" s="3" t="n">
-        <v>50.95</v>
+      <c r="J84" s="4" t="n">
+        <v>45.25</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -4628,32 +4628,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4764.17</v>
+        <v>4749.28</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>+$0.36</t>
+          <t>$-1.84</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4928.3</v>
+        <v>4896.4</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>164.13</v>
+        <v>147.12</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -4665,8 +4665,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J85" s="3" t="n">
-        <v>59.04</v>
+      <c r="J85" s="4" t="n">
+        <v>50.95</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -4677,32 +4677,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4719.81</v>
+        <v>4764.17</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>+$19.77</t>
+          <t>+$0.36</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4885.4</v>
+        <v>4928.3</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>+2.02%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>165.59</v>
+        <v>164.13</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4714,8 +4714,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J86" s="3" t="n">
-        <v>68.06</v>
+      <c r="J86" s="4" t="n">
+        <v>59.04</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -4726,32 +4726,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>4702.05</v>
+        <v>4719.81</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>+$1.79</t>
+          <t>+$19.77</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4788.9</v>
+        <v>4885.4</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+2.02%</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>86.84999999999999</v>
+        <v>165.59</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4763,8 +4763,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J87" s="3" t="n">
-        <v>67.61</v>
+      <c r="J87" s="4" t="n">
+        <v>68.06</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -4775,20 +4775,20 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>4649.73</v>
+        <v>4702.05</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>$-3.57</t>
+          <t>+$1.79</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -4796,11 +4796,11 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>139.17</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4812,8 +4812,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J88" s="3" t="n">
-        <v>64.22</v>
+      <c r="J88" s="4" t="n">
+        <v>67.61</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -4824,32 +4824,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>4678.89</v>
+        <v>4649.73</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>$-0.67</t>
+          <t>$-3.57</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4784.1</v>
+        <v>4788.9</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>-2.74%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>105.21</v>
+        <v>139.17</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4861,8 +4861,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J89" s="3" t="n">
-        <v>65.06999999999999</v>
+      <c r="J89" s="4" t="n">
+        <v>64.22</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -4873,32 +4873,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>4758.74</v>
+        <v>4678.89</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>+$2.49</t>
+          <t>$-0.67</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4919.1</v>
+        <v>4784.1</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>+2.91%</t>
+          <t>-2.74%</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>160.36</v>
+        <v>105.21</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4910,8 +4910,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J90" s="3" t="n">
-        <v>61.51</v>
+      <c r="J90" s="4" t="n">
+        <v>65.06999999999999</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -4922,32 +4922,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>4668.9</v>
+        <v>4758.74</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>+3.50%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>+$2.18</t>
+          <t>+$2.49</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4780.2</v>
+        <v>4919.1</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>+2.64%</t>
+          <t>+2.91%</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>111.3</v>
+        <v>160.36</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4959,8 +4959,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J91" s="3" t="n">
-        <v>61.02</v>
+      <c r="J91" s="4" t="n">
+        <v>61.51</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -4971,32 +4971,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>4511.22</v>
+        <v>4668.9</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+3.50%</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>$-0.71</t>
+          <t>+$2.18</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4657.4</v>
+        <v>4780.2</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+2.64%</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>146.18</v>
+        <v>111.3</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -5008,8 +5008,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J92" s="3" t="n">
-        <v>61.83</v>
+      <c r="J92" s="4" t="n">
+        <v>61.02</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -5020,32 +5020,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>4493.8</v>
+        <v>4511.22</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>+$12.74</t>
+          <t>$-0.71</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4624.8</v>
+        <v>4657.4</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>+2.62%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>131</v>
+        <v>146.18</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -5057,8 +5057,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J93" s="3" t="n">
-        <v>66.98999999999999</v>
+      <c r="J93" s="4" t="n">
+        <v>61.83</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -5069,32 +5069,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>4377.64</v>
+        <v>4493.8</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>+$5.15</t>
+          <t>+$12.74</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4506.7</v>
+        <v>4624.8</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>-3.82%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>129.06</v>
+        <v>131</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -5106,8 +5106,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J94" s="3" t="n">
-        <v>68.39</v>
+      <c r="J94" s="4" t="n">
+        <v>66.98999999999999</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -5118,32 +5118,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>4505.69</v>
+        <v>4377.64</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>$-19.39</t>
+          <t>+$5.15</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4685.7</v>
+        <v>4506.7</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>+3.37%</t>
+          <t>-3.82%</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>180.01</v>
+        <v>129.06</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -5155,8 +5155,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J95" s="3" t="n">
-        <v>65.34999999999999</v>
+      <c r="J95" s="4" t="n">
+        <v>68.39</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -5167,32 +5167,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>4491.37</v>
+        <v>4505.69</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>+$6.43</t>
+          <t>$-19.39</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4532.8</v>
+        <v>4685.7</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+3.37%</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>41.43</v>
+        <v>180.01</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -5204,44 +5204,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J96" s="3" t="n">
-        <v>55.61</v>
+      <c r="J96" s="4" t="n">
+        <v>65.34999999999999</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>4407.46</v>
+        <v>4491.37</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>$-41.67</t>
+          <t>+$6.43</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4539.3</v>
+        <v>4532.8</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>131.84</v>
+        <v>41.43</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -5253,44 +5253,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J97" s="3" t="n">
-        <v>52.06</v>
+      <c r="J97" s="4" t="n">
+        <v>55.61</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>4490.66</v>
+        <v>4407.46</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>-3.43%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>+$0.88</t>
+          <t>$-41.67</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4716.2</v>
+        <v>4539.3</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>-3.75%</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>225.54</v>
+        <v>131.84</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -5302,8 +5302,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J98" s="3" t="n">
-        <v>48.26</v>
+      <c r="J98" s="4" t="n">
+        <v>52.06</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -5314,32 +5314,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>4650.11</v>
+        <v>4490.66</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>-3.50%</t>
+          <t>-3.43%</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>+$5.66</t>
+          <t>+$0.88</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4745.4</v>
+        <v>4716.2</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>-5.88%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>95.29000000000001</v>
+        <v>225.54</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -5351,8 +5351,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J99" s="3" t="n">
-        <v>40.68</v>
+      <c r="J99" s="4" t="n">
+        <v>48.26</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -5363,32 +5363,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>4818.71</v>
+        <v>4650.11</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>-3.74%</t>
+          <t>-3.50%</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>$-0.26</t>
+          <t>+$5.66</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5041.7</v>
+        <v>4745.4</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>-2.23%</t>
+          <t>-5.88%</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>222.99</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -5400,8 +5400,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J100" s="3" t="n">
-        <v>34.38</v>
+      <c r="J100" s="4" t="n">
+        <v>40.68</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -5412,32 +5412,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>5006.14</v>
+        <v>4818.71</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-3.74%</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>+$3.07</t>
+          <t>$-0.26</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5156.7</v>
+        <v>5041.7</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-2.23%</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>150.56</v>
+        <v>222.99</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -5449,8 +5449,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J101" s="3" t="n">
-        <v>33</v>
+      <c r="J101" s="4" t="n">
+        <v>34.38</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -5461,32 +5461,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>5004.67</v>
+        <v>5006.14</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>$-13.14</t>
+          <t>+$3.07</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5150.3</v>
+        <v>5156.7</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>145.63</v>
+        <v>150.56</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -5498,8 +5498,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J102" s="3" t="n">
-        <v>34.78</v>
+      <c r="J102" s="4" t="n">
+        <v>33</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -5510,32 +5510,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>5019</v>
+        <v>5004.67</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>+$0.70</t>
+          <t>$-13.14</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5210.4</v>
+        <v>5150.3</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>-1.25%</t>
+          <t>-1.15%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>191.4</v>
+        <v>145.63</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -5547,8 +5547,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J103" s="3" t="n">
-        <v>34.04</v>
+      <c r="J103" s="4" t="n">
+        <v>34.78</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -5559,32 +5559,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>5079.6</v>
+        <v>5019</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>+$2.23</t>
+          <t>+$0.70</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5276.4</v>
+        <v>5210.4</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>-1.25%</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>196.8</v>
+        <v>191.4</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -5596,8 +5596,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J104" s="3" t="n">
-        <v>35.66</v>
+      <c r="J104" s="4" t="n">
+        <v>34.04</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -5608,32 +5608,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>5176.23</v>
+        <v>5079.6</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>$-3.94</t>
+          <t>+$2.23</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5330.9</v>
+        <v>5276.4</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>154.67</v>
+        <v>196.8</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -5645,8 +5645,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J105" s="3" t="n">
-        <v>34.34</v>
+      <c r="J105" s="4" t="n">
+        <v>35.66</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -5657,32 +5657,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>5191.58</v>
+        <v>5176.23</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>+$0.98</t>
+          <t>$-3.94</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5392.5</v>
+        <v>5330.9</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>200.92</v>
+        <v>154.67</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -5694,8 +5694,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J106" s="3" t="n">
-        <v>33.19</v>
+      <c r="J106" s="4" t="n">
+        <v>34.34</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -5706,32 +5706,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>5138.45</v>
+        <v>5191.58</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>+$8.38</t>
+          <t>+$0.98</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5251.9</v>
+        <v>5392.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>113.45</v>
+        <v>200.92</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -5743,8 +5743,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J107" s="6" t="n">
-        <v>27.57</v>
+      <c r="J107" s="4" t="n">
+        <v>33.19</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -5755,32 +5755,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>5171.8</v>
+        <v>5138.45</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>+$1.60</t>
+          <t>+$8.38</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5306.8</v>
+        <v>5251.9</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>135</v>
+        <v>113.45</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -5792,8 +5792,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J108" s="6" t="n">
-        <v>27.41</v>
+      <c r="J108" s="7" t="n">
+        <v>27.57</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -5804,32 +5804,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>5082.25</v>
+        <v>5171.8</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>+$15.58</t>
+          <t>+$1.60</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5225.6</v>
+        <v>5306.8</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>143.35</v>
+        <v>135</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -5841,8 +5841,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J109" s="6" t="n">
-        <v>28.59</v>
+      <c r="J109" s="7" t="n">
+        <v>27.41</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -5853,32 +5853,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>5140.39</v>
+        <v>5082.25</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>+$15.99</t>
+          <t>+$15.58</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5281.6</v>
+        <v>5225.6</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-1.06%</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>141.21</v>
+        <v>143.35</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5890,8 +5890,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J110" s="6" t="n">
-        <v>29.02</v>
+      <c r="J110" s="7" t="n">
+        <v>28.59</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -5902,32 +5902,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>5087.78</v>
+        <v>5140.39</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>-4.39%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>+$3.27</t>
+          <t>+$15.99</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5269.7</v>
+        <v>5281.6</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>-3.53%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>181.92</v>
+        <v>141.21</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5939,8 +5939,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J111" s="6" t="n">
-        <v>26.89</v>
+      <c r="J111" s="7" t="n">
+        <v>29.02</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -5951,32 +5951,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>5321.3</v>
+        <v>5087.78</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>+0.80%</t>
+          <t>-4.39%</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>+$22.33</t>
+          <t>+$3.27</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5462.6</v>
+        <v>5269.7</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-3.53%</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>141.3</v>
+        <v>181.92</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5988,8 +5988,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J112" s="6" t="n">
-        <v>25</v>
+      <c r="J112" s="7" t="n">
+        <v>26.89</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -6000,32 +6000,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>5278.9</v>
+        <v>5321.3</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>+1.83%</t>
+          <t>+0.80%</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>+$3.50</t>
+          <t>+$22.33</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5396.2</v>
+        <v>5462.6</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>117.3</v>
+        <v>141.3</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -6037,8 +6037,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J113" s="6" t="n">
-        <v>23.93</v>
+      <c r="J113" s="7" t="n">
+        <v>25</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -6049,32 +6049,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>5184.25</v>
+        <v>5278.9</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+1.83%</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>$-2.63</t>
+          <t>+$3.50</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5341.1</v>
+        <v>5396.2</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>156.85</v>
+        <v>117.3</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -6086,8 +6086,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J114" s="6" t="n">
-        <v>27.52</v>
+      <c r="J114" s="7" t="n">
+        <v>23.93</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -6098,32 +6098,32 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>5164.29</v>
+        <v>5184.25</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>+$0.50</t>
+          <t>$-2.63</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5374.2</v>
+        <v>5341.1</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>209.91</v>
+        <v>156.85</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -6135,8 +6135,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J115" s="3" t="n">
-        <v>32.13</v>
+      <c r="J115" s="7" t="n">
+        <v>27.52</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -6147,32 +6147,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>5142.79</v>
+        <v>5164.29</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>-1.62%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>+$2.64</t>
+          <t>+$0.50</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5322.8</v>
+        <v>5374.2</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>180.01</v>
+        <v>209.91</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -6184,8 +6184,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J116" s="3" t="n">
-        <v>30.2</v>
+      <c r="J116" s="4" t="n">
+        <v>32.13</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -6196,32 +6196,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>5227.48</v>
+        <v>5142.79</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>+2.36%</t>
+          <t>-1.62%</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>+$2.32</t>
+          <t>+$2.64</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5372</v>
+        <v>5322.8</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>144.52</v>
+        <v>180.01</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -6233,8 +6233,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J117" s="6" t="n">
-        <v>28.13</v>
+      <c r="J117" s="4" t="n">
+        <v>30.2</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -6245,32 +6245,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>5106.96</v>
+        <v>5227.48</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>+2.22%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>+$2.74</t>
+          <t>+$2.32</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5223.4</v>
+        <v>5372</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>+1.70%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>116.44</v>
+        <v>144.52</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -6282,8 +6282,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J118" s="3" t="n">
-        <v>35.59</v>
+      <c r="J118" s="7" t="n">
+        <v>28.13</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -6294,32 +6294,32 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>4996.02</v>
+        <v>5106.96</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+2.22%</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>$-2.27</t>
+          <t>+$2.74</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5136.1</v>
+        <v>5223.4</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+1.70%</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>140.08</v>
+        <v>116.44</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -6331,8 +6331,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J119" s="3" t="n">
-        <v>44.31</v>
+      <c r="J119" s="4" t="n">
+        <v>35.59</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -6343,32 +6343,32 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>4977.18</v>
+        <v>4996.02</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>+2.03%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>+$1.09</t>
+          <t>$-2.27</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5147.3</v>
+        <v>5136.1</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>170.12</v>
+        <v>140.08</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -6380,8 +6380,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J120" s="3" t="n">
-        <v>46.23</v>
+      <c r="J120" s="4" t="n">
+        <v>44.31</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -6392,32 +6392,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>4878.1</v>
+        <v>4977.18</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>-3.25%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>$-45.72</t>
+          <t>+$1.09</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5039.4</v>
+        <v>5147.3</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>-2.79%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>161.3</v>
+        <v>170.12</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -6429,8 +6429,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J121" s="3" t="n">
-        <v>46.39</v>
+      <c r="J121" s="4" t="n">
+        <v>46.23</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -6441,32 +6441,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>5041.86</v>
+        <v>4878.1</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>+2.44%</t>
+          <t>-3.25%</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>+$4.32</t>
+          <t>$-45.72</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5183.8</v>
+        <v>5039.4</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>+1.87%</t>
+          <t>-2.79%</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>141.94</v>
+        <v>161.3</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -6478,8 +6478,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J122" s="3" t="n">
-        <v>57.41</v>
+      <c r="J122" s="4" t="n">
+        <v>46.39</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -6490,32 +6490,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>4921.59</v>
+        <v>5041.86</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>-3.19%</t>
+          <t>+2.44%</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>+$1.40</t>
+          <t>+$4.32</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5088.4</v>
+        <v>5183.8</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>-2.94%</t>
+          <t>+1.87%</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>166.81</v>
+        <v>141.94</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -6527,8 +6527,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J123" s="3" t="n">
-        <v>62.1</v>
+      <c r="J123" s="4" t="n">
+        <v>57.41</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -6539,32 +6539,32 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>5083.84</v>
+        <v>4921.59</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>+1.18%</t>
+          <t>-3.19%</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>+$2.13</t>
+          <t>+$1.40</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5242.5</v>
+        <v>5088.4</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-2.94%</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>158.66</v>
+        <v>166.81</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -6576,8 +6576,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J124" s="3" t="n">
-        <v>63</v>
+      <c r="J124" s="4" t="n">
+        <v>62.1</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -6588,32 +6588,32 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>5024.38</v>
+        <v>5083.84</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>+1.18%</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>$-0.65</t>
+          <t>+$2.13</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5172.2</v>
+        <v>5242.5</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>147.82</v>
+        <v>158.66</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -6625,8 +6625,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J125" s="3" t="n">
-        <v>64.01000000000001</v>
+      <c r="J125" s="4" t="n">
+        <v>63</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -6637,32 +6637,32 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>5060.14</v>
+        <v>5024.38</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>+1.88%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>+$17.25</t>
+          <t>$-0.65</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5222.1</v>
+        <v>5172.2</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>+2.00%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>161.96</v>
+        <v>147.82</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -6674,8 +6674,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J126" s="3" t="n">
-        <v>63.42</v>
+      <c r="J126" s="4" t="n">
+        <v>64.01000000000001</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -6686,32 +6686,32 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>4966.93</v>
+        <v>5060.14</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>+3.92%</t>
+          <t>+1.88%</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>+$12.55</t>
+          <t>+$17.25</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5119.8</v>
+        <v>5222.1</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>+1.94%</t>
+          <t>+2.00%</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>152.87</v>
+        <v>161.96</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -6723,8 +6723,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J127" s="3" t="n">
-        <v>63.27</v>
+      <c r="J127" s="4" t="n">
+        <v>63.42</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -6735,32 +6735,32 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>4779.63</v>
+        <v>4966.93</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>-3.71%</t>
+          <t>+3.92%</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>+$12.00</t>
+          <t>+$12.55</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5022.3</v>
+        <v>5119.8</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>+1.94%</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>242.67</v>
+        <v>152.87</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -6772,8 +6772,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J128" s="3" t="n">
-        <v>57.48</v>
+      <c r="J128" s="4" t="n">
+        <v>63.27</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -6784,32 +6784,32 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>4963.89</v>
+        <v>4779.63</v>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-3.71%</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>+$1.30</t>
+          <t>+$12.00</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5089</v>
+        <v>5022.3</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>125.11</v>
+        <v>242.67</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -6821,8 +6821,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J129" s="3" t="n">
-        <v>49.25</v>
+      <c r="J129" s="4" t="n">
+        <v>57.48</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -6833,32 +6833,32 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>4944.42</v>
+        <v>4963.89</v>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>+6.13%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>+$13.04</t>
+          <t>+$1.30</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5072.5</v>
+        <v>5089</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>+6.11%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>128.08</v>
+        <v>125.11</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -6870,8 +6870,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J130" s="3" t="n">
-        <v>49.09</v>
+      <c r="J130" s="4" t="n">
+        <v>49.25</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -6882,32 +6882,32 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>4658.73</v>
+        <v>4944.42</v>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>-4.75%</t>
+          <t>+6.13%</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>$-76.67</t>
+          <t>+$13.04</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4780.4</v>
+        <v>5072.5</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>+6.11%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>121.67</v>
+        <v>128.08</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -6919,8 +6919,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J131" s="3" t="n">
-        <v>48.95</v>
+      <c r="J131" s="4" t="n">
+        <v>49.09</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -6931,36 +6931,36 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>4890.97</v>
+        <v>4658.73</v>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>-8.99%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>+$8.73</t>
+          <t>$-76.67</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4880</v>
+        <v>4780.4</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>-11.41%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>-10.97</v>
-      </c>
-      <c r="H132" s="7" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>121.67</v>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
@@ -6968,48 +6968,48 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J132" s="3" t="n">
-        <v>41.41</v>
+      <c r="J132" s="4" t="n">
+        <v>48.95</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>5373.91</v>
+        <v>4890.97</v>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-8.99%</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>+$5.87</t>
+          <t>+$8.73</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5508.6</v>
+        <v>4880</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-11.41%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>134.69</v>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-10.97</v>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
@@ -7017,44 +7017,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J133" s="3" t="n">
-        <v>31.72</v>
+      <c r="J133" s="4" t="n">
+        <v>41.41</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>5416.79</v>
+        <v>5373.91</v>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>+4.60%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>+$5.87</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5494.6</v>
+        <v>5508.6</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>+4.32%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>77.81</v>
+        <v>134.69</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -7066,8 +7066,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J134" s="3" t="n">
-        <v>29.24</v>
+      <c r="J134" s="4" t="n">
+        <v>31.72</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -7078,32 +7078,32 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>5178.46</v>
+        <v>5416.79</v>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>+3.36%</t>
+          <t>+4.60%</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>+$3.14</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5267.3</v>
+        <v>5494.6</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+4.32%</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>88.84</v>
+        <v>77.81</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -7115,8 +7115,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J135" s="6" t="n">
-        <v>28.65</v>
+      <c r="J135" s="4" t="n">
+        <v>29.24</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -7127,32 +7127,32 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>5010.31</v>
+        <v>5178.46</v>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+3.36%</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>+$20.73</t>
+          <t>+$3.14</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5272.8</v>
+        <v>5267.3</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>262.49</v>
+        <v>88.84</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -7164,8 +7164,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J136" s="6" t="n">
-        <v>16.43</v>
+      <c r="J136" s="7" t="n">
+        <v>28.65</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -7176,32 +7176,32 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>4988.56</v>
+        <v>5010.31</v>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>+1.07%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>+$5.34</t>
+          <t>+$20.73</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5160.4</v>
+        <v>5272.8</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+2.18%</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>171.84</v>
+        <v>262.49</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -7213,8 +7213,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J137" s="6" t="n">
-        <v>10.44</v>
+      <c r="J137" s="7" t="n">
+        <v>16.43</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -7225,32 +7225,32 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>4935.8</v>
+        <v>4988.56</v>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>+$0.94</t>
+          <t>+$5.34</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5086.9</v>
+        <v>5160.4</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>+1.59%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>151.1</v>
+        <v>171.84</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -7262,8 +7262,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J138" s="6" t="n">
-        <v>8.960000000000001</v>
+      <c r="J138" s="7" t="n">
+        <v>10.44</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -7274,32 +7274,32 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>4831.51</v>
+        <v>4935.8</v>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+2.16%</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>+$0.31</t>
+          <t>+$0.94</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5007.5</v>
+        <v>5086.9</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>+1.51%</t>
+          <t>+1.59%</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>175.99</v>
+        <v>151.1</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -7311,7 +7311,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J139" s="2" t="inlineStr"/>
+      <c r="J139" s="7" t="n">
+        <v>8.960000000000001</v>
+      </c>
       <c r="K139" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -7321,32 +7323,32 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>4762.99</v>
+        <v>4831.51</v>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>+3.63%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>+$75.81</t>
+          <t>+$0.31</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4933</v>
+        <v>5007.5</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>+3.65%</t>
+          <t>+1.51%</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>170.01</v>
+        <v>175.99</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -7368,32 +7370,32 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>4596.18</v>
+        <v>4762.99</v>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+3.63%</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>+$1.80</t>
+          <t>+$75.81</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4759.2</v>
+        <v>4933</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>+3.65%</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>163.02</v>
+        <v>170.01</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -7415,32 +7417,32 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>4615.95</v>
+        <v>4596.18</v>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>+$6.28</t>
+          <t>+$1.80</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4787.7</v>
+        <v>4759.2</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>171.75</v>
+        <v>163.02</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -7462,32 +7464,32 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>4624.8</v>
+        <v>4615.95</v>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>+$3.59</t>
+          <t>+$6.28</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4798.9</v>
+        <v>4787.7</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>174.1</v>
+        <v>171.75</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -7509,32 +7511,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>4585.44</v>
+        <v>4624.8</v>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>+$5.33</t>
+          <t>+$3.59</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4760.2</v>
+        <v>4798.9</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>174.76</v>
+        <v>174.1</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -7556,32 +7558,32 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>4598.46</v>
+        <v>4585.44</v>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>+1.98%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>+$9.47</t>
+          <t>+$5.33</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4777.7</v>
+        <v>4760.2</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>+2.49%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>179.24</v>
+        <v>174.76</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -7603,32 +7605,32 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>4509.27</v>
+        <v>4598.46</v>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>+$1.86</t>
+          <t>+$9.47</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4661.4</v>
+        <v>4777.7</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>+0.90%</t>
+          <t>+2.49%</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>152.13</v>
+        <v>179.24</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -7650,32 +7652,32 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>4477.84</v>
+        <v>4509.27</v>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>$-0.03</t>
+          <t>+$1.86</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4620</v>
+        <v>4661.4</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.90%</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>142.16</v>
+        <v>152.13</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -7697,32 +7699,32 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>4456.26</v>
+        <v>4477.84</v>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>+$0.08</t>
+          <t>$-0.03</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4620.6</v>
+        <v>4620</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>-0.76%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>164.34</v>
+        <v>142.16</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -7744,32 +7746,32 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>4494.61</v>
+        <v>4456.26</v>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.85%</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>$-0.07</t>
+          <t>+$0.08</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4656.2</v>
+        <v>4620.6</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>-0.76%</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>161.59</v>
+        <v>164.34</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -7791,32 +7793,32 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>4449.11</v>
+        <v>4494.61</v>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>+2.70%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>+$28.96</t>
+          <t>$-0.07</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4608.1</v>
+        <v>4656.2</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>+2.76%</t>
+          <t>+1.04%</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>158.99</v>
+        <v>161.59</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -7838,32 +7840,32 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>4332.17</v>
+        <v>4449.11</v>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.70%</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+$28.96</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4484.4</v>
+        <v>4608.1</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.76%</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>152.23</v>
+        <v>158.99</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -7877,6 +7879,53 @@
       </c>
       <c r="J151" s="2" t="inlineStr"/>
       <c r="K151" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>4332.17</v>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>4484.4</v>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>152.23</v>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -50,14 +50,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-        <bgColor rgb="00C00000"/>
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
       </patternFill>
     </fill>
     <fill>
@@ -105,10 +105,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K152"/>
+  <dimension ref="A1:K153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -561,36 +561,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4402.09</v>
+        <v>4332.24</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-1.59%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>$-31.56</t>
+          <t>$-48.32</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4390.3</v>
+        <v>4437.3</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-1.53%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-11.79</v>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>105.06</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -598,8 +598,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>55.8</v>
+      <c r="J2" s="3" t="n">
+        <v>62.44</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -610,36 +610,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4404</v>
+        <v>4402.09</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+1.43%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+$47.82</t>
+          <t>$-31.56</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4458.5</v>
+        <v>4390.3</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.53%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-11.79</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -647,8 +647,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>51.72</v>
+      <c r="J3" s="3" t="n">
+        <v>55.8</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -659,32 +659,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4341.84</v>
+        <v>4404</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+1.61%</t>
+          <t>+1.43%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$-34.98</t>
+          <t>+$47.82</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4461</v>
+        <v>4458.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+3.79%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>119.16</v>
+        <v>54.5</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -696,8 +696,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>47.58</v>
+      <c r="J4" s="3" t="n">
+        <v>51.72</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -708,32 +708,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4273.01</v>
+        <v>4341.84</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+4.29%</t>
+          <t>+1.61%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+$151.16</t>
+          <t>$-34.98</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4298.3</v>
+        <v>4461</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>+3.79%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>25.29</v>
+        <v>119.16</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -745,8 +745,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>41.84</v>
+      <c r="J5" s="3" t="n">
+        <v>47.58</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -757,130 +757,130 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4097.29</v>
+        <v>4273.01</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>+4.29%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$22.75</t>
+          <t>+$151.16</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4339</v>
+        <v>4298.3</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+4.39%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>241.71</v>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="n">
-        <v>28.06</v>
+        <v>25.29</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>41.84</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4055.15</v>
+        <v>4097.29</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+1.04%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$33.39</t>
+          <t>+$22.75</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4156.4</v>
+        <v>4339</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>+4.39%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>101.25</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>241.71</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J7" s="7" t="n">
-        <v>19.9</v>
+        <v>28.06</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4044.36</v>
+        <v>4055.15</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$33.39</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4110.9</v>
+        <v>4156.4</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>66.54000000000001</v>
+        <v>101.25</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="J8" s="7" t="n">
-        <v>18.29</v>
+        <v>19.9</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -904,32 +904,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4103.64</v>
+        <v>4044.36</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$0.17</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4160.6</v>
+        <v>4110.9</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>56.96</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="J9" s="7" t="n">
-        <v>18.21</v>
+        <v>18.29</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -953,32 +953,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4066.23</v>
+        <v>4103.64</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$1.59</t>
+          <t>+$0.17</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4097</v>
+        <v>4160.6</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>30.77</v>
+        <v>56.96</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="J10" s="7" t="n">
-        <v>18.03</v>
+        <v>18.21</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1002,32 +1002,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4028.54</v>
+        <v>4066.23</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$2.81</t>
+          <t>+$1.59</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4098.6</v>
+        <v>4097</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>70.06</v>
+        <v>30.77</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="J11" s="7" t="n">
-        <v>16.18</v>
+        <v>18.03</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1051,32 +1051,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4076.6</v>
+        <v>4028.54</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$43.44</t>
+          <t>+$2.81</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4136.4</v>
+        <v>4098.6</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>59.8</v>
+        <v>70.06</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="J12" s="7" t="n">
-        <v>18.87</v>
+        <v>16.18</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1100,32 +1100,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4052.74</v>
+        <v>4076.6</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$0.61</t>
+          <t>+$43.44</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4129.7</v>
+        <v>4136.4</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>76.95999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="J13" s="7" t="n">
-        <v>21.15</v>
+        <v>18.87</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1149,32 +1149,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4049.43</v>
+        <v>4052.74</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$-10.76</t>
+          <t>+$0.61</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4108.8</v>
+        <v>4129.7</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>59.37</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="J14" s="7" t="n">
-        <v>19.94</v>
+        <v>21.15</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1198,32 +1198,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4130.11</v>
+        <v>4049.43</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+$1.94</t>
+          <t>$-10.76</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4210.3</v>
+        <v>4108.8</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+1.84%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>80.19</v>
+        <v>59.37</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="J15" s="7" t="n">
-        <v>21.96</v>
+        <v>19.94</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1247,32 +1247,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4077.87</v>
+        <v>4130.11</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$1.94</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4134.2</v>
+        <v>4210.3</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+1.84%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>56.33</v>
+        <v>80.19</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="J16" s="7" t="n">
-        <v>21.74</v>
+        <v>21.96</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1296,32 +1296,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4007.49</v>
+        <v>4077.87</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>$-12.24</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4073</v>
+        <v>4134.2</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>65.51000000000001</v>
+        <v>56.33</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="J17" s="7" t="n">
-        <v>21.72</v>
+        <v>21.74</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1345,32 +1345,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4017.04</v>
+        <v>4007.49</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+$1.19</t>
+          <t>$-12.24</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4075.8</v>
+        <v>4073</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>58.76</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="J18" s="7" t="n">
-        <v>22.33</v>
+        <v>21.72</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1394,32 +1394,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3976.48</v>
+        <v>4017.04</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$4.31</t>
+          <t>+$1.19</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4048.7</v>
+        <v>4075.8</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>72.22</v>
+        <v>58.76</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="J19" s="7" t="n">
-        <v>22.36</v>
+        <v>22.33</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1443,32 +1443,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4060.55</v>
+        <v>3976.48</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$0.46</t>
+          <t>+$4.31</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4109.3</v>
+        <v>4048.7</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>48.75</v>
+        <v>72.22</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="J20" s="7" t="n">
-        <v>21.54</v>
+        <v>22.36</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1492,32 +1492,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4052.92</v>
+        <v>4060.55</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$5.21</t>
+          <t>+$0.46</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4127.9</v>
+        <v>4109.3</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+1.58%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>74.98</v>
+        <v>48.75</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="J21" s="7" t="n">
-        <v>21.93</v>
+        <v>21.54</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1541,32 +1541,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4000.78</v>
+        <v>4052.92</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$5.21</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4063.6</v>
+        <v>4127.9</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>+1.58%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>62.82</v>
+        <v>74.98</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="J22" s="7" t="n">
-        <v>22.96</v>
+        <v>21.93</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1590,32 +1590,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4119.29</v>
+        <v>4000.78</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>$-20.33</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4173.6</v>
+        <v>4063.6</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>54.31</v>
+        <v>62.82</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="J23" s="7" t="n">
-        <v>24.16</v>
+        <v>22.96</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1639,32 +1639,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4123.38</v>
+        <v>4119.29</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>+$2.30</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4201.4</v>
+        <v>4173.6</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+1.43%</t>
+          <t>-0.66%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>78.02</v>
+        <v>54.31</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="J24" s="7" t="n">
-        <v>28.73</v>
+        <v>24.16</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1688,32 +1688,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4077.4</v>
+        <v>4123.38</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$-8.21</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4142.1</v>
+        <v>4201.4</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>+1.43%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>64.7</v>
+        <v>78.02</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1725,8 +1725,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n">
-        <v>34.99</v>
+      <c r="J25" s="7" t="n">
+        <v>28.73</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1737,32 +1737,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4105.67</v>
+        <v>4077.4</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$-0.30</t>
+          <t>$-8.21</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4218.3</v>
+        <v>4142.1</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>112.63</v>
+        <v>64.7</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1774,8 +1774,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n">
-        <v>32.93</v>
+      <c r="J26" s="3" t="n">
+        <v>34.99</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1786,32 +1786,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4165.04</v>
+        <v>4105.67</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+$53.63</t>
+          <t>$-0.30</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4228.6</v>
+        <v>4218.3</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>63.56</v>
+        <v>112.63</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1823,8 +1823,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n">
-        <v>31.11</v>
+      <c r="J27" s="3" t="n">
+        <v>32.93</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1835,32 +1835,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4123.77</v>
+        <v>4165.04</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+$2.98</t>
+          <t>+$53.63</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4186.6</v>
+        <v>4228.6</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>62.83</v>
+        <v>63.56</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1872,8 +1872,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J28" s="4" t="n">
-        <v>39.51</v>
+      <c r="J28" s="3" t="n">
+        <v>31.11</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1884,32 +1884,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4031.01</v>
+        <v>4123.77</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+$11.76</t>
+          <t>+$2.98</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4142.9</v>
+        <v>4186.6</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>111.89</v>
+        <v>62.83</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1921,8 +1921,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n">
-        <v>47.43</v>
+      <c r="J29" s="3" t="n">
+        <v>39.51</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1933,32 +1933,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4007.41</v>
+        <v>4031.01</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+$7.94</t>
+          <t>+$11.76</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4098.5</v>
+        <v>4142.9</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>91.09</v>
+        <v>111.89</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1970,8 +1970,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n">
-        <v>48.29</v>
+      <c r="J30" s="3" t="n">
+        <v>47.43</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1982,32 +1982,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4016.54</v>
+        <v>4007.41</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>$-5.13</t>
+          <t>+$7.94</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4098.8</v>
+        <v>4098.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>82.26000000000001</v>
+        <v>91.09</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2019,8 +2019,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n">
-        <v>48.18</v>
+      <c r="J31" s="3" t="n">
+        <v>48.29</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2031,32 +2031,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4089.95</v>
+        <v>4016.54</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+$2.53</t>
+          <t>$-5.13</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4156.9</v>
+        <v>4098.8</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>66.95</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2068,8 +2068,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J32" s="4" t="n">
-        <v>47.32</v>
+      <c r="J32" s="3" t="n">
+        <v>48.18</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2080,32 +2080,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4026.57</v>
+        <v>4089.95</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$2.53</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4107.5</v>
+        <v>4156.9</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>80.93000000000001</v>
+        <v>66.95</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2117,8 +2117,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n">
-        <v>46.73</v>
+      <c r="J33" s="3" t="n">
+        <v>47.32</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2129,32 +2129,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3999.06</v>
+        <v>4026.57</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>+$6.24</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4068.1</v>
+        <v>4107.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-3.39%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>69.04000000000001</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2166,8 +2166,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J34" s="4" t="n">
-        <v>46.06</v>
+      <c r="J34" s="3" t="n">
+        <v>46.73</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2178,32 +2178,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4110.14</v>
+        <v>3999.06</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+$1.65</t>
+          <t>+$6.24</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4210.9</v>
+        <v>4068.1</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-3.39%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>100.76</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2215,8 +2215,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J35" s="4" t="n">
-        <v>43.81</v>
+      <c r="J35" s="3" t="n">
+        <v>46.06</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2227,32 +2227,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4191.26</v>
+        <v>4110.14</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>$-64.06</t>
+          <t>+$1.65</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4265.4</v>
+        <v>4210.9</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>74.14</v>
+        <v>100.76</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2264,8 +2264,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J36" s="4" t="n">
-        <v>42.64</v>
+      <c r="J36" s="3" t="n">
+        <v>43.81</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2276,32 +2276,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4209.02</v>
+        <v>4191.26</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>$-3.73</t>
+          <t>$-64.06</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4308.5</v>
+        <v>4265.4</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>99.48</v>
+        <v>74.14</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2313,8 +2313,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J37" s="4" t="n">
-        <v>43.1</v>
+      <c r="J37" s="3" t="n">
+        <v>42.64</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2325,130 +2325,130 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4257.71</v>
+        <v>4209.02</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+$1.76</t>
+          <t>$-3.73</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4444.8</v>
+        <v>4308.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>-3.07%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>187.09</v>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>38.11</v>
+        <v>99.48</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>43.1</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4331.14</v>
+        <v>4257.71</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+$7.23</t>
+          <t>+$1.76</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4417.3</v>
+        <v>4444.8</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>86.16</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>31.79</v>
+        <v>187.09</v>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>38.11</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4309.03</v>
+        <v>4331.14</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+$52.77</t>
+          <t>+$7.23</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4414.3</v>
+        <v>4417.3</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>105.27</v>
+        <v>86.16</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2460,8 +2460,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J40" s="4" t="n">
-        <v>30.77</v>
+      <c r="J40" s="3" t="n">
+        <v>31.79</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2472,32 +2472,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4218.71</v>
+        <v>4309.03</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>$-1.08</t>
+          <t>+$52.77</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4300.4</v>
+        <v>4414.3</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>81.69</v>
+        <v>105.27</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2509,8 +2509,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J41" s="4" t="n">
-        <v>30.55</v>
+      <c r="J41" s="3" t="n">
+        <v>30.77</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2521,36 +2521,36 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4210.69</v>
+        <v>4218.71</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+$10.16</t>
+          <t>$-1.08</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4174</v>
+        <v>4300.4</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+3.03%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>-36.69</v>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>81.69</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2558,48 +2558,48 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J42" s="7" t="n">
-        <v>23.08</v>
+      <c r="J42" s="3" t="n">
+        <v>30.55</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4071.28</v>
+        <v>4210.69</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>$-5.95</t>
+          <t>+$10.16</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4194.5</v>
+        <v>4174</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-3.57%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>123.22</v>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-36.69</v>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2608,43 +2608,43 @@
         </is>
       </c>
       <c r="J43" s="7" t="n">
-        <v>12.35</v>
+        <v>23.08</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4259.29</v>
+        <v>4071.28</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-4.41%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-5.95</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4349.6</v>
+        <v>4194.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>-3.57%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>90.31</v>
+        <v>123.22</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="J44" s="7" t="n">
-        <v>12.67</v>
+        <v>12.35</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2668,32 +2668,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4329.75</v>
+        <v>4259.29</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>$-2.37</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4427.3</v>
+        <v>4349.6</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>97.55</v>
+        <v>90.31</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="J45" s="7" t="n">
-        <v>14.73</v>
+        <v>12.67</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2717,32 +2717,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4328.15</v>
+        <v>4329.75</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>-3.29%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+$7.90</t>
+          <t>$-2.37</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4429</v>
+        <v>4427.3</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>100.85</v>
+        <v>97.55</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="J46" s="7" t="n">
-        <v>16.65</v>
+        <v>14.73</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2766,32 +2766,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4475.25</v>
+        <v>4328.15</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-3.29%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+$7.80</t>
+          <t>+$7.90</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4570.4</v>
+        <v>4429</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>95.15000000000001</v>
+        <v>100.85</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="J47" s="7" t="n">
-        <v>17.2</v>
+        <v>16.65</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2815,32 +2815,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4434.3</v>
+        <v>4475.25</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+$3.39</t>
+          <t>+$7.80</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4532</v>
+        <v>4570.4</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>97.7</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="J48" s="7" t="n">
-        <v>18.03</v>
+        <v>17.2</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2864,32 +2864,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4487.78</v>
+        <v>4434.3</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>$-3.86</t>
+          <t>+$3.39</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4585.6</v>
+        <v>4532</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>97.81999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="J49" s="7" t="n">
-        <v>21.29</v>
+        <v>18.03</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2913,32 +2913,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4484.69</v>
+        <v>4487.78</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>$-1.44</t>
+          <t>$-3.86</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4572.2</v>
+        <v>4585.6</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>87.51000000000001</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="J50" s="7" t="n">
-        <v>22.22</v>
+        <v>21.29</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2962,32 +2962,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4540.28</v>
+        <v>4484.69</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+$1.89</t>
+          <t>$-1.44</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4659.5</v>
+        <v>4572.2</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>119.22</v>
+        <v>87.51000000000001</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="J51" s="7" t="n">
-        <v>21.39</v>
+        <v>22.22</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -3011,32 +3011,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4495.57</v>
+        <v>4540.28</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>$-4.31</t>
+          <t>+$1.89</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4597</v>
+        <v>4659.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>101.43</v>
+        <v>119.22</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="J52" s="7" t="n">
-        <v>20.79</v>
+        <v>21.39</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3060,32 +3060,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4456.15</v>
+        <v>4495.57</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>$-6.52</t>
+          <t>$-4.31</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4545.1</v>
+        <v>4597</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>88.95</v>
+        <v>101.43</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="J53" s="7" t="n">
-        <v>21.4</v>
+        <v>20.79</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3109,32 +3109,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4507.46</v>
+        <v>4456.15</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+$58.22</t>
+          <t>$-6.52</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4601.2</v>
+        <v>4545.1</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>93.73999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="J54" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3158,32 +3158,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4509.11</v>
+        <v>4507.46</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>$-1.21</t>
+          <t>+$58.22</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4623.4</v>
+        <v>4601.2</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>114.29</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="J55" s="7" t="n">
-        <v>20.06</v>
+        <v>21.43</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3207,32 +3207,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4543.11</v>
+        <v>4509.11</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.75%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>$-3.76</t>
+          <t>$-1.21</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4643.6</v>
+        <v>4623.4</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>100.49</v>
+        <v>114.29</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="J56" s="7" t="n">
-        <v>20.67</v>
+        <v>20.06</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3256,32 +3256,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4543.62</v>
+        <v>4543.11</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>+$1.23</t>
+          <t>$-3.76</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4634.4</v>
+        <v>4643.6</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>90.78</v>
+        <v>100.49</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="J57" s="7" t="n">
-        <v>21.65</v>
+        <v>20.67</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -3305,32 +3305,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4481.92</v>
+        <v>4543.62</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>+$1.98</t>
+          <t>+$1.23</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4610.1</v>
+        <v>4634.4</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>128.18</v>
+        <v>90.78</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="J58" s="7" t="n">
-        <v>19.55</v>
+        <v>21.65</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -3354,32 +3354,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4566.08</v>
+        <v>4481.92</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>$-10.86</t>
+          <t>+$1.98</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4658.2</v>
+        <v>4610.1</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>92.12</v>
+        <v>128.18</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="J59" s="7" t="n">
-        <v>17.38</v>
+        <v>19.55</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -3403,32 +3403,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4539.94</v>
+        <v>4566.08</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>+$0.18</t>
+          <t>$-10.86</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4662.2</v>
+        <v>4658.2</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>122.26</v>
+        <v>92.12</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="J60" s="7" t="n">
-        <v>15.41</v>
+        <v>17.38</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -3452,32 +3452,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4652.24</v>
+        <v>4539.94</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>+$3.43</t>
+          <t>+$0.18</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4787.9</v>
+        <v>4662.2</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-2.63%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>135.66</v>
+        <v>122.26</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="J61" s="7" t="n">
-        <v>15.84</v>
+        <v>15.41</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -3501,32 +3501,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4688.75</v>
+        <v>4652.24</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>$-3.60</t>
+          <t>+$3.43</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4810.3</v>
+        <v>4787.9</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>121.55</v>
+        <v>135.66</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="J62" s="7" t="n">
-        <v>14.88</v>
+        <v>15.84</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -3550,32 +3550,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4715.2</v>
+        <v>4688.75</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>+$2.34</t>
+          <t>$-3.60</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4790.9</v>
+        <v>4810.3</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>75.7</v>
+        <v>121.55</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3588,43 +3588,43 @@
         </is>
       </c>
       <c r="J63" s="7" t="n">
-        <v>12.74</v>
+        <v>14.88</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4734.64</v>
+        <v>4715.2</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>$-33.15</t>
+          <t>+$2.34</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4833.6</v>
+        <v>4790.9</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>98.95999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3637,43 +3637,43 @@
         </is>
       </c>
       <c r="J64" s="7" t="n">
-        <v>12.08</v>
+        <v>12.74</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4715.83</v>
+        <v>4734.64</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>$-8.63</t>
+          <t>$-33.15</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4834.9</v>
+        <v>4833.6</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>119.07</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="J65" s="7" t="n">
-        <v>11.42</v>
+        <v>12.08</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -3697,32 +3697,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4687.08</v>
+        <v>4715.83</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>+$7.02</t>
+          <t>$-8.63</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4815.5</v>
+        <v>4834.9</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>128.42</v>
+        <v>119.07</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="J66" s="7" t="n">
-        <v>13.66</v>
+        <v>11.42</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -3746,32 +3746,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4690.82</v>
+        <v>4687.08</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>+2.93%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>+$3.16</t>
+          <t>+$7.02</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4798.2</v>
+        <v>4815.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>+2.74%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>107.38</v>
+        <v>128.42</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="J67" s="7" t="n">
-        <v>14.27</v>
+        <v>13.66</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -3795,32 +3795,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4557.42</v>
+        <v>4690.82</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>+0.74%</t>
+          <t>+2.93%</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>+$3.16</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4670.1</v>
+        <v>4798.2</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>+2.74%</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>112.68</v>
+        <v>107.38</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="J68" s="7" t="n">
-        <v>14.95</v>
+        <v>14.27</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -3844,32 +3844,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4523.72</v>
+        <v>4557.42</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>+0.74%</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>+$18.71</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4635.1</v>
+        <v>4670.1</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>+0.76%</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>111.38</v>
+        <v>112.68</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="J69" s="7" t="n">
-        <v>16.42</v>
+        <v>14.95</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -3893,32 +3893,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>4614.08</v>
+        <v>4523.72</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>+$4.06</t>
+          <t>+$18.71</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4747.8</v>
+        <v>4635.1</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-2.37%</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>133.72</v>
+        <v>111.38</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="J70" s="7" t="n">
-        <v>15.85</v>
+        <v>16.42</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -3942,32 +3942,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4621.53</v>
+        <v>4614.08</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>+$1.89</t>
+          <t>+$4.06</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4731.8</v>
+        <v>4747.8</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>110.27</v>
+        <v>133.72</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="J71" s="7" t="n">
-        <v>15.16</v>
+        <v>15.85</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -3991,32 +3991,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4543.37</v>
+        <v>4621.53</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>$-3.14</t>
+          <t>+$1.89</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4661.7</v>
+        <v>4731.8</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>118.33</v>
+        <v>110.27</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="J72" s="7" t="n">
-        <v>15.8</v>
+        <v>15.16</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -4040,32 +4040,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4596.87</v>
+        <v>4543.37</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>+$3.24</t>
+          <t>$-3.14</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4709.6</v>
+        <v>4661.7</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>112.73</v>
+        <v>118.33</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="J73" s="7" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -4089,32 +4089,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>4681.73</v>
+        <v>4596.87</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>$-12.44</t>
+          <t>+$3.24</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4797</v>
+        <v>4709.6</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>-0.99%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>115.27</v>
+        <v>112.73</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="J74" s="7" t="n">
-        <v>20.95</v>
+        <v>15.5</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -4138,32 +4138,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4710.12</v>
+        <v>4681.73</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>+$12.00</t>
+          <t>$-12.44</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4844.8</v>
+        <v>4797</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>134.68</v>
+        <v>115.27</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="J75" s="7" t="n">
-        <v>23.3</v>
+        <v>20.95</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -4187,32 +4187,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4694.36</v>
+        <v>4710.12</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>+$4.60</t>
+          <t>+$12.00</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4828.3</v>
+        <v>4844.8</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>133.94</v>
+        <v>134.68</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="J76" s="7" t="n">
-        <v>25.67</v>
+        <v>23.3</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -4236,32 +4236,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>4740.15</v>
+        <v>4694.36</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>$-0.84</t>
+          <t>+$4.60</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4858.2</v>
+        <v>4828.3</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>118.05</v>
+        <v>133.94</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="J77" s="7" t="n">
-        <v>28.47</v>
+        <v>25.67</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -4285,32 +4285,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>4720.07</v>
+        <v>4740.15</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>-2.09%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>+$0.62</t>
+          <t>$-0.84</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4824.1</v>
+        <v>4858.2</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>-2.26%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>104.03</v>
+        <v>118.05</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -4322,8 +4322,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J78" s="4" t="n">
-        <v>30.98</v>
+      <c r="J78" s="7" t="n">
+        <v>28.47</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -4334,32 +4334,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>4820.58</v>
+        <v>4720.07</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>$-56.03</t>
+          <t>+$0.62</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4935.4</v>
+        <v>4824.1</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>-1.04%</t>
+          <t>-2.26%</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>114.82</v>
+        <v>104.03</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -4371,8 +4371,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J79" s="4" t="n">
-        <v>32.7</v>
+      <c r="J79" s="3" t="n">
+        <v>30.98</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -4383,32 +4383,32 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>4831.76</v>
+        <v>4820.58</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>+$1.68</t>
+          <t>$-56.03</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4987.3</v>
+        <v>4935.4</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>-1.04%</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>155.54</v>
+        <v>114.82</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -4420,8 +4420,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J80" s="4" t="n">
-        <v>30.87</v>
+      <c r="J80" s="3" t="n">
+        <v>32.7</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -4432,32 +4432,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4790.65</v>
+        <v>4831.76</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>$-1.72</t>
+          <t>+$1.68</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4916.6</v>
+        <v>4987.3</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>125.95</v>
+        <v>155.54</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -4469,8 +4469,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J81" s="7" t="n">
-        <v>28.9</v>
+      <c r="J81" s="3" t="n">
+        <v>30.87</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -4481,32 +4481,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>4791.81</v>
+        <v>4790.65</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>$-2.31</t>
+          <t>$-1.72</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4932.6</v>
+        <v>4916.6</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>140.79</v>
+        <v>125.95</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -4518,8 +4518,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J82" s="4" t="n">
-        <v>31.48</v>
+      <c r="J82" s="7" t="n">
+        <v>28.9</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -4530,32 +4530,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4841.67</v>
+        <v>4791.81</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>+2.09%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>+$1.90</t>
+          <t>$-2.31</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4960.6</v>
+        <v>4932.6</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>+1.74%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>118.93</v>
+        <v>140.79</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -4567,8 +4567,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J83" s="4" t="n">
-        <v>39.82</v>
+      <c r="J83" s="3" t="n">
+        <v>31.48</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -4579,32 +4579,32 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>4742.69</v>
+        <v>4841.67</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+2.09%</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>$-109.35</t>
+          <t>+$1.90</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4876</v>
+        <v>4960.6</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+1.74%</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>133.31</v>
+        <v>118.93</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -4616,8 +4616,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J84" s="4" t="n">
-        <v>45.25</v>
+      <c r="J84" s="3" t="n">
+        <v>39.82</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -4628,32 +4628,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4749.28</v>
+        <v>4742.69</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>$-1.84</t>
+          <t>$-109.35</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4896.4</v>
+        <v>4876</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>147.12</v>
+        <v>133.31</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -4665,8 +4665,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J85" s="4" t="n">
-        <v>50.95</v>
+      <c r="J85" s="3" t="n">
+        <v>45.25</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -4677,32 +4677,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4764.17</v>
+        <v>4749.28</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>+$0.36</t>
+          <t>$-1.84</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4928.3</v>
+        <v>4896.4</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>164.13</v>
+        <v>147.12</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4714,8 +4714,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J86" s="4" t="n">
-        <v>59.04</v>
+      <c r="J86" s="3" t="n">
+        <v>50.95</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -4726,32 +4726,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>4719.81</v>
+        <v>4764.17</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>+$19.77</t>
+          <t>+$0.36</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4885.4</v>
+        <v>4928.3</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>+2.02%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>165.59</v>
+        <v>164.13</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4763,8 +4763,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J87" s="4" t="n">
-        <v>68.06</v>
+      <c r="J87" s="3" t="n">
+        <v>59.04</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -4775,32 +4775,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>4702.05</v>
+        <v>4719.81</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>+$1.79</t>
+          <t>+$19.77</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4788.9</v>
+        <v>4885.4</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+2.02%</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>86.84999999999999</v>
+        <v>165.59</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4812,8 +4812,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J88" s="4" t="n">
-        <v>67.61</v>
+      <c r="J88" s="3" t="n">
+        <v>68.06</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -4824,20 +4824,20 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>4649.73</v>
+        <v>4702.05</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>$-3.57</t>
+          <t>+$1.79</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -4845,11 +4845,11 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>139.17</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4861,8 +4861,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J89" s="4" t="n">
-        <v>64.22</v>
+      <c r="J89" s="3" t="n">
+        <v>67.61</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -4873,32 +4873,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>4678.89</v>
+        <v>4649.73</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>$-0.67</t>
+          <t>$-3.57</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4784.1</v>
+        <v>4788.9</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>-2.74%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>105.21</v>
+        <v>139.17</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4910,8 +4910,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J90" s="4" t="n">
-        <v>65.06999999999999</v>
+      <c r="J90" s="3" t="n">
+        <v>64.22</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -4922,32 +4922,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>4758.74</v>
+        <v>4678.89</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>+$2.49</t>
+          <t>$-0.67</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4919.1</v>
+        <v>4784.1</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>+2.91%</t>
+          <t>-2.74%</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>160.36</v>
+        <v>105.21</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4959,8 +4959,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J91" s="4" t="n">
-        <v>61.51</v>
+      <c r="J91" s="3" t="n">
+        <v>65.06999999999999</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -4971,32 +4971,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>4668.9</v>
+        <v>4758.74</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>+3.50%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>+$2.18</t>
+          <t>+$2.49</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4780.2</v>
+        <v>4919.1</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>+2.64%</t>
+          <t>+2.91%</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>111.3</v>
+        <v>160.36</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -5008,8 +5008,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J92" s="4" t="n">
-        <v>61.02</v>
+      <c r="J92" s="3" t="n">
+        <v>61.51</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -5020,32 +5020,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>4511.22</v>
+        <v>4668.9</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+3.50%</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>$-0.71</t>
+          <t>+$2.18</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4657.4</v>
+        <v>4780.2</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+2.64%</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>146.18</v>
+        <v>111.3</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -5057,8 +5057,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J93" s="4" t="n">
-        <v>61.83</v>
+      <c r="J93" s="3" t="n">
+        <v>61.02</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -5069,32 +5069,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>4493.8</v>
+        <v>4511.22</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>+$12.74</t>
+          <t>$-0.71</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4624.8</v>
+        <v>4657.4</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>+2.62%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>131</v>
+        <v>146.18</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -5106,8 +5106,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J94" s="4" t="n">
-        <v>66.98999999999999</v>
+      <c r="J94" s="3" t="n">
+        <v>61.83</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -5118,32 +5118,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>4377.64</v>
+        <v>4493.8</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>+$5.15</t>
+          <t>+$12.74</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4506.7</v>
+        <v>4624.8</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>-3.82%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>129.06</v>
+        <v>131</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -5155,8 +5155,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J95" s="4" t="n">
-        <v>68.39</v>
+      <c r="J95" s="3" t="n">
+        <v>66.98999999999999</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -5167,32 +5167,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>4505.69</v>
+        <v>4377.64</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>$-19.39</t>
+          <t>+$5.15</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4685.7</v>
+        <v>4506.7</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>+3.37%</t>
+          <t>-3.82%</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>180.01</v>
+        <v>129.06</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -5204,8 +5204,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J96" s="4" t="n">
-        <v>65.34999999999999</v>
+      <c r="J96" s="3" t="n">
+        <v>68.39</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -5216,32 +5216,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>4491.37</v>
+        <v>4505.69</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>+$6.43</t>
+          <t>$-19.39</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4532.8</v>
+        <v>4685.7</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+3.37%</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>41.43</v>
+        <v>180.01</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -5253,44 +5253,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J97" s="4" t="n">
-        <v>55.61</v>
+      <c r="J97" s="3" t="n">
+        <v>65.34999999999999</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>4407.46</v>
+        <v>4491.37</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>$-41.67</t>
+          <t>+$6.43</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4539.3</v>
+        <v>4532.8</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>131.84</v>
+        <v>41.43</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -5302,44 +5302,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J98" s="4" t="n">
-        <v>52.06</v>
+      <c r="J98" s="3" t="n">
+        <v>55.61</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>4490.66</v>
+        <v>4407.46</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>-3.43%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>+$0.88</t>
+          <t>$-41.67</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4716.2</v>
+        <v>4539.3</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>-3.75%</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>225.54</v>
+        <v>131.84</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -5351,8 +5351,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J99" s="4" t="n">
-        <v>48.26</v>
+      <c r="J99" s="3" t="n">
+        <v>52.06</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -5363,32 +5363,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>4650.11</v>
+        <v>4490.66</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>-3.50%</t>
+          <t>-3.43%</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>+$5.66</t>
+          <t>+$0.88</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4745.4</v>
+        <v>4716.2</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>-5.88%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>95.29000000000001</v>
+        <v>225.54</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -5400,8 +5400,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J100" s="4" t="n">
-        <v>40.68</v>
+      <c r="J100" s="3" t="n">
+        <v>48.26</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -5412,32 +5412,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>4818.71</v>
+        <v>4650.11</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>-3.74%</t>
+          <t>-3.50%</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>$-0.26</t>
+          <t>+$5.66</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5041.7</v>
+        <v>4745.4</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>-2.23%</t>
+          <t>-5.88%</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>222.99</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -5449,8 +5449,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J101" s="4" t="n">
-        <v>34.38</v>
+      <c r="J101" s="3" t="n">
+        <v>40.68</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -5461,32 +5461,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>5006.14</v>
+        <v>4818.71</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-3.74%</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>+$3.07</t>
+          <t>$-0.26</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5156.7</v>
+        <v>5041.7</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-2.23%</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>150.56</v>
+        <v>222.99</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -5498,8 +5498,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J102" s="4" t="n">
-        <v>33</v>
+      <c r="J102" s="3" t="n">
+        <v>34.38</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -5510,32 +5510,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>5004.67</v>
+        <v>5006.14</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>$-13.14</t>
+          <t>+$3.07</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5150.3</v>
+        <v>5156.7</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>145.63</v>
+        <v>150.56</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -5547,8 +5547,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J103" s="4" t="n">
-        <v>34.78</v>
+      <c r="J103" s="3" t="n">
+        <v>33</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -5559,32 +5559,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>5019</v>
+        <v>5004.67</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>+$0.70</t>
+          <t>$-13.14</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5210.4</v>
+        <v>5150.3</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>-1.25%</t>
+          <t>-1.15%</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>191.4</v>
+        <v>145.63</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -5596,8 +5596,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J104" s="4" t="n">
-        <v>34.04</v>
+      <c r="J104" s="3" t="n">
+        <v>34.78</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -5608,32 +5608,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>5079.6</v>
+        <v>5019</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>+$2.23</t>
+          <t>+$0.70</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5276.4</v>
+        <v>5210.4</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>-1.25%</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>196.8</v>
+        <v>191.4</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -5645,8 +5645,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J105" s="4" t="n">
-        <v>35.66</v>
+      <c r="J105" s="3" t="n">
+        <v>34.04</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -5657,32 +5657,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>5176.23</v>
+        <v>5079.6</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>$-3.94</t>
+          <t>+$2.23</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5330.9</v>
+        <v>5276.4</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>154.67</v>
+        <v>196.8</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -5694,8 +5694,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J106" s="4" t="n">
-        <v>34.34</v>
+      <c r="J106" s="3" t="n">
+        <v>35.66</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -5706,32 +5706,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>5191.58</v>
+        <v>5176.23</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>+$0.98</t>
+          <t>$-3.94</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5392.5</v>
+        <v>5330.9</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>200.92</v>
+        <v>154.67</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -5743,8 +5743,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J107" s="4" t="n">
-        <v>33.19</v>
+      <c r="J107" s="3" t="n">
+        <v>34.34</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -5755,32 +5755,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>5138.45</v>
+        <v>5191.58</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>+$8.38</t>
+          <t>+$0.98</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5251.9</v>
+        <v>5392.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>113.45</v>
+        <v>200.92</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -5792,8 +5792,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J108" s="7" t="n">
-        <v>27.57</v>
+      <c r="J108" s="3" t="n">
+        <v>33.19</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -5804,32 +5804,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>5171.8</v>
+        <v>5138.45</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>+$1.60</t>
+          <t>+$8.38</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5306.8</v>
+        <v>5251.9</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>135</v>
+        <v>113.45</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         </is>
       </c>
       <c r="J109" s="7" t="n">
-        <v>27.41</v>
+        <v>27.57</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -5853,32 +5853,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>5082.25</v>
+        <v>5171.8</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>+$15.58</t>
+          <t>+$1.60</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5225.6</v>
+        <v>5306.8</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>143.35</v>
+        <v>135</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="J110" s="7" t="n">
-        <v>28.59</v>
+        <v>27.41</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -5902,32 +5902,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>5140.39</v>
+        <v>5082.25</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>+$15.99</t>
+          <t>+$15.58</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5281.6</v>
+        <v>5225.6</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-1.06%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>141.21</v>
+        <v>143.35</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         </is>
       </c>
       <c r="J111" s="7" t="n">
-        <v>29.02</v>
+        <v>28.59</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -5951,32 +5951,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>5087.78</v>
+        <v>5140.39</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>-4.39%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>+$3.27</t>
+          <t>+$15.99</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5269.7</v>
+        <v>5281.6</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>-3.53%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>181.92</v>
+        <v>141.21</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="J112" s="7" t="n">
-        <v>26.89</v>
+        <v>29.02</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -6000,32 +6000,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>5321.3</v>
+        <v>5087.78</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>+0.80%</t>
+          <t>-4.39%</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>+$22.33</t>
+          <t>+$3.27</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5462.6</v>
+        <v>5269.7</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-3.53%</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>141.3</v>
+        <v>181.92</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="J113" s="7" t="n">
-        <v>25</v>
+        <v>26.89</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -6049,32 +6049,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>5278.9</v>
+        <v>5321.3</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>+1.83%</t>
+          <t>+0.80%</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>+$3.50</t>
+          <t>+$22.33</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5396.2</v>
+        <v>5462.6</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>117.3</v>
+        <v>141.3</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="J114" s="7" t="n">
-        <v>23.93</v>
+        <v>25</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -6098,32 +6098,32 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>5184.25</v>
+        <v>5278.9</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+1.83%</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>$-2.63</t>
+          <t>+$3.50</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5341.1</v>
+        <v>5396.2</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>156.85</v>
+        <v>117.3</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="J115" s="7" t="n">
-        <v>27.52</v>
+        <v>23.93</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -6147,32 +6147,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>5164.29</v>
+        <v>5184.25</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>+$0.50</t>
+          <t>$-2.63</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5374.2</v>
+        <v>5341.1</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>209.91</v>
+        <v>156.85</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -6184,8 +6184,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J116" s="4" t="n">
-        <v>32.13</v>
+      <c r="J116" s="7" t="n">
+        <v>27.52</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -6196,32 +6196,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>5142.79</v>
+        <v>5164.29</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>-1.62%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>+$2.64</t>
+          <t>+$0.50</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5322.8</v>
+        <v>5374.2</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>180.01</v>
+        <v>209.91</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -6233,8 +6233,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J117" s="4" t="n">
-        <v>30.2</v>
+      <c r="J117" s="3" t="n">
+        <v>32.13</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -6245,32 +6245,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>5227.48</v>
+        <v>5142.79</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>+2.36%</t>
+          <t>-1.62%</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>+$2.32</t>
+          <t>+$2.64</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5372</v>
+        <v>5322.8</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>144.52</v>
+        <v>180.01</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -6282,8 +6282,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J118" s="7" t="n">
-        <v>28.13</v>
+      <c r="J118" s="3" t="n">
+        <v>30.2</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -6294,32 +6294,32 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>5106.96</v>
+        <v>5227.48</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>+2.22%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>+$2.74</t>
+          <t>+$2.32</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5223.4</v>
+        <v>5372</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>+1.70%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>116.44</v>
+        <v>144.52</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -6331,8 +6331,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J119" s="4" t="n">
-        <v>35.59</v>
+      <c r="J119" s="7" t="n">
+        <v>28.13</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -6343,32 +6343,32 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>4996.02</v>
+        <v>5106.96</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+2.22%</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>$-2.27</t>
+          <t>+$2.74</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5136.1</v>
+        <v>5223.4</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+1.70%</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>140.08</v>
+        <v>116.44</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -6380,8 +6380,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J120" s="4" t="n">
-        <v>44.31</v>
+      <c r="J120" s="3" t="n">
+        <v>35.59</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -6392,32 +6392,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>4977.18</v>
+        <v>4996.02</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>+2.03%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>+$1.09</t>
+          <t>$-2.27</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5147.3</v>
+        <v>5136.1</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>170.12</v>
+        <v>140.08</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -6429,8 +6429,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J121" s="4" t="n">
-        <v>46.23</v>
+      <c r="J121" s="3" t="n">
+        <v>44.31</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -6441,32 +6441,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>4878.1</v>
+        <v>4977.18</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>-3.25%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>$-45.72</t>
+          <t>+$1.09</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5039.4</v>
+        <v>5147.3</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>-2.79%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>161.3</v>
+        <v>170.12</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -6478,8 +6478,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J122" s="4" t="n">
-        <v>46.39</v>
+      <c r="J122" s="3" t="n">
+        <v>46.23</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -6490,32 +6490,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>5041.86</v>
+        <v>4878.1</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>+2.44%</t>
+          <t>-3.25%</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>+$4.32</t>
+          <t>$-45.72</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5183.8</v>
+        <v>5039.4</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>+1.87%</t>
+          <t>-2.79%</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>141.94</v>
+        <v>161.3</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -6527,8 +6527,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J123" s="4" t="n">
-        <v>57.41</v>
+      <c r="J123" s="3" t="n">
+        <v>46.39</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -6539,32 +6539,32 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>4921.59</v>
+        <v>5041.86</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>-3.19%</t>
+          <t>+2.44%</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>+$1.40</t>
+          <t>+$4.32</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5088.4</v>
+        <v>5183.8</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>-2.94%</t>
+          <t>+1.87%</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>166.81</v>
+        <v>141.94</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -6576,8 +6576,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J124" s="4" t="n">
-        <v>62.1</v>
+      <c r="J124" s="3" t="n">
+        <v>57.41</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -6588,32 +6588,32 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>5083.84</v>
+        <v>4921.59</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>+1.18%</t>
+          <t>-3.19%</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>+$2.13</t>
+          <t>+$1.40</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5242.5</v>
+        <v>5088.4</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-2.94%</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>158.66</v>
+        <v>166.81</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -6625,8 +6625,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J125" s="4" t="n">
-        <v>63</v>
+      <c r="J125" s="3" t="n">
+        <v>62.1</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -6637,32 +6637,32 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>5024.38</v>
+        <v>5083.84</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>+1.18%</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>$-0.65</t>
+          <t>+$2.13</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5172.2</v>
+        <v>5242.5</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>147.82</v>
+        <v>158.66</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -6674,8 +6674,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J126" s="4" t="n">
-        <v>64.01000000000001</v>
+      <c r="J126" s="3" t="n">
+        <v>63</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -6686,32 +6686,32 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>5060.14</v>
+        <v>5024.38</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>+1.88%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>+$17.25</t>
+          <t>$-0.65</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5222.1</v>
+        <v>5172.2</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>+2.00%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>161.96</v>
+        <v>147.82</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -6723,8 +6723,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J127" s="4" t="n">
-        <v>63.42</v>
+      <c r="J127" s="3" t="n">
+        <v>64.01000000000001</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -6735,32 +6735,32 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>4966.93</v>
+        <v>5060.14</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>+3.92%</t>
+          <t>+1.88%</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>+$12.55</t>
+          <t>+$17.25</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5119.8</v>
+        <v>5222.1</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>+1.94%</t>
+          <t>+2.00%</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>152.87</v>
+        <v>161.96</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -6772,8 +6772,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J128" s="4" t="n">
-        <v>63.27</v>
+      <c r="J128" s="3" t="n">
+        <v>63.42</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -6784,32 +6784,32 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>4779.63</v>
+        <v>4966.93</v>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>-3.71%</t>
+          <t>+3.92%</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>+$12.00</t>
+          <t>+$12.55</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5022.3</v>
+        <v>5119.8</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>+1.94%</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>242.67</v>
+        <v>152.87</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -6821,8 +6821,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J129" s="4" t="n">
-        <v>57.48</v>
+      <c r="J129" s="3" t="n">
+        <v>63.27</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -6833,32 +6833,32 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>4963.89</v>
+        <v>4779.63</v>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-3.71%</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>+$1.30</t>
+          <t>+$12.00</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5089</v>
+        <v>5022.3</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>125.11</v>
+        <v>242.67</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -6870,8 +6870,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J130" s="4" t="n">
-        <v>49.25</v>
+      <c r="J130" s="3" t="n">
+        <v>57.48</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -6882,32 +6882,32 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>4944.42</v>
+        <v>4963.89</v>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>+6.13%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>+$13.04</t>
+          <t>+$1.30</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5072.5</v>
+        <v>5089</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>+6.11%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>128.08</v>
+        <v>125.11</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -6919,8 +6919,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J131" s="4" t="n">
-        <v>49.09</v>
+      <c r="J131" s="3" t="n">
+        <v>49.25</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -6931,32 +6931,32 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>4658.73</v>
+        <v>4944.42</v>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>-4.75%</t>
+          <t>+6.13%</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>$-76.67</t>
+          <t>+$13.04</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4780.4</v>
+        <v>5072.5</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>+6.11%</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>121.67</v>
+        <v>128.08</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -6968,8 +6968,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J132" s="4" t="n">
-        <v>48.95</v>
+      <c r="J132" s="3" t="n">
+        <v>49.09</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -6980,36 +6980,36 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>4890.97</v>
+        <v>4658.73</v>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>-8.99%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>+$8.73</t>
+          <t>$-76.67</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4880</v>
+        <v>4780.4</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>-11.41%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>-10.97</v>
-      </c>
-      <c r="H133" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>121.67</v>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
@@ -7017,48 +7017,48 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J133" s="4" t="n">
-        <v>41.41</v>
+      <c r="J133" s="3" t="n">
+        <v>48.95</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>5373.91</v>
+        <v>4890.97</v>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-8.99%</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>+$5.87</t>
+          <t>+$8.73</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5508.6</v>
+        <v>4880</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-11.41%</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>134.69</v>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-10.97</v>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
@@ -7066,44 +7066,44 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J134" s="4" t="n">
-        <v>31.72</v>
+      <c r="J134" s="3" t="n">
+        <v>41.41</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>5416.79</v>
+        <v>5373.91</v>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>+4.60%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>+$0.28</t>
+          <t>+$5.87</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5494.6</v>
+        <v>5508.6</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>+4.32%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>77.81</v>
+        <v>134.69</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -7115,8 +7115,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J135" s="4" t="n">
-        <v>29.24</v>
+      <c r="J135" s="3" t="n">
+        <v>31.72</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -7127,32 +7127,32 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>5178.46</v>
+        <v>5416.79</v>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>+3.36%</t>
+          <t>+4.60%</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>+$3.14</t>
+          <t>+$0.28</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5267.3</v>
+        <v>5494.6</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+4.32%</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>88.84</v>
+        <v>77.81</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="J136" s="7" t="n">
-        <v>28.65</v>
+        <v>29.24</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -7176,32 +7176,32 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>5010.31</v>
+        <v>5178.46</v>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+3.36%</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>+$20.73</t>
+          <t>+$3.14</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5272.8</v>
+        <v>5267.3</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>262.49</v>
+        <v>88.84</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="J137" s="7" t="n">
-        <v>16.43</v>
+        <v>28.65</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -7225,32 +7225,32 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>4988.56</v>
+        <v>5010.31</v>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>+1.07%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>+$5.34</t>
+          <t>+$20.73</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5160.4</v>
+        <v>5272.8</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+2.18%</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>171.84</v>
+        <v>262.49</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="J138" s="7" t="n">
-        <v>10.44</v>
+        <v>16.43</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -7274,32 +7274,32 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>4935.8</v>
+        <v>4988.56</v>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>+$0.94</t>
+          <t>+$5.34</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5086.9</v>
+        <v>5160.4</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>+1.59%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>151.1</v>
+        <v>171.84</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="J139" s="7" t="n">
-        <v>8.960000000000001</v>
+        <v>10.44</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -7323,32 +7323,32 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>4831.51</v>
+        <v>4935.8</v>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+2.16%</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>+$0.31</t>
+          <t>+$0.94</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5007.5</v>
+        <v>5086.9</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>+1.51%</t>
+          <t>+1.59%</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>175.99</v>
+        <v>151.1</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -7360,7 +7360,9 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J140" s="2" t="inlineStr"/>
+      <c r="J140" s="7" t="n">
+        <v>8.960000000000001</v>
+      </c>
       <c r="K140" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -7370,32 +7372,32 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>4762.99</v>
+        <v>4831.51</v>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>+3.63%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>+$75.81</t>
+          <t>+$0.31</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4933</v>
+        <v>5007.5</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>+3.65%</t>
+          <t>+1.51%</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>170.01</v>
+        <v>175.99</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -7417,32 +7419,32 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>4596.18</v>
+        <v>4762.99</v>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+3.63%</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>+$1.80</t>
+          <t>+$75.81</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4759.2</v>
+        <v>4933</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>+3.65%</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>163.02</v>
+        <v>170.01</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -7464,32 +7466,32 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>4615.95</v>
+        <v>4596.18</v>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>+$6.28</t>
+          <t>+$1.80</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4787.7</v>
+        <v>4759.2</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>171.75</v>
+        <v>163.02</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -7511,32 +7513,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>4624.8</v>
+        <v>4615.95</v>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>+$3.59</t>
+          <t>+$6.28</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4798.9</v>
+        <v>4787.7</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>174.1</v>
+        <v>171.75</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -7558,32 +7560,32 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>4585.44</v>
+        <v>4624.8</v>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>+$5.33</t>
+          <t>+$3.59</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4760.2</v>
+        <v>4798.9</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>174.76</v>
+        <v>174.1</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -7605,32 +7607,32 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>4598.46</v>
+        <v>4585.44</v>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>+1.98%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>+$9.47</t>
+          <t>+$5.33</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4777.7</v>
+        <v>4760.2</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>+2.49%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>179.24</v>
+        <v>174.76</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -7652,32 +7654,32 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>4509.27</v>
+        <v>4598.46</v>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>+$1.86</t>
+          <t>+$9.47</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4661.4</v>
+        <v>4777.7</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>+0.90%</t>
+          <t>+2.49%</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>152.13</v>
+        <v>179.24</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -7699,32 +7701,32 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>4477.84</v>
+        <v>4509.27</v>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>$-0.03</t>
+          <t>+$1.86</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4620</v>
+        <v>4661.4</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.90%</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>142.16</v>
+        <v>152.13</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -7746,32 +7748,32 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>4456.26</v>
+        <v>4477.84</v>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>+$0.08</t>
+          <t>$-0.03</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4620.6</v>
+        <v>4620</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>-0.76%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>164.34</v>
+        <v>142.16</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -7793,32 +7795,32 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>4494.61</v>
+        <v>4456.26</v>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.85%</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>$-0.07</t>
+          <t>+$0.08</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4656.2</v>
+        <v>4620.6</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>-0.76%</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>161.59</v>
+        <v>164.34</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -7840,32 +7842,32 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>4449.11</v>
+        <v>4494.61</v>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>+2.70%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>+$28.96</t>
+          <t>$-0.07</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4608.1</v>
+        <v>4656.2</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>+2.76%</t>
+          <t>+1.04%</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>158.99</v>
+        <v>161.59</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -7887,32 +7889,32 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>4332.17</v>
+        <v>4449.11</v>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.70%</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+$28.96</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4484.4</v>
+        <v>4608.1</v>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.76%</t>
         </is>
       </c>
       <c r="G152" t="n">
-        <v>152.23</v>
+        <v>158.99</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -7926,6 +7928,53 @@
       </c>
       <c r="J152" s="2" t="inlineStr"/>
       <c r="K152" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>4332.17</v>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>4484.4</v>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>152.23</v>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/Gold_Price_Gap_Theory_2026.xlsx
+++ b/Gold_Price_Gap_Theory_2026.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K153"/>
+  <dimension ref="A1:K156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -569,12 +569,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-1.59%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>$-48.32</t>
+          <t>+$2.59</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -582,7 +582,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+1.07%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>62.44</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -610,36 +610,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4402.09</v>
+        <v>4351.18</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>$-31.56</t>
+          <t>+$8.32</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4390.3</v>
+        <v>4420.4</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-1.53%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-11.79</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
+        <v>69.22</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>55.8</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -659,36 +659,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4404</v>
+        <v>4402.09</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+1.43%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+$47.82</t>
+          <t>$-31.56</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4458.5</v>
+        <v>4390.3</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.53%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-11.79</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>51.72</v>
+        <v>59.93</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -708,32 +708,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4341.84</v>
+        <v>4404</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+1.61%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>$-34.98</t>
+          <t>$-0.88</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4461</v>
+        <v>4458.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+3.79%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>119.16</v>
+        <v>54.5</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>47.58</v>
+        <v>56.68</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -757,32 +757,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4273.01</v>
+        <v>4390.54</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+4.29%</t>
+          <t>+1.12%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+$151.16</t>
+          <t>+$1.59</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4298.3</v>
+        <v>4419.7</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>25.29</v>
+        <v>29.16</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>41.84</v>
+        <v>56.57</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -806,81 +806,81 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4097.29</v>
+        <v>4341.84</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>+1.61%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+$22.75</t>
+          <t>$-34.98</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4339</v>
+        <v>4461</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+4.39%</t>
+          <t>+3.79%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>241.71</v>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="n">
-        <v>28.06</v>
+        <v>119.16</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Contango (Normal Market)</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>50.8</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4055.15</v>
+        <v>4273.01</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+4.29%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+$33.39</t>
+          <t>+$151.16</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4156.4</v>
+        <v>4298.3</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>101.25</v>
+        <v>25.29</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -892,8 +892,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="7" t="n">
-        <v>19.9</v>
+      <c r="J8" s="3" t="n">
+        <v>44.58</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -904,81 +904,81 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4044.36</v>
+        <v>4097.29</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$0.65</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4110.9</v>
+        <v>4339</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+4.49%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>66.54000000000001</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
+        <v>241.71</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Contango (Extreme Oversupply / Glut)</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>🎯 BANK BUY ARBITRAGE</t>
         </is>
       </c>
       <c r="J9" s="7" t="n">
-        <v>18.29</v>
+        <v>30.08</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4103.64</v>
+        <v>4077.25</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>+0.54%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+$0.17</t>
+          <t>$-5.07</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4160.6</v>
+        <v>4152.6</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>56.96</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="J10" s="7" t="n">
-        <v>18.21</v>
+        <v>19.87</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1002,32 +1002,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4066.23</v>
+        <v>4055.15</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+$1.59</t>
+          <t>+$33.39</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4097</v>
+        <v>4156.4</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>30.77</v>
+        <v>101.25</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="J11" s="7" t="n">
-        <v>18.03</v>
+        <v>19.9</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1051,32 +1051,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4028.54</v>
+        <v>4044.36</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+$2.81</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4098.6</v>
+        <v>4110.9</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>70.06</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="J12" s="7" t="n">
-        <v>16.18</v>
+        <v>18.29</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1100,32 +1100,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4076.6</v>
+        <v>4103.64</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+$43.44</t>
+          <t>+$0.17</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4136.4</v>
+        <v>4160.6</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>59.8</v>
+        <v>56.96</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="J13" s="7" t="n">
-        <v>18.87</v>
+        <v>18.21</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1149,32 +1149,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4052.74</v>
+        <v>4066.23</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+$0.61</t>
+          <t>+$1.59</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4129.7</v>
+        <v>4097</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>76.95999999999999</v>
+        <v>30.77</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="J14" s="7" t="n">
-        <v>21.15</v>
+        <v>18.03</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1198,32 +1198,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4049.43</v>
+        <v>4028.54</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$-10.76</t>
+          <t>+$2.81</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4108.8</v>
+        <v>4098.6</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>59.37</v>
+        <v>70.06</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="J15" s="7" t="n">
-        <v>19.94</v>
+        <v>16.18</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1247,32 +1247,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4130.11</v>
+        <v>4076.6</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+$1.94</t>
+          <t>+$43.44</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4210.3</v>
+        <v>4136.4</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+1.84%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>80.19</v>
+        <v>59.8</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="J16" s="7" t="n">
-        <v>21.96</v>
+        <v>18.87</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1296,32 +1296,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4077.87</v>
+        <v>4052.74</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+$2.71</t>
+          <t>+$0.61</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4134.2</v>
+        <v>4129.7</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>56.33</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="J17" s="7" t="n">
-        <v>21.74</v>
+        <v>21.15</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1345,32 +1345,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4007.49</v>
+        <v>4049.43</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$-12.24</t>
+          <t>$-10.76</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4073</v>
+        <v>4108.8</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>65.51000000000001</v>
+        <v>59.37</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="J18" s="7" t="n">
-        <v>21.72</v>
+        <v>19.94</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1394,32 +1394,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4017.04</v>
+        <v>4130.11</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+$1.19</t>
+          <t>+$1.94</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4075.8</v>
+        <v>4210.3</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+1.84%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>58.76</v>
+        <v>80.19</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="J19" s="7" t="n">
-        <v>22.33</v>
+        <v>21.96</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1443,32 +1443,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3976.48</v>
+        <v>4077.87</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+$4.31</t>
+          <t>+$2.71</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4048.7</v>
+        <v>4134.2</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>72.22</v>
+        <v>56.33</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="J20" s="7" t="n">
-        <v>22.36</v>
+        <v>21.74</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1492,32 +1492,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4060.55</v>
+        <v>4007.49</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+$0.46</t>
+          <t>$-12.24</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4109.3</v>
+        <v>4073</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>48.75</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="J21" s="7" t="n">
-        <v>21.54</v>
+        <v>21.72</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1541,32 +1541,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4052.92</v>
+        <v>4017.04</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+$5.21</t>
+          <t>+$1.19</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4127.9</v>
+        <v>4075.8</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+1.58%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>74.98</v>
+        <v>58.76</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="J22" s="7" t="n">
-        <v>21.93</v>
+        <v>22.33</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1590,32 +1590,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4000.78</v>
+        <v>3976.48</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$-20.33</t>
+          <t>+$4.31</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4063.6</v>
+        <v>4048.7</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>62.82</v>
+        <v>72.22</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="J23" s="7" t="n">
-        <v>22.96</v>
+        <v>22.36</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1639,32 +1639,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4119.29</v>
+        <v>4060.55</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+$2.30</t>
+          <t>+$0.46</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4173.6</v>
+        <v>4109.3</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>54.31</v>
+        <v>48.75</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="J24" s="7" t="n">
-  